--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1533" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB1AF40E-3D95-484D-BC98-43B1E38C4A87}"/>
+  <xr:revisionPtr revIDLastSave="1536" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7B527E9-9986-4AD8-8797-1894A1EEF863}"/>
   <bookViews>
-    <workbookView xWindow="4185" yWindow="3690" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3333,7 +3333,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
+  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Beltone Commence 3 62-DRWC Digital RIE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A75:V89">
     <sortCondition ref="I1:I199"/>
   </sortState>
@@ -4435,7 +4441,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="15">
+    <row r="2" spans="1:31" ht="15" hidden="1">
       <c r="A2" s="42" t="s">
         <v>130</v>
       </c>
@@ -4505,7 +4511,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="15">
+    <row r="3" spans="1:31" ht="15" hidden="1">
       <c r="A3" s="42" t="s">
         <v>130</v>
       </c>
@@ -4574,7 +4580,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="15">
+    <row r="4" spans="1:31" ht="15" hidden="1">
       <c r="A4" s="42" t="s">
         <v>130</v>
       </c>
@@ -4646,7 +4652,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="15">
+    <row r="5" spans="1:31" ht="15" hidden="1">
       <c r="A5" s="42" t="s">
         <v>130</v>
       </c>
@@ -4718,7 +4724,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="15">
+    <row r="6" spans="1:31" ht="15" hidden="1">
       <c r="A6" s="42" t="s">
         <v>120</v>
       </c>
@@ -4785,7 +4791,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="15">
+    <row r="7" spans="1:31" ht="15" hidden="1">
       <c r="A7" s="42" t="s">
         <v>120</v>
       </c>
@@ -4849,7 +4855,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="15">
+    <row r="8" spans="1:31" ht="15" hidden="1">
       <c r="A8" s="42" t="s">
         <v>132</v>
       </c>
@@ -4918,7 +4924,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="15">
+    <row r="9" spans="1:31" ht="15" hidden="1">
       <c r="A9" s="42" t="s">
         <v>132</v>
       </c>
@@ -4990,7 +4996,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="15">
+    <row r="10" spans="1:31" ht="15" hidden="1">
       <c r="A10" s="42" t="s">
         <v>132</v>
       </c>
@@ -5062,7 +5068,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="15">
+    <row r="11" spans="1:31" ht="15" hidden="1">
       <c r="A11" s="42" t="s">
         <v>134</v>
       </c>
@@ -5131,7 +5137,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="15">
+    <row r="12" spans="1:31" ht="15" hidden="1">
       <c r="A12" s="42" t="s">
         <v>132</v>
       </c>
@@ -5200,7 +5206,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="15">
+    <row r="13" spans="1:31" ht="15" hidden="1">
       <c r="A13" s="42" t="s">
         <v>134</v>
       </c>
@@ -5269,7 +5275,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="15">
+    <row r="14" spans="1:31" ht="15" hidden="1">
       <c r="A14" s="42" t="s">
         <v>134</v>
       </c>
@@ -5341,7 +5347,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="15">
+    <row r="15" spans="1:31" ht="15" hidden="1">
       <c r="A15" s="42" t="s">
         <v>134</v>
       </c>
@@ -5414,7 +5420,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="15">
+    <row r="16" spans="1:31" ht="15" hidden="1">
       <c r="A16" s="42" t="s">
         <v>139</v>
       </c>
@@ -5487,7 +5493,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="15">
+    <row r="17" spans="1:31" ht="15" hidden="1">
       <c r="A17" s="42" t="s">
         <v>139</v>
       </c>
@@ -5560,7 +5566,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="15">
+    <row r="18" spans="1:31" ht="15" hidden="1">
       <c r="A18" s="42" t="s">
         <v>142</v>
       </c>
@@ -5632,7 +5638,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="15">
+    <row r="19" spans="1:31" ht="15" hidden="1">
       <c r="A19" s="42" t="s">
         <v>142</v>
       </c>
@@ -5705,7 +5711,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="15">
+    <row r="20" spans="1:31" ht="15" hidden="1">
       <c r="A20" s="42" t="s">
         <v>144</v>
       </c>
@@ -5777,7 +5783,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="15">
+    <row r="21" spans="1:31" ht="15" hidden="1">
       <c r="A21" s="42" t="s">
         <v>144</v>
       </c>
@@ -5850,7 +5856,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="15">
+    <row r="22" spans="1:31" ht="15" hidden="1">
       <c r="A22" s="42" t="s">
         <v>146</v>
       </c>
@@ -5922,7 +5928,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="15">
+    <row r="23" spans="1:31" ht="15" hidden="1">
       <c r="A23" s="42" t="s">
         <v>146</v>
       </c>
@@ -5994,7 +6000,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15">
+    <row r="24" spans="1:31" ht="15" hidden="1">
       <c r="A24" s="42" t="s">
         <v>148</v>
       </c>
@@ -6066,7 +6072,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15">
+    <row r="25" spans="1:31" ht="15" hidden="1">
       <c r="A25" s="42" t="s">
         <v>148</v>
       </c>
@@ -6140,7 +6146,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15">
+    <row r="26" spans="1:31" ht="15" hidden="1">
       <c r="A26" s="42" t="s">
         <v>150</v>
       </c>
@@ -6213,7 +6219,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15">
+    <row r="27" spans="1:31" ht="15" hidden="1">
       <c r="A27" s="42" t="s">
         <v>150</v>
       </c>
@@ -6287,7 +6293,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15">
+    <row r="28" spans="1:31" ht="15" hidden="1">
       <c r="A28" s="42" t="s">
         <v>43</v>
       </c>
@@ -6350,7 +6356,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15">
+    <row r="29" spans="1:31" ht="15" hidden="1">
       <c r="A29" s="42" t="s">
         <v>43</v>
       </c>
@@ -6431,17 +6437,17 @@
       </c>
       <c r="C30" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D30" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E30" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G30" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -6503,17 +6509,17 @@
       </c>
       <c r="C31" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D31" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E31" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G31" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -6574,17 +6580,17 @@
       </c>
       <c r="C32" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D32" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E32" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F32" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G32" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -6646,17 +6652,17 @@
       </c>
       <c r="C33" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D33" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E33" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F33" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G33" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -6718,17 +6724,17 @@
       </c>
       <c r="C34" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D34" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E34" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F34" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G34" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -6790,17 +6796,17 @@
       </c>
       <c r="C35" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D35" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E35" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F35" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G35" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -6862,17 +6868,17 @@
       </c>
       <c r="C36" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D36" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E36" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F36" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G36" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -6935,17 +6941,17 @@
       </c>
       <c r="C37" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D37" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E37" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F37" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G37" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -7007,17 +7013,17 @@
       </c>
       <c r="C38" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D38" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E38" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F38" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G38" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -7079,17 +7085,17 @@
       </c>
       <c r="C39" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D39" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E39" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F39" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G39" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -7151,17 +7157,17 @@
       </c>
       <c r="C40" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D40" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E40" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F40" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G40" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -7223,17 +7229,17 @@
       </c>
       <c r="C41" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D41" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E41" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F41" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G41" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -7295,17 +7301,17 @@
       </c>
       <c r="C42" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>5143</v>
+        <v>4903</v>
       </c>
       <c r="D42" s="105">
-        <v>2459</v>
+        <v>2339</v>
       </c>
       <c r="E42" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F42" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>576.5</v>
+        <v>456.5</v>
       </c>
       <c r="G42" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -7358,7 +7364,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="15">
+    <row r="43" spans="1:31" ht="15" hidden="1">
       <c r="A43" s="42" t="s">
         <v>53</v>
       </c>
@@ -7436,7 +7442,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="15">
+    <row r="44" spans="1:31" ht="15" hidden="1">
       <c r="A44" s="42" t="s">
         <v>53</v>
       </c>
@@ -7514,7 +7520,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="15">
+    <row r="45" spans="1:31" ht="15" hidden="1">
       <c r="A45" s="42" t="s">
         <v>53</v>
       </c>
@@ -7592,7 +7598,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="15">
+    <row r="46" spans="1:31" ht="15" hidden="1">
       <c r="A46" s="42" t="s">
         <v>53</v>
       </c>
@@ -7670,7 +7676,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="15">
+    <row r="47" spans="1:31" ht="15" hidden="1">
       <c r="A47" s="42" t="s">
         <v>53</v>
       </c>
@@ -7745,7 +7751,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="15">
+    <row r="48" spans="1:31" ht="15" hidden="1">
       <c r="A48" s="42" t="s">
         <v>53</v>
       </c>
@@ -7820,7 +7826,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="15">
+    <row r="49" spans="1:32" ht="15" hidden="1">
       <c r="A49" s="42" t="s">
         <v>53</v>
       </c>
@@ -7896,7 +7902,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="15">
+    <row r="50" spans="1:32" ht="15" hidden="1">
       <c r="A50" s="42" t="s">
         <v>53</v>
       </c>
@@ -7972,7 +7978,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="15">
+    <row r="51" spans="1:32" ht="15" hidden="1">
       <c r="A51" s="42" t="s">
         <v>53</v>
       </c>
@@ -8048,7 +8054,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="15">
+    <row r="52" spans="1:32" ht="15" hidden="1">
       <c r="A52" s="42" t="s">
         <v>53</v>
       </c>
@@ -8118,7 +8124,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="15">
+    <row r="53" spans="1:32" ht="15" hidden="1">
       <c r="A53" s="42" t="s">
         <v>53</v>
       </c>
@@ -8191,7 +8197,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="15">
+    <row r="54" spans="1:32" ht="15" hidden="1">
       <c r="A54" s="42" t="s">
         <v>53</v>
       </c>
@@ -8264,7 +8270,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="15">
+    <row r="55" spans="1:32" ht="15" hidden="1">
       <c r="A55" s="42" t="s">
         <v>53</v>
       </c>
@@ -8337,7 +8343,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="15">
+    <row r="56" spans="1:32" ht="15" hidden="1">
       <c r="A56" s="42" t="s">
         <v>53</v>
       </c>
@@ -8411,7 +8417,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="15">
+    <row r="57" spans="1:32" ht="15" hidden="1">
       <c r="A57" s="42" t="s">
         <v>53</v>
       </c>
@@ -8484,7 +8490,7 @@
       <c r="AE57" s="16"/>
       <c r="AF57" s="16"/>
     </row>
-    <row r="58" spans="1:32" ht="15">
+    <row r="58" spans="1:32" ht="15" hidden="1">
       <c r="A58" s="42" t="s">
         <v>50</v>
       </c>
@@ -8556,7 +8562,7 @@
       <c r="AE58" s="16"/>
       <c r="AF58" s="16"/>
     </row>
-    <row r="59" spans="1:32" ht="15">
+    <row r="59" spans="1:32" ht="15" hidden="1">
       <c r="A59" s="42" t="s">
         <v>50</v>
       </c>
@@ -8628,7 +8634,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="15">
+    <row r="60" spans="1:32" ht="15" hidden="1">
       <c r="A60" s="42" t="s">
         <v>57</v>
       </c>
@@ -8706,7 +8712,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="15">
+    <row r="61" spans="1:32" ht="15" hidden="1">
       <c r="A61" s="42" t="s">
         <v>57</v>
       </c>
@@ -8785,7 +8791,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="15">
+    <row r="62" spans="1:32" ht="15" hidden="1">
       <c r="A62" s="42" t="s">
         <v>57</v>
       </c>
@@ -8864,7 +8870,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="15">
+    <row r="63" spans="1:32" ht="15" hidden="1">
       <c r="A63" s="42" t="s">
         <v>57</v>
       </c>
@@ -8943,7 +8949,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="15">
+    <row r="64" spans="1:32" ht="15" hidden="1">
       <c r="A64" s="42" t="s">
         <v>57</v>
       </c>
@@ -9019,7 +9025,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15">
+    <row r="65" spans="1:31" ht="15" hidden="1">
       <c r="A65" s="42" t="s">
         <v>57</v>
       </c>
@@ -9095,7 +9101,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15">
+    <row r="66" spans="1:31" ht="15" hidden="1">
       <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
@@ -9171,7 +9177,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15">
+    <row r="67" spans="1:31" ht="15" hidden="1">
       <c r="A67" s="42" t="s">
         <v>57</v>
       </c>
@@ -9247,7 +9253,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15">
+    <row r="68" spans="1:31" ht="15" hidden="1">
       <c r="A68" s="42" t="s">
         <v>57</v>
       </c>
@@ -9323,7 +9329,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15">
+    <row r="69" spans="1:31" ht="15" hidden="1">
       <c r="A69" s="42" t="s">
         <v>57</v>
       </c>
@@ -9393,7 +9399,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15">
+    <row r="70" spans="1:31" ht="15" hidden="1">
       <c r="A70" s="42" t="s">
         <v>57</v>
       </c>
@@ -9466,7 +9472,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15">
+    <row r="71" spans="1:31" ht="15" hidden="1">
       <c r="A71" s="42" t="s">
         <v>57</v>
       </c>
@@ -9539,7 +9545,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15">
+    <row r="72" spans="1:31" ht="15" hidden="1">
       <c r="A72" s="42" t="s">
         <v>57</v>
       </c>
@@ -9612,7 +9618,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15">
+    <row r="73" spans="1:31" ht="15" hidden="1">
       <c r="A73" s="42" t="s">
         <v>57</v>
       </c>
@@ -9686,7 +9692,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="15">
+    <row r="74" spans="1:31" ht="15" hidden="1">
       <c r="A74" s="42" t="s">
         <v>57</v>
       </c>
@@ -9759,7 +9765,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="15">
+    <row r="75" spans="1:31" ht="15" hidden="1">
       <c r="A75" s="42" t="s">
         <v>59</v>
       </c>
@@ -9832,7 +9838,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="15">
+    <row r="76" spans="1:31" ht="15" hidden="1">
       <c r="A76" s="42" t="s">
         <v>59</v>
       </c>
@@ -9911,7 +9917,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="15">
+    <row r="77" spans="1:31" ht="15" hidden="1">
       <c r="A77" s="42" t="s">
         <v>59</v>
       </c>
@@ -9984,7 +9990,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="15">
+    <row r="78" spans="1:31" ht="15" hidden="1">
       <c r="A78" s="42" t="s">
         <v>59</v>
       </c>
@@ -10057,7 +10063,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="15">
+    <row r="79" spans="1:31" ht="15" hidden="1">
       <c r="A79" s="42" t="s">
         <v>59</v>
       </c>
@@ -10130,7 +10136,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="15">
+    <row r="80" spans="1:31" ht="15" hidden="1">
       <c r="A80" s="42" t="s">
         <v>59</v>
       </c>
@@ -10209,7 +10215,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="15">
+    <row r="81" spans="1:31" ht="15" hidden="1">
       <c r="A81" s="42" t="s">
         <v>59</v>
       </c>
@@ -10288,7 +10294,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="15">
+    <row r="82" spans="1:31" ht="15" hidden="1">
       <c r="A82" s="42" t="s">
         <v>59</v>
       </c>
@@ -10367,7 +10373,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="15">
+    <row r="83" spans="1:31" ht="15" hidden="1">
       <c r="A83" s="42" t="s">
         <v>59</v>
       </c>
@@ -10441,7 +10447,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="15">
+    <row r="84" spans="1:31" ht="15" hidden="1">
       <c r="A84" s="42" t="s">
         <v>59</v>
       </c>
@@ -10517,7 +10523,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="15">
+    <row r="85" spans="1:31" ht="15" hidden="1">
       <c r="A85" s="42" t="s">
         <v>59</v>
       </c>
@@ -10593,7 +10599,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="15">
+    <row r="86" spans="1:31" ht="15" hidden="1">
       <c r="A86" s="42" t="s">
         <v>59</v>
       </c>
@@ -10666,7 +10672,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="15">
+    <row r="87" spans="1:31" ht="15" hidden="1">
       <c r="A87" s="42" t="s">
         <v>59</v>
       </c>
@@ -10742,7 +10748,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="15">
+    <row r="88" spans="1:31" ht="15" hidden="1">
       <c r="A88" s="42" t="s">
         <v>59</v>
       </c>
@@ -10818,7 +10824,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="15">
+    <row r="89" spans="1:31" ht="15" hidden="1">
       <c r="A89" s="42" t="s">
         <v>59</v>
       </c>
@@ -10894,7 +10900,7 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="15">
+    <row r="90" spans="1:31" ht="15" hidden="1">
       <c r="A90" s="42" t="s">
         <v>638</v>
       </c>
@@ -10967,7 +10973,7 @@
       <c r="AD90"/>
       <c r="AE90"/>
     </row>
-    <row r="91" spans="1:31" ht="15">
+    <row r="91" spans="1:31" ht="15" hidden="1">
       <c r="A91" s="42" t="s">
         <v>638</v>
       </c>
@@ -11039,7 +11045,7 @@
       <c r="AD91"/>
       <c r="AE91"/>
     </row>
-    <row r="92" spans="1:31" ht="15">
+    <row r="92" spans="1:31" ht="15" hidden="1">
       <c r="A92" s="42" t="s">
         <v>638</v>
       </c>
@@ -11111,7 +11117,7 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="15">
+    <row r="93" spans="1:31" ht="15" hidden="1">
       <c r="A93" s="42" t="s">
         <v>640</v>
       </c>
@@ -11183,7 +11189,7 @@
       <c r="AD93"/>
       <c r="AE93"/>
     </row>
-    <row r="94" spans="1:31" ht="15">
+    <row r="94" spans="1:31" ht="15" hidden="1">
       <c r="A94" s="42" t="s">
         <v>642</v>
       </c>
@@ -11255,7 +11261,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="15">
+    <row r="95" spans="1:31" ht="15" hidden="1">
       <c r="A95" s="42" t="s">
         <v>642</v>
       </c>
@@ -11327,7 +11333,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="15">
+    <row r="96" spans="1:31" ht="15" hidden="1">
       <c r="A96" s="42" t="s">
         <v>642</v>
       </c>
@@ -11400,7 +11406,7 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="15">
+    <row r="97" spans="1:31" ht="15" hidden="1">
       <c r="A97" s="42" t="s">
         <v>644</v>
       </c>
@@ -11472,7 +11478,7 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="15">
+    <row r="98" spans="1:31" ht="15" hidden="1">
       <c r="A98" s="42" t="s">
         <v>644</v>
       </c>
@@ -11544,7 +11550,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="15">
+    <row r="99" spans="1:31" ht="15" hidden="1">
       <c r="A99" s="42" t="s">
         <v>644</v>
       </c>
@@ -11616,7 +11622,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="15">
+    <row r="100" spans="1:31" ht="15" hidden="1">
       <c r="A100" s="42" t="s">
         <v>61</v>
       </c>
@@ -11685,7 +11691,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="15">
+    <row r="101" spans="1:31" ht="15" hidden="1">
       <c r="A101" s="42" t="s">
         <v>61</v>
       </c>
@@ -11757,7 +11763,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="15">
+    <row r="102" spans="1:31" ht="15" hidden="1">
       <c r="A102" s="42" t="s">
         <v>64</v>
       </c>
@@ -11826,7 +11832,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="15">
+    <row r="103" spans="1:31" ht="15" hidden="1">
       <c r="A103" s="42" t="s">
         <v>64</v>
       </c>
@@ -11898,7 +11904,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="15">
+    <row r="104" spans="1:31" ht="15" hidden="1">
       <c r="A104" s="42" t="s">
         <v>66</v>
       </c>
@@ -11967,7 +11973,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="15">
+    <row r="105" spans="1:31" ht="15" hidden="1">
       <c r="A105" s="42" t="s">
         <v>66</v>
       </c>
@@ -12039,7 +12045,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="15">
+    <row r="106" spans="1:31" ht="15" hidden="1">
       <c r="A106" s="42" t="s">
         <v>70</v>
       </c>
@@ -12108,7 +12114,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="15">
+    <row r="107" spans="1:31" ht="15" hidden="1">
       <c r="A107" s="42" t="s">
         <v>70</v>
       </c>
@@ -12180,7 +12186,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="15">
+    <row r="108" spans="1:31" ht="15" hidden="1">
       <c r="A108" s="42" t="s">
         <v>72</v>
       </c>
@@ -12249,7 +12255,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="15">
+    <row r="109" spans="1:31" ht="15" hidden="1">
       <c r="A109" s="42" t="s">
         <v>72</v>
       </c>
@@ -12321,7 +12327,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="15">
+    <row r="110" spans="1:31" ht="15" hidden="1">
       <c r="A110" s="42" t="s">
         <v>75</v>
       </c>
@@ -12390,7 +12396,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="15">
+    <row r="111" spans="1:31" ht="15" hidden="1">
       <c r="A111" s="42" t="s">
         <v>75</v>
       </c>
@@ -12462,7 +12468,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="15">
+    <row r="112" spans="1:31" ht="15" hidden="1">
       <c r="A112" s="42" t="s">
         <v>77</v>
       </c>
@@ -12529,7 +12535,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="15">
+    <row r="113" spans="1:31" ht="15" hidden="1">
       <c r="A113" s="42" t="s">
         <v>77</v>
       </c>
@@ -12599,7 +12605,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="15">
+    <row r="114" spans="1:31" ht="15" hidden="1">
       <c r="A114" s="42" t="s">
         <v>80</v>
       </c>
@@ -12666,7 +12672,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="15">
+    <row r="115" spans="1:31" ht="15" hidden="1">
       <c r="A115" s="42" t="s">
         <v>80</v>
       </c>
@@ -12736,7 +12742,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="15">
+    <row r="116" spans="1:31" ht="15" hidden="1">
       <c r="A116" s="42" t="s">
         <v>82</v>
       </c>
@@ -12806,7 +12812,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="15">
+    <row r="117" spans="1:31" ht="15" hidden="1">
       <c r="A117" s="42" t="s">
         <v>82</v>
       </c>
@@ -12879,7 +12885,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="15">
+    <row r="118" spans="1:31" ht="15" hidden="1">
       <c r="A118" s="42" t="s">
         <v>84</v>
       </c>
@@ -12949,7 +12955,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="15">
+    <row r="119" spans="1:31" ht="15" hidden="1">
       <c r="A119" s="42" t="s">
         <v>84</v>
       </c>
@@ -13022,7 +13028,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="15">
+    <row r="120" spans="1:31" ht="15" hidden="1">
       <c r="A120" s="42" t="s">
         <v>86</v>
       </c>
@@ -13092,7 +13098,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="15">
+    <row r="121" spans="1:31" ht="15" hidden="1">
       <c r="A121" s="42" t="s">
         <v>86</v>
       </c>
@@ -13165,7 +13171,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="15">
+    <row r="122" spans="1:31" ht="15" hidden="1">
       <c r="A122" s="42" t="s">
         <v>88</v>
       </c>
@@ -13235,7 +13241,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="15">
+    <row r="123" spans="1:31" ht="15" hidden="1">
       <c r="A123" s="42" t="s">
         <v>88</v>
       </c>
@@ -13308,7 +13314,7 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="15">
+    <row r="124" spans="1:31" ht="15" hidden="1">
       <c r="A124" s="42" t="s">
         <v>90</v>
       </c>
@@ -13378,7 +13384,7 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="15">
+    <row r="125" spans="1:31" ht="15" hidden="1">
       <c r="A125" s="42" t="s">
         <v>90</v>
       </c>
@@ -13451,7 +13457,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="15">
+    <row r="126" spans="1:31" ht="15" hidden="1">
       <c r="A126" s="42" t="s">
         <v>92</v>
       </c>
@@ -13521,7 +13527,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="15">
+    <row r="127" spans="1:31" ht="15" hidden="1">
       <c r="A127" s="42" t="s">
         <v>92</v>
       </c>
@@ -13594,7 +13600,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="15">
+    <row r="128" spans="1:31" ht="15" hidden="1">
       <c r="A128" s="42" t="s">
         <v>94</v>
       </c>
@@ -13664,7 +13670,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="15">
+    <row r="129" spans="1:31" ht="15" hidden="1">
       <c r="A129" s="42" t="s">
         <v>94</v>
       </c>
@@ -13737,7 +13743,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="15">
+    <row r="130" spans="1:31" ht="15" hidden="1">
       <c r="A130" s="42" t="s">
         <v>96</v>
       </c>
@@ -13805,7 +13811,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="15">
+    <row r="131" spans="1:31" ht="15" hidden="1">
       <c r="A131" s="42" t="s">
         <v>96</v>
       </c>
@@ -13876,7 +13882,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="15">
+    <row r="132" spans="1:31" ht="15" hidden="1">
       <c r="A132" s="42" t="s">
         <v>98</v>
       </c>
@@ -13944,7 +13950,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="15">
+    <row r="133" spans="1:31" ht="15" hidden="1">
       <c r="A133" s="79" t="s">
         <v>98</v>
       </c>
@@ -14014,7 +14020,7 @@
       <c r="AC133" s="46"/>
       <c r="AD133" s="46"/>
     </row>
-    <row r="134" spans="1:31" ht="15">
+    <row r="134" spans="1:31" ht="15" hidden="1">
       <c r="A134" s="79" t="s">
         <v>100</v>
       </c>
@@ -14081,7 +14087,7 @@
       <c r="AC134" s="46"/>
       <c r="AD134" s="46"/>
     </row>
-    <row r="135" spans="1:31" ht="15">
+    <row r="135" spans="1:31" ht="15" hidden="1">
       <c r="A135" s="79" t="s">
         <v>100</v>
       </c>
@@ -14151,7 +14157,7 @@
       <c r="AC135" s="46"/>
       <c r="AD135" s="44"/>
     </row>
-    <row r="136" spans="1:31" ht="15">
+    <row r="136" spans="1:31" ht="15" hidden="1">
       <c r="A136" s="79" t="s">
         <v>102</v>
       </c>
@@ -14220,7 +14226,7 @@
       <c r="AC136" s="46"/>
       <c r="AD136" s="44"/>
     </row>
-    <row r="137" spans="1:31" ht="15">
+    <row r="137" spans="1:31" ht="15" hidden="1">
       <c r="A137" s="79" t="s">
         <v>102</v>
       </c>
@@ -14292,7 +14298,7 @@
       <c r="AC137" s="46"/>
       <c r="AD137" s="44"/>
     </row>
-    <row r="138" spans="1:31" ht="15">
+    <row r="138" spans="1:31" ht="15" hidden="1">
       <c r="A138" s="79" t="s">
         <v>104</v>
       </c>
@@ -14361,7 +14367,7 @@
       <c r="AC138" s="46"/>
       <c r="AD138" s="44"/>
     </row>
-    <row r="139" spans="1:31" ht="15">
+    <row r="139" spans="1:31" ht="15" hidden="1">
       <c r="A139" s="79" t="s">
         <v>104</v>
       </c>
@@ -14434,7 +14440,7 @@
       <c r="AD139" s="44"/>
       <c r="AE139" s="16"/>
     </row>
-    <row r="140" spans="1:31" ht="15">
+    <row r="140" spans="1:31" ht="15" hidden="1">
       <c r="A140" s="79" t="s">
         <v>106</v>
       </c>
@@ -14504,7 +14510,7 @@
       <c r="AD140" s="7"/>
       <c r="AE140" s="16"/>
     </row>
-    <row r="141" spans="1:31" ht="15">
+    <row r="141" spans="1:31" ht="15" hidden="1">
       <c r="A141" s="79" t="s">
         <v>106</v>
       </c>
@@ -14577,7 +14583,7 @@
       <c r="AD141" s="7"/>
       <c r="AE141" s="16"/>
     </row>
-    <row r="142" spans="1:31" ht="15">
+    <row r="142" spans="1:31" ht="15" hidden="1">
       <c r="A142" s="79" t="s">
         <v>108</v>
       </c>
@@ -14646,7 +14652,7 @@
       <c r="AC142" s="46"/>
       <c r="AD142" s="7"/>
     </row>
-    <row r="143" spans="1:31" ht="15">
+    <row r="143" spans="1:31" ht="15" hidden="1">
       <c r="A143" s="79" t="s">
         <v>108</v>
       </c>
@@ -14718,7 +14724,7 @@
       <c r="AC143" s="46"/>
       <c r="AD143" s="7"/>
     </row>
-    <row r="144" spans="1:31" ht="15">
+    <row r="144" spans="1:31" ht="15" hidden="1">
       <c r="A144" s="79" t="s">
         <v>110</v>
       </c>
@@ -14787,7 +14793,7 @@
       <c r="AC144" s="46"/>
       <c r="AD144" s="7"/>
     </row>
-    <row r="145" spans="1:31" ht="15">
+    <row r="145" spans="1:31" ht="15" hidden="1">
       <c r="A145" s="79" t="s">
         <v>110</v>
       </c>
@@ -14859,7 +14865,7 @@
       <c r="AC145" s="46"/>
       <c r="AD145" s="7"/>
     </row>
-    <row r="146" spans="1:31" ht="15">
+    <row r="146" spans="1:31" ht="15" hidden="1">
       <c r="A146" s="85" t="s">
         <v>112</v>
       </c>
@@ -14928,7 +14934,7 @@
       <c r="AC146" s="46"/>
       <c r="AD146" s="44"/>
     </row>
-    <row r="147" spans="1:31" ht="15">
+    <row r="147" spans="1:31" ht="15" hidden="1">
       <c r="A147" s="42" t="s">
         <v>112</v>
       </c>
@@ -15000,7 +15006,7 @@
       <c r="AD147"/>
       <c r="AE147"/>
     </row>
-    <row r="148" spans="1:31" ht="15">
+    <row r="148" spans="1:31" ht="15" hidden="1">
       <c r="A148" s="42" t="s">
         <v>114</v>
       </c>
@@ -15067,7 +15073,7 @@
       <c r="AD148"/>
       <c r="AE148"/>
     </row>
-    <row r="149" spans="1:31" ht="15">
+    <row r="149" spans="1:31" ht="15" hidden="1">
       <c r="A149" s="42" t="s">
         <v>114</v>
       </c>
@@ -15137,7 +15143,7 @@
       <c r="AD149"/>
       <c r="AE149"/>
     </row>
-    <row r="150" spans="1:31" ht="15">
+    <row r="150" spans="1:31" ht="15" hidden="1">
       <c r="A150" s="42" t="s">
         <v>116</v>
       </c>
@@ -15204,7 +15210,7 @@
       <c r="AD150"/>
       <c r="AE150"/>
     </row>
-    <row r="151" spans="1:31" ht="15">
+    <row r="151" spans="1:31" ht="15" hidden="1">
       <c r="A151" s="42" t="s">
         <v>116</v>
       </c>
@@ -15274,7 +15280,7 @@
       <c r="AD151"/>
       <c r="AE151"/>
     </row>
-    <row r="152" spans="1:31" ht="15">
+    <row r="152" spans="1:31" ht="15" hidden="1">
       <c r="A152" s="42" t="s">
         <v>118</v>
       </c>
@@ -15342,7 +15348,7 @@
       <c r="AD152"/>
       <c r="AE152"/>
     </row>
-    <row r="153" spans="1:31" ht="15">
+    <row r="153" spans="1:31" ht="15" hidden="1">
       <c r="A153" s="42" t="s">
         <v>118</v>
       </c>
@@ -15413,7 +15419,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="15">
+    <row r="154" spans="1:31" ht="15" hidden="1">
       <c r="A154" s="42" t="s">
         <v>123</v>
       </c>
@@ -15485,7 +15491,7 @@
       <c r="AC154" s="46"/>
       <c r="AD154" s="46"/>
     </row>
-    <row r="155" spans="1:31" ht="15">
+    <row r="155" spans="1:31" ht="15" hidden="1">
       <c r="A155" s="42" t="s">
         <v>123</v>
       </c>
@@ -15557,7 +15563,7 @@
       <c r="AC155" s="46"/>
       <c r="AD155" s="44"/>
     </row>
-    <row r="156" spans="1:31" ht="15">
+    <row r="156" spans="1:31" ht="15" hidden="1">
       <c r="A156" s="42" t="s">
         <v>123</v>
       </c>
@@ -15629,7 +15635,7 @@
       <c r="AC156" s="46"/>
       <c r="AD156" s="44"/>
     </row>
-    <row r="157" spans="1:31" ht="15">
+    <row r="157" spans="1:31" ht="15" hidden="1">
       <c r="A157" s="42" t="s">
         <v>123</v>
       </c>
@@ -15701,7 +15707,7 @@
       <c r="AC157" s="46"/>
       <c r="AD157" s="7"/>
     </row>
-    <row r="158" spans="1:31" ht="15">
+    <row r="158" spans="1:31" ht="15" hidden="1">
       <c r="A158" s="79" t="s">
         <v>123</v>
       </c>
@@ -15773,7 +15779,7 @@
       <c r="AC158" s="46"/>
       <c r="AD158" s="7"/>
     </row>
-    <row r="159" spans="1:31" ht="15">
+    <row r="159" spans="1:31" ht="15" hidden="1">
       <c r="A159" s="79" t="s">
         <v>123</v>
       </c>
@@ -15846,7 +15852,7 @@
       <c r="AC159" s="46"/>
       <c r="AD159" s="7"/>
     </row>
-    <row r="160" spans="1:31" ht="15">
+    <row r="160" spans="1:31" ht="15" hidden="1">
       <c r="A160" s="79" t="s">
         <v>123</v>
       </c>
@@ -15918,7 +15924,7 @@
       <c r="AC160" s="46"/>
       <c r="AD160" s="7"/>
     </row>
-    <row r="161" spans="1:30" ht="15">
+    <row r="161" spans="1:30" ht="15" hidden="1">
       <c r="A161" s="79" t="s">
         <v>123</v>
       </c>
@@ -15990,7 +15996,7 @@
       <c r="AC161" s="46"/>
       <c r="AD161" s="46"/>
     </row>
-    <row r="162" spans="1:30" ht="15">
+    <row r="162" spans="1:30" ht="15" hidden="1">
       <c r="A162" s="79" t="s">
         <v>123</v>
       </c>
@@ -16062,7 +16068,7 @@
       <c r="AC162" s="46"/>
       <c r="AD162" s="7"/>
     </row>
-    <row r="163" spans="1:30" ht="15">
+    <row r="163" spans="1:30" ht="15" hidden="1">
       <c r="A163" s="79" t="s">
         <v>123</v>
       </c>
@@ -16134,7 +16140,7 @@
       <c r="AC163" s="46"/>
       <c r="AD163" s="46"/>
     </row>
-    <row r="164" spans="1:30" ht="15">
+    <row r="164" spans="1:30" ht="15" hidden="1">
       <c r="A164" s="79" t="s">
         <v>123</v>
       </c>
@@ -16206,7 +16212,7 @@
       <c r="AC164" s="46"/>
       <c r="AD164" s="44"/>
     </row>
-    <row r="165" spans="1:30" ht="15">
+    <row r="165" spans="1:30" ht="15" hidden="1">
       <c r="A165" s="79" t="s">
         <v>123</v>
       </c>
@@ -16278,7 +16284,7 @@
       <c r="AC165" s="46"/>
       <c r="AD165" s="44"/>
     </row>
-    <row r="166" spans="1:30" ht="15">
+    <row r="166" spans="1:30" ht="15" hidden="1">
       <c r="A166" s="79" t="s">
         <v>123</v>
       </c>
@@ -16350,7 +16356,7 @@
       <c r="AC166" s="46"/>
       <c r="AD166" s="44"/>
     </row>
-    <row r="167" spans="1:30" ht="15">
+    <row r="167" spans="1:30" ht="15" hidden="1">
       <c r="A167" s="85" t="s">
         <v>123</v>
       </c>
@@ -16422,7 +16428,7 @@
       <c r="AC167" s="46"/>
       <c r="AD167" s="44"/>
     </row>
-    <row r="168" spans="1:30" ht="15">
+    <row r="168" spans="1:30" ht="15" hidden="1">
       <c r="A168" s="79" t="s">
         <v>125</v>
       </c>
@@ -16494,7 +16500,7 @@
       <c r="AC168" s="46"/>
       <c r="AD168" s="44"/>
     </row>
-    <row r="169" spans="1:30" ht="15">
+    <row r="169" spans="1:30" ht="15" hidden="1">
       <c r="A169" s="79" t="s">
         <v>125</v>
       </c>
@@ -16566,7 +16572,7 @@
       <c r="AC169" s="46"/>
       <c r="AD169" s="7"/>
     </row>
-    <row r="170" spans="1:30" ht="15">
+    <row r="170" spans="1:30" ht="15" hidden="1">
       <c r="A170" s="79" t="s">
         <v>125</v>
       </c>
@@ -16638,7 +16644,7 @@
       <c r="AC170" s="46"/>
       <c r="AD170" s="7"/>
     </row>
-    <row r="171" spans="1:30" ht="15">
+    <row r="171" spans="1:30" ht="15" hidden="1">
       <c r="A171" s="79" t="s">
         <v>125</v>
       </c>
@@ -16709,7 +16715,7 @@
       <c r="AB171" s="73"/>
       <c r="AD171" s="16"/>
     </row>
-    <row r="172" spans="1:30" ht="15">
+    <row r="172" spans="1:30" ht="15" hidden="1">
       <c r="A172" s="79" t="s">
         <v>125</v>
       </c>
@@ -16781,7 +16787,7 @@
       <c r="AC172" s="44"/>
       <c r="AD172" s="44"/>
     </row>
-    <row r="173" spans="1:30" ht="15">
+    <row r="173" spans="1:30" ht="15" hidden="1">
       <c r="A173" s="79" t="s">
         <v>125</v>
       </c>
@@ -16854,7 +16860,7 @@
       <c r="AC173" s="44"/>
       <c r="AD173" s="44"/>
     </row>
-    <row r="174" spans="1:30" ht="15">
+    <row r="174" spans="1:30" ht="15" hidden="1">
       <c r="A174" s="79" t="s">
         <v>125</v>
       </c>
@@ -16926,7 +16932,7 @@
       <c r="AC174" s="44"/>
       <c r="AD174" s="44"/>
     </row>
-    <row r="175" spans="1:30" ht="15">
+    <row r="175" spans="1:30" ht="15" hidden="1">
       <c r="A175" s="79" t="s">
         <v>125</v>
       </c>
@@ -16998,7 +17004,7 @@
       <c r="AC175" s="44"/>
       <c r="AD175" s="44"/>
     </row>
-    <row r="176" spans="1:30" ht="15">
+    <row r="176" spans="1:30" ht="15" hidden="1">
       <c r="A176" s="79" t="s">
         <v>125</v>
       </c>
@@ -17070,7 +17076,7 @@
       <c r="AC176" s="44"/>
       <c r="AD176" s="44"/>
     </row>
-    <row r="177" spans="1:30" ht="15">
+    <row r="177" spans="1:30" ht="15" hidden="1">
       <c r="A177" s="79" t="s">
         <v>125</v>
       </c>
@@ -17142,7 +17148,7 @@
       <c r="AC177" s="44"/>
       <c r="AD177" s="44"/>
     </row>
-    <row r="178" spans="1:30" ht="15">
+    <row r="178" spans="1:30" ht="15" hidden="1">
       <c r="A178" s="79" t="s">
         <v>125</v>
       </c>
@@ -17214,7 +17220,7 @@
       <c r="AC178" s="44"/>
       <c r="AD178" s="44"/>
     </row>
-    <row r="179" spans="1:30" ht="15">
+    <row r="179" spans="1:30" ht="15" hidden="1">
       <c r="A179" s="79" t="s">
         <v>125</v>
       </c>
@@ -17286,7 +17292,7 @@
       <c r="AC179" s="44"/>
       <c r="AD179" s="44"/>
     </row>
-    <row r="180" spans="1:30" ht="15">
+    <row r="180" spans="1:30" ht="15" hidden="1">
       <c r="A180" s="79" t="s">
         <v>125</v>
       </c>
@@ -17358,7 +17364,7 @@
       <c r="AC180" s="44"/>
       <c r="AD180" s="44"/>
     </row>
-    <row r="181" spans="1:30" ht="15">
+    <row r="181" spans="1:30" ht="15" hidden="1">
       <c r="A181" s="79" t="s">
         <v>125</v>
       </c>
@@ -17430,7 +17436,7 @@
       <c r="AC181" s="44"/>
       <c r="AD181" s="44"/>
     </row>
-    <row r="182" spans="1:30" ht="15">
+    <row r="182" spans="1:30" ht="15" hidden="1">
       <c r="A182" s="79" t="s">
         <v>127</v>
       </c>
@@ -17502,7 +17508,7 @@
       <c r="AC182" s="44"/>
       <c r="AD182" s="44"/>
     </row>
-    <row r="183" spans="1:30" ht="15">
+    <row r="183" spans="1:30" ht="15" hidden="1">
       <c r="A183" s="79" t="s">
         <v>127</v>
       </c>
@@ -17574,7 +17580,7 @@
       <c r="AC183" s="44"/>
       <c r="AD183" s="44"/>
     </row>
-    <row r="184" spans="1:30" ht="15">
+    <row r="184" spans="1:30" ht="15" hidden="1">
       <c r="A184" s="79" t="s">
         <v>127</v>
       </c>
@@ -17646,7 +17652,7 @@
       <c r="AC184" s="44"/>
       <c r="AD184" s="44"/>
     </row>
-    <row r="185" spans="1:30" ht="15">
+    <row r="185" spans="1:30" ht="15" hidden="1">
       <c r="A185" s="79" t="s">
         <v>127</v>
       </c>
@@ -17718,7 +17724,7 @@
       <c r="AC185" s="44"/>
       <c r="AD185" s="44"/>
     </row>
-    <row r="186" spans="1:30" ht="15">
+    <row r="186" spans="1:30" ht="15" hidden="1">
       <c r="A186" s="79" t="s">
         <v>127</v>
       </c>
@@ -17790,7 +17796,7 @@
       <c r="AC186" s="44"/>
       <c r="AD186" s="44"/>
     </row>
-    <row r="187" spans="1:30" ht="15">
+    <row r="187" spans="1:30" ht="15" hidden="1">
       <c r="A187" s="79" t="s">
         <v>127</v>
       </c>
@@ -17863,7 +17869,7 @@
       <c r="AC187" s="44"/>
       <c r="AD187" s="44"/>
     </row>
-    <row r="188" spans="1:30" ht="15">
+    <row r="188" spans="1:30" ht="15" hidden="1">
       <c r="A188" s="79" t="s">
         <v>127</v>
       </c>
@@ -17935,7 +17941,7 @@
       <c r="AC188" s="44"/>
       <c r="AD188" s="44"/>
     </row>
-    <row r="189" spans="1:30" ht="15">
+    <row r="189" spans="1:30" ht="15" hidden="1">
       <c r="A189" s="79" t="s">
         <v>127</v>
       </c>
@@ -18007,7 +18013,7 @@
       <c r="AC189" s="44"/>
       <c r="AD189" s="44"/>
     </row>
-    <row r="190" spans="1:30" ht="15">
+    <row r="190" spans="1:30" ht="15" hidden="1">
       <c r="A190" s="79" t="s">
         <v>127</v>
       </c>
@@ -18079,7 +18085,7 @@
       <c r="AC190" s="44"/>
       <c r="AD190" s="44"/>
     </row>
-    <row r="191" spans="1:30" ht="15">
+    <row r="191" spans="1:30" ht="15" hidden="1">
       <c r="A191" s="79" t="s">
         <v>127</v>
       </c>
@@ -18151,7 +18157,7 @@
       <c r="AC191" s="44"/>
       <c r="AD191" s="44"/>
     </row>
-    <row r="192" spans="1:30" ht="15">
+    <row r="192" spans="1:30" ht="15" hidden="1">
       <c r="A192" s="79" t="s">
         <v>127</v>
       </c>
@@ -18223,7 +18229,7 @@
       <c r="AC192" s="44"/>
       <c r="AD192" s="44"/>
     </row>
-    <row r="193" spans="1:30" ht="15">
+    <row r="193" spans="1:30" ht="15" hidden="1">
       <c r="A193" s="79" t="s">
         <v>127</v>
       </c>
@@ -18295,7 +18301,7 @@
       <c r="AC193" s="44"/>
       <c r="AD193" s="44"/>
     </row>
-    <row r="194" spans="1:30" ht="15">
+    <row r="194" spans="1:30" ht="15" hidden="1">
       <c r="A194" s="79" t="s">
         <v>127</v>
       </c>
@@ -18367,7 +18373,7 @@
       <c r="AC194" s="44"/>
       <c r="AD194" s="44"/>
     </row>
-    <row r="195" spans="1:30" ht="15">
+    <row r="195" spans="1:30" ht="15" hidden="1">
       <c r="A195" s="79" t="s">
         <v>127</v>
       </c>
@@ -18437,7 +18443,7 @@
       <c r="AC195" s="44"/>
       <c r="AD195" s="44"/>
     </row>
-    <row r="196" spans="1:30" ht="15">
+    <row r="196" spans="1:30" ht="15" hidden="1">
       <c r="A196" s="79" t="s">
         <v>165</v>
       </c>
@@ -18516,7 +18522,7 @@
       <c r="AC196" s="44"/>
       <c r="AD196" s="44"/>
     </row>
-    <row r="197" spans="1:30" ht="15">
+    <row r="197" spans="1:30" ht="15" hidden="1">
       <c r="A197" s="79" t="s">
         <v>167</v>
       </c>
@@ -18595,7 +18601,7 @@
       <c r="AC197" s="44"/>
       <c r="AD197" s="44"/>
     </row>
-    <row r="198" spans="1:30" ht="15">
+    <row r="198" spans="1:30" ht="15" hidden="1">
       <c r="A198" s="79" t="s">
         <v>169</v>
       </c>
@@ -18674,7 +18680,7 @@
       <c r="AC198" s="44"/>
       <c r="AD198" s="44"/>
     </row>
-    <row r="199" spans="1:30" ht="15">
+    <row r="199" spans="1:30" ht="15" hidden="1">
       <c r="A199" s="85" t="s">
         <v>1</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1536" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7B527E9-9986-4AD8-8797-1894A1EEF863}"/>
+  <xr:revisionPtr revIDLastSave="1555" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4847A2AD-1565-469C-918A-0BDC5B2EF7B2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="649">
   <si>
     <t>Choose Hearing Aid Model</t>
   </si>
@@ -2002,6 +2002,15 @@
   </si>
   <si>
     <t>Beltone Illuminate 9 62S-DRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Beltone Serene 6 ITC-DW Digital ITC</t>
+  </si>
+  <si>
+    <t>Beltone ITC Digital Serene 6 ITC-DW</t>
+  </si>
+  <si>
+    <t>NaphCare</t>
   </si>
 </sst>
 </file>
@@ -2130,7 +2139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -2355,6 +2364,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2362,7 +2384,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2565,6 +2587,16 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="11" fillId="6" borderId="20" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="11" fillId="6" borderId="20" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3332,14 +3364,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Beltone Commence 3 62-DRWC Digital RIE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V200" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+  <autoFilter ref="A1:V200" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A75:V89">
     <sortCondition ref="I1:I199"/>
   </sortState>
@@ -4441,7 +4467,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="15" hidden="1">
+    <row r="2" spans="1:31" ht="15">
       <c r="A2" s="42" t="s">
         <v>130</v>
       </c>
@@ -4511,7 +4537,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="15" hidden="1">
+    <row r="3" spans="1:31" ht="15">
       <c r="A3" s="42" t="s">
         <v>130</v>
       </c>
@@ -4580,7 +4606,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="15" hidden="1">
+    <row r="4" spans="1:31" ht="15">
       <c r="A4" s="42" t="s">
         <v>130</v>
       </c>
@@ -4652,7 +4678,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="15" hidden="1">
+    <row r="5" spans="1:31" ht="15">
       <c r="A5" s="42" t="s">
         <v>130</v>
       </c>
@@ -4724,7 +4750,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="15" hidden="1">
+    <row r="6" spans="1:31" ht="15">
       <c r="A6" s="42" t="s">
         <v>120</v>
       </c>
@@ -4791,7 +4817,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="15" hidden="1">
+    <row r="7" spans="1:31" ht="15">
       <c r="A7" s="42" t="s">
         <v>120</v>
       </c>
@@ -4855,7 +4881,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="15" hidden="1">
+    <row r="8" spans="1:31" ht="15">
       <c r="A8" s="42" t="s">
         <v>132</v>
       </c>
@@ -4924,7 +4950,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="15" hidden="1">
+    <row r="9" spans="1:31" ht="15">
       <c r="A9" s="42" t="s">
         <v>132</v>
       </c>
@@ -4996,7 +5022,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="15" hidden="1">
+    <row r="10" spans="1:31" ht="15">
       <c r="A10" s="42" t="s">
         <v>132</v>
       </c>
@@ -5068,7 +5094,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="15" hidden="1">
+    <row r="11" spans="1:31" ht="15">
       <c r="A11" s="42" t="s">
         <v>134</v>
       </c>
@@ -5137,7 +5163,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="15" hidden="1">
+    <row r="12" spans="1:31" ht="15">
       <c r="A12" s="42" t="s">
         <v>132</v>
       </c>
@@ -5206,7 +5232,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="15" hidden="1">
+    <row r="13" spans="1:31" ht="15">
       <c r="A13" s="42" t="s">
         <v>134</v>
       </c>
@@ -5275,7 +5301,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="15" hidden="1">
+    <row r="14" spans="1:31" ht="15">
       <c r="A14" s="42" t="s">
         <v>134</v>
       </c>
@@ -5347,7 +5373,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="15" hidden="1">
+    <row r="15" spans="1:31" ht="15">
       <c r="A15" s="42" t="s">
         <v>134</v>
       </c>
@@ -5420,7 +5446,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="15" hidden="1">
+    <row r="16" spans="1:31" ht="15">
       <c r="A16" s="42" t="s">
         <v>139</v>
       </c>
@@ -5493,7 +5519,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="15" hidden="1">
+    <row r="17" spans="1:31" ht="15">
       <c r="A17" s="42" t="s">
         <v>139</v>
       </c>
@@ -5566,7 +5592,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="15" hidden="1">
+    <row r="18" spans="1:31" ht="15">
       <c r="A18" s="42" t="s">
         <v>142</v>
       </c>
@@ -5638,7 +5664,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="15" hidden="1">
+    <row r="19" spans="1:31" ht="15">
       <c r="A19" s="42" t="s">
         <v>142</v>
       </c>
@@ -5711,7 +5737,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="15" hidden="1">
+    <row r="20" spans="1:31" ht="15">
       <c r="A20" s="42" t="s">
         <v>144</v>
       </c>
@@ -5783,7 +5809,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="15" hidden="1">
+    <row r="21" spans="1:31" ht="15">
       <c r="A21" s="42" t="s">
         <v>144</v>
       </c>
@@ -5856,7 +5882,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="15" hidden="1">
+    <row r="22" spans="1:31" ht="15">
       <c r="A22" s="42" t="s">
         <v>146</v>
       </c>
@@ -5928,7 +5954,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="15" hidden="1">
+    <row r="23" spans="1:31" ht="15">
       <c r="A23" s="42" t="s">
         <v>146</v>
       </c>
@@ -6000,7 +6026,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15" hidden="1">
+    <row r="24" spans="1:31" ht="15">
       <c r="A24" s="42" t="s">
         <v>148</v>
       </c>
@@ -6072,7 +6098,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15" hidden="1">
+    <row r="25" spans="1:31" ht="15">
       <c r="A25" s="42" t="s">
         <v>148</v>
       </c>
@@ -6146,7 +6172,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15" hidden="1">
+    <row r="26" spans="1:31" ht="15">
       <c r="A26" s="42" t="s">
         <v>150</v>
       </c>
@@ -6219,7 +6245,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15" hidden="1">
+    <row r="27" spans="1:31" ht="15">
       <c r="A27" s="42" t="s">
         <v>150</v>
       </c>
@@ -6293,7 +6319,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15" hidden="1">
+    <row r="28" spans="1:31" ht="15">
       <c r="A28" s="42" t="s">
         <v>43</v>
       </c>
@@ -6356,7 +6382,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15" hidden="1">
+    <row r="29" spans="1:31" ht="15">
       <c r="A29" s="42" t="s">
         <v>43</v>
       </c>
@@ -7364,7 +7390,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="15" hidden="1">
+    <row r="43" spans="1:31" ht="15">
       <c r="A43" s="42" t="s">
         <v>53</v>
       </c>
@@ -7442,7 +7468,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="15" hidden="1">
+    <row r="44" spans="1:31" ht="15">
       <c r="A44" s="42" t="s">
         <v>53</v>
       </c>
@@ -7520,7 +7546,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="15" hidden="1">
+    <row r="45" spans="1:31" ht="15">
       <c r="A45" s="42" t="s">
         <v>53</v>
       </c>
@@ -7598,7 +7624,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="15" hidden="1">
+    <row r="46" spans="1:31" ht="15">
       <c r="A46" s="42" t="s">
         <v>53</v>
       </c>
@@ -7676,7 +7702,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="15" hidden="1">
+    <row r="47" spans="1:31" ht="15">
       <c r="A47" s="42" t="s">
         <v>53</v>
       </c>
@@ -7751,7 +7777,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="15" hidden="1">
+    <row r="48" spans="1:31" ht="15">
       <c r="A48" s="42" t="s">
         <v>53</v>
       </c>
@@ -7826,7 +7852,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="15" hidden="1">
+    <row r="49" spans="1:32" ht="15">
       <c r="A49" s="42" t="s">
         <v>53</v>
       </c>
@@ -7902,7 +7928,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="15" hidden="1">
+    <row r="50" spans="1:32" ht="15">
       <c r="A50" s="42" t="s">
         <v>53</v>
       </c>
@@ -7978,7 +8004,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="15" hidden="1">
+    <row r="51" spans="1:32" ht="15">
       <c r="A51" s="42" t="s">
         <v>53</v>
       </c>
@@ -8054,7 +8080,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="15" hidden="1">
+    <row r="52" spans="1:32" ht="15">
       <c r="A52" s="42" t="s">
         <v>53</v>
       </c>
@@ -8124,7 +8150,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="15" hidden="1">
+    <row r="53" spans="1:32" ht="15">
       <c r="A53" s="42" t="s">
         <v>53</v>
       </c>
@@ -8197,7 +8223,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="15" hidden="1">
+    <row r="54" spans="1:32" ht="15">
       <c r="A54" s="42" t="s">
         <v>53</v>
       </c>
@@ -8270,7 +8296,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="15" hidden="1">
+    <row r="55" spans="1:32" ht="15">
       <c r="A55" s="42" t="s">
         <v>53</v>
       </c>
@@ -8343,7 +8369,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="15" hidden="1">
+    <row r="56" spans="1:32" ht="15">
       <c r="A56" s="42" t="s">
         <v>53</v>
       </c>
@@ -8417,7 +8443,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="15" hidden="1">
+    <row r="57" spans="1:32" ht="15">
       <c r="A57" s="42" t="s">
         <v>53</v>
       </c>
@@ -8490,7 +8516,7 @@
       <c r="AE57" s="16"/>
       <c r="AF57" s="16"/>
     </row>
-    <row r="58" spans="1:32" ht="15" hidden="1">
+    <row r="58" spans="1:32" ht="15">
       <c r="A58" s="42" t="s">
         <v>50</v>
       </c>
@@ -8562,7 +8588,7 @@
       <c r="AE58" s="16"/>
       <c r="AF58" s="16"/>
     </row>
-    <row r="59" spans="1:32" ht="15" hidden="1">
+    <row r="59" spans="1:32" ht="15">
       <c r="A59" s="42" t="s">
         <v>50</v>
       </c>
@@ -8634,7 +8660,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="15" hidden="1">
+    <row r="60" spans="1:32" ht="15">
       <c r="A60" s="42" t="s">
         <v>57</v>
       </c>
@@ -8712,7 +8738,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="15" hidden="1">
+    <row r="61" spans="1:32" ht="15">
       <c r="A61" s="42" t="s">
         <v>57</v>
       </c>
@@ -8791,7 +8817,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="15" hidden="1">
+    <row r="62" spans="1:32" ht="15">
       <c r="A62" s="42" t="s">
         <v>57</v>
       </c>
@@ -8870,7 +8896,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="15" hidden="1">
+    <row r="63" spans="1:32" ht="15">
       <c r="A63" s="42" t="s">
         <v>57</v>
       </c>
@@ -8949,7 +8975,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="15" hidden="1">
+    <row r="64" spans="1:32" ht="15">
       <c r="A64" s="42" t="s">
         <v>57</v>
       </c>
@@ -9025,7 +9051,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15" hidden="1">
+    <row r="65" spans="1:31" ht="15">
       <c r="A65" s="42" t="s">
         <v>57</v>
       </c>
@@ -9101,7 +9127,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15" hidden="1">
+    <row r="66" spans="1:31" ht="15">
       <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
@@ -9177,7 +9203,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15" hidden="1">
+    <row r="67" spans="1:31" ht="15">
       <c r="A67" s="42" t="s">
         <v>57</v>
       </c>
@@ -9253,7 +9279,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15" hidden="1">
+    <row r="68" spans="1:31" ht="15">
       <c r="A68" s="42" t="s">
         <v>57</v>
       </c>
@@ -9329,7 +9355,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15" hidden="1">
+    <row r="69" spans="1:31" ht="15">
       <c r="A69" s="42" t="s">
         <v>57</v>
       </c>
@@ -9399,7 +9425,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15" hidden="1">
+    <row r="70" spans="1:31" ht="15">
       <c r="A70" s="42" t="s">
         <v>57</v>
       </c>
@@ -9472,7 +9498,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15" hidden="1">
+    <row r="71" spans="1:31" ht="15">
       <c r="A71" s="42" t="s">
         <v>57</v>
       </c>
@@ -9545,7 +9571,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15" hidden="1">
+    <row r="72" spans="1:31" ht="15">
       <c r="A72" s="42" t="s">
         <v>57</v>
       </c>
@@ -9618,7 +9644,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15" hidden="1">
+    <row r="73" spans="1:31" ht="15">
       <c r="A73" s="42" t="s">
         <v>57</v>
       </c>
@@ -9692,7 +9718,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="15" hidden="1">
+    <row r="74" spans="1:31" ht="15">
       <c r="A74" s="42" t="s">
         <v>57</v>
       </c>
@@ -9765,7 +9791,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="15" hidden="1">
+    <row r="75" spans="1:31" ht="15">
       <c r="A75" s="42" t="s">
         <v>59</v>
       </c>
@@ -9838,7 +9864,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="15" hidden="1">
+    <row r="76" spans="1:31" ht="15">
       <c r="A76" s="42" t="s">
         <v>59</v>
       </c>
@@ -9917,7 +9943,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="15" hidden="1">
+    <row r="77" spans="1:31" ht="15">
       <c r="A77" s="42" t="s">
         <v>59</v>
       </c>
@@ -9990,7 +10016,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="15" hidden="1">
+    <row r="78" spans="1:31" ht="15">
       <c r="A78" s="42" t="s">
         <v>59</v>
       </c>
@@ -10063,7 +10089,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="15" hidden="1">
+    <row r="79" spans="1:31" ht="15">
       <c r="A79" s="42" t="s">
         <v>59</v>
       </c>
@@ -10136,7 +10162,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="15" hidden="1">
+    <row r="80" spans="1:31" ht="15">
       <c r="A80" s="42" t="s">
         <v>59</v>
       </c>
@@ -10215,7 +10241,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="15" hidden="1">
+    <row r="81" spans="1:31" ht="15">
       <c r="A81" s="42" t="s">
         <v>59</v>
       </c>
@@ -10294,7 +10320,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="15" hidden="1">
+    <row r="82" spans="1:31" ht="15">
       <c r="A82" s="42" t="s">
         <v>59</v>
       </c>
@@ -10373,7 +10399,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="15" hidden="1">
+    <row r="83" spans="1:31" ht="15">
       <c r="A83" s="42" t="s">
         <v>59</v>
       </c>
@@ -10447,7 +10473,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="15" hidden="1">
+    <row r="84" spans="1:31" ht="15">
       <c r="A84" s="42" t="s">
         <v>59</v>
       </c>
@@ -10523,7 +10549,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="15" hidden="1">
+    <row r="85" spans="1:31" ht="15">
       <c r="A85" s="42" t="s">
         <v>59</v>
       </c>
@@ -10599,7 +10625,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="15" hidden="1">
+    <row r="86" spans="1:31" ht="15">
       <c r="A86" s="42" t="s">
         <v>59</v>
       </c>
@@ -10672,7 +10698,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="15" hidden="1">
+    <row r="87" spans="1:31" ht="15">
       <c r="A87" s="42" t="s">
         <v>59</v>
       </c>
@@ -10748,7 +10774,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="15" hidden="1">
+    <row r="88" spans="1:31" ht="15">
       <c r="A88" s="42" t="s">
         <v>59</v>
       </c>
@@ -10824,7 +10850,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="15" hidden="1">
+    <row r="89" spans="1:31" ht="15">
       <c r="A89" s="42" t="s">
         <v>59</v>
       </c>
@@ -10900,7 +10926,7 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="15" hidden="1">
+    <row r="90" spans="1:31" ht="15">
       <c r="A90" s="42" t="s">
         <v>638</v>
       </c>
@@ -10973,7 +10999,7 @@
       <c r="AD90"/>
       <c r="AE90"/>
     </row>
-    <row r="91" spans="1:31" ht="15" hidden="1">
+    <row r="91" spans="1:31" ht="15">
       <c r="A91" s="42" t="s">
         <v>638</v>
       </c>
@@ -11045,7 +11071,7 @@
       <c r="AD91"/>
       <c r="AE91"/>
     </row>
-    <row r="92" spans="1:31" ht="15" hidden="1">
+    <row r="92" spans="1:31" ht="15">
       <c r="A92" s="42" t="s">
         <v>638</v>
       </c>
@@ -11117,7 +11143,7 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="15" hidden="1">
+    <row r="93" spans="1:31" ht="15">
       <c r="A93" s="42" t="s">
         <v>640</v>
       </c>
@@ -11189,7 +11215,7 @@
       <c r="AD93"/>
       <c r="AE93"/>
     </row>
-    <row r="94" spans="1:31" ht="15" hidden="1">
+    <row r="94" spans="1:31" ht="15">
       <c r="A94" s="42" t="s">
         <v>642</v>
       </c>
@@ -11261,7 +11287,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="15" hidden="1">
+    <row r="95" spans="1:31" ht="15">
       <c r="A95" s="42" t="s">
         <v>642</v>
       </c>
@@ -11333,7 +11359,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="15" hidden="1">
+    <row r="96" spans="1:31" ht="15">
       <c r="A96" s="42" t="s">
         <v>642</v>
       </c>
@@ -11406,7 +11432,7 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="15" hidden="1">
+    <row r="97" spans="1:31" ht="15">
       <c r="A97" s="42" t="s">
         <v>644</v>
       </c>
@@ -11478,7 +11504,7 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="15" hidden="1">
+    <row r="98" spans="1:31" ht="15">
       <c r="A98" s="42" t="s">
         <v>644</v>
       </c>
@@ -11550,7 +11576,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="15" hidden="1">
+    <row r="99" spans="1:31" ht="15">
       <c r="A99" s="42" t="s">
         <v>644</v>
       </c>
@@ -11622,7 +11648,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="15" hidden="1">
+    <row r="100" spans="1:31" ht="15">
       <c r="A100" s="42" t="s">
         <v>61</v>
       </c>
@@ -11691,7 +11717,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="15" hidden="1">
+    <row r="101" spans="1:31" ht="15">
       <c r="A101" s="42" t="s">
         <v>61</v>
       </c>
@@ -11763,7 +11789,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="15" hidden="1">
+    <row r="102" spans="1:31" ht="15">
       <c r="A102" s="42" t="s">
         <v>64</v>
       </c>
@@ -11832,7 +11858,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="15" hidden="1">
+    <row r="103" spans="1:31" ht="15">
       <c r="A103" s="42" t="s">
         <v>64</v>
       </c>
@@ -11904,7 +11930,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="15" hidden="1">
+    <row r="104" spans="1:31" ht="15">
       <c r="A104" s="42" t="s">
         <v>66</v>
       </c>
@@ -11973,7 +11999,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="15" hidden="1">
+    <row r="105" spans="1:31" ht="15">
       <c r="A105" s="42" t="s">
         <v>66</v>
       </c>
@@ -12045,7 +12071,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="15" hidden="1">
+    <row r="106" spans="1:31" ht="15">
       <c r="A106" s="42" t="s">
         <v>70</v>
       </c>
@@ -12114,7 +12140,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="15" hidden="1">
+    <row r="107" spans="1:31" ht="15">
       <c r="A107" s="42" t="s">
         <v>70</v>
       </c>
@@ -12186,7 +12212,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="15" hidden="1">
+    <row r="108" spans="1:31" ht="15">
       <c r="A108" s="42" t="s">
         <v>72</v>
       </c>
@@ -12255,7 +12281,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="15" hidden="1">
+    <row r="109" spans="1:31" ht="15">
       <c r="A109" s="42" t="s">
         <v>72</v>
       </c>
@@ -12327,7 +12353,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="15" hidden="1">
+    <row r="110" spans="1:31" ht="15">
       <c r="A110" s="42" t="s">
         <v>75</v>
       </c>
@@ -12396,7 +12422,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="15" hidden="1">
+    <row r="111" spans="1:31" ht="15">
       <c r="A111" s="42" t="s">
         <v>75</v>
       </c>
@@ -12468,7 +12494,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="15" hidden="1">
+    <row r="112" spans="1:31" ht="15">
       <c r="A112" s="42" t="s">
         <v>77</v>
       </c>
@@ -12535,7 +12561,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="15" hidden="1">
+    <row r="113" spans="1:31" ht="15">
       <c r="A113" s="42" t="s">
         <v>77</v>
       </c>
@@ -12605,7 +12631,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="15" hidden="1">
+    <row r="114" spans="1:31" ht="15">
       <c r="A114" s="42" t="s">
         <v>80</v>
       </c>
@@ -12672,7 +12698,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="15" hidden="1">
+    <row r="115" spans="1:31" ht="15">
       <c r="A115" s="42" t="s">
         <v>80</v>
       </c>
@@ -12742,7 +12768,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="15" hidden="1">
+    <row r="116" spans="1:31" ht="15">
       <c r="A116" s="42" t="s">
         <v>82</v>
       </c>
@@ -12812,7 +12838,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="15" hidden="1">
+    <row r="117" spans="1:31" ht="15">
       <c r="A117" s="42" t="s">
         <v>82</v>
       </c>
@@ -12885,7 +12911,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="15" hidden="1">
+    <row r="118" spans="1:31" ht="15">
       <c r="A118" s="42" t="s">
         <v>84</v>
       </c>
@@ -12955,7 +12981,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="15" hidden="1">
+    <row r="119" spans="1:31" ht="15">
       <c r="A119" s="42" t="s">
         <v>84</v>
       </c>
@@ -13028,7 +13054,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="15" hidden="1">
+    <row r="120" spans="1:31" ht="15">
       <c r="A120" s="42" t="s">
         <v>86</v>
       </c>
@@ -13098,7 +13124,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="15" hidden="1">
+    <row r="121" spans="1:31" ht="15">
       <c r="A121" s="42" t="s">
         <v>86</v>
       </c>
@@ -13171,7 +13197,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="15" hidden="1">
+    <row r="122" spans="1:31" ht="15">
       <c r="A122" s="42" t="s">
         <v>88</v>
       </c>
@@ -13241,7 +13267,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="15" hidden="1">
+    <row r="123" spans="1:31" ht="15">
       <c r="A123" s="42" t="s">
         <v>88</v>
       </c>
@@ -13314,7 +13340,7 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="15" hidden="1">
+    <row r="124" spans="1:31" ht="15">
       <c r="A124" s="42" t="s">
         <v>90</v>
       </c>
@@ -13384,7 +13410,7 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="15" hidden="1">
+    <row r="125" spans="1:31" ht="15">
       <c r="A125" s="42" t="s">
         <v>90</v>
       </c>
@@ -13457,7 +13483,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="15" hidden="1">
+    <row r="126" spans="1:31" ht="15">
       <c r="A126" s="42" t="s">
         <v>92</v>
       </c>
@@ -13527,7 +13553,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="15" hidden="1">
+    <row r="127" spans="1:31" ht="15">
       <c r="A127" s="42" t="s">
         <v>92</v>
       </c>
@@ -13600,7 +13626,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="15" hidden="1">
+    <row r="128" spans="1:31" ht="15">
       <c r="A128" s="42" t="s">
         <v>94</v>
       </c>
@@ -13670,7 +13696,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="15" hidden="1">
+    <row r="129" spans="1:31" ht="15">
       <c r="A129" s="42" t="s">
         <v>94</v>
       </c>
@@ -13743,7 +13769,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="15" hidden="1">
+    <row r="130" spans="1:31" ht="15">
       <c r="A130" s="42" t="s">
         <v>96</v>
       </c>
@@ -13811,7 +13837,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="15" hidden="1">
+    <row r="131" spans="1:31" ht="15">
       <c r="A131" s="42" t="s">
         <v>96</v>
       </c>
@@ -13882,7 +13908,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="15" hidden="1">
+    <row r="132" spans="1:31" ht="15">
       <c r="A132" s="42" t="s">
         <v>98</v>
       </c>
@@ -13950,7 +13976,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="15" hidden="1">
+    <row r="133" spans="1:31" ht="15">
       <c r="A133" s="79" t="s">
         <v>98</v>
       </c>
@@ -14020,7 +14046,7 @@
       <c r="AC133" s="46"/>
       <c r="AD133" s="46"/>
     </row>
-    <row r="134" spans="1:31" ht="15" hidden="1">
+    <row r="134" spans="1:31" ht="15">
       <c r="A134" s="79" t="s">
         <v>100</v>
       </c>
@@ -14087,7 +14113,7 @@
       <c r="AC134" s="46"/>
       <c r="AD134" s="46"/>
     </row>
-    <row r="135" spans="1:31" ht="15" hidden="1">
+    <row r="135" spans="1:31" ht="15">
       <c r="A135" s="79" t="s">
         <v>100</v>
       </c>
@@ -14157,7 +14183,7 @@
       <c r="AC135" s="46"/>
       <c r="AD135" s="44"/>
     </row>
-    <row r="136" spans="1:31" ht="15" hidden="1">
+    <row r="136" spans="1:31" ht="15">
       <c r="A136" s="79" t="s">
         <v>102</v>
       </c>
@@ -14226,7 +14252,7 @@
       <c r="AC136" s="46"/>
       <c r="AD136" s="44"/>
     </row>
-    <row r="137" spans="1:31" ht="15" hidden="1">
+    <row r="137" spans="1:31" ht="15">
       <c r="A137" s="79" t="s">
         <v>102</v>
       </c>
@@ -14298,7 +14324,7 @@
       <c r="AC137" s="46"/>
       <c r="AD137" s="44"/>
     </row>
-    <row r="138" spans="1:31" ht="15" hidden="1">
+    <row r="138" spans="1:31" ht="15">
       <c r="A138" s="79" t="s">
         <v>104</v>
       </c>
@@ -14367,7 +14393,7 @@
       <c r="AC138" s="46"/>
       <c r="AD138" s="44"/>
     </row>
-    <row r="139" spans="1:31" ht="15" hidden="1">
+    <row r="139" spans="1:31" ht="15">
       <c r="A139" s="79" t="s">
         <v>104</v>
       </c>
@@ -14440,7 +14466,7 @@
       <c r="AD139" s="44"/>
       <c r="AE139" s="16"/>
     </row>
-    <row r="140" spans="1:31" ht="15" hidden="1">
+    <row r="140" spans="1:31" ht="15">
       <c r="A140" s="79" t="s">
         <v>106</v>
       </c>
@@ -14510,7 +14536,7 @@
       <c r="AD140" s="7"/>
       <c r="AE140" s="16"/>
     </row>
-    <row r="141" spans="1:31" ht="15" hidden="1">
+    <row r="141" spans="1:31" ht="15">
       <c r="A141" s="79" t="s">
         <v>106</v>
       </c>
@@ -14583,7 +14609,7 @@
       <c r="AD141" s="7"/>
       <c r="AE141" s="16"/>
     </row>
-    <row r="142" spans="1:31" ht="15" hidden="1">
+    <row r="142" spans="1:31" ht="15">
       <c r="A142" s="79" t="s">
         <v>108</v>
       </c>
@@ -14652,7 +14678,7 @@
       <c r="AC142" s="46"/>
       <c r="AD142" s="7"/>
     </row>
-    <row r="143" spans="1:31" ht="15" hidden="1">
+    <row r="143" spans="1:31" ht="15">
       <c r="A143" s="79" t="s">
         <v>108</v>
       </c>
@@ -14724,7 +14750,7 @@
       <c r="AC143" s="46"/>
       <c r="AD143" s="7"/>
     </row>
-    <row r="144" spans="1:31" ht="15" hidden="1">
+    <row r="144" spans="1:31" ht="15">
       <c r="A144" s="79" t="s">
         <v>110</v>
       </c>
@@ -14793,7 +14819,7 @@
       <c r="AC144" s="46"/>
       <c r="AD144" s="7"/>
     </row>
-    <row r="145" spans="1:31" ht="15" hidden="1">
+    <row r="145" spans="1:31" ht="15">
       <c r="A145" s="79" t="s">
         <v>110</v>
       </c>
@@ -14865,7 +14891,7 @@
       <c r="AC145" s="46"/>
       <c r="AD145" s="7"/>
     </row>
-    <row r="146" spans="1:31" ht="15" hidden="1">
+    <row r="146" spans="1:31" ht="15">
       <c r="A146" s="85" t="s">
         <v>112</v>
       </c>
@@ -14934,7 +14960,7 @@
       <c r="AC146" s="46"/>
       <c r="AD146" s="44"/>
     </row>
-    <row r="147" spans="1:31" ht="15" hidden="1">
+    <row r="147" spans="1:31" ht="15">
       <c r="A147" s="42" t="s">
         <v>112</v>
       </c>
@@ -15006,7 +15032,7 @@
       <c r="AD147"/>
       <c r="AE147"/>
     </row>
-    <row r="148" spans="1:31" ht="15" hidden="1">
+    <row r="148" spans="1:31" ht="15">
       <c r="A148" s="42" t="s">
         <v>114</v>
       </c>
@@ -15073,7 +15099,7 @@
       <c r="AD148"/>
       <c r="AE148"/>
     </row>
-    <row r="149" spans="1:31" ht="15" hidden="1">
+    <row r="149" spans="1:31" ht="15">
       <c r="A149" s="42" t="s">
         <v>114</v>
       </c>
@@ -15143,7 +15169,7 @@
       <c r="AD149"/>
       <c r="AE149"/>
     </row>
-    <row r="150" spans="1:31" ht="15" hidden="1">
+    <row r="150" spans="1:31" ht="15">
       <c r="A150" s="42" t="s">
         <v>116</v>
       </c>
@@ -15210,7 +15236,7 @@
       <c r="AD150"/>
       <c r="AE150"/>
     </row>
-    <row r="151" spans="1:31" ht="15" hidden="1">
+    <row r="151" spans="1:31" ht="15">
       <c r="A151" s="42" t="s">
         <v>116</v>
       </c>
@@ -15280,7 +15306,7 @@
       <c r="AD151"/>
       <c r="AE151"/>
     </row>
-    <row r="152" spans="1:31" ht="15" hidden="1">
+    <row r="152" spans="1:31" ht="15">
       <c r="A152" s="42" t="s">
         <v>118</v>
       </c>
@@ -15348,7 +15374,7 @@
       <c r="AD152"/>
       <c r="AE152"/>
     </row>
-    <row r="153" spans="1:31" ht="15" hidden="1">
+    <row r="153" spans="1:31" ht="15">
       <c r="A153" s="42" t="s">
         <v>118</v>
       </c>
@@ -15419,7 +15445,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="15" hidden="1">
+    <row r="154" spans="1:31" ht="15">
       <c r="A154" s="42" t="s">
         <v>123</v>
       </c>
@@ -15491,7 +15517,7 @@
       <c r="AC154" s="46"/>
       <c r="AD154" s="46"/>
     </row>
-    <row r="155" spans="1:31" ht="15" hidden="1">
+    <row r="155" spans="1:31" ht="15">
       <c r="A155" s="42" t="s">
         <v>123</v>
       </c>
@@ -15563,7 +15589,7 @@
       <c r="AC155" s="46"/>
       <c r="AD155" s="44"/>
     </row>
-    <row r="156" spans="1:31" ht="15" hidden="1">
+    <row r="156" spans="1:31" ht="15">
       <c r="A156" s="42" t="s">
         <v>123</v>
       </c>
@@ -15635,7 +15661,7 @@
       <c r="AC156" s="46"/>
       <c r="AD156" s="44"/>
     </row>
-    <row r="157" spans="1:31" ht="15" hidden="1">
+    <row r="157" spans="1:31" ht="15">
       <c r="A157" s="42" t="s">
         <v>123</v>
       </c>
@@ -15707,7 +15733,7 @@
       <c r="AC157" s="46"/>
       <c r="AD157" s="7"/>
     </row>
-    <row r="158" spans="1:31" ht="15" hidden="1">
+    <row r="158" spans="1:31" ht="15">
       <c r="A158" s="79" t="s">
         <v>123</v>
       </c>
@@ -15779,7 +15805,7 @@
       <c r="AC158" s="46"/>
       <c r="AD158" s="7"/>
     </row>
-    <row r="159" spans="1:31" ht="15" hidden="1">
+    <row r="159" spans="1:31" ht="15">
       <c r="A159" s="79" t="s">
         <v>123</v>
       </c>
@@ -15852,7 +15878,7 @@
       <c r="AC159" s="46"/>
       <c r="AD159" s="7"/>
     </row>
-    <row r="160" spans="1:31" ht="15" hidden="1">
+    <row r="160" spans="1:31" ht="15">
       <c r="A160" s="79" t="s">
         <v>123</v>
       </c>
@@ -15924,7 +15950,7 @@
       <c r="AC160" s="46"/>
       <c r="AD160" s="7"/>
     </row>
-    <row r="161" spans="1:30" ht="15" hidden="1">
+    <row r="161" spans="1:30" ht="15">
       <c r="A161" s="79" t="s">
         <v>123</v>
       </c>
@@ -15996,7 +16022,7 @@
       <c r="AC161" s="46"/>
       <c r="AD161" s="46"/>
     </row>
-    <row r="162" spans="1:30" ht="15" hidden="1">
+    <row r="162" spans="1:30" ht="15">
       <c r="A162" s="79" t="s">
         <v>123</v>
       </c>
@@ -16068,7 +16094,7 @@
       <c r="AC162" s="46"/>
       <c r="AD162" s="7"/>
     </row>
-    <row r="163" spans="1:30" ht="15" hidden="1">
+    <row r="163" spans="1:30" ht="15">
       <c r="A163" s="79" t="s">
         <v>123</v>
       </c>
@@ -16140,7 +16166,7 @@
       <c r="AC163" s="46"/>
       <c r="AD163" s="46"/>
     </row>
-    <row r="164" spans="1:30" ht="15" hidden="1">
+    <row r="164" spans="1:30" ht="15">
       <c r="A164" s="79" t="s">
         <v>123</v>
       </c>
@@ -16212,7 +16238,7 @@
       <c r="AC164" s="46"/>
       <c r="AD164" s="44"/>
     </row>
-    <row r="165" spans="1:30" ht="15" hidden="1">
+    <row r="165" spans="1:30" ht="15">
       <c r="A165" s="79" t="s">
         <v>123</v>
       </c>
@@ -16284,7 +16310,7 @@
       <c r="AC165" s="46"/>
       <c r="AD165" s="44"/>
     </row>
-    <row r="166" spans="1:30" ht="15" hidden="1">
+    <row r="166" spans="1:30" ht="15">
       <c r="A166" s="79" t="s">
         <v>123</v>
       </c>
@@ -16356,7 +16382,7 @@
       <c r="AC166" s="46"/>
       <c r="AD166" s="44"/>
     </row>
-    <row r="167" spans="1:30" ht="15" hidden="1">
+    <row r="167" spans="1:30" ht="15">
       <c r="A167" s="85" t="s">
         <v>123</v>
       </c>
@@ -16428,7 +16454,7 @@
       <c r="AC167" s="46"/>
       <c r="AD167" s="44"/>
     </row>
-    <row r="168" spans="1:30" ht="15" hidden="1">
+    <row r="168" spans="1:30" ht="15">
       <c r="A168" s="79" t="s">
         <v>125</v>
       </c>
@@ -16500,7 +16526,7 @@
       <c r="AC168" s="46"/>
       <c r="AD168" s="44"/>
     </row>
-    <row r="169" spans="1:30" ht="15" hidden="1">
+    <row r="169" spans="1:30" ht="15">
       <c r="A169" s="79" t="s">
         <v>125</v>
       </c>
@@ -16572,7 +16598,7 @@
       <c r="AC169" s="46"/>
       <c r="AD169" s="7"/>
     </row>
-    <row r="170" spans="1:30" ht="15" hidden="1">
+    <row r="170" spans="1:30" ht="15">
       <c r="A170" s="79" t="s">
         <v>125</v>
       </c>
@@ -16644,7 +16670,7 @@
       <c r="AC170" s="46"/>
       <c r="AD170" s="7"/>
     </row>
-    <row r="171" spans="1:30" ht="15" hidden="1">
+    <row r="171" spans="1:30" ht="15">
       <c r="A171" s="79" t="s">
         <v>125</v>
       </c>
@@ -16715,7 +16741,7 @@
       <c r="AB171" s="73"/>
       <c r="AD171" s="16"/>
     </row>
-    <row r="172" spans="1:30" ht="15" hidden="1">
+    <row r="172" spans="1:30" ht="15">
       <c r="A172" s="79" t="s">
         <v>125</v>
       </c>
@@ -16787,7 +16813,7 @@
       <c r="AC172" s="44"/>
       <c r="AD172" s="44"/>
     </row>
-    <row r="173" spans="1:30" ht="15" hidden="1">
+    <row r="173" spans="1:30" ht="15">
       <c r="A173" s="79" t="s">
         <v>125</v>
       </c>
@@ -16860,7 +16886,7 @@
       <c r="AC173" s="44"/>
       <c r="AD173" s="44"/>
     </row>
-    <row r="174" spans="1:30" ht="15" hidden="1">
+    <row r="174" spans="1:30" ht="15">
       <c r="A174" s="79" t="s">
         <v>125</v>
       </c>
@@ -16932,7 +16958,7 @@
       <c r="AC174" s="44"/>
       <c r="AD174" s="44"/>
     </row>
-    <row r="175" spans="1:30" ht="15" hidden="1">
+    <row r="175" spans="1:30" ht="15">
       <c r="A175" s="79" t="s">
         <v>125</v>
       </c>
@@ -17004,7 +17030,7 @@
       <c r="AC175" s="44"/>
       <c r="AD175" s="44"/>
     </row>
-    <row r="176" spans="1:30" ht="15" hidden="1">
+    <row r="176" spans="1:30" ht="15">
       <c r="A176" s="79" t="s">
         <v>125</v>
       </c>
@@ -17076,7 +17102,7 @@
       <c r="AC176" s="44"/>
       <c r="AD176" s="44"/>
     </row>
-    <row r="177" spans="1:30" ht="15" hidden="1">
+    <row r="177" spans="1:30" ht="15">
       <c r="A177" s="79" t="s">
         <v>125</v>
       </c>
@@ -17148,7 +17174,7 @@
       <c r="AC177" s="44"/>
       <c r="AD177" s="44"/>
     </row>
-    <row r="178" spans="1:30" ht="15" hidden="1">
+    <row r="178" spans="1:30" ht="15">
       <c r="A178" s="79" t="s">
         <v>125</v>
       </c>
@@ -17220,7 +17246,7 @@
       <c r="AC178" s="44"/>
       <c r="AD178" s="44"/>
     </row>
-    <row r="179" spans="1:30" ht="15" hidden="1">
+    <row r="179" spans="1:30" ht="15">
       <c r="A179" s="79" t="s">
         <v>125</v>
       </c>
@@ -17292,7 +17318,7 @@
       <c r="AC179" s="44"/>
       <c r="AD179" s="44"/>
     </row>
-    <row r="180" spans="1:30" ht="15" hidden="1">
+    <row r="180" spans="1:30" ht="15">
       <c r="A180" s="79" t="s">
         <v>125</v>
       </c>
@@ -17364,7 +17390,7 @@
       <c r="AC180" s="44"/>
       <c r="AD180" s="44"/>
     </row>
-    <row r="181" spans="1:30" ht="15" hidden="1">
+    <row r="181" spans="1:30" ht="15">
       <c r="A181" s="79" t="s">
         <v>125</v>
       </c>
@@ -17436,7 +17462,7 @@
       <c r="AC181" s="44"/>
       <c r="AD181" s="44"/>
     </row>
-    <row r="182" spans="1:30" ht="15" hidden="1">
+    <row r="182" spans="1:30" ht="15">
       <c r="A182" s="79" t="s">
         <v>127</v>
       </c>
@@ -17508,7 +17534,7 @@
       <c r="AC182" s="44"/>
       <c r="AD182" s="44"/>
     </row>
-    <row r="183" spans="1:30" ht="15" hidden="1">
+    <row r="183" spans="1:30" ht="15">
       <c r="A183" s="79" t="s">
         <v>127</v>
       </c>
@@ -17580,7 +17606,7 @@
       <c r="AC183" s="44"/>
       <c r="AD183" s="44"/>
     </row>
-    <row r="184" spans="1:30" ht="15" hidden="1">
+    <row r="184" spans="1:30" ht="15">
       <c r="A184" s="79" t="s">
         <v>127</v>
       </c>
@@ -17652,7 +17678,7 @@
       <c r="AC184" s="44"/>
       <c r="AD184" s="44"/>
     </row>
-    <row r="185" spans="1:30" ht="15" hidden="1">
+    <row r="185" spans="1:30" ht="15">
       <c r="A185" s="79" t="s">
         <v>127</v>
       </c>
@@ -17724,7 +17750,7 @@
       <c r="AC185" s="44"/>
       <c r="AD185" s="44"/>
     </row>
-    <row r="186" spans="1:30" ht="15" hidden="1">
+    <row r="186" spans="1:30" ht="15">
       <c r="A186" s="79" t="s">
         <v>127</v>
       </c>
@@ -17796,7 +17822,7 @@
       <c r="AC186" s="44"/>
       <c r="AD186" s="44"/>
     </row>
-    <row r="187" spans="1:30" ht="15" hidden="1">
+    <row r="187" spans="1:30" ht="15">
       <c r="A187" s="79" t="s">
         <v>127</v>
       </c>
@@ -17869,7 +17895,7 @@
       <c r="AC187" s="44"/>
       <c r="AD187" s="44"/>
     </row>
-    <row r="188" spans="1:30" ht="15" hidden="1">
+    <row r="188" spans="1:30" ht="15">
       <c r="A188" s="79" t="s">
         <v>127</v>
       </c>
@@ -17941,7 +17967,7 @@
       <c r="AC188" s="44"/>
       <c r="AD188" s="44"/>
     </row>
-    <row r="189" spans="1:30" ht="15" hidden="1">
+    <row r="189" spans="1:30" ht="15">
       <c r="A189" s="79" t="s">
         <v>127</v>
       </c>
@@ -18013,7 +18039,7 @@
       <c r="AC189" s="44"/>
       <c r="AD189" s="44"/>
     </row>
-    <row r="190" spans="1:30" ht="15" hidden="1">
+    <row r="190" spans="1:30" ht="15">
       <c r="A190" s="79" t="s">
         <v>127</v>
       </c>
@@ -18085,7 +18111,7 @@
       <c r="AC190" s="44"/>
       <c r="AD190" s="44"/>
     </row>
-    <row r="191" spans="1:30" ht="15" hidden="1">
+    <row r="191" spans="1:30" ht="15">
       <c r="A191" s="79" t="s">
         <v>127</v>
       </c>
@@ -18157,7 +18183,7 @@
       <c r="AC191" s="44"/>
       <c r="AD191" s="44"/>
     </row>
-    <row r="192" spans="1:30" ht="15" hidden="1">
+    <row r="192" spans="1:30" ht="15">
       <c r="A192" s="79" t="s">
         <v>127</v>
       </c>
@@ -18229,7 +18255,7 @@
       <c r="AC192" s="44"/>
       <c r="AD192" s="44"/>
     </row>
-    <row r="193" spans="1:30" ht="15" hidden="1">
+    <row r="193" spans="1:30" ht="15">
       <c r="A193" s="79" t="s">
         <v>127</v>
       </c>
@@ -18301,7 +18327,7 @@
       <c r="AC193" s="44"/>
       <c r="AD193" s="44"/>
     </row>
-    <row r="194" spans="1:30" ht="15" hidden="1">
+    <row r="194" spans="1:30" ht="15">
       <c r="A194" s="79" t="s">
         <v>127</v>
       </c>
@@ -18373,7 +18399,7 @@
       <c r="AC194" s="44"/>
       <c r="AD194" s="44"/>
     </row>
-    <row r="195" spans="1:30" ht="15" hidden="1">
+    <row r="195" spans="1:30" ht="15">
       <c r="A195" s="79" t="s">
         <v>127</v>
       </c>
@@ -18443,7 +18469,7 @@
       <c r="AC195" s="44"/>
       <c r="AD195" s="44"/>
     </row>
-    <row r="196" spans="1:30" ht="15" hidden="1">
+    <row r="196" spans="1:30" ht="15">
       <c r="A196" s="79" t="s">
         <v>165</v>
       </c>
@@ -18522,7 +18548,7 @@
       <c r="AC196" s="44"/>
       <c r="AD196" s="44"/>
     </row>
-    <row r="197" spans="1:30" ht="15" hidden="1">
+    <row r="197" spans="1:30" ht="15">
       <c r="A197" s="79" t="s">
         <v>167</v>
       </c>
@@ -18601,7 +18627,7 @@
       <c r="AC197" s="44"/>
       <c r="AD197" s="44"/>
     </row>
-    <row r="198" spans="1:30" ht="15" hidden="1">
+    <row r="198" spans="1:30" ht="15">
       <c r="A198" s="79" t="s">
         <v>169</v>
       </c>
@@ -18680,7 +18706,7 @@
       <c r="AC198" s="44"/>
       <c r="AD198" s="44"/>
     </row>
-    <row r="199" spans="1:30" ht="15" hidden="1">
+    <row r="199" spans="1:30" ht="15">
       <c r="A199" s="85" t="s">
         <v>1</v>
       </c>
@@ -18759,24 +18785,82 @@
       <c r="AC199" s="44"/>
       <c r="AD199" s="44"/>
     </row>
-    <row r="200" spans="1:30" ht="12.75">
-      <c r="A200" s="42"/>
-      <c r="B200" s="42"/>
-      <c r="C200" s="42"/>
-      <c r="I200" s="44"/>
-      <c r="J200" s="44"/>
-      <c r="K200" s="44"/>
-      <c r="M200" s="44"/>
-      <c r="N200" s="44"/>
-      <c r="O200" s="44"/>
-      <c r="Q200" s="55"/>
-      <c r="U200" s="44"/>
-      <c r="X200" s="44"/>
-      <c r="Y200" s="44"/>
-      <c r="Z200" s="44"/>
-      <c r="AA200" s="44"/>
-      <c r="AB200" s="44"/>
-      <c r="AC200" s="44"/>
+    <row r="200" spans="1:30" ht="15">
+      <c r="A200" s="112" t="s">
+        <v>647</v>
+      </c>
+      <c r="B200" s="113" t="s">
+        <v>646</v>
+      </c>
+      <c r="C200" s="117">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7378</v>
+      </c>
+      <c r="D200" s="118">
+        <v>3689</v>
+      </c>
+      <c r="E200" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F200" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>164</v>
+      </c>
+      <c r="G200" s="114">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>3525</v>
+      </c>
+      <c r="H200" s="105">
+        <v>7050</v>
+      </c>
+      <c r="I200" s="94" t="s">
+        <v>648</v>
+      </c>
+      <c r="J200" s="46">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>230</v>
+      </c>
+      <c r="K200" s="114">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3295</v>
+      </c>
+      <c r="L200" s="119">
+        <v>6590</v>
+      </c>
+      <c r="M200" s="86"/>
+      <c r="N200" s="115">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3295</v>
+      </c>
+      <c r="O200" s="115">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P200" s="86"/>
+      <c r="Q200" s="88">
+        <v>0</v>
+      </c>
+      <c r="R200" s="88" t="s">
+        <v>52</v>
+      </c>
+      <c r="S200" s="88">
+        <v>0</v>
+      </c>
+      <c r="T200" s="89" t="s">
+        <v>55</v>
+      </c>
+      <c r="U200" s="89">
+        <v>0</v>
+      </c>
+      <c r="V200" s="116" t="s">
+        <v>56</v>
+      </c>
+      <c r="X200" s="46"/>
+      <c r="Y200" s="46"/>
+      <c r="Z200" s="46"/>
+      <c r="AA200" s="46"/>
+      <c r="AB200" s="46"/>
+      <c r="AC200" s="46"/>
       <c r="AD200" s="44"/>
     </row>
     <row r="201" spans="1:30" ht="12.75">

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1555" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4847A2AD-1565-469C-918A-0BDC5B2EF7B2}"/>
+  <xr:revisionPtr revIDLastSave="1556" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2CEA89C-C41E-4A70-8891-8D16C1AD85C3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="646">
   <si>
     <t>Choose Hearing Aid Model</t>
   </si>
@@ -2002,15 +2002,6 @@
   </si>
   <si>
     <t>Beltone Illuminate 9 62S-DRWC Digital RIE</t>
-  </si>
-  <si>
-    <t>Beltone Serene 6 ITC-DW Digital ITC</t>
-  </si>
-  <si>
-    <t>Beltone ITC Digital Serene 6 ITC-DW</t>
-  </si>
-  <si>
-    <t>NaphCare</t>
   </si>
 </sst>
 </file>
@@ -2139,7 +2130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -2364,19 +2355,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2384,7 +2362,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2587,16 +2565,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="11" fillId="6" borderId="20" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="11" fillId="6" borderId="20" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3364,8 +3332,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V200" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:V200" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A75:V89">
     <sortCondition ref="I1:I199"/>
   </sortState>
@@ -4360,7 +4328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8E355-D10F-45CB-8710-0B743D2C5CA5}">
-  <dimension ref="A1:AF213"/>
+  <dimension ref="A1:AF212"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="53.85546875" customWidth="1"/>
@@ -18785,82 +18753,24 @@
       <c r="AC199" s="44"/>
       <c r="AD199" s="44"/>
     </row>
-    <row r="200" spans="1:30" ht="15">
-      <c r="A200" s="112" t="s">
-        <v>647</v>
-      </c>
-      <c r="B200" s="113" t="s">
-        <v>646</v>
-      </c>
-      <c r="C200" s="117">
-        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7378</v>
-      </c>
-      <c r="D200" s="118">
-        <v>3689</v>
-      </c>
-      <c r="E200" s="86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F200" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>164</v>
-      </c>
-      <c r="G200" s="114">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3525</v>
-      </c>
-      <c r="H200" s="105">
-        <v>7050</v>
-      </c>
-      <c r="I200" s="94" t="s">
-        <v>648</v>
-      </c>
-      <c r="J200" s="46">
-        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>230</v>
-      </c>
-      <c r="K200" s="114">
-        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3295</v>
-      </c>
-      <c r="L200" s="119">
-        <v>6590</v>
-      </c>
-      <c r="M200" s="86"/>
-      <c r="N200" s="115">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>3295</v>
-      </c>
-      <c r="O200" s="115">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
-      </c>
-      <c r="P200" s="86"/>
-      <c r="Q200" s="88">
-        <v>0</v>
-      </c>
-      <c r="R200" s="88" t="s">
-        <v>52</v>
-      </c>
-      <c r="S200" s="88">
-        <v>0</v>
-      </c>
-      <c r="T200" s="89" t="s">
-        <v>55</v>
-      </c>
-      <c r="U200" s="89">
-        <v>0</v>
-      </c>
-      <c r="V200" s="116" t="s">
-        <v>56</v>
-      </c>
-      <c r="X200" s="46"/>
-      <c r="Y200" s="46"/>
-      <c r="Z200" s="46"/>
-      <c r="AA200" s="46"/>
-      <c r="AB200" s="46"/>
-      <c r="AC200" s="46"/>
+    <row r="200" spans="1:30" ht="12.75">
+      <c r="A200" s="42"/>
+      <c r="B200" s="42"/>
+      <c r="C200" s="42"/>
+      <c r="I200" s="44"/>
+      <c r="J200" s="44"/>
+      <c r="K200" s="44"/>
+      <c r="M200" s="44"/>
+      <c r="N200" s="44"/>
+      <c r="O200" s="44"/>
+      <c r="Q200" s="55"/>
+      <c r="U200" s="44"/>
+      <c r="X200" s="44"/>
+      <c r="Y200" s="44"/>
+      <c r="Z200" s="44"/>
+      <c r="AA200" s="44"/>
+      <c r="AB200" s="44"/>
+      <c r="AC200" s="44"/>
       <c r="AD200" s="44"/>
     </row>
     <row r="201" spans="1:30" ht="12.75">
@@ -18990,7 +18900,6 @@
       <c r="I207" s="44"/>
       <c r="J207" s="44"/>
       <c r="K207" s="44"/>
-      <c r="M207" s="44"/>
       <c r="N207" s="44"/>
       <c r="O207" s="44"/>
       <c r="Q207" s="55"/>
@@ -19052,13 +18961,6 @@
       <c r="O210" s="44"/>
       <c r="Q210" s="55"/>
       <c r="U210" s="44"/>
-      <c r="X210" s="44"/>
-      <c r="Y210" s="44"/>
-      <c r="Z210" s="44"/>
-      <c r="AA210" s="44"/>
-      <c r="AB210" s="44"/>
-      <c r="AC210" s="44"/>
-      <c r="AD210" s="44"/>
     </row>
     <row r="211" spans="1:30" ht="12.75">
       <c r="A211" s="42"/>
@@ -19083,18 +18985,6 @@
       <c r="O212" s="44"/>
       <c r="Q212" s="55"/>
       <c r="U212" s="44"/>
-    </row>
-    <row r="213" spans="1:30" ht="12.75">
-      <c r="A213" s="42"/>
-      <c r="B213" s="42"/>
-      <c r="C213" s="42"/>
-      <c r="I213" s="44"/>
-      <c r="J213" s="44"/>
-      <c r="K213" s="44"/>
-      <c r="N213" s="44"/>
-      <c r="O213" s="44"/>
-      <c r="Q213" s="55"/>
-      <c r="U213" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1556" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2CEA89C-C41E-4A70-8891-8D16C1AD85C3}"/>
+  <xr:revisionPtr revIDLastSave="1565" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{852350F0-0916-4668-95FF-7736CDE1FE40}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -3333,8 +3333,17 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A75:V89">
+  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Beltone Illuminate 17 62S-DRWC Digital RIE"/>
+        <filter val="Beltone Illuminate 4 62S-DRWC Digital RIE"/>
+        <filter val="Beltone Illuminate 6 62S-DRWC Digital RIE"/>
+        <filter val="Beltone Illuminate 9 62S-DRWC Digital RIE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A90:V99">
     <sortCondition ref="I1:I199"/>
   </sortState>
   <tableColumns count="22">
@@ -4435,7 +4444,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="15">
+    <row r="2" spans="1:31" ht="15" hidden="1">
       <c r="A2" s="42" t="s">
         <v>130</v>
       </c>
@@ -4505,7 +4514,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="15">
+    <row r="3" spans="1:31" ht="15" hidden="1">
       <c r="A3" s="42" t="s">
         <v>130</v>
       </c>
@@ -4574,7 +4583,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="15">
+    <row r="4" spans="1:31" ht="15" hidden="1">
       <c r="A4" s="42" t="s">
         <v>130</v>
       </c>
@@ -4646,7 +4655,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="15">
+    <row r="5" spans="1:31" ht="15" hidden="1">
       <c r="A5" s="42" t="s">
         <v>130</v>
       </c>
@@ -4718,7 +4727,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="15">
+    <row r="6" spans="1:31" ht="15" hidden="1">
       <c r="A6" s="42" t="s">
         <v>120</v>
       </c>
@@ -4785,7 +4794,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="15">
+    <row r="7" spans="1:31" ht="15" hidden="1">
       <c r="A7" s="42" t="s">
         <v>120</v>
       </c>
@@ -4849,7 +4858,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="15">
+    <row r="8" spans="1:31" ht="15" hidden="1">
       <c r="A8" s="42" t="s">
         <v>132</v>
       </c>
@@ -4918,7 +4927,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="15">
+    <row r="9" spans="1:31" ht="15" hidden="1">
       <c r="A9" s="42" t="s">
         <v>132</v>
       </c>
@@ -4990,7 +4999,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="15">
+    <row r="10" spans="1:31" ht="15" hidden="1">
       <c r="A10" s="42" t="s">
         <v>132</v>
       </c>
@@ -5062,7 +5071,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="15">
+    <row r="11" spans="1:31" ht="15" hidden="1">
       <c r="A11" s="42" t="s">
         <v>134</v>
       </c>
@@ -5131,7 +5140,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="15">
+    <row r="12" spans="1:31" ht="15" hidden="1">
       <c r="A12" s="42" t="s">
         <v>132</v>
       </c>
@@ -5200,7 +5209,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="15">
+    <row r="13" spans="1:31" ht="15" hidden="1">
       <c r="A13" s="42" t="s">
         <v>134</v>
       </c>
@@ -5269,7 +5278,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="15">
+    <row r="14" spans="1:31" ht="15" hidden="1">
       <c r="A14" s="42" t="s">
         <v>134</v>
       </c>
@@ -5341,7 +5350,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="15">
+    <row r="15" spans="1:31" ht="15" hidden="1">
       <c r="A15" s="42" t="s">
         <v>134</v>
       </c>
@@ -5414,7 +5423,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="15">
+    <row r="16" spans="1:31" ht="15" hidden="1">
       <c r="A16" s="42" t="s">
         <v>139</v>
       </c>
@@ -5487,7 +5496,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="15">
+    <row r="17" spans="1:31" ht="15" hidden="1">
       <c r="A17" s="42" t="s">
         <v>139</v>
       </c>
@@ -5560,7 +5569,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="15">
+    <row r="18" spans="1:31" ht="15" hidden="1">
       <c r="A18" s="42" t="s">
         <v>142</v>
       </c>
@@ -5632,7 +5641,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="15">
+    <row r="19" spans="1:31" ht="15" hidden="1">
       <c r="A19" s="42" t="s">
         <v>142</v>
       </c>
@@ -5705,7 +5714,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="15">
+    <row r="20" spans="1:31" ht="15" hidden="1">
       <c r="A20" s="42" t="s">
         <v>144</v>
       </c>
@@ -5777,7 +5786,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="15">
+    <row r="21" spans="1:31" ht="15" hidden="1">
       <c r="A21" s="42" t="s">
         <v>144</v>
       </c>
@@ -5850,7 +5859,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="15">
+    <row r="22" spans="1:31" ht="15" hidden="1">
       <c r="A22" s="42" t="s">
         <v>146</v>
       </c>
@@ -5922,7 +5931,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="15">
+    <row r="23" spans="1:31" ht="15" hidden="1">
       <c r="A23" s="42" t="s">
         <v>146</v>
       </c>
@@ -5994,7 +6003,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15">
+    <row r="24" spans="1:31" ht="15" hidden="1">
       <c r="A24" s="42" t="s">
         <v>148</v>
       </c>
@@ -6066,7 +6075,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15">
+    <row r="25" spans="1:31" ht="15" hidden="1">
       <c r="A25" s="42" t="s">
         <v>148</v>
       </c>
@@ -6140,7 +6149,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15">
+    <row r="26" spans="1:31" ht="15" hidden="1">
       <c r="A26" s="42" t="s">
         <v>150</v>
       </c>
@@ -6213,7 +6222,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15">
+    <row r="27" spans="1:31" ht="15" hidden="1">
       <c r="A27" s="42" t="s">
         <v>150</v>
       </c>
@@ -6287,7 +6296,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15">
+    <row r="28" spans="1:31" ht="15" hidden="1">
       <c r="A28" s="42" t="s">
         <v>43</v>
       </c>
@@ -6350,7 +6359,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15">
+    <row r="29" spans="1:31" ht="15" hidden="1">
       <c r="A29" s="42" t="s">
         <v>43</v>
       </c>
@@ -6422,7 +6431,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="15">
+    <row r="30" spans="1:31" ht="15" hidden="1">
       <c r="A30" s="42" t="s">
         <v>47</v>
       </c>
@@ -6494,7 +6503,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="15">
+    <row r="31" spans="1:31" ht="15" hidden="1">
       <c r="A31" s="42" t="s">
         <v>47</v>
       </c>
@@ -6565,7 +6574,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="15">
+    <row r="32" spans="1:31" ht="15" hidden="1">
       <c r="A32" s="42" t="s">
         <v>47</v>
       </c>
@@ -6637,7 +6646,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="15">
+    <row r="33" spans="1:31" ht="15" hidden="1">
       <c r="A33" s="42" t="s">
         <v>47</v>
       </c>
@@ -6709,7 +6718,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="15">
+    <row r="34" spans="1:31" ht="15" hidden="1">
       <c r="A34" s="42" t="s">
         <v>47</v>
       </c>
@@ -6781,7 +6790,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:31" ht="15">
+    <row r="35" spans="1:31" ht="15" hidden="1">
       <c r="A35" s="42" t="s">
         <v>47</v>
       </c>
@@ -6853,7 +6862,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="15">
+    <row r="36" spans="1:31" ht="15" hidden="1">
       <c r="A36" s="42" t="s">
         <v>47</v>
       </c>
@@ -6926,7 +6935,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="15">
+    <row r="37" spans="1:31" ht="15" hidden="1">
       <c r="A37" s="42" t="s">
         <v>47</v>
       </c>
@@ -6998,7 +7007,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="15">
+    <row r="38" spans="1:31" ht="15" hidden="1">
       <c r="A38" s="42" t="s">
         <v>47</v>
       </c>
@@ -7070,7 +7079,7 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="15">
+    <row r="39" spans="1:31" ht="15" hidden="1">
       <c r="A39" s="42" t="s">
         <v>47</v>
       </c>
@@ -7142,7 +7151,7 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="15">
+    <row r="40" spans="1:31" ht="15" hidden="1">
       <c r="A40" s="42" t="s">
         <v>47</v>
       </c>
@@ -7214,7 +7223,7 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="15">
+    <row r="41" spans="1:31" ht="15" hidden="1">
       <c r="A41" s="42" t="s">
         <v>47</v>
       </c>
@@ -7286,7 +7295,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="15">
+    <row r="42" spans="1:31" ht="15" hidden="1">
       <c r="A42" s="42" t="s">
         <v>47</v>
       </c>
@@ -7358,7 +7367,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="15">
+    <row r="43" spans="1:31" ht="15" hidden="1">
       <c r="A43" s="42" t="s">
         <v>53</v>
       </c>
@@ -7436,7 +7445,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="15">
+    <row r="44" spans="1:31" ht="15" hidden="1">
       <c r="A44" s="42" t="s">
         <v>53</v>
       </c>
@@ -7514,7 +7523,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="15">
+    <row r="45" spans="1:31" ht="15" hidden="1">
       <c r="A45" s="42" t="s">
         <v>53</v>
       </c>
@@ -7592,7 +7601,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="15">
+    <row r="46" spans="1:31" ht="15" hidden="1">
       <c r="A46" s="42" t="s">
         <v>53</v>
       </c>
@@ -7670,7 +7679,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="15">
+    <row r="47" spans="1:31" ht="15" hidden="1">
       <c r="A47" s="42" t="s">
         <v>53</v>
       </c>
@@ -7745,7 +7754,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="15">
+    <row r="48" spans="1:31" ht="15" hidden="1">
       <c r="A48" s="42" t="s">
         <v>53</v>
       </c>
@@ -7820,7 +7829,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="15">
+    <row r="49" spans="1:32" ht="15" hidden="1">
       <c r="A49" s="42" t="s">
         <v>53</v>
       </c>
@@ -7896,7 +7905,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="15">
+    <row r="50" spans="1:32" ht="15" hidden="1">
       <c r="A50" s="42" t="s">
         <v>53</v>
       </c>
@@ -7972,7 +7981,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="15">
+    <row r="51" spans="1:32" ht="15" hidden="1">
       <c r="A51" s="42" t="s">
         <v>53</v>
       </c>
@@ -8048,7 +8057,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="15">
+    <row r="52" spans="1:32" ht="15" hidden="1">
       <c r="A52" s="42" t="s">
         <v>53</v>
       </c>
@@ -8118,7 +8127,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="15">
+    <row r="53" spans="1:32" ht="15" hidden="1">
       <c r="A53" s="42" t="s">
         <v>53</v>
       </c>
@@ -8191,7 +8200,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="15">
+    <row r="54" spans="1:32" ht="15" hidden="1">
       <c r="A54" s="42" t="s">
         <v>53</v>
       </c>
@@ -8264,7 +8273,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="15">
+    <row r="55" spans="1:32" ht="15" hidden="1">
       <c r="A55" s="42" t="s">
         <v>53</v>
       </c>
@@ -8337,7 +8346,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="15">
+    <row r="56" spans="1:32" ht="15" hidden="1">
       <c r="A56" s="42" t="s">
         <v>53</v>
       </c>
@@ -8411,7 +8420,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="15">
+    <row r="57" spans="1:32" ht="15" hidden="1">
       <c r="A57" s="42" t="s">
         <v>53</v>
       </c>
@@ -8484,7 +8493,7 @@
       <c r="AE57" s="16"/>
       <c r="AF57" s="16"/>
     </row>
-    <row r="58" spans="1:32" ht="15">
+    <row r="58" spans="1:32" ht="15" hidden="1">
       <c r="A58" s="42" t="s">
         <v>50</v>
       </c>
@@ -8556,7 +8565,7 @@
       <c r="AE58" s="16"/>
       <c r="AF58" s="16"/>
     </row>
-    <row r="59" spans="1:32" ht="15">
+    <row r="59" spans="1:32" ht="15" hidden="1">
       <c r="A59" s="42" t="s">
         <v>50</v>
       </c>
@@ -8628,7 +8637,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="15">
+    <row r="60" spans="1:32" ht="15" hidden="1">
       <c r="A60" s="42" t="s">
         <v>57</v>
       </c>
@@ -8706,7 +8715,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="15">
+    <row r="61" spans="1:32" ht="15" hidden="1">
       <c r="A61" s="42" t="s">
         <v>57</v>
       </c>
@@ -8785,7 +8794,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="15">
+    <row r="62" spans="1:32" ht="15" hidden="1">
       <c r="A62" s="42" t="s">
         <v>57</v>
       </c>
@@ -8864,7 +8873,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="15">
+    <row r="63" spans="1:32" ht="15" hidden="1">
       <c r="A63" s="42" t="s">
         <v>57</v>
       </c>
@@ -8943,7 +8952,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="15">
+    <row r="64" spans="1:32" ht="15" hidden="1">
       <c r="A64" s="42" t="s">
         <v>57</v>
       </c>
@@ -9019,7 +9028,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15">
+    <row r="65" spans="1:31" ht="15" hidden="1">
       <c r="A65" s="42" t="s">
         <v>57</v>
       </c>
@@ -9095,7 +9104,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15">
+    <row r="66" spans="1:31" ht="15" hidden="1">
       <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
@@ -9171,7 +9180,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15">
+    <row r="67" spans="1:31" ht="15" hidden="1">
       <c r="A67" s="42" t="s">
         <v>57</v>
       </c>
@@ -9247,7 +9256,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15">
+    <row r="68" spans="1:31" ht="15" hidden="1">
       <c r="A68" s="42" t="s">
         <v>57</v>
       </c>
@@ -9323,7 +9332,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15">
+    <row r="69" spans="1:31" ht="15" hidden="1">
       <c r="A69" s="42" t="s">
         <v>57</v>
       </c>
@@ -9393,7 +9402,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15">
+    <row r="70" spans="1:31" ht="15" hidden="1">
       <c r="A70" s="42" t="s">
         <v>57</v>
       </c>
@@ -9466,7 +9475,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15">
+    <row r="71" spans="1:31" ht="15" hidden="1">
       <c r="A71" s="42" t="s">
         <v>57</v>
       </c>
@@ -9539,7 +9548,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15">
+    <row r="72" spans="1:31" ht="15" hidden="1">
       <c r="A72" s="42" t="s">
         <v>57</v>
       </c>
@@ -9612,7 +9621,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15">
+    <row r="73" spans="1:31" ht="15" hidden="1">
       <c r="A73" s="42" t="s">
         <v>57</v>
       </c>
@@ -9686,7 +9695,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="15">
+    <row r="74" spans="1:31" ht="15" hidden="1">
       <c r="A74" s="42" t="s">
         <v>57</v>
       </c>
@@ -9759,7 +9768,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="15">
+    <row r="75" spans="1:31" ht="15" hidden="1">
       <c r="A75" s="42" t="s">
         <v>59</v>
       </c>
@@ -9832,7 +9841,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="15">
+    <row r="76" spans="1:31" ht="15" hidden="1">
       <c r="A76" s="42" t="s">
         <v>59</v>
       </c>
@@ -9911,7 +9920,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="15">
+    <row r="77" spans="1:31" ht="15" hidden="1">
       <c r="A77" s="42" t="s">
         <v>59</v>
       </c>
@@ -9984,7 +9993,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="15">
+    <row r="78" spans="1:31" ht="15" hidden="1">
       <c r="A78" s="42" t="s">
         <v>59</v>
       </c>
@@ -10057,7 +10066,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="15">
+    <row r="79" spans="1:31" ht="15" hidden="1">
       <c r="A79" s="42" t="s">
         <v>59</v>
       </c>
@@ -10130,7 +10139,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="15">
+    <row r="80" spans="1:31" ht="15" hidden="1">
       <c r="A80" s="42" t="s">
         <v>59</v>
       </c>
@@ -10209,7 +10218,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="15">
+    <row r="81" spans="1:31" ht="15" hidden="1">
       <c r="A81" s="42" t="s">
         <v>59</v>
       </c>
@@ -10288,7 +10297,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="15">
+    <row r="82" spans="1:31" ht="15" hidden="1">
       <c r="A82" s="42" t="s">
         <v>59</v>
       </c>
@@ -10367,7 +10376,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="15">
+    <row r="83" spans="1:31" ht="15" hidden="1">
       <c r="A83" s="42" t="s">
         <v>59</v>
       </c>
@@ -10441,7 +10450,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="15">
+    <row r="84" spans="1:31" ht="15" hidden="1">
       <c r="A84" s="42" t="s">
         <v>59</v>
       </c>
@@ -10517,7 +10526,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="15">
+    <row r="85" spans="1:31" ht="15" hidden="1">
       <c r="A85" s="42" t="s">
         <v>59</v>
       </c>
@@ -10593,7 +10602,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="15">
+    <row r="86" spans="1:31" ht="15" hidden="1">
       <c r="A86" s="42" t="s">
         <v>59</v>
       </c>
@@ -10666,7 +10675,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="15">
+    <row r="87" spans="1:31" ht="15" hidden="1">
       <c r="A87" s="42" t="s">
         <v>59</v>
       </c>
@@ -10742,7 +10751,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="15">
+    <row r="88" spans="1:31" ht="15" hidden="1">
       <c r="A88" s="42" t="s">
         <v>59</v>
       </c>
@@ -10818,7 +10827,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="15">
+    <row r="89" spans="1:31" ht="15" hidden="1">
       <c r="A89" s="42" t="s">
         <v>59</v>
       </c>
@@ -10969,45 +10978,45 @@
     </row>
     <row r="91" spans="1:31" ht="15">
       <c r="A91" s="42" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B91" s="95" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C91" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>12203</v>
+        <v>6623</v>
       </c>
       <c r="D91" s="105">
-        <v>5939</v>
+        <v>3149</v>
       </c>
       <c r="E91" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1276.5</v>
+        <v>636.5</v>
       </c>
       <c r="G91" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4662.5</v>
+        <v>2512.5</v>
       </c>
       <c r="H91" s="105">
-        <v>9650</v>
+        <v>5350</v>
       </c>
       <c r="I91" s="77" t="s">
-        <v>156</v>
+        <v>45</v>
       </c>
       <c r="J91" s="46">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K91" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4162.5</v>
+        <v>2512.5</v>
       </c>
       <c r="L91" s="106">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>8650</v>
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
+        <v>5350</v>
       </c>
       <c r="M91" s="46"/>
       <c r="N91" s="46"/>
@@ -11041,49 +11050,49 @@
     </row>
     <row r="92" spans="1:31" ht="15">
       <c r="A92" s="42" t="s">
-        <v>638</v>
-      </c>
-      <c r="B92" s="42" t="s">
-        <v>639</v>
+        <v>642</v>
+      </c>
+      <c r="B92" s="95" t="s">
+        <v>643</v>
       </c>
       <c r="C92" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>12203</v>
+        <v>8003</v>
       </c>
       <c r="D92" s="105">
-        <v>5939</v>
+        <v>3839</v>
       </c>
       <c r="E92" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F92" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1276.5</v>
+        <v>276.5</v>
       </c>
       <c r="G92" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4662.5</v>
+        <v>3562.5</v>
       </c>
       <c r="H92" s="105">
-        <v>9650</v>
+        <v>7450</v>
       </c>
       <c r="I92" s="77" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="J92" s="46">
-        <v>925</v>
+        <v>0</v>
       </c>
       <c r="K92" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3737.5</v>
+        <v>3562.5</v>
       </c>
       <c r="L92" s="106">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>8650</v>
-      </c>
-      <c r="M92" s="77"/>
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
+        <v>7450</v>
+      </c>
+      <c r="M92" s="46"/>
       <c r="N92" s="46"/>
-      <c r="O92" s="77"/>
+      <c r="O92" s="46"/>
       <c r="P92" s="46"/>
       <c r="Q92" s="47">
         <v>1</v>
@@ -11113,31 +11122,31 @@
     </row>
     <row r="93" spans="1:31" ht="15">
       <c r="A93" s="42" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B93" s="95" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C93" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>6623</v>
+        <v>10403</v>
       </c>
       <c r="D93" s="105">
-        <v>3149</v>
+        <v>5039</v>
       </c>
       <c r="E93" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F93" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>636.5</v>
+        <v>926.5</v>
       </c>
       <c r="G93" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>2512.5</v>
+        <v>4112.5</v>
       </c>
       <c r="H93" s="105">
-        <v>5350</v>
+        <v>8550</v>
       </c>
       <c r="I93" s="77" t="s">
         <v>45</v>
@@ -11147,11 +11156,11 @@
       </c>
       <c r="K93" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2512.5</v>
+        <v>4112.5</v>
       </c>
       <c r="L93" s="106">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
-        <v>5350</v>
+        <v>8550</v>
       </c>
       <c r="M93" s="46"/>
       <c r="N93" s="46"/>
@@ -11185,45 +11194,45 @@
     </row>
     <row r="94" spans="1:31" ht="15">
       <c r="A94" s="42" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B94" s="95" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C94" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
+        <v>12203</v>
       </c>
       <c r="D94" s="105">
-        <v>3839</v>
+        <v>5939</v>
       </c>
       <c r="E94" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F94" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>276.5</v>
+        <v>1276.5</v>
       </c>
       <c r="G94" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3562.5</v>
+        <v>4662.5</v>
       </c>
       <c r="H94" s="105">
-        <v>7450</v>
+        <v>9650</v>
       </c>
       <c r="I94" s="77" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="J94" s="46">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K94" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3562.5</v>
+        <v>4162.5</v>
       </c>
       <c r="L94" s="106">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
-        <v>7450</v>
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>8650</v>
       </c>
       <c r="M94" s="46"/>
       <c r="N94" s="46"/>
@@ -11329,49 +11338,49 @@
     </row>
     <row r="96" spans="1:31" ht="15">
       <c r="A96" s="42" t="s">
-        <v>642</v>
-      </c>
-      <c r="B96" s="42" t="s">
-        <v>643</v>
+        <v>644</v>
+      </c>
+      <c r="B96" s="95" t="s">
+        <v>645</v>
       </c>
       <c r="C96" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
+        <v>10403</v>
       </c>
       <c r="D96" s="105">
-        <v>3839</v>
+        <v>5039</v>
       </c>
       <c r="E96" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F96" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>276.5</v>
+        <v>926.5</v>
       </c>
       <c r="G96" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3562.5</v>
+        <v>4112.5</v>
       </c>
       <c r="H96" s="105">
-        <v>7450</v>
+        <v>8550</v>
       </c>
       <c r="I96" s="77" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J96" s="46">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="K96" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2937.5</v>
+        <v>3612.5</v>
       </c>
       <c r="L96" s="106">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>6450</v>
-      </c>
-      <c r="M96" s="77"/>
+        <v>7550</v>
+      </c>
+      <c r="M96" s="46"/>
       <c r="N96" s="46"/>
-      <c r="O96" s="77"/>
+      <c r="O96" s="46"/>
       <c r="P96" s="46"/>
       <c r="Q96" s="47">
         <v>1</v>
@@ -11402,49 +11411,48 @@
     </row>
     <row r="97" spans="1:31" ht="15">
       <c r="A97" s="42" t="s">
-        <v>644</v>
-      </c>
-      <c r="B97" s="95" t="s">
-        <v>645</v>
+        <v>638</v>
+      </c>
+      <c r="B97" s="42" t="s">
+        <v>639</v>
       </c>
       <c r="C97" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
+        <v>12203</v>
       </c>
       <c r="D97" s="105">
-        <v>5039</v>
+        <v>5939</v>
       </c>
       <c r="E97" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F97" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>926.5</v>
+        <v>1276.5</v>
       </c>
       <c r="G97" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4112.5</v>
+        <v>4662.5</v>
       </c>
       <c r="H97" s="105">
-        <v>8550</v>
+        <v>9650</v>
       </c>
       <c r="I97" s="77" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="J97" s="46">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="K97" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4112.5</v>
+        <v>3737.5</v>
       </c>
       <c r="L97" s="106">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
-        <v>8550</v>
-      </c>
-      <c r="M97" s="46"/>
+        <v>8200</v>
+      </c>
+      <c r="M97" s="77"/>
       <c r="N97" s="46"/>
-      <c r="O97" s="46"/>
+      <c r="O97" s="77"/>
       <c r="P97" s="46"/>
       <c r="Q97" s="47">
         <v>1</v>
@@ -11474,49 +11482,48 @@
     </row>
     <row r="98" spans="1:31" ht="15">
       <c r="A98" s="42" t="s">
-        <v>644</v>
-      </c>
-      <c r="B98" s="95" t="s">
-        <v>645</v>
+        <v>642</v>
+      </c>
+      <c r="B98" s="42" t="s">
+        <v>643</v>
       </c>
       <c r="C98" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
+        <v>8003</v>
       </c>
       <c r="D98" s="105">
-        <v>5039</v>
+        <v>3839</v>
       </c>
       <c r="E98" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F98" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>926.5</v>
+        <v>276.5</v>
       </c>
       <c r="G98" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4112.5</v>
+        <v>3562.5</v>
       </c>
       <c r="H98" s="105">
-        <v>8550</v>
+        <v>7450</v>
       </c>
       <c r="I98" s="77" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J98" s="46">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="K98" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3612.5</v>
+        <v>2937.5</v>
       </c>
       <c r="L98" s="106">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>7550</v>
-      </c>
-      <c r="M98" s="46"/>
+        <v>6400</v>
+      </c>
+      <c r="M98" s="77"/>
       <c r="N98" s="46"/>
-      <c r="O98" s="46"/>
+      <c r="O98" s="77"/>
       <c r="P98" s="46"/>
       <c r="Q98" s="47">
         <v>1</v>
@@ -11583,8 +11590,7 @@
         <v>3237.5</v>
       </c>
       <c r="L99" s="106">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>7550</v>
+        <v>7300</v>
       </c>
       <c r="M99" s="77"/>
       <c r="N99" s="46"/>
@@ -11616,7 +11622,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="15">
+    <row r="100" spans="1:31" ht="15" hidden="1">
       <c r="A100" s="42" t="s">
         <v>61</v>
       </c>
@@ -11685,7 +11691,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="15">
+    <row r="101" spans="1:31" ht="15" hidden="1">
       <c r="A101" s="42" t="s">
         <v>61</v>
       </c>
@@ -11757,7 +11763,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="15">
+    <row r="102" spans="1:31" ht="15" hidden="1">
       <c r="A102" s="42" t="s">
         <v>64</v>
       </c>
@@ -11826,7 +11832,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="15">
+    <row r="103" spans="1:31" ht="15" hidden="1">
       <c r="A103" s="42" t="s">
         <v>64</v>
       </c>
@@ -11898,7 +11904,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="15">
+    <row r="104" spans="1:31" ht="15" hidden="1">
       <c r="A104" s="42" t="s">
         <v>66</v>
       </c>
@@ -11967,7 +11973,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="15">
+    <row r="105" spans="1:31" ht="15" hidden="1">
       <c r="A105" s="42" t="s">
         <v>66</v>
       </c>
@@ -12039,7 +12045,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="15">
+    <row r="106" spans="1:31" ht="15" hidden="1">
       <c r="A106" s="42" t="s">
         <v>70</v>
       </c>
@@ -12108,7 +12114,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="15">
+    <row r="107" spans="1:31" ht="15" hidden="1">
       <c r="A107" s="42" t="s">
         <v>70</v>
       </c>
@@ -12180,7 +12186,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="15">
+    <row r="108" spans="1:31" ht="15" hidden="1">
       <c r="A108" s="42" t="s">
         <v>72</v>
       </c>
@@ -12249,7 +12255,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="15">
+    <row r="109" spans="1:31" ht="15" hidden="1">
       <c r="A109" s="42" t="s">
         <v>72</v>
       </c>
@@ -12321,7 +12327,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="15">
+    <row r="110" spans="1:31" ht="15" hidden="1">
       <c r="A110" s="42" t="s">
         <v>75</v>
       </c>
@@ -12390,7 +12396,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="15">
+    <row r="111" spans="1:31" ht="15" hidden="1">
       <c r="A111" s="42" t="s">
         <v>75</v>
       </c>
@@ -12462,7 +12468,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="15">
+    <row r="112" spans="1:31" ht="15" hidden="1">
       <c r="A112" s="42" t="s">
         <v>77</v>
       </c>
@@ -12529,7 +12535,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="15">
+    <row r="113" spans="1:31" ht="15" hidden="1">
       <c r="A113" s="42" t="s">
         <v>77</v>
       </c>
@@ -12599,7 +12605,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="15">
+    <row r="114" spans="1:31" ht="15" hidden="1">
       <c r="A114" s="42" t="s">
         <v>80</v>
       </c>
@@ -12666,7 +12672,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="15">
+    <row r="115" spans="1:31" ht="15" hidden="1">
       <c r="A115" s="42" t="s">
         <v>80</v>
       </c>
@@ -12736,7 +12742,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="15">
+    <row r="116" spans="1:31" ht="15" hidden="1">
       <c r="A116" s="42" t="s">
         <v>82</v>
       </c>
@@ -12806,7 +12812,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="15">
+    <row r="117" spans="1:31" ht="15" hidden="1">
       <c r="A117" s="42" t="s">
         <v>82</v>
       </c>
@@ -12879,7 +12885,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="15">
+    <row r="118" spans="1:31" ht="15" hidden="1">
       <c r="A118" s="42" t="s">
         <v>84</v>
       </c>
@@ -12949,7 +12955,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="15">
+    <row r="119" spans="1:31" ht="15" hidden="1">
       <c r="A119" s="42" t="s">
         <v>84</v>
       </c>
@@ -13022,7 +13028,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="15">
+    <row r="120" spans="1:31" ht="15" hidden="1">
       <c r="A120" s="42" t="s">
         <v>86</v>
       </c>
@@ -13092,7 +13098,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="15">
+    <row r="121" spans="1:31" ht="15" hidden="1">
       <c r="A121" s="42" t="s">
         <v>86</v>
       </c>
@@ -13165,7 +13171,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="15">
+    <row r="122" spans="1:31" ht="15" hidden="1">
       <c r="A122" s="42" t="s">
         <v>88</v>
       </c>
@@ -13235,7 +13241,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="15">
+    <row r="123" spans="1:31" ht="15" hidden="1">
       <c r="A123" s="42" t="s">
         <v>88</v>
       </c>
@@ -13308,7 +13314,7 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="15">
+    <row r="124" spans="1:31" ht="15" hidden="1">
       <c r="A124" s="42" t="s">
         <v>90</v>
       </c>
@@ -13378,7 +13384,7 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="15">
+    <row r="125" spans="1:31" ht="15" hidden="1">
       <c r="A125" s="42" t="s">
         <v>90</v>
       </c>
@@ -13451,7 +13457,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="15">
+    <row r="126" spans="1:31" ht="15" hidden="1">
       <c r="A126" s="42" t="s">
         <v>92</v>
       </c>
@@ -13521,7 +13527,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="15">
+    <row r="127" spans="1:31" ht="15" hidden="1">
       <c r="A127" s="42" t="s">
         <v>92</v>
       </c>
@@ -13594,7 +13600,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="15">
+    <row r="128" spans="1:31" ht="15" hidden="1">
       <c r="A128" s="42" t="s">
         <v>94</v>
       </c>
@@ -13664,7 +13670,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="15">
+    <row r="129" spans="1:31" ht="15" hidden="1">
       <c r="A129" s="42" t="s">
         <v>94</v>
       </c>
@@ -13737,7 +13743,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="15">
+    <row r="130" spans="1:31" ht="15" hidden="1">
       <c r="A130" s="42" t="s">
         <v>96</v>
       </c>
@@ -13805,7 +13811,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="15">
+    <row r="131" spans="1:31" ht="15" hidden="1">
       <c r="A131" s="42" t="s">
         <v>96</v>
       </c>
@@ -13876,7 +13882,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="15">
+    <row r="132" spans="1:31" ht="15" hidden="1">
       <c r="A132" s="42" t="s">
         <v>98</v>
       </c>
@@ -13944,7 +13950,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="15">
+    <row r="133" spans="1:31" ht="15" hidden="1">
       <c r="A133" s="79" t="s">
         <v>98</v>
       </c>
@@ -14014,7 +14020,7 @@
       <c r="AC133" s="46"/>
       <c r="AD133" s="46"/>
     </row>
-    <row r="134" spans="1:31" ht="15">
+    <row r="134" spans="1:31" ht="15" hidden="1">
       <c r="A134" s="79" t="s">
         <v>100</v>
       </c>
@@ -14081,7 +14087,7 @@
       <c r="AC134" s="46"/>
       <c r="AD134" s="46"/>
     </row>
-    <row r="135" spans="1:31" ht="15">
+    <row r="135" spans="1:31" ht="15" hidden="1">
       <c r="A135" s="79" t="s">
         <v>100</v>
       </c>
@@ -14151,7 +14157,7 @@
       <c r="AC135" s="46"/>
       <c r="AD135" s="44"/>
     </row>
-    <row r="136" spans="1:31" ht="15">
+    <row r="136" spans="1:31" ht="15" hidden="1">
       <c r="A136" s="79" t="s">
         <v>102</v>
       </c>
@@ -14220,7 +14226,7 @@
       <c r="AC136" s="46"/>
       <c r="AD136" s="44"/>
     </row>
-    <row r="137" spans="1:31" ht="15">
+    <row r="137" spans="1:31" ht="15" hidden="1">
       <c r="A137" s="79" t="s">
         <v>102</v>
       </c>
@@ -14292,7 +14298,7 @@
       <c r="AC137" s="46"/>
       <c r="AD137" s="44"/>
     </row>
-    <row r="138" spans="1:31" ht="15">
+    <row r="138" spans="1:31" ht="15" hidden="1">
       <c r="A138" s="79" t="s">
         <v>104</v>
       </c>
@@ -14361,7 +14367,7 @@
       <c r="AC138" s="46"/>
       <c r="AD138" s="44"/>
     </row>
-    <row r="139" spans="1:31" ht="15">
+    <row r="139" spans="1:31" ht="15" hidden="1">
       <c r="A139" s="79" t="s">
         <v>104</v>
       </c>
@@ -14434,7 +14440,7 @@
       <c r="AD139" s="44"/>
       <c r="AE139" s="16"/>
     </row>
-    <row r="140" spans="1:31" ht="15">
+    <row r="140" spans="1:31" ht="15" hidden="1">
       <c r="A140" s="79" t="s">
         <v>106</v>
       </c>
@@ -14504,7 +14510,7 @@
       <c r="AD140" s="7"/>
       <c r="AE140" s="16"/>
     </row>
-    <row r="141" spans="1:31" ht="15">
+    <row r="141" spans="1:31" ht="15" hidden="1">
       <c r="A141" s="79" t="s">
         <v>106</v>
       </c>
@@ -14577,7 +14583,7 @@
       <c r="AD141" s="7"/>
       <c r="AE141" s="16"/>
     </row>
-    <row r="142" spans="1:31" ht="15">
+    <row r="142" spans="1:31" ht="15" hidden="1">
       <c r="A142" s="79" t="s">
         <v>108</v>
       </c>
@@ -14646,7 +14652,7 @@
       <c r="AC142" s="46"/>
       <c r="AD142" s="7"/>
     </row>
-    <row r="143" spans="1:31" ht="15">
+    <row r="143" spans="1:31" ht="15" hidden="1">
       <c r="A143" s="79" t="s">
         <v>108</v>
       </c>
@@ -14718,7 +14724,7 @@
       <c r="AC143" s="46"/>
       <c r="AD143" s="7"/>
     </row>
-    <row r="144" spans="1:31" ht="15">
+    <row r="144" spans="1:31" ht="15" hidden="1">
       <c r="A144" s="79" t="s">
         <v>110</v>
       </c>
@@ -14787,7 +14793,7 @@
       <c r="AC144" s="46"/>
       <c r="AD144" s="7"/>
     </row>
-    <row r="145" spans="1:31" ht="15">
+    <row r="145" spans="1:31" ht="15" hidden="1">
       <c r="A145" s="79" t="s">
         <v>110</v>
       </c>
@@ -14859,7 +14865,7 @@
       <c r="AC145" s="46"/>
       <c r="AD145" s="7"/>
     </row>
-    <row r="146" spans="1:31" ht="15">
+    <row r="146" spans="1:31" ht="15" hidden="1">
       <c r="A146" s="85" t="s">
         <v>112</v>
       </c>
@@ -14928,7 +14934,7 @@
       <c r="AC146" s="46"/>
       <c r="AD146" s="44"/>
     </row>
-    <row r="147" spans="1:31" ht="15">
+    <row r="147" spans="1:31" ht="15" hidden="1">
       <c r="A147" s="42" t="s">
         <v>112</v>
       </c>
@@ -15000,7 +15006,7 @@
       <c r="AD147"/>
       <c r="AE147"/>
     </row>
-    <row r="148" spans="1:31" ht="15">
+    <row r="148" spans="1:31" ht="15" hidden="1">
       <c r="A148" s="42" t="s">
         <v>114</v>
       </c>
@@ -15067,7 +15073,7 @@
       <c r="AD148"/>
       <c r="AE148"/>
     </row>
-    <row r="149" spans="1:31" ht="15">
+    <row r="149" spans="1:31" ht="15" hidden="1">
       <c r="A149" s="42" t="s">
         <v>114</v>
       </c>
@@ -15137,7 +15143,7 @@
       <c r="AD149"/>
       <c r="AE149"/>
     </row>
-    <row r="150" spans="1:31" ht="15">
+    <row r="150" spans="1:31" ht="15" hidden="1">
       <c r="A150" s="42" t="s">
         <v>116</v>
       </c>
@@ -15204,7 +15210,7 @@
       <c r="AD150"/>
       <c r="AE150"/>
     </row>
-    <row r="151" spans="1:31" ht="15">
+    <row r="151" spans="1:31" ht="15" hidden="1">
       <c r="A151" s="42" t="s">
         <v>116</v>
       </c>
@@ -15274,7 +15280,7 @@
       <c r="AD151"/>
       <c r="AE151"/>
     </row>
-    <row r="152" spans="1:31" ht="15">
+    <row r="152" spans="1:31" ht="15" hidden="1">
       <c r="A152" s="42" t="s">
         <v>118</v>
       </c>
@@ -15342,7 +15348,7 @@
       <c r="AD152"/>
       <c r="AE152"/>
     </row>
-    <row r="153" spans="1:31" ht="15">
+    <row r="153" spans="1:31" ht="15" hidden="1">
       <c r="A153" s="42" t="s">
         <v>118</v>
       </c>
@@ -15413,7 +15419,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="15">
+    <row r="154" spans="1:31" ht="15" hidden="1">
       <c r="A154" s="42" t="s">
         <v>123</v>
       </c>
@@ -15485,7 +15491,7 @@
       <c r="AC154" s="46"/>
       <c r="AD154" s="46"/>
     </row>
-    <row r="155" spans="1:31" ht="15">
+    <row r="155" spans="1:31" ht="15" hidden="1">
       <c r="A155" s="42" t="s">
         <v>123</v>
       </c>
@@ -15557,7 +15563,7 @@
       <c r="AC155" s="46"/>
       <c r="AD155" s="44"/>
     </row>
-    <row r="156" spans="1:31" ht="15">
+    <row r="156" spans="1:31" ht="15" hidden="1">
       <c r="A156" s="42" t="s">
         <v>123</v>
       </c>
@@ -15629,7 +15635,7 @@
       <c r="AC156" s="46"/>
       <c r="AD156" s="44"/>
     </row>
-    <row r="157" spans="1:31" ht="15">
+    <row r="157" spans="1:31" ht="15" hidden="1">
       <c r="A157" s="42" t="s">
         <v>123</v>
       </c>
@@ -15701,7 +15707,7 @@
       <c r="AC157" s="46"/>
       <c r="AD157" s="7"/>
     </row>
-    <row r="158" spans="1:31" ht="15">
+    <row r="158" spans="1:31" ht="15" hidden="1">
       <c r="A158" s="79" t="s">
         <v>123</v>
       </c>
@@ -15773,7 +15779,7 @@
       <c r="AC158" s="46"/>
       <c r="AD158" s="7"/>
     </row>
-    <row r="159" spans="1:31" ht="15">
+    <row r="159" spans="1:31" ht="15" hidden="1">
       <c r="A159" s="79" t="s">
         <v>123</v>
       </c>
@@ -15846,7 +15852,7 @@
       <c r="AC159" s="46"/>
       <c r="AD159" s="7"/>
     </row>
-    <row r="160" spans="1:31" ht="15">
+    <row r="160" spans="1:31" ht="15" hidden="1">
       <c r="A160" s="79" t="s">
         <v>123</v>
       </c>
@@ -15918,7 +15924,7 @@
       <c r="AC160" s="46"/>
       <c r="AD160" s="7"/>
     </row>
-    <row r="161" spans="1:30" ht="15">
+    <row r="161" spans="1:30" ht="15" hidden="1">
       <c r="A161" s="79" t="s">
         <v>123</v>
       </c>
@@ -15990,7 +15996,7 @@
       <c r="AC161" s="46"/>
       <c r="AD161" s="46"/>
     </row>
-    <row r="162" spans="1:30" ht="15">
+    <row r="162" spans="1:30" ht="15" hidden="1">
       <c r="A162" s="79" t="s">
         <v>123</v>
       </c>
@@ -16062,7 +16068,7 @@
       <c r="AC162" s="46"/>
       <c r="AD162" s="7"/>
     </row>
-    <row r="163" spans="1:30" ht="15">
+    <row r="163" spans="1:30" ht="15" hidden="1">
       <c r="A163" s="79" t="s">
         <v>123</v>
       </c>
@@ -16134,7 +16140,7 @@
       <c r="AC163" s="46"/>
       <c r="AD163" s="46"/>
     </row>
-    <row r="164" spans="1:30" ht="15">
+    <row r="164" spans="1:30" ht="15" hidden="1">
       <c r="A164" s="79" t="s">
         <v>123</v>
       </c>
@@ -16206,7 +16212,7 @@
       <c r="AC164" s="46"/>
       <c r="AD164" s="44"/>
     </row>
-    <row r="165" spans="1:30" ht="15">
+    <row r="165" spans="1:30" ht="15" hidden="1">
       <c r="A165" s="79" t="s">
         <v>123</v>
       </c>
@@ -16278,7 +16284,7 @@
       <c r="AC165" s="46"/>
       <c r="AD165" s="44"/>
     </row>
-    <row r="166" spans="1:30" ht="15">
+    <row r="166" spans="1:30" ht="15" hidden="1">
       <c r="A166" s="79" t="s">
         <v>123</v>
       </c>
@@ -16350,7 +16356,7 @@
       <c r="AC166" s="46"/>
       <c r="AD166" s="44"/>
     </row>
-    <row r="167" spans="1:30" ht="15">
+    <row r="167" spans="1:30" ht="15" hidden="1">
       <c r="A167" s="85" t="s">
         <v>123</v>
       </c>
@@ -16422,7 +16428,7 @@
       <c r="AC167" s="46"/>
       <c r="AD167" s="44"/>
     </row>
-    <row r="168" spans="1:30" ht="15">
+    <row r="168" spans="1:30" ht="15" hidden="1">
       <c r="A168" s="79" t="s">
         <v>125</v>
       </c>
@@ -16494,7 +16500,7 @@
       <c r="AC168" s="46"/>
       <c r="AD168" s="44"/>
     </row>
-    <row r="169" spans="1:30" ht="15">
+    <row r="169" spans="1:30" ht="15" hidden="1">
       <c r="A169" s="79" t="s">
         <v>125</v>
       </c>
@@ -16566,7 +16572,7 @@
       <c r="AC169" s="46"/>
       <c r="AD169" s="7"/>
     </row>
-    <row r="170" spans="1:30" ht="15">
+    <row r="170" spans="1:30" ht="15" hidden="1">
       <c r="A170" s="79" t="s">
         <v>125</v>
       </c>
@@ -16638,7 +16644,7 @@
       <c r="AC170" s="46"/>
       <c r="AD170" s="7"/>
     </row>
-    <row r="171" spans="1:30" ht="15">
+    <row r="171" spans="1:30" ht="15" hidden="1">
       <c r="A171" s="79" t="s">
         <v>125</v>
       </c>
@@ -16709,7 +16715,7 @@
       <c r="AB171" s="73"/>
       <c r="AD171" s="16"/>
     </row>
-    <row r="172" spans="1:30" ht="15">
+    <row r="172" spans="1:30" ht="15" hidden="1">
       <c r="A172" s="79" t="s">
         <v>125</v>
       </c>
@@ -16781,7 +16787,7 @@
       <c r="AC172" s="44"/>
       <c r="AD172" s="44"/>
     </row>
-    <row r="173" spans="1:30" ht="15">
+    <row r="173" spans="1:30" ht="15" hidden="1">
       <c r="A173" s="79" t="s">
         <v>125</v>
       </c>
@@ -16854,7 +16860,7 @@
       <c r="AC173" s="44"/>
       <c r="AD173" s="44"/>
     </row>
-    <row r="174" spans="1:30" ht="15">
+    <row r="174" spans="1:30" ht="15" hidden="1">
       <c r="A174" s="79" t="s">
         <v>125</v>
       </c>
@@ -16926,7 +16932,7 @@
       <c r="AC174" s="44"/>
       <c r="AD174" s="44"/>
     </row>
-    <row r="175" spans="1:30" ht="15">
+    <row r="175" spans="1:30" ht="15" hidden="1">
       <c r="A175" s="79" t="s">
         <v>125</v>
       </c>
@@ -16998,7 +17004,7 @@
       <c r="AC175" s="44"/>
       <c r="AD175" s="44"/>
     </row>
-    <row r="176" spans="1:30" ht="15">
+    <row r="176" spans="1:30" ht="15" hidden="1">
       <c r="A176" s="79" t="s">
         <v>125</v>
       </c>
@@ -17070,7 +17076,7 @@
       <c r="AC176" s="44"/>
       <c r="AD176" s="44"/>
     </row>
-    <row r="177" spans="1:30" ht="15">
+    <row r="177" spans="1:30" ht="15" hidden="1">
       <c r="A177" s="79" t="s">
         <v>125</v>
       </c>
@@ -17142,7 +17148,7 @@
       <c r="AC177" s="44"/>
       <c r="AD177" s="44"/>
     </row>
-    <row r="178" spans="1:30" ht="15">
+    <row r="178" spans="1:30" ht="15" hidden="1">
       <c r="A178" s="79" t="s">
         <v>125</v>
       </c>
@@ -17214,7 +17220,7 @@
       <c r="AC178" s="44"/>
       <c r="AD178" s="44"/>
     </row>
-    <row r="179" spans="1:30" ht="15">
+    <row r="179" spans="1:30" ht="15" hidden="1">
       <c r="A179" s="79" t="s">
         <v>125</v>
       </c>
@@ -17286,7 +17292,7 @@
       <c r="AC179" s="44"/>
       <c r="AD179" s="44"/>
     </row>
-    <row r="180" spans="1:30" ht="15">
+    <row r="180" spans="1:30" ht="15" hidden="1">
       <c r="A180" s="79" t="s">
         <v>125</v>
       </c>
@@ -17358,7 +17364,7 @@
       <c r="AC180" s="44"/>
       <c r="AD180" s="44"/>
     </row>
-    <row r="181" spans="1:30" ht="15">
+    <row r="181" spans="1:30" ht="15" hidden="1">
       <c r="A181" s="79" t="s">
         <v>125</v>
       </c>
@@ -17430,7 +17436,7 @@
       <c r="AC181" s="44"/>
       <c r="AD181" s="44"/>
     </row>
-    <row r="182" spans="1:30" ht="15">
+    <row r="182" spans="1:30" ht="15" hidden="1">
       <c r="A182" s="79" t="s">
         <v>127</v>
       </c>
@@ -17502,7 +17508,7 @@
       <c r="AC182" s="44"/>
       <c r="AD182" s="44"/>
     </row>
-    <row r="183" spans="1:30" ht="15">
+    <row r="183" spans="1:30" ht="15" hidden="1">
       <c r="A183" s="79" t="s">
         <v>127</v>
       </c>
@@ -17574,7 +17580,7 @@
       <c r="AC183" s="44"/>
       <c r="AD183" s="44"/>
     </row>
-    <row r="184" spans="1:30" ht="15">
+    <row r="184" spans="1:30" ht="15" hidden="1">
       <c r="A184" s="79" t="s">
         <v>127</v>
       </c>
@@ -17646,7 +17652,7 @@
       <c r="AC184" s="44"/>
       <c r="AD184" s="44"/>
     </row>
-    <row r="185" spans="1:30" ht="15">
+    <row r="185" spans="1:30" ht="15" hidden="1">
       <c r="A185" s="79" t="s">
         <v>127</v>
       </c>
@@ -17718,7 +17724,7 @@
       <c r="AC185" s="44"/>
       <c r="AD185" s="44"/>
     </row>
-    <row r="186" spans="1:30" ht="15">
+    <row r="186" spans="1:30" ht="15" hidden="1">
       <c r="A186" s="79" t="s">
         <v>127</v>
       </c>
@@ -17790,7 +17796,7 @@
       <c r="AC186" s="44"/>
       <c r="AD186" s="44"/>
     </row>
-    <row r="187" spans="1:30" ht="15">
+    <row r="187" spans="1:30" ht="15" hidden="1">
       <c r="A187" s="79" t="s">
         <v>127</v>
       </c>
@@ -17863,7 +17869,7 @@
       <c r="AC187" s="44"/>
       <c r="AD187" s="44"/>
     </row>
-    <row r="188" spans="1:30" ht="15">
+    <row r="188" spans="1:30" ht="15" hidden="1">
       <c r="A188" s="79" t="s">
         <v>127</v>
       </c>
@@ -17935,7 +17941,7 @@
       <c r="AC188" s="44"/>
       <c r="AD188" s="44"/>
     </row>
-    <row r="189" spans="1:30" ht="15">
+    <row r="189" spans="1:30" ht="15" hidden="1">
       <c r="A189" s="79" t="s">
         <v>127</v>
       </c>
@@ -18007,7 +18013,7 @@
       <c r="AC189" s="44"/>
       <c r="AD189" s="44"/>
     </row>
-    <row r="190" spans="1:30" ht="15">
+    <row r="190" spans="1:30" ht="15" hidden="1">
       <c r="A190" s="79" t="s">
         <v>127</v>
       </c>
@@ -18079,7 +18085,7 @@
       <c r="AC190" s="44"/>
       <c r="AD190" s="44"/>
     </row>
-    <row r="191" spans="1:30" ht="15">
+    <row r="191" spans="1:30" ht="15" hidden="1">
       <c r="A191" s="79" t="s">
         <v>127</v>
       </c>
@@ -18151,7 +18157,7 @@
       <c r="AC191" s="44"/>
       <c r="AD191" s="44"/>
     </row>
-    <row r="192" spans="1:30" ht="15">
+    <row r="192" spans="1:30" ht="15" hidden="1">
       <c r="A192" s="79" t="s">
         <v>127</v>
       </c>
@@ -18223,7 +18229,7 @@
       <c r="AC192" s="44"/>
       <c r="AD192" s="44"/>
     </row>
-    <row r="193" spans="1:30" ht="15">
+    <row r="193" spans="1:30" ht="15" hidden="1">
       <c r="A193" s="79" t="s">
         <v>127</v>
       </c>
@@ -18295,7 +18301,7 @@
       <c r="AC193" s="44"/>
       <c r="AD193" s="44"/>
     </row>
-    <row r="194" spans="1:30" ht="15">
+    <row r="194" spans="1:30" ht="15" hidden="1">
       <c r="A194" s="79" t="s">
         <v>127</v>
       </c>
@@ -18367,7 +18373,7 @@
       <c r="AC194" s="44"/>
       <c r="AD194" s="44"/>
     </row>
-    <row r="195" spans="1:30" ht="15">
+    <row r="195" spans="1:30" ht="15" hidden="1">
       <c r="A195" s="79" t="s">
         <v>127</v>
       </c>
@@ -18437,7 +18443,7 @@
       <c r="AC195" s="44"/>
       <c r="AD195" s="44"/>
     </row>
-    <row r="196" spans="1:30" ht="15">
+    <row r="196" spans="1:30" ht="15" hidden="1">
       <c r="A196" s="79" t="s">
         <v>165</v>
       </c>
@@ -18516,7 +18522,7 @@
       <c r="AC196" s="44"/>
       <c r="AD196" s="44"/>
     </row>
-    <row r="197" spans="1:30" ht="15">
+    <row r="197" spans="1:30" ht="15" hidden="1">
       <c r="A197" s="79" t="s">
         <v>167</v>
       </c>
@@ -18595,7 +18601,7 @@
       <c r="AC197" s="44"/>
       <c r="AD197" s="44"/>
     </row>
-    <row r="198" spans="1:30" ht="15">
+    <row r="198" spans="1:30" ht="15" hidden="1">
       <c r="A198" s="79" t="s">
         <v>169</v>
       </c>
@@ -18674,7 +18680,7 @@
       <c r="AC198" s="44"/>
       <c r="AD198" s="44"/>
     </row>
-    <row r="199" spans="1:30" ht="15">
+    <row r="199" spans="1:30" ht="15" hidden="1">
       <c r="A199" s="85" t="s">
         <v>1</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1565" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{852350F0-0916-4668-95FF-7736CDE1FE40}"/>
+  <xr:revisionPtr revIDLastSave="1566" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55753934-226F-47BA-87F8-BADB407319CE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView minimized="1" xWindow="28755" yWindow="1110" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3333,16 +3333,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Beltone Illuminate 17 62S-DRWC Digital RIE"/>
-        <filter val="Beltone Illuminate 4 62S-DRWC Digital RIE"/>
-        <filter val="Beltone Illuminate 6 62S-DRWC Digital RIE"/>
-        <filter val="Beltone Illuminate 9 62S-DRWC Digital RIE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A90:V99">
     <sortCondition ref="I1:I199"/>
   </sortState>
@@ -4444,7 +4435,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="15" hidden="1">
+    <row r="2" spans="1:31" ht="15">
       <c r="A2" s="42" t="s">
         <v>130</v>
       </c>
@@ -4514,7 +4505,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="15" hidden="1">
+    <row r="3" spans="1:31" ht="15">
       <c r="A3" s="42" t="s">
         <v>130</v>
       </c>
@@ -4583,7 +4574,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="15" hidden="1">
+    <row r="4" spans="1:31" ht="15">
       <c r="A4" s="42" t="s">
         <v>130</v>
       </c>
@@ -4655,7 +4646,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="15" hidden="1">
+    <row r="5" spans="1:31" ht="15">
       <c r="A5" s="42" t="s">
         <v>130</v>
       </c>
@@ -4727,7 +4718,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="15" hidden="1">
+    <row r="6" spans="1:31" ht="15">
       <c r="A6" s="42" t="s">
         <v>120</v>
       </c>
@@ -4794,7 +4785,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="15" hidden="1">
+    <row r="7" spans="1:31" ht="15">
       <c r="A7" s="42" t="s">
         <v>120</v>
       </c>
@@ -4858,7 +4849,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="15" hidden="1">
+    <row r="8" spans="1:31" ht="15">
       <c r="A8" s="42" t="s">
         <v>132</v>
       </c>
@@ -4927,7 +4918,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="15" hidden="1">
+    <row r="9" spans="1:31" ht="15">
       <c r="A9" s="42" t="s">
         <v>132</v>
       </c>
@@ -4999,7 +4990,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="15" hidden="1">
+    <row r="10" spans="1:31" ht="15">
       <c r="A10" s="42" t="s">
         <v>132</v>
       </c>
@@ -5071,7 +5062,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="15" hidden="1">
+    <row r="11" spans="1:31" ht="15">
       <c r="A11" s="42" t="s">
         <v>134</v>
       </c>
@@ -5140,7 +5131,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="15" hidden="1">
+    <row r="12" spans="1:31" ht="15">
       <c r="A12" s="42" t="s">
         <v>132</v>
       </c>
@@ -5209,7 +5200,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="15" hidden="1">
+    <row r="13" spans="1:31" ht="15">
       <c r="A13" s="42" t="s">
         <v>134</v>
       </c>
@@ -5278,7 +5269,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="15" hidden="1">
+    <row r="14" spans="1:31" ht="15">
       <c r="A14" s="42" t="s">
         <v>134</v>
       </c>
@@ -5350,7 +5341,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="15" hidden="1">
+    <row r="15" spans="1:31" ht="15">
       <c r="A15" s="42" t="s">
         <v>134</v>
       </c>
@@ -5423,7 +5414,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="15" hidden="1">
+    <row r="16" spans="1:31" ht="15">
       <c r="A16" s="42" t="s">
         <v>139</v>
       </c>
@@ -5496,7 +5487,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="15" hidden="1">
+    <row r="17" spans="1:31" ht="15">
       <c r="A17" s="42" t="s">
         <v>139</v>
       </c>
@@ -5569,7 +5560,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="15" hidden="1">
+    <row r="18" spans="1:31" ht="15">
       <c r="A18" s="42" t="s">
         <v>142</v>
       </c>
@@ -5641,7 +5632,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="15" hidden="1">
+    <row r="19" spans="1:31" ht="15">
       <c r="A19" s="42" t="s">
         <v>142</v>
       </c>
@@ -5714,7 +5705,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="15" hidden="1">
+    <row r="20" spans="1:31" ht="15">
       <c r="A20" s="42" t="s">
         <v>144</v>
       </c>
@@ -5786,7 +5777,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="15" hidden="1">
+    <row r="21" spans="1:31" ht="15">
       <c r="A21" s="42" t="s">
         <v>144</v>
       </c>
@@ -5859,7 +5850,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="15" hidden="1">
+    <row r="22" spans="1:31" ht="15">
       <c r="A22" s="42" t="s">
         <v>146</v>
       </c>
@@ -5931,7 +5922,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="15" hidden="1">
+    <row r="23" spans="1:31" ht="15">
       <c r="A23" s="42" t="s">
         <v>146</v>
       </c>
@@ -6003,7 +5994,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15" hidden="1">
+    <row r="24" spans="1:31" ht="15">
       <c r="A24" s="42" t="s">
         <v>148</v>
       </c>
@@ -6075,7 +6066,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15" hidden="1">
+    <row r="25" spans="1:31" ht="15">
       <c r="A25" s="42" t="s">
         <v>148</v>
       </c>
@@ -6149,7 +6140,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15" hidden="1">
+    <row r="26" spans="1:31" ht="15">
       <c r="A26" s="42" t="s">
         <v>150</v>
       </c>
@@ -6222,7 +6213,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15" hidden="1">
+    <row r="27" spans="1:31" ht="15">
       <c r="A27" s="42" t="s">
         <v>150</v>
       </c>
@@ -6296,7 +6287,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15" hidden="1">
+    <row r="28" spans="1:31" ht="15">
       <c r="A28" s="42" t="s">
         <v>43</v>
       </c>
@@ -6359,7 +6350,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15" hidden="1">
+    <row r="29" spans="1:31" ht="15">
       <c r="A29" s="42" t="s">
         <v>43</v>
       </c>
@@ -6431,7 +6422,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="15" hidden="1">
+    <row r="30" spans="1:31" ht="15">
       <c r="A30" s="42" t="s">
         <v>47</v>
       </c>
@@ -6503,7 +6494,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="15" hidden="1">
+    <row r="31" spans="1:31" ht="15">
       <c r="A31" s="42" t="s">
         <v>47</v>
       </c>
@@ -6574,7 +6565,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="15" hidden="1">
+    <row r="32" spans="1:31" ht="15">
       <c r="A32" s="42" t="s">
         <v>47</v>
       </c>
@@ -6646,7 +6637,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="15" hidden="1">
+    <row r="33" spans="1:31" ht="15">
       <c r="A33" s="42" t="s">
         <v>47</v>
       </c>
@@ -6718,7 +6709,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="15" hidden="1">
+    <row r="34" spans="1:31" ht="15">
       <c r="A34" s="42" t="s">
         <v>47</v>
       </c>
@@ -6790,7 +6781,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:31" ht="15" hidden="1">
+    <row r="35" spans="1:31" ht="15">
       <c r="A35" s="42" t="s">
         <v>47</v>
       </c>
@@ -6862,7 +6853,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="15" hidden="1">
+    <row r="36" spans="1:31" ht="15">
       <c r="A36" s="42" t="s">
         <v>47</v>
       </c>
@@ -6935,7 +6926,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="15" hidden="1">
+    <row r="37" spans="1:31" ht="15">
       <c r="A37" s="42" t="s">
         <v>47</v>
       </c>
@@ -7007,7 +6998,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="15" hidden="1">
+    <row r="38" spans="1:31" ht="15">
       <c r="A38" s="42" t="s">
         <v>47</v>
       </c>
@@ -7079,7 +7070,7 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="15" hidden="1">
+    <row r="39" spans="1:31" ht="15">
       <c r="A39" s="42" t="s">
         <v>47</v>
       </c>
@@ -7151,7 +7142,7 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="15" hidden="1">
+    <row r="40" spans="1:31" ht="15">
       <c r="A40" s="42" t="s">
         <v>47</v>
       </c>
@@ -7223,7 +7214,7 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="15" hidden="1">
+    <row r="41" spans="1:31" ht="15">
       <c r="A41" s="42" t="s">
         <v>47</v>
       </c>
@@ -7295,7 +7286,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="15" hidden="1">
+    <row r="42" spans="1:31" ht="15">
       <c r="A42" s="42" t="s">
         <v>47</v>
       </c>
@@ -7367,7 +7358,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="15" hidden="1">
+    <row r="43" spans="1:31" ht="15">
       <c r="A43" s="42" t="s">
         <v>53</v>
       </c>
@@ -7445,7 +7436,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="15" hidden="1">
+    <row r="44" spans="1:31" ht="15">
       <c r="A44" s="42" t="s">
         <v>53</v>
       </c>
@@ -7523,7 +7514,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="15" hidden="1">
+    <row r="45" spans="1:31" ht="15">
       <c r="A45" s="42" t="s">
         <v>53</v>
       </c>
@@ -7601,7 +7592,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="15" hidden="1">
+    <row r="46" spans="1:31" ht="15">
       <c r="A46" s="42" t="s">
         <v>53</v>
       </c>
@@ -7679,7 +7670,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="15" hidden="1">
+    <row r="47" spans="1:31" ht="15">
       <c r="A47" s="42" t="s">
         <v>53</v>
       </c>
@@ -7754,7 +7745,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="15" hidden="1">
+    <row r="48" spans="1:31" ht="15">
       <c r="A48" s="42" t="s">
         <v>53</v>
       </c>
@@ -7829,7 +7820,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="15" hidden="1">
+    <row r="49" spans="1:32" ht="15">
       <c r="A49" s="42" t="s">
         <v>53</v>
       </c>
@@ -7905,7 +7896,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="15" hidden="1">
+    <row r="50" spans="1:32" ht="15">
       <c r="A50" s="42" t="s">
         <v>53</v>
       </c>
@@ -7981,7 +7972,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="15" hidden="1">
+    <row r="51" spans="1:32" ht="15">
       <c r="A51" s="42" t="s">
         <v>53</v>
       </c>
@@ -8057,7 +8048,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="15" hidden="1">
+    <row r="52" spans="1:32" ht="15">
       <c r="A52" s="42" t="s">
         <v>53</v>
       </c>
@@ -8127,7 +8118,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="15" hidden="1">
+    <row r="53" spans="1:32" ht="15">
       <c r="A53" s="42" t="s">
         <v>53</v>
       </c>
@@ -8200,7 +8191,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="15" hidden="1">
+    <row r="54" spans="1:32" ht="15">
       <c r="A54" s="42" t="s">
         <v>53</v>
       </c>
@@ -8273,7 +8264,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="15" hidden="1">
+    <row r="55" spans="1:32" ht="15">
       <c r="A55" s="42" t="s">
         <v>53</v>
       </c>
@@ -8346,7 +8337,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="15" hidden="1">
+    <row r="56" spans="1:32" ht="15">
       <c r="A56" s="42" t="s">
         <v>53</v>
       </c>
@@ -8420,7 +8411,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="15" hidden="1">
+    <row r="57" spans="1:32" ht="15">
       <c r="A57" s="42" t="s">
         <v>53</v>
       </c>
@@ -8493,7 +8484,7 @@
       <c r="AE57" s="16"/>
       <c r="AF57" s="16"/>
     </row>
-    <row r="58" spans="1:32" ht="15" hidden="1">
+    <row r="58" spans="1:32" ht="15">
       <c r="A58" s="42" t="s">
         <v>50</v>
       </c>
@@ -8565,7 +8556,7 @@
       <c r="AE58" s="16"/>
       <c r="AF58" s="16"/>
     </row>
-    <row r="59" spans="1:32" ht="15" hidden="1">
+    <row r="59" spans="1:32" ht="15">
       <c r="A59" s="42" t="s">
         <v>50</v>
       </c>
@@ -8637,7 +8628,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="15" hidden="1">
+    <row r="60" spans="1:32" ht="15">
       <c r="A60" s="42" t="s">
         <v>57</v>
       </c>
@@ -8715,7 +8706,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="15" hidden="1">
+    <row r="61" spans="1:32" ht="15">
       <c r="A61" s="42" t="s">
         <v>57</v>
       </c>
@@ -8794,7 +8785,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="15" hidden="1">
+    <row r="62" spans="1:32" ht="15">
       <c r="A62" s="42" t="s">
         <v>57</v>
       </c>
@@ -8873,7 +8864,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="15" hidden="1">
+    <row r="63" spans="1:32" ht="15">
       <c r="A63" s="42" t="s">
         <v>57</v>
       </c>
@@ -8952,7 +8943,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="15" hidden="1">
+    <row r="64" spans="1:32" ht="15">
       <c r="A64" s="42" t="s">
         <v>57</v>
       </c>
@@ -9028,7 +9019,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15" hidden="1">
+    <row r="65" spans="1:31" ht="15">
       <c r="A65" s="42" t="s">
         <v>57</v>
       </c>
@@ -9104,7 +9095,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15" hidden="1">
+    <row r="66" spans="1:31" ht="15">
       <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
@@ -9180,7 +9171,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15" hidden="1">
+    <row r="67" spans="1:31" ht="15">
       <c r="A67" s="42" t="s">
         <v>57</v>
       </c>
@@ -9256,7 +9247,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15" hidden="1">
+    <row r="68" spans="1:31" ht="15">
       <c r="A68" s="42" t="s">
         <v>57</v>
       </c>
@@ -9332,7 +9323,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15" hidden="1">
+    <row r="69" spans="1:31" ht="15">
       <c r="A69" s="42" t="s">
         <v>57</v>
       </c>
@@ -9402,7 +9393,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15" hidden="1">
+    <row r="70" spans="1:31" ht="15">
       <c r="A70" s="42" t="s">
         <v>57</v>
       </c>
@@ -9475,7 +9466,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15" hidden="1">
+    <row r="71" spans="1:31" ht="15">
       <c r="A71" s="42" t="s">
         <v>57</v>
       </c>
@@ -9548,7 +9539,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15" hidden="1">
+    <row r="72" spans="1:31" ht="15">
       <c r="A72" s="42" t="s">
         <v>57</v>
       </c>
@@ -9621,7 +9612,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15" hidden="1">
+    <row r="73" spans="1:31" ht="15">
       <c r="A73" s="42" t="s">
         <v>57</v>
       </c>
@@ -9695,7 +9686,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="15" hidden="1">
+    <row r="74" spans="1:31" ht="15">
       <c r="A74" s="42" t="s">
         <v>57</v>
       </c>
@@ -9768,7 +9759,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="15" hidden="1">
+    <row r="75" spans="1:31" ht="15">
       <c r="A75" s="42" t="s">
         <v>59</v>
       </c>
@@ -9841,7 +9832,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="15" hidden="1">
+    <row r="76" spans="1:31" ht="15">
       <c r="A76" s="42" t="s">
         <v>59</v>
       </c>
@@ -9920,7 +9911,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="15" hidden="1">
+    <row r="77" spans="1:31" ht="15">
       <c r="A77" s="42" t="s">
         <v>59</v>
       </c>
@@ -9993,7 +9984,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="15" hidden="1">
+    <row r="78" spans="1:31" ht="15">
       <c r="A78" s="42" t="s">
         <v>59</v>
       </c>
@@ -10066,7 +10057,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="15" hidden="1">
+    <row r="79" spans="1:31" ht="15">
       <c r="A79" s="42" t="s">
         <v>59</v>
       </c>
@@ -10139,7 +10130,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="15" hidden="1">
+    <row r="80" spans="1:31" ht="15">
       <c r="A80" s="42" t="s">
         <v>59</v>
       </c>
@@ -10218,7 +10209,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="15" hidden="1">
+    <row r="81" spans="1:31" ht="15">
       <c r="A81" s="42" t="s">
         <v>59</v>
       </c>
@@ -10297,7 +10288,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="15" hidden="1">
+    <row r="82" spans="1:31" ht="15">
       <c r="A82" s="42" t="s">
         <v>59</v>
       </c>
@@ -10376,7 +10367,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="15" hidden="1">
+    <row r="83" spans="1:31" ht="15">
       <c r="A83" s="42" t="s">
         <v>59</v>
       </c>
@@ -10450,7 +10441,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="15" hidden="1">
+    <row r="84" spans="1:31" ht="15">
       <c r="A84" s="42" t="s">
         <v>59</v>
       </c>
@@ -10526,7 +10517,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="15" hidden="1">
+    <row r="85" spans="1:31" ht="15">
       <c r="A85" s="42" t="s">
         <v>59</v>
       </c>
@@ -10602,7 +10593,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="15" hidden="1">
+    <row r="86" spans="1:31" ht="15">
       <c r="A86" s="42" t="s">
         <v>59</v>
       </c>
@@ -10675,7 +10666,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="15" hidden="1">
+    <row r="87" spans="1:31" ht="15">
       <c r="A87" s="42" t="s">
         <v>59</v>
       </c>
@@ -10751,7 +10742,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="15" hidden="1">
+    <row r="88" spans="1:31" ht="15">
       <c r="A88" s="42" t="s">
         <v>59</v>
       </c>
@@ -10827,7 +10818,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="15" hidden="1">
+    <row r="89" spans="1:31" ht="15">
       <c r="A89" s="42" t="s">
         <v>59</v>
       </c>
@@ -11622,7 +11613,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="15" hidden="1">
+    <row r="100" spans="1:31" ht="15">
       <c r="A100" s="42" t="s">
         <v>61</v>
       </c>
@@ -11691,7 +11682,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="15" hidden="1">
+    <row r="101" spans="1:31" ht="15">
       <c r="A101" s="42" t="s">
         <v>61</v>
       </c>
@@ -11763,7 +11754,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="15" hidden="1">
+    <row r="102" spans="1:31" ht="15">
       <c r="A102" s="42" t="s">
         <v>64</v>
       </c>
@@ -11832,7 +11823,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="15" hidden="1">
+    <row r="103" spans="1:31" ht="15">
       <c r="A103" s="42" t="s">
         <v>64</v>
       </c>
@@ -11904,7 +11895,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="15" hidden="1">
+    <row r="104" spans="1:31" ht="15">
       <c r="A104" s="42" t="s">
         <v>66</v>
       </c>
@@ -11973,7 +11964,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="15" hidden="1">
+    <row r="105" spans="1:31" ht="15">
       <c r="A105" s="42" t="s">
         <v>66</v>
       </c>
@@ -12045,7 +12036,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="15" hidden="1">
+    <row r="106" spans="1:31" ht="15">
       <c r="A106" s="42" t="s">
         <v>70</v>
       </c>
@@ -12114,7 +12105,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="15" hidden="1">
+    <row r="107" spans="1:31" ht="15">
       <c r="A107" s="42" t="s">
         <v>70</v>
       </c>
@@ -12186,7 +12177,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="15" hidden="1">
+    <row r="108" spans="1:31" ht="15">
       <c r="A108" s="42" t="s">
         <v>72</v>
       </c>
@@ -12255,7 +12246,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="15" hidden="1">
+    <row r="109" spans="1:31" ht="15">
       <c r="A109" s="42" t="s">
         <v>72</v>
       </c>
@@ -12327,7 +12318,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="15" hidden="1">
+    <row r="110" spans="1:31" ht="15">
       <c r="A110" s="42" t="s">
         <v>75</v>
       </c>
@@ -12396,7 +12387,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="15" hidden="1">
+    <row r="111" spans="1:31" ht="15">
       <c r="A111" s="42" t="s">
         <v>75</v>
       </c>
@@ -12468,7 +12459,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="15" hidden="1">
+    <row r="112" spans="1:31" ht="15">
       <c r="A112" s="42" t="s">
         <v>77</v>
       </c>
@@ -12535,7 +12526,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="15" hidden="1">
+    <row r="113" spans="1:31" ht="15">
       <c r="A113" s="42" t="s">
         <v>77</v>
       </c>
@@ -12605,7 +12596,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="15" hidden="1">
+    <row r="114" spans="1:31" ht="15">
       <c r="A114" s="42" t="s">
         <v>80</v>
       </c>
@@ -12672,7 +12663,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="15" hidden="1">
+    <row r="115" spans="1:31" ht="15">
       <c r="A115" s="42" t="s">
         <v>80</v>
       </c>
@@ -12742,7 +12733,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="15" hidden="1">
+    <row r="116" spans="1:31" ht="15">
       <c r="A116" s="42" t="s">
         <v>82</v>
       </c>
@@ -12812,7 +12803,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="15" hidden="1">
+    <row r="117" spans="1:31" ht="15">
       <c r="A117" s="42" t="s">
         <v>82</v>
       </c>
@@ -12885,7 +12876,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="15" hidden="1">
+    <row r="118" spans="1:31" ht="15">
       <c r="A118" s="42" t="s">
         <v>84</v>
       </c>
@@ -12955,7 +12946,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="15" hidden="1">
+    <row r="119" spans="1:31" ht="15">
       <c r="A119" s="42" t="s">
         <v>84</v>
       </c>
@@ -13028,7 +13019,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="15" hidden="1">
+    <row r="120" spans="1:31" ht="15">
       <c r="A120" s="42" t="s">
         <v>86</v>
       </c>
@@ -13098,7 +13089,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="15" hidden="1">
+    <row r="121" spans="1:31" ht="15">
       <c r="A121" s="42" t="s">
         <v>86</v>
       </c>
@@ -13171,7 +13162,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="15" hidden="1">
+    <row r="122" spans="1:31" ht="15">
       <c r="A122" s="42" t="s">
         <v>88</v>
       </c>
@@ -13241,7 +13232,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="15" hidden="1">
+    <row r="123" spans="1:31" ht="15">
       <c r="A123" s="42" t="s">
         <v>88</v>
       </c>
@@ -13314,7 +13305,7 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="15" hidden="1">
+    <row r="124" spans="1:31" ht="15">
       <c r="A124" s="42" t="s">
         <v>90</v>
       </c>
@@ -13384,7 +13375,7 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="15" hidden="1">
+    <row r="125" spans="1:31" ht="15">
       <c r="A125" s="42" t="s">
         <v>90</v>
       </c>
@@ -13457,7 +13448,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="15" hidden="1">
+    <row r="126" spans="1:31" ht="15">
       <c r="A126" s="42" t="s">
         <v>92</v>
       </c>
@@ -13527,7 +13518,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="15" hidden="1">
+    <row r="127" spans="1:31" ht="15">
       <c r="A127" s="42" t="s">
         <v>92</v>
       </c>
@@ -13600,7 +13591,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="15" hidden="1">
+    <row r="128" spans="1:31" ht="15">
       <c r="A128" s="42" t="s">
         <v>94</v>
       </c>
@@ -13670,7 +13661,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="15" hidden="1">
+    <row r="129" spans="1:31" ht="15">
       <c r="A129" s="42" t="s">
         <v>94</v>
       </c>
@@ -13743,7 +13734,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="15" hidden="1">
+    <row r="130" spans="1:31" ht="15">
       <c r="A130" s="42" t="s">
         <v>96</v>
       </c>
@@ -13811,7 +13802,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="15" hidden="1">
+    <row r="131" spans="1:31" ht="15">
       <c r="A131" s="42" t="s">
         <v>96</v>
       </c>
@@ -13882,7 +13873,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="15" hidden="1">
+    <row r="132" spans="1:31" ht="15">
       <c r="A132" s="42" t="s">
         <v>98</v>
       </c>
@@ -13950,7 +13941,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="15" hidden="1">
+    <row r="133" spans="1:31" ht="15">
       <c r="A133" s="79" t="s">
         <v>98</v>
       </c>
@@ -14020,7 +14011,7 @@
       <c r="AC133" s="46"/>
       <c r="AD133" s="46"/>
     </row>
-    <row r="134" spans="1:31" ht="15" hidden="1">
+    <row r="134" spans="1:31" ht="15">
       <c r="A134" s="79" t="s">
         <v>100</v>
       </c>
@@ -14087,7 +14078,7 @@
       <c r="AC134" s="46"/>
       <c r="AD134" s="46"/>
     </row>
-    <row r="135" spans="1:31" ht="15" hidden="1">
+    <row r="135" spans="1:31" ht="15">
       <c r="A135" s="79" t="s">
         <v>100</v>
       </c>
@@ -14157,7 +14148,7 @@
       <c r="AC135" s="46"/>
       <c r="AD135" s="44"/>
     </row>
-    <row r="136" spans="1:31" ht="15" hidden="1">
+    <row r="136" spans="1:31" ht="15">
       <c r="A136" s="79" t="s">
         <v>102</v>
       </c>
@@ -14226,7 +14217,7 @@
       <c r="AC136" s="46"/>
       <c r="AD136" s="44"/>
     </row>
-    <row r="137" spans="1:31" ht="15" hidden="1">
+    <row r="137" spans="1:31" ht="15">
       <c r="A137" s="79" t="s">
         <v>102</v>
       </c>
@@ -14298,7 +14289,7 @@
       <c r="AC137" s="46"/>
       <c r="AD137" s="44"/>
     </row>
-    <row r="138" spans="1:31" ht="15" hidden="1">
+    <row r="138" spans="1:31" ht="15">
       <c r="A138" s="79" t="s">
         <v>104</v>
       </c>
@@ -14367,7 +14358,7 @@
       <c r="AC138" s="46"/>
       <c r="AD138" s="44"/>
     </row>
-    <row r="139" spans="1:31" ht="15" hidden="1">
+    <row r="139" spans="1:31" ht="15">
       <c r="A139" s="79" t="s">
         <v>104</v>
       </c>
@@ -14440,7 +14431,7 @@
       <c r="AD139" s="44"/>
       <c r="AE139" s="16"/>
     </row>
-    <row r="140" spans="1:31" ht="15" hidden="1">
+    <row r="140" spans="1:31" ht="15">
       <c r="A140" s="79" t="s">
         <v>106</v>
       </c>
@@ -14510,7 +14501,7 @@
       <c r="AD140" s="7"/>
       <c r="AE140" s="16"/>
     </row>
-    <row r="141" spans="1:31" ht="15" hidden="1">
+    <row r="141" spans="1:31" ht="15">
       <c r="A141" s="79" t="s">
         <v>106</v>
       </c>
@@ -14583,7 +14574,7 @@
       <c r="AD141" s="7"/>
       <c r="AE141" s="16"/>
     </row>
-    <row r="142" spans="1:31" ht="15" hidden="1">
+    <row r="142" spans="1:31" ht="15">
       <c r="A142" s="79" t="s">
         <v>108</v>
       </c>
@@ -14652,7 +14643,7 @@
       <c r="AC142" s="46"/>
       <c r="AD142" s="7"/>
     </row>
-    <row r="143" spans="1:31" ht="15" hidden="1">
+    <row r="143" spans="1:31" ht="15">
       <c r="A143" s="79" t="s">
         <v>108</v>
       </c>
@@ -14724,7 +14715,7 @@
       <c r="AC143" s="46"/>
       <c r="AD143" s="7"/>
     </row>
-    <row r="144" spans="1:31" ht="15" hidden="1">
+    <row r="144" spans="1:31" ht="15">
       <c r="A144" s="79" t="s">
         <v>110</v>
       </c>
@@ -14793,7 +14784,7 @@
       <c r="AC144" s="46"/>
       <c r="AD144" s="7"/>
     </row>
-    <row r="145" spans="1:31" ht="15" hidden="1">
+    <row r="145" spans="1:31" ht="15">
       <c r="A145" s="79" t="s">
         <v>110</v>
       </c>
@@ -14865,7 +14856,7 @@
       <c r="AC145" s="46"/>
       <c r="AD145" s="7"/>
     </row>
-    <row r="146" spans="1:31" ht="15" hidden="1">
+    <row r="146" spans="1:31" ht="15">
       <c r="A146" s="85" t="s">
         <v>112</v>
       </c>
@@ -14934,7 +14925,7 @@
       <c r="AC146" s="46"/>
       <c r="AD146" s="44"/>
     </row>
-    <row r="147" spans="1:31" ht="15" hidden="1">
+    <row r="147" spans="1:31" ht="15">
       <c r="A147" s="42" t="s">
         <v>112</v>
       </c>
@@ -15006,7 +14997,7 @@
       <c r="AD147"/>
       <c r="AE147"/>
     </row>
-    <row r="148" spans="1:31" ht="15" hidden="1">
+    <row r="148" spans="1:31" ht="15">
       <c r="A148" s="42" t="s">
         <v>114</v>
       </c>
@@ -15073,7 +15064,7 @@
       <c r="AD148"/>
       <c r="AE148"/>
     </row>
-    <row r="149" spans="1:31" ht="15" hidden="1">
+    <row r="149" spans="1:31" ht="15">
       <c r="A149" s="42" t="s">
         <v>114</v>
       </c>
@@ -15143,7 +15134,7 @@
       <c r="AD149"/>
       <c r="AE149"/>
     </row>
-    <row r="150" spans="1:31" ht="15" hidden="1">
+    <row r="150" spans="1:31" ht="15">
       <c r="A150" s="42" t="s">
         <v>116</v>
       </c>
@@ -15210,7 +15201,7 @@
       <c r="AD150"/>
       <c r="AE150"/>
     </row>
-    <row r="151" spans="1:31" ht="15" hidden="1">
+    <row r="151" spans="1:31" ht="15">
       <c r="A151" s="42" t="s">
         <v>116</v>
       </c>
@@ -15280,7 +15271,7 @@
       <c r="AD151"/>
       <c r="AE151"/>
     </row>
-    <row r="152" spans="1:31" ht="15" hidden="1">
+    <row r="152" spans="1:31" ht="15">
       <c r="A152" s="42" t="s">
         <v>118</v>
       </c>
@@ -15348,7 +15339,7 @@
       <c r="AD152"/>
       <c r="AE152"/>
     </row>
-    <row r="153" spans="1:31" ht="15" hidden="1">
+    <row r="153" spans="1:31" ht="15">
       <c r="A153" s="42" t="s">
         <v>118</v>
       </c>
@@ -15419,7 +15410,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="15" hidden="1">
+    <row r="154" spans="1:31" ht="15">
       <c r="A154" s="42" t="s">
         <v>123</v>
       </c>
@@ -15491,7 +15482,7 @@
       <c r="AC154" s="46"/>
       <c r="AD154" s="46"/>
     </row>
-    <row r="155" spans="1:31" ht="15" hidden="1">
+    <row r="155" spans="1:31" ht="15">
       <c r="A155" s="42" t="s">
         <v>123</v>
       </c>
@@ -15563,7 +15554,7 @@
       <c r="AC155" s="46"/>
       <c r="AD155" s="44"/>
     </row>
-    <row r="156" spans="1:31" ht="15" hidden="1">
+    <row r="156" spans="1:31" ht="15">
       <c r="A156" s="42" t="s">
         <v>123</v>
       </c>
@@ -15635,7 +15626,7 @@
       <c r="AC156" s="46"/>
       <c r="AD156" s="44"/>
     </row>
-    <row r="157" spans="1:31" ht="15" hidden="1">
+    <row r="157" spans="1:31" ht="15">
       <c r="A157" s="42" t="s">
         <v>123</v>
       </c>
@@ -15707,7 +15698,7 @@
       <c r="AC157" s="46"/>
       <c r="AD157" s="7"/>
     </row>
-    <row r="158" spans="1:31" ht="15" hidden="1">
+    <row r="158" spans="1:31" ht="15">
       <c r="A158" s="79" t="s">
         <v>123</v>
       </c>
@@ -15779,7 +15770,7 @@
       <c r="AC158" s="46"/>
       <c r="AD158" s="7"/>
     </row>
-    <row r="159" spans="1:31" ht="15" hidden="1">
+    <row r="159" spans="1:31" ht="15">
       <c r="A159" s="79" t="s">
         <v>123</v>
       </c>
@@ -15852,7 +15843,7 @@
       <c r="AC159" s="46"/>
       <c r="AD159" s="7"/>
     </row>
-    <row r="160" spans="1:31" ht="15" hidden="1">
+    <row r="160" spans="1:31" ht="15">
       <c r="A160" s="79" t="s">
         <v>123</v>
       </c>
@@ -15924,7 +15915,7 @@
       <c r="AC160" s="46"/>
       <c r="AD160" s="7"/>
     </row>
-    <row r="161" spans="1:30" ht="15" hidden="1">
+    <row r="161" spans="1:30" ht="15">
       <c r="A161" s="79" t="s">
         <v>123</v>
       </c>
@@ -15996,7 +15987,7 @@
       <c r="AC161" s="46"/>
       <c r="AD161" s="46"/>
     </row>
-    <row r="162" spans="1:30" ht="15" hidden="1">
+    <row r="162" spans="1:30" ht="15">
       <c r="A162" s="79" t="s">
         <v>123</v>
       </c>
@@ -16068,7 +16059,7 @@
       <c r="AC162" s="46"/>
       <c r="AD162" s="7"/>
     </row>
-    <row r="163" spans="1:30" ht="15" hidden="1">
+    <row r="163" spans="1:30" ht="15">
       <c r="A163" s="79" t="s">
         <v>123</v>
       </c>
@@ -16140,7 +16131,7 @@
       <c r="AC163" s="46"/>
       <c r="AD163" s="46"/>
     </row>
-    <row r="164" spans="1:30" ht="15" hidden="1">
+    <row r="164" spans="1:30" ht="15">
       <c r="A164" s="79" t="s">
         <v>123</v>
       </c>
@@ -16212,7 +16203,7 @@
       <c r="AC164" s="46"/>
       <c r="AD164" s="44"/>
     </row>
-    <row r="165" spans="1:30" ht="15" hidden="1">
+    <row r="165" spans="1:30" ht="15">
       <c r="A165" s="79" t="s">
         <v>123</v>
       </c>
@@ -16284,7 +16275,7 @@
       <c r="AC165" s="46"/>
       <c r="AD165" s="44"/>
     </row>
-    <row r="166" spans="1:30" ht="15" hidden="1">
+    <row r="166" spans="1:30" ht="15">
       <c r="A166" s="79" t="s">
         <v>123</v>
       </c>
@@ -16356,7 +16347,7 @@
       <c r="AC166" s="46"/>
       <c r="AD166" s="44"/>
     </row>
-    <row r="167" spans="1:30" ht="15" hidden="1">
+    <row r="167" spans="1:30" ht="15">
       <c r="A167" s="85" t="s">
         <v>123</v>
       </c>
@@ -16428,7 +16419,7 @@
       <c r="AC167" s="46"/>
       <c r="AD167" s="44"/>
     </row>
-    <row r="168" spans="1:30" ht="15" hidden="1">
+    <row r="168" spans="1:30" ht="15">
       <c r="A168" s="79" t="s">
         <v>125</v>
       </c>
@@ -16500,7 +16491,7 @@
       <c r="AC168" s="46"/>
       <c r="AD168" s="44"/>
     </row>
-    <row r="169" spans="1:30" ht="15" hidden="1">
+    <row r="169" spans="1:30" ht="15">
       <c r="A169" s="79" t="s">
         <v>125</v>
       </c>
@@ -16572,7 +16563,7 @@
       <c r="AC169" s="46"/>
       <c r="AD169" s="7"/>
     </row>
-    <row r="170" spans="1:30" ht="15" hidden="1">
+    <row r="170" spans="1:30" ht="15">
       <c r="A170" s="79" t="s">
         <v>125</v>
       </c>
@@ -16644,7 +16635,7 @@
       <c r="AC170" s="46"/>
       <c r="AD170" s="7"/>
     </row>
-    <row r="171" spans="1:30" ht="15" hidden="1">
+    <row r="171" spans="1:30" ht="15">
       <c r="A171" s="79" t="s">
         <v>125</v>
       </c>
@@ -16715,7 +16706,7 @@
       <c r="AB171" s="73"/>
       <c r="AD171" s="16"/>
     </row>
-    <row r="172" spans="1:30" ht="15" hidden="1">
+    <row r="172" spans="1:30" ht="15">
       <c r="A172" s="79" t="s">
         <v>125</v>
       </c>
@@ -16787,7 +16778,7 @@
       <c r="AC172" s="44"/>
       <c r="AD172" s="44"/>
     </row>
-    <row r="173" spans="1:30" ht="15" hidden="1">
+    <row r="173" spans="1:30" ht="15">
       <c r="A173" s="79" t="s">
         <v>125</v>
       </c>
@@ -16860,7 +16851,7 @@
       <c r="AC173" s="44"/>
       <c r="AD173" s="44"/>
     </row>
-    <row r="174" spans="1:30" ht="15" hidden="1">
+    <row r="174" spans="1:30" ht="15">
       <c r="A174" s="79" t="s">
         <v>125</v>
       </c>
@@ -16932,7 +16923,7 @@
       <c r="AC174" s="44"/>
       <c r="AD174" s="44"/>
     </row>
-    <row r="175" spans="1:30" ht="15" hidden="1">
+    <row r="175" spans="1:30" ht="15">
       <c r="A175" s="79" t="s">
         <v>125</v>
       </c>
@@ -17004,7 +16995,7 @@
       <c r="AC175" s="44"/>
       <c r="AD175" s="44"/>
     </row>
-    <row r="176" spans="1:30" ht="15" hidden="1">
+    <row r="176" spans="1:30" ht="15">
       <c r="A176" s="79" t="s">
         <v>125</v>
       </c>
@@ -17076,7 +17067,7 @@
       <c r="AC176" s="44"/>
       <c r="AD176" s="44"/>
     </row>
-    <row r="177" spans="1:30" ht="15" hidden="1">
+    <row r="177" spans="1:30" ht="15">
       <c r="A177" s="79" t="s">
         <v>125</v>
       </c>
@@ -17148,7 +17139,7 @@
       <c r="AC177" s="44"/>
       <c r="AD177" s="44"/>
     </row>
-    <row r="178" spans="1:30" ht="15" hidden="1">
+    <row r="178" spans="1:30" ht="15">
       <c r="A178" s="79" t="s">
         <v>125</v>
       </c>
@@ -17220,7 +17211,7 @@
       <c r="AC178" s="44"/>
       <c r="AD178" s="44"/>
     </row>
-    <row r="179" spans="1:30" ht="15" hidden="1">
+    <row r="179" spans="1:30" ht="15">
       <c r="A179" s="79" t="s">
         <v>125</v>
       </c>
@@ -17292,7 +17283,7 @@
       <c r="AC179" s="44"/>
       <c r="AD179" s="44"/>
     </row>
-    <row r="180" spans="1:30" ht="15" hidden="1">
+    <row r="180" spans="1:30" ht="15">
       <c r="A180" s="79" t="s">
         <v>125</v>
       </c>
@@ -17364,7 +17355,7 @@
       <c r="AC180" s="44"/>
       <c r="AD180" s="44"/>
     </row>
-    <row r="181" spans="1:30" ht="15" hidden="1">
+    <row r="181" spans="1:30" ht="15">
       <c r="A181" s="79" t="s">
         <v>125</v>
       </c>
@@ -17436,7 +17427,7 @@
       <c r="AC181" s="44"/>
       <c r="AD181" s="44"/>
     </row>
-    <row r="182" spans="1:30" ht="15" hidden="1">
+    <row r="182" spans="1:30" ht="15">
       <c r="A182" s="79" t="s">
         <v>127</v>
       </c>
@@ -17508,7 +17499,7 @@
       <c r="AC182" s="44"/>
       <c r="AD182" s="44"/>
     </row>
-    <row r="183" spans="1:30" ht="15" hidden="1">
+    <row r="183" spans="1:30" ht="15">
       <c r="A183" s="79" t="s">
         <v>127</v>
       </c>
@@ -17580,7 +17571,7 @@
       <c r="AC183" s="44"/>
       <c r="AD183" s="44"/>
     </row>
-    <row r="184" spans="1:30" ht="15" hidden="1">
+    <row r="184" spans="1:30" ht="15">
       <c r="A184" s="79" t="s">
         <v>127</v>
       </c>
@@ -17652,7 +17643,7 @@
       <c r="AC184" s="44"/>
       <c r="AD184" s="44"/>
     </row>
-    <row r="185" spans="1:30" ht="15" hidden="1">
+    <row r="185" spans="1:30" ht="15">
       <c r="A185" s="79" t="s">
         <v>127</v>
       </c>
@@ -17724,7 +17715,7 @@
       <c r="AC185" s="44"/>
       <c r="AD185" s="44"/>
     </row>
-    <row r="186" spans="1:30" ht="15" hidden="1">
+    <row r="186" spans="1:30" ht="15">
       <c r="A186" s="79" t="s">
         <v>127</v>
       </c>
@@ -17796,7 +17787,7 @@
       <c r="AC186" s="44"/>
       <c r="AD186" s="44"/>
     </row>
-    <row r="187" spans="1:30" ht="15" hidden="1">
+    <row r="187" spans="1:30" ht="15">
       <c r="A187" s="79" t="s">
         <v>127</v>
       </c>
@@ -17869,7 +17860,7 @@
       <c r="AC187" s="44"/>
       <c r="AD187" s="44"/>
     </row>
-    <row r="188" spans="1:30" ht="15" hidden="1">
+    <row r="188" spans="1:30" ht="15">
       <c r="A188" s="79" t="s">
         <v>127</v>
       </c>
@@ -17941,7 +17932,7 @@
       <c r="AC188" s="44"/>
       <c r="AD188" s="44"/>
     </row>
-    <row r="189" spans="1:30" ht="15" hidden="1">
+    <row r="189" spans="1:30" ht="15">
       <c r="A189" s="79" t="s">
         <v>127</v>
       </c>
@@ -18013,7 +18004,7 @@
       <c r="AC189" s="44"/>
       <c r="AD189" s="44"/>
     </row>
-    <row r="190" spans="1:30" ht="15" hidden="1">
+    <row r="190" spans="1:30" ht="15">
       <c r="A190" s="79" t="s">
         <v>127</v>
       </c>
@@ -18085,7 +18076,7 @@
       <c r="AC190" s="44"/>
       <c r="AD190" s="44"/>
     </row>
-    <row r="191" spans="1:30" ht="15" hidden="1">
+    <row r="191" spans="1:30" ht="15">
       <c r="A191" s="79" t="s">
         <v>127</v>
       </c>
@@ -18157,7 +18148,7 @@
       <c r="AC191" s="44"/>
       <c r="AD191" s="44"/>
     </row>
-    <row r="192" spans="1:30" ht="15" hidden="1">
+    <row r="192" spans="1:30" ht="15">
       <c r="A192" s="79" t="s">
         <v>127</v>
       </c>
@@ -18229,7 +18220,7 @@
       <c r="AC192" s="44"/>
       <c r="AD192" s="44"/>
     </row>
-    <row r="193" spans="1:30" ht="15" hidden="1">
+    <row r="193" spans="1:30" ht="15">
       <c r="A193" s="79" t="s">
         <v>127</v>
       </c>
@@ -18301,7 +18292,7 @@
       <c r="AC193" s="44"/>
       <c r="AD193" s="44"/>
     </row>
-    <row r="194" spans="1:30" ht="15" hidden="1">
+    <row r="194" spans="1:30" ht="15">
       <c r="A194" s="79" t="s">
         <v>127</v>
       </c>
@@ -18373,7 +18364,7 @@
       <c r="AC194" s="44"/>
       <c r="AD194" s="44"/>
     </row>
-    <row r="195" spans="1:30" ht="15" hidden="1">
+    <row r="195" spans="1:30" ht="15">
       <c r="A195" s="79" t="s">
         <v>127</v>
       </c>
@@ -18443,7 +18434,7 @@
       <c r="AC195" s="44"/>
       <c r="AD195" s="44"/>
     </row>
-    <row r="196" spans="1:30" ht="15" hidden="1">
+    <row r="196" spans="1:30" ht="15">
       <c r="A196" s="79" t="s">
         <v>165</v>
       </c>
@@ -18522,7 +18513,7 @@
       <c r="AC196" s="44"/>
       <c r="AD196" s="44"/>
     </row>
-    <row r="197" spans="1:30" ht="15" hidden="1">
+    <row r="197" spans="1:30" ht="15">
       <c r="A197" s="79" t="s">
         <v>167</v>
       </c>
@@ -18601,7 +18592,7 @@
       <c r="AC197" s="44"/>
       <c r="AD197" s="44"/>
     </row>
-    <row r="198" spans="1:30" ht="15" hidden="1">
+    <row r="198" spans="1:30" ht="15">
       <c r="A198" s="79" t="s">
         <v>169</v>
       </c>
@@ -18680,7 +18671,7 @@
       <c r="AC198" s="44"/>
       <c r="AD198" s="44"/>
     </row>
-    <row r="199" spans="1:30" ht="15" hidden="1">
+    <row r="199" spans="1:30" ht="15">
       <c r="A199" s="85" t="s">
         <v>1</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1566" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55753934-226F-47BA-87F8-BADB407319CE}"/>
+  <xr:revisionPtr revIDLastSave="1571" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DEC5E4B-8A2E-4F05-A5E9-1E2C0F05877A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="28755" yWindow="1110" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3333,7 +3333,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
+  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="Open House Special"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A90:V99">
     <sortCondition ref="I1:I199"/>
   </sortState>
@@ -4435,7 +4441,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="15">
+    <row r="2" spans="1:31" ht="15" hidden="1">
       <c r="A2" s="42" t="s">
         <v>130</v>
       </c>
@@ -4505,7 +4511,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="15">
+    <row r="3" spans="1:31" ht="15" hidden="1">
       <c r="A3" s="42" t="s">
         <v>130</v>
       </c>
@@ -4574,7 +4580,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="15">
+    <row r="4" spans="1:31" ht="15" hidden="1">
       <c r="A4" s="42" t="s">
         <v>130</v>
       </c>
@@ -4718,7 +4724,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="15">
+    <row r="6" spans="1:31" ht="15" hidden="1">
       <c r="A6" s="42" t="s">
         <v>120</v>
       </c>
@@ -4785,7 +4791,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="15">
+    <row r="7" spans="1:31" ht="15" hidden="1">
       <c r="A7" s="42" t="s">
         <v>120</v>
       </c>
@@ -4849,7 +4855,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="15">
+    <row r="8" spans="1:31" ht="15" hidden="1">
       <c r="A8" s="42" t="s">
         <v>132</v>
       </c>
@@ -4918,7 +4924,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="15">
+    <row r="9" spans="1:31" ht="15" hidden="1">
       <c r="A9" s="42" t="s">
         <v>132</v>
       </c>
@@ -5062,7 +5068,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="15">
+    <row r="11" spans="1:31" ht="15" hidden="1">
       <c r="A11" s="42" t="s">
         <v>134</v>
       </c>
@@ -5131,7 +5137,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="15">
+    <row r="12" spans="1:31" ht="15" hidden="1">
       <c r="A12" s="42" t="s">
         <v>132</v>
       </c>
@@ -5200,7 +5206,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="15">
+    <row r="13" spans="1:31" ht="15" hidden="1">
       <c r="A13" s="42" t="s">
         <v>134</v>
       </c>
@@ -5269,7 +5275,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="15">
+    <row r="14" spans="1:31" ht="15" hidden="1">
       <c r="A14" s="42" t="s">
         <v>134</v>
       </c>
@@ -5414,7 +5420,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="15">
+    <row r="16" spans="1:31" ht="15" hidden="1">
       <c r="A16" s="42" t="s">
         <v>139</v>
       </c>
@@ -5487,7 +5493,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="15">
+    <row r="17" spans="1:31" ht="15" hidden="1">
       <c r="A17" s="42" t="s">
         <v>139</v>
       </c>
@@ -5560,7 +5566,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="15">
+    <row r="18" spans="1:31" ht="15" hidden="1">
       <c r="A18" s="42" t="s">
         <v>142</v>
       </c>
@@ -5632,7 +5638,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="15">
+    <row r="19" spans="1:31" ht="15" hidden="1">
       <c r="A19" s="42" t="s">
         <v>142</v>
       </c>
@@ -5705,7 +5711,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="15">
+    <row r="20" spans="1:31" ht="15" hidden="1">
       <c r="A20" s="42" t="s">
         <v>144</v>
       </c>
@@ -5777,7 +5783,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="15">
+    <row r="21" spans="1:31" ht="15" hidden="1">
       <c r="A21" s="42" t="s">
         <v>144</v>
       </c>
@@ -5850,7 +5856,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="15">
+    <row r="22" spans="1:31" ht="15" hidden="1">
       <c r="A22" s="42" t="s">
         <v>146</v>
       </c>
@@ -5922,7 +5928,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="15">
+    <row r="23" spans="1:31" ht="15" hidden="1">
       <c r="A23" s="42" t="s">
         <v>146</v>
       </c>
@@ -5994,7 +6000,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15">
+    <row r="24" spans="1:31" ht="15" hidden="1">
       <c r="A24" s="42" t="s">
         <v>148</v>
       </c>
@@ -6066,7 +6072,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15">
+    <row r="25" spans="1:31" ht="15" hidden="1">
       <c r="A25" s="42" t="s">
         <v>148</v>
       </c>
@@ -6140,7 +6146,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15">
+    <row r="26" spans="1:31" ht="15" hidden="1">
       <c r="A26" s="42" t="s">
         <v>150</v>
       </c>
@@ -6213,7 +6219,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15">
+    <row r="27" spans="1:31" ht="15" hidden="1">
       <c r="A27" s="42" t="s">
         <v>150</v>
       </c>
@@ -6287,7 +6293,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15">
+    <row r="28" spans="1:31" ht="15" hidden="1">
       <c r="A28" s="42" t="s">
         <v>43</v>
       </c>
@@ -6350,7 +6356,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15">
+    <row r="29" spans="1:31" ht="15" hidden="1">
       <c r="A29" s="42" t="s">
         <v>43</v>
       </c>
@@ -6422,7 +6428,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="15">
+    <row r="30" spans="1:31" ht="15" hidden="1">
       <c r="A30" s="42" t="s">
         <v>47</v>
       </c>
@@ -6494,7 +6500,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="15">
+    <row r="31" spans="1:31" ht="15" hidden="1">
       <c r="A31" s="42" t="s">
         <v>47</v>
       </c>
@@ -6565,7 +6571,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="15">
+    <row r="32" spans="1:31" ht="15" hidden="1">
       <c r="A32" s="42" t="s">
         <v>47</v>
       </c>
@@ -6637,7 +6643,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="15">
+    <row r="33" spans="1:31" ht="15" hidden="1">
       <c r="A33" s="42" t="s">
         <v>47</v>
       </c>
@@ -6709,7 +6715,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="15">
+    <row r="34" spans="1:31" ht="15" hidden="1">
       <c r="A34" s="42" t="s">
         <v>47</v>
       </c>
@@ -6781,7 +6787,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:31" ht="15">
+    <row r="35" spans="1:31" ht="15" hidden="1">
       <c r="A35" s="42" t="s">
         <v>47</v>
       </c>
@@ -6853,7 +6859,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="15">
+    <row r="36" spans="1:31" ht="15" hidden="1">
       <c r="A36" s="42" t="s">
         <v>47</v>
       </c>
@@ -6926,7 +6932,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="15">
+    <row r="37" spans="1:31" ht="15" hidden="1">
       <c r="A37" s="42" t="s">
         <v>47</v>
       </c>
@@ -6998,7 +7004,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="15">
+    <row r="38" spans="1:31" ht="15" hidden="1">
       <c r="A38" s="42" t="s">
         <v>47</v>
       </c>
@@ -7070,7 +7076,7 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="15">
+    <row r="39" spans="1:31" ht="15" hidden="1">
       <c r="A39" s="42" t="s">
         <v>47</v>
       </c>
@@ -7142,7 +7148,7 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="15">
+    <row r="40" spans="1:31" ht="15" hidden="1">
       <c r="A40" s="42" t="s">
         <v>47</v>
       </c>
@@ -7214,7 +7220,7 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="15">
+    <row r="41" spans="1:31" ht="15" hidden="1">
       <c r="A41" s="42" t="s">
         <v>47</v>
       </c>
@@ -7286,7 +7292,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="15">
+    <row r="42" spans="1:31" ht="15" hidden="1">
       <c r="A42" s="42" t="s">
         <v>47</v>
       </c>
@@ -7358,7 +7364,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="15">
+    <row r="43" spans="1:31" ht="15" hidden="1">
       <c r="A43" s="42" t="s">
         <v>53</v>
       </c>
@@ -7436,7 +7442,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="15">
+    <row r="44" spans="1:31" ht="15" hidden="1">
       <c r="A44" s="42" t="s">
         <v>53</v>
       </c>
@@ -7514,7 +7520,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="15">
+    <row r="45" spans="1:31" ht="15" hidden="1">
       <c r="A45" s="42" t="s">
         <v>53</v>
       </c>
@@ -7592,7 +7598,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="15">
+    <row r="46" spans="1:31" ht="15" hidden="1">
       <c r="A46" s="42" t="s">
         <v>53</v>
       </c>
@@ -7670,7 +7676,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="15">
+    <row r="47" spans="1:31" ht="15" hidden="1">
       <c r="A47" s="42" t="s">
         <v>53</v>
       </c>
@@ -7745,7 +7751,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="15">
+    <row r="48" spans="1:31" ht="15" hidden="1">
       <c r="A48" s="42" t="s">
         <v>53</v>
       </c>
@@ -7820,7 +7826,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="15">
+    <row r="49" spans="1:32" ht="15" hidden="1">
       <c r="A49" s="42" t="s">
         <v>53</v>
       </c>
@@ -7896,7 +7902,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="15">
+    <row r="50" spans="1:32" ht="15" hidden="1">
       <c r="A50" s="42" t="s">
         <v>53</v>
       </c>
@@ -7972,7 +7978,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="15">
+    <row r="51" spans="1:32" ht="15" hidden="1">
       <c r="A51" s="42" t="s">
         <v>53</v>
       </c>
@@ -8048,7 +8054,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="15">
+    <row r="52" spans="1:32" ht="15" hidden="1">
       <c r="A52" s="42" t="s">
         <v>53</v>
       </c>
@@ -8118,7 +8124,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="15">
+    <row r="53" spans="1:32" ht="15" hidden="1">
       <c r="A53" s="42" t="s">
         <v>53</v>
       </c>
@@ -8191,7 +8197,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="15">
+    <row r="54" spans="1:32" ht="15" hidden="1">
       <c r="A54" s="42" t="s">
         <v>53</v>
       </c>
@@ -8264,7 +8270,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="15">
+    <row r="55" spans="1:32" ht="15" hidden="1">
       <c r="A55" s="42" t="s">
         <v>53</v>
       </c>
@@ -8337,7 +8343,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="15">
+    <row r="56" spans="1:32" ht="15" hidden="1">
       <c r="A56" s="42" t="s">
         <v>53</v>
       </c>
@@ -8484,7 +8490,7 @@
       <c r="AE57" s="16"/>
       <c r="AF57" s="16"/>
     </row>
-    <row r="58" spans="1:32" ht="15">
+    <row r="58" spans="1:32" ht="15" hidden="1">
       <c r="A58" s="42" t="s">
         <v>50</v>
       </c>
@@ -8556,7 +8562,7 @@
       <c r="AE58" s="16"/>
       <c r="AF58" s="16"/>
     </row>
-    <row r="59" spans="1:32" ht="15">
+    <row r="59" spans="1:32" ht="15" hidden="1">
       <c r="A59" s="42" t="s">
         <v>50</v>
       </c>
@@ -8628,7 +8634,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="15">
+    <row r="60" spans="1:32" ht="15" hidden="1">
       <c r="A60" s="42" t="s">
         <v>57</v>
       </c>
@@ -8706,7 +8712,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="15">
+    <row r="61" spans="1:32" ht="15" hidden="1">
       <c r="A61" s="42" t="s">
         <v>57</v>
       </c>
@@ -8785,7 +8791,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="15">
+    <row r="62" spans="1:32" ht="15" hidden="1">
       <c r="A62" s="42" t="s">
         <v>57</v>
       </c>
@@ -8864,7 +8870,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="15">
+    <row r="63" spans="1:32" ht="15" hidden="1">
       <c r="A63" s="42" t="s">
         <v>57</v>
       </c>
@@ -8943,7 +8949,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="15">
+    <row r="64" spans="1:32" ht="15" hidden="1">
       <c r="A64" s="42" t="s">
         <v>57</v>
       </c>
@@ -9019,7 +9025,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15">
+    <row r="65" spans="1:31" ht="15" hidden="1">
       <c r="A65" s="42" t="s">
         <v>57</v>
       </c>
@@ -9095,7 +9101,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15">
+    <row r="66" spans="1:31" ht="15" hidden="1">
       <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
@@ -9171,7 +9177,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15">
+    <row r="67" spans="1:31" ht="15" hidden="1">
       <c r="A67" s="42" t="s">
         <v>57</v>
       </c>
@@ -9247,7 +9253,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15">
+    <row r="68" spans="1:31" ht="15" hidden="1">
       <c r="A68" s="42" t="s">
         <v>57</v>
       </c>
@@ -9323,7 +9329,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15">
+    <row r="69" spans="1:31" ht="15" hidden="1">
       <c r="A69" s="42" t="s">
         <v>57</v>
       </c>
@@ -9393,7 +9399,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15">
+    <row r="70" spans="1:31" ht="15" hidden="1">
       <c r="A70" s="42" t="s">
         <v>57</v>
       </c>
@@ -9466,7 +9472,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15">
+    <row r="71" spans="1:31" ht="15" hidden="1">
       <c r="A71" s="42" t="s">
         <v>57</v>
       </c>
@@ -9539,7 +9545,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15">
+    <row r="72" spans="1:31" ht="15" hidden="1">
       <c r="A72" s="42" t="s">
         <v>57</v>
       </c>
@@ -9612,7 +9618,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15">
+    <row r="73" spans="1:31" ht="15" hidden="1">
       <c r="A73" s="42" t="s">
         <v>57</v>
       </c>
@@ -9759,7 +9765,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="15">
+    <row r="75" spans="1:31" ht="15" hidden="1">
       <c r="A75" s="42" t="s">
         <v>59</v>
       </c>
@@ -9832,7 +9838,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="15">
+    <row r="76" spans="1:31" ht="15" hidden="1">
       <c r="A76" s="42" t="s">
         <v>59</v>
       </c>
@@ -9911,7 +9917,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="15">
+    <row r="77" spans="1:31" ht="15" hidden="1">
       <c r="A77" s="42" t="s">
         <v>59</v>
       </c>
@@ -9984,7 +9990,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="15">
+    <row r="78" spans="1:31" ht="15" hidden="1">
       <c r="A78" s="42" t="s">
         <v>59</v>
       </c>
@@ -10057,7 +10063,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="15">
+    <row r="79" spans="1:31" ht="15" hidden="1">
       <c r="A79" s="42" t="s">
         <v>59</v>
       </c>
@@ -10130,7 +10136,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="15">
+    <row r="80" spans="1:31" ht="15" hidden="1">
       <c r="A80" s="42" t="s">
         <v>59</v>
       </c>
@@ -10209,7 +10215,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="15">
+    <row r="81" spans="1:31" ht="15" hidden="1">
       <c r="A81" s="42" t="s">
         <v>59</v>
       </c>
@@ -10288,7 +10294,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="15">
+    <row r="82" spans="1:31" ht="15" hidden="1">
       <c r="A82" s="42" t="s">
         <v>59</v>
       </c>
@@ -10367,7 +10373,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="15">
+    <row r="83" spans="1:31" ht="15" hidden="1">
       <c r="A83" s="42" t="s">
         <v>59</v>
       </c>
@@ -10441,7 +10447,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="15">
+    <row r="84" spans="1:31" ht="15" hidden="1">
       <c r="A84" s="42" t="s">
         <v>59</v>
       </c>
@@ -10517,7 +10523,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="15">
+    <row r="85" spans="1:31" ht="15" hidden="1">
       <c r="A85" s="42" t="s">
         <v>59</v>
       </c>
@@ -10666,7 +10672,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="15">
+    <row r="87" spans="1:31" ht="15" hidden="1">
       <c r="A87" s="42" t="s">
         <v>59</v>
       </c>
@@ -10742,7 +10748,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="15">
+    <row r="88" spans="1:31" ht="15" hidden="1">
       <c r="A88" s="42" t="s">
         <v>59</v>
       </c>
@@ -10818,7 +10824,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="15">
+    <row r="89" spans="1:31" ht="15" hidden="1">
       <c r="A89" s="42" t="s">
         <v>59</v>
       </c>
@@ -10894,7 +10900,7 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="15">
+    <row r="90" spans="1:31" ht="15" hidden="1">
       <c r="A90" s="42" t="s">
         <v>638</v>
       </c>
@@ -10967,7 +10973,7 @@
       <c r="AD90"/>
       <c r="AE90"/>
     </row>
-    <row r="91" spans="1:31" ht="15">
+    <row r="91" spans="1:31" ht="15" hidden="1">
       <c r="A91" s="42" t="s">
         <v>640</v>
       </c>
@@ -11039,7 +11045,7 @@
       <c r="AD91"/>
       <c r="AE91"/>
     </row>
-    <row r="92" spans="1:31" ht="15">
+    <row r="92" spans="1:31" ht="15" hidden="1">
       <c r="A92" s="42" t="s">
         <v>642</v>
       </c>
@@ -11111,7 +11117,7 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="15">
+    <row r="93" spans="1:31" ht="15" hidden="1">
       <c r="A93" s="42" t="s">
         <v>644</v>
       </c>
@@ -11183,7 +11189,7 @@
       <c r="AD93"/>
       <c r="AE93"/>
     </row>
-    <row r="94" spans="1:31" ht="15">
+    <row r="94" spans="1:31" ht="15" hidden="1">
       <c r="A94" s="42" t="s">
         <v>638</v>
       </c>
@@ -11255,7 +11261,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="15">
+    <row r="95" spans="1:31" ht="15" hidden="1">
       <c r="A95" s="42" t="s">
         <v>642</v>
       </c>
@@ -11327,7 +11333,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="15">
+    <row r="96" spans="1:31" ht="15" hidden="1">
       <c r="A96" s="42" t="s">
         <v>644</v>
       </c>
@@ -11503,11 +11509,11 @@
         <v>159</v>
       </c>
       <c r="J98" s="46">
-        <v>625</v>
+        <v>525</v>
       </c>
       <c r="K98" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2937.5</v>
+        <v>3037.5</v>
       </c>
       <c r="L98" s="106">
         <v>6400</v>
@@ -11574,11 +11580,11 @@
         <v>159</v>
       </c>
       <c r="J99" s="46">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="K99" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3237.5</v>
+        <v>3487.5</v>
       </c>
       <c r="L99" s="106">
         <v>7300</v>
@@ -11613,7 +11619,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="15">
+    <row r="100" spans="1:31" ht="15" hidden="1">
       <c r="A100" s="42" t="s">
         <v>61</v>
       </c>
@@ -11682,7 +11688,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="15">
+    <row r="101" spans="1:31" ht="15" hidden="1">
       <c r="A101" s="42" t="s">
         <v>61</v>
       </c>
@@ -11754,7 +11760,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="15">
+    <row r="102" spans="1:31" ht="15" hidden="1">
       <c r="A102" s="42" t="s">
         <v>64</v>
       </c>
@@ -11823,7 +11829,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="15">
+    <row r="103" spans="1:31" ht="15" hidden="1">
       <c r="A103" s="42" t="s">
         <v>64</v>
       </c>
@@ -11895,7 +11901,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="15">
+    <row r="104" spans="1:31" ht="15" hidden="1">
       <c r="A104" s="42" t="s">
         <v>66</v>
       </c>
@@ -11964,7 +11970,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="15">
+    <row r="105" spans="1:31" ht="15" hidden="1">
       <c r="A105" s="42" t="s">
         <v>66</v>
       </c>
@@ -12036,7 +12042,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="15">
+    <row r="106" spans="1:31" ht="15" hidden="1">
       <c r="A106" s="42" t="s">
         <v>70</v>
       </c>
@@ -12105,7 +12111,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="15">
+    <row r="107" spans="1:31" ht="15" hidden="1">
       <c r="A107" s="42" t="s">
         <v>70</v>
       </c>
@@ -12177,7 +12183,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="15">
+    <row r="108" spans="1:31" ht="15" hidden="1">
       <c r="A108" s="42" t="s">
         <v>72</v>
       </c>
@@ -12246,7 +12252,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="15">
+    <row r="109" spans="1:31" ht="15" hidden="1">
       <c r="A109" s="42" t="s">
         <v>72</v>
       </c>
@@ -12318,7 +12324,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="15">
+    <row r="110" spans="1:31" ht="15" hidden="1">
       <c r="A110" s="42" t="s">
         <v>75</v>
       </c>
@@ -12387,7 +12393,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="15">
+    <row r="111" spans="1:31" ht="15" hidden="1">
       <c r="A111" s="42" t="s">
         <v>75</v>
       </c>
@@ -12459,7 +12465,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="15">
+    <row r="112" spans="1:31" ht="15" hidden="1">
       <c r="A112" s="42" t="s">
         <v>77</v>
       </c>
@@ -12526,7 +12532,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="15">
+    <row r="113" spans="1:31" ht="15" hidden="1">
       <c r="A113" s="42" t="s">
         <v>77</v>
       </c>
@@ -12596,7 +12602,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="15">
+    <row r="114" spans="1:31" ht="15" hidden="1">
       <c r="A114" s="42" t="s">
         <v>80</v>
       </c>
@@ -12663,7 +12669,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="15">
+    <row r="115" spans="1:31" ht="15" hidden="1">
       <c r="A115" s="42" t="s">
         <v>80</v>
       </c>
@@ -12733,7 +12739,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="15">
+    <row r="116" spans="1:31" ht="15" hidden="1">
       <c r="A116" s="42" t="s">
         <v>82</v>
       </c>
@@ -12803,7 +12809,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="15">
+    <row r="117" spans="1:31" ht="15" hidden="1">
       <c r="A117" s="42" t="s">
         <v>82</v>
       </c>
@@ -12876,7 +12882,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="15">
+    <row r="118" spans="1:31" ht="15" hidden="1">
       <c r="A118" s="42" t="s">
         <v>84</v>
       </c>
@@ -12946,7 +12952,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="15">
+    <row r="119" spans="1:31" ht="15" hidden="1">
       <c r="A119" s="42" t="s">
         <v>84</v>
       </c>
@@ -13019,7 +13025,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="15">
+    <row r="120" spans="1:31" ht="15" hidden="1">
       <c r="A120" s="42" t="s">
         <v>86</v>
       </c>
@@ -13089,7 +13095,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="15">
+    <row r="121" spans="1:31" ht="15" hidden="1">
       <c r="A121" s="42" t="s">
         <v>86</v>
       </c>
@@ -13162,7 +13168,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="15">
+    <row r="122" spans="1:31" ht="15" hidden="1">
       <c r="A122" s="42" t="s">
         <v>88</v>
       </c>
@@ -13232,7 +13238,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="15">
+    <row r="123" spans="1:31" ht="15" hidden="1">
       <c r="A123" s="42" t="s">
         <v>88</v>
       </c>
@@ -13305,7 +13311,7 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="15">
+    <row r="124" spans="1:31" ht="15" hidden="1">
       <c r="A124" s="42" t="s">
         <v>90</v>
       </c>
@@ -13375,7 +13381,7 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="15">
+    <row r="125" spans="1:31" ht="15" hidden="1">
       <c r="A125" s="42" t="s">
         <v>90</v>
       </c>
@@ -13448,7 +13454,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="15">
+    <row r="126" spans="1:31" ht="15" hidden="1">
       <c r="A126" s="42" t="s">
         <v>92</v>
       </c>
@@ -13518,7 +13524,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="15">
+    <row r="127" spans="1:31" ht="15" hidden="1">
       <c r="A127" s="42" t="s">
         <v>92</v>
       </c>
@@ -13591,7 +13597,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="15">
+    <row r="128" spans="1:31" ht="15" hidden="1">
       <c r="A128" s="42" t="s">
         <v>94</v>
       </c>
@@ -13661,7 +13667,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="15">
+    <row r="129" spans="1:31" ht="15" hidden="1">
       <c r="A129" s="42" t="s">
         <v>94</v>
       </c>
@@ -13734,7 +13740,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="15">
+    <row r="130" spans="1:31" ht="15" hidden="1">
       <c r="A130" s="42" t="s">
         <v>96</v>
       </c>
@@ -13802,7 +13808,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="15">
+    <row r="131" spans="1:31" ht="15" hidden="1">
       <c r="A131" s="42" t="s">
         <v>96</v>
       </c>
@@ -13873,7 +13879,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="15">
+    <row r="132" spans="1:31" ht="15" hidden="1">
       <c r="A132" s="42" t="s">
         <v>98</v>
       </c>
@@ -13941,7 +13947,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="15">
+    <row r="133" spans="1:31" ht="15" hidden="1">
       <c r="A133" s="79" t="s">
         <v>98</v>
       </c>
@@ -14011,7 +14017,7 @@
       <c r="AC133" s="46"/>
       <c r="AD133" s="46"/>
     </row>
-    <row r="134" spans="1:31" ht="15">
+    <row r="134" spans="1:31" ht="15" hidden="1">
       <c r="A134" s="79" t="s">
         <v>100</v>
       </c>
@@ -14078,7 +14084,7 @@
       <c r="AC134" s="46"/>
       <c r="AD134" s="46"/>
     </row>
-    <row r="135" spans="1:31" ht="15">
+    <row r="135" spans="1:31" ht="15" hidden="1">
       <c r="A135" s="79" t="s">
         <v>100</v>
       </c>
@@ -14148,7 +14154,7 @@
       <c r="AC135" s="46"/>
       <c r="AD135" s="44"/>
     </row>
-    <row r="136" spans="1:31" ht="15">
+    <row r="136" spans="1:31" ht="15" hidden="1">
       <c r="A136" s="79" t="s">
         <v>102</v>
       </c>
@@ -14217,7 +14223,7 @@
       <c r="AC136" s="46"/>
       <c r="AD136" s="44"/>
     </row>
-    <row r="137" spans="1:31" ht="15">
+    <row r="137" spans="1:31" ht="15" hidden="1">
       <c r="A137" s="79" t="s">
         <v>102</v>
       </c>
@@ -14289,7 +14295,7 @@
       <c r="AC137" s="46"/>
       <c r="AD137" s="44"/>
     </row>
-    <row r="138" spans="1:31" ht="15">
+    <row r="138" spans="1:31" ht="15" hidden="1">
       <c r="A138" s="79" t="s">
         <v>104</v>
       </c>
@@ -14358,7 +14364,7 @@
       <c r="AC138" s="46"/>
       <c r="AD138" s="44"/>
     </row>
-    <row r="139" spans="1:31" ht="15">
+    <row r="139" spans="1:31" ht="15" hidden="1">
       <c r="A139" s="79" t="s">
         <v>104</v>
       </c>
@@ -14431,7 +14437,7 @@
       <c r="AD139" s="44"/>
       <c r="AE139" s="16"/>
     </row>
-    <row r="140" spans="1:31" ht="15">
+    <row r="140" spans="1:31" ht="15" hidden="1">
       <c r="A140" s="79" t="s">
         <v>106</v>
       </c>
@@ -14501,7 +14507,7 @@
       <c r="AD140" s="7"/>
       <c r="AE140" s="16"/>
     </row>
-    <row r="141" spans="1:31" ht="15">
+    <row r="141" spans="1:31" ht="15" hidden="1">
       <c r="A141" s="79" t="s">
         <v>106</v>
       </c>
@@ -14574,7 +14580,7 @@
       <c r="AD141" s="7"/>
       <c r="AE141" s="16"/>
     </row>
-    <row r="142" spans="1:31" ht="15">
+    <row r="142" spans="1:31" ht="15" hidden="1">
       <c r="A142" s="79" t="s">
         <v>108</v>
       </c>
@@ -14643,7 +14649,7 @@
       <c r="AC142" s="46"/>
       <c r="AD142" s="7"/>
     </row>
-    <row r="143" spans="1:31" ht="15">
+    <row r="143" spans="1:31" ht="15" hidden="1">
       <c r="A143" s="79" t="s">
         <v>108</v>
       </c>
@@ -14715,7 +14721,7 @@
       <c r="AC143" s="46"/>
       <c r="AD143" s="7"/>
     </row>
-    <row r="144" spans="1:31" ht="15">
+    <row r="144" spans="1:31" ht="15" hidden="1">
       <c r="A144" s="79" t="s">
         <v>110</v>
       </c>
@@ -14784,7 +14790,7 @@
       <c r="AC144" s="46"/>
       <c r="AD144" s="7"/>
     </row>
-    <row r="145" spans="1:31" ht="15">
+    <row r="145" spans="1:31" ht="15" hidden="1">
       <c r="A145" s="79" t="s">
         <v>110</v>
       </c>
@@ -14856,7 +14862,7 @@
       <c r="AC145" s="46"/>
       <c r="AD145" s="7"/>
     </row>
-    <row r="146" spans="1:31" ht="15">
+    <row r="146" spans="1:31" ht="15" hidden="1">
       <c r="A146" s="85" t="s">
         <v>112</v>
       </c>
@@ -14925,7 +14931,7 @@
       <c r="AC146" s="46"/>
       <c r="AD146" s="44"/>
     </row>
-    <row r="147" spans="1:31" ht="15">
+    <row r="147" spans="1:31" ht="15" hidden="1">
       <c r="A147" s="42" t="s">
         <v>112</v>
       </c>
@@ -14997,7 +15003,7 @@
       <c r="AD147"/>
       <c r="AE147"/>
     </row>
-    <row r="148" spans="1:31" ht="15">
+    <row r="148" spans="1:31" ht="15" hidden="1">
       <c r="A148" s="42" t="s">
         <v>114</v>
       </c>
@@ -15064,7 +15070,7 @@
       <c r="AD148"/>
       <c r="AE148"/>
     </row>
-    <row r="149" spans="1:31" ht="15">
+    <row r="149" spans="1:31" ht="15" hidden="1">
       <c r="A149" s="42" t="s">
         <v>114</v>
       </c>
@@ -15134,7 +15140,7 @@
       <c r="AD149"/>
       <c r="AE149"/>
     </row>
-    <row r="150" spans="1:31" ht="15">
+    <row r="150" spans="1:31" ht="15" hidden="1">
       <c r="A150" s="42" t="s">
         <v>116</v>
       </c>
@@ -15201,7 +15207,7 @@
       <c r="AD150"/>
       <c r="AE150"/>
     </row>
-    <row r="151" spans="1:31" ht="15">
+    <row r="151" spans="1:31" ht="15" hidden="1">
       <c r="A151" s="42" t="s">
         <v>116</v>
       </c>
@@ -15271,7 +15277,7 @@
       <c r="AD151"/>
       <c r="AE151"/>
     </row>
-    <row r="152" spans="1:31" ht="15">
+    <row r="152" spans="1:31" ht="15" hidden="1">
       <c r="A152" s="42" t="s">
         <v>118</v>
       </c>
@@ -15339,7 +15345,7 @@
       <c r="AD152"/>
       <c r="AE152"/>
     </row>
-    <row r="153" spans="1:31" ht="15">
+    <row r="153" spans="1:31" ht="15" hidden="1">
       <c r="A153" s="42" t="s">
         <v>118</v>
       </c>
@@ -15410,7 +15416,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="15">
+    <row r="154" spans="1:31" ht="15" hidden="1">
       <c r="A154" s="42" t="s">
         <v>123</v>
       </c>
@@ -15482,7 +15488,7 @@
       <c r="AC154" s="46"/>
       <c r="AD154" s="46"/>
     </row>
-    <row r="155" spans="1:31" ht="15">
+    <row r="155" spans="1:31" ht="15" hidden="1">
       <c r="A155" s="42" t="s">
         <v>123</v>
       </c>
@@ -15554,7 +15560,7 @@
       <c r="AC155" s="46"/>
       <c r="AD155" s="44"/>
     </row>
-    <row r="156" spans="1:31" ht="15">
+    <row r="156" spans="1:31" ht="15" hidden="1">
       <c r="A156" s="42" t="s">
         <v>123</v>
       </c>
@@ -15626,7 +15632,7 @@
       <c r="AC156" s="46"/>
       <c r="AD156" s="44"/>
     </row>
-    <row r="157" spans="1:31" ht="15">
+    <row r="157" spans="1:31" ht="15" hidden="1">
       <c r="A157" s="42" t="s">
         <v>123</v>
       </c>
@@ -15698,7 +15704,7 @@
       <c r="AC157" s="46"/>
       <c r="AD157" s="7"/>
     </row>
-    <row r="158" spans="1:31" ht="15">
+    <row r="158" spans="1:31" ht="15" hidden="1">
       <c r="A158" s="79" t="s">
         <v>123</v>
       </c>
@@ -15770,7 +15776,7 @@
       <c r="AC158" s="46"/>
       <c r="AD158" s="7"/>
     </row>
-    <row r="159" spans="1:31" ht="15">
+    <row r="159" spans="1:31" ht="15" hidden="1">
       <c r="A159" s="79" t="s">
         <v>123</v>
       </c>
@@ -15843,7 +15849,7 @@
       <c r="AC159" s="46"/>
       <c r="AD159" s="7"/>
     </row>
-    <row r="160" spans="1:31" ht="15">
+    <row r="160" spans="1:31" ht="15" hidden="1">
       <c r="A160" s="79" t="s">
         <v>123</v>
       </c>
@@ -15915,7 +15921,7 @@
       <c r="AC160" s="46"/>
       <c r="AD160" s="7"/>
     </row>
-    <row r="161" spans="1:30" ht="15">
+    <row r="161" spans="1:30" ht="15" hidden="1">
       <c r="A161" s="79" t="s">
         <v>123</v>
       </c>
@@ -15987,7 +15993,7 @@
       <c r="AC161" s="46"/>
       <c r="AD161" s="46"/>
     </row>
-    <row r="162" spans="1:30" ht="15">
+    <row r="162" spans="1:30" ht="15" hidden="1">
       <c r="A162" s="79" t="s">
         <v>123</v>
       </c>
@@ -16059,7 +16065,7 @@
       <c r="AC162" s="46"/>
       <c r="AD162" s="7"/>
     </row>
-    <row r="163" spans="1:30" ht="15">
+    <row r="163" spans="1:30" ht="15" hidden="1">
       <c r="A163" s="79" t="s">
         <v>123</v>
       </c>
@@ -16131,7 +16137,7 @@
       <c r="AC163" s="46"/>
       <c r="AD163" s="46"/>
     </row>
-    <row r="164" spans="1:30" ht="15">
+    <row r="164" spans="1:30" ht="15" hidden="1">
       <c r="A164" s="79" t="s">
         <v>123</v>
       </c>
@@ -16203,7 +16209,7 @@
       <c r="AC164" s="46"/>
       <c r="AD164" s="44"/>
     </row>
-    <row r="165" spans="1:30" ht="15">
+    <row r="165" spans="1:30" ht="15" hidden="1">
       <c r="A165" s="79" t="s">
         <v>123</v>
       </c>
@@ -16275,7 +16281,7 @@
       <c r="AC165" s="46"/>
       <c r="AD165" s="44"/>
     </row>
-    <row r="166" spans="1:30" ht="15">
+    <row r="166" spans="1:30" ht="15" hidden="1">
       <c r="A166" s="79" t="s">
         <v>123</v>
       </c>
@@ -16347,7 +16353,7 @@
       <c r="AC166" s="46"/>
       <c r="AD166" s="44"/>
     </row>
-    <row r="167" spans="1:30" ht="15">
+    <row r="167" spans="1:30" ht="15" hidden="1">
       <c r="A167" s="85" t="s">
         <v>123</v>
       </c>
@@ -16419,7 +16425,7 @@
       <c r="AC167" s="46"/>
       <c r="AD167" s="44"/>
     </row>
-    <row r="168" spans="1:30" ht="15">
+    <row r="168" spans="1:30" ht="15" hidden="1">
       <c r="A168" s="79" t="s">
         <v>125</v>
       </c>
@@ -16491,7 +16497,7 @@
       <c r="AC168" s="46"/>
       <c r="AD168" s="44"/>
     </row>
-    <row r="169" spans="1:30" ht="15">
+    <row r="169" spans="1:30" ht="15" hidden="1">
       <c r="A169" s="79" t="s">
         <v>125</v>
       </c>
@@ -16563,7 +16569,7 @@
       <c r="AC169" s="46"/>
       <c r="AD169" s="7"/>
     </row>
-    <row r="170" spans="1:30" ht="15">
+    <row r="170" spans="1:30" ht="15" hidden="1">
       <c r="A170" s="79" t="s">
         <v>125</v>
       </c>
@@ -16635,7 +16641,7 @@
       <c r="AC170" s="46"/>
       <c r="AD170" s="7"/>
     </row>
-    <row r="171" spans="1:30" ht="15">
+    <row r="171" spans="1:30" ht="15" hidden="1">
       <c r="A171" s="79" t="s">
         <v>125</v>
       </c>
@@ -16706,7 +16712,7 @@
       <c r="AB171" s="73"/>
       <c r="AD171" s="16"/>
     </row>
-    <row r="172" spans="1:30" ht="15">
+    <row r="172" spans="1:30" ht="15" hidden="1">
       <c r="A172" s="79" t="s">
         <v>125</v>
       </c>
@@ -16778,7 +16784,7 @@
       <c r="AC172" s="44"/>
       <c r="AD172" s="44"/>
     </row>
-    <row r="173" spans="1:30" ht="15">
+    <row r="173" spans="1:30" ht="15" hidden="1">
       <c r="A173" s="79" t="s">
         <v>125</v>
       </c>
@@ -16851,7 +16857,7 @@
       <c r="AC173" s="44"/>
       <c r="AD173" s="44"/>
     </row>
-    <row r="174" spans="1:30" ht="15">
+    <row r="174" spans="1:30" ht="15" hidden="1">
       <c r="A174" s="79" t="s">
         <v>125</v>
       </c>
@@ -16923,7 +16929,7 @@
       <c r="AC174" s="44"/>
       <c r="AD174" s="44"/>
     </row>
-    <row r="175" spans="1:30" ht="15">
+    <row r="175" spans="1:30" ht="15" hidden="1">
       <c r="A175" s="79" t="s">
         <v>125</v>
       </c>
@@ -16995,7 +17001,7 @@
       <c r="AC175" s="44"/>
       <c r="AD175" s="44"/>
     </row>
-    <row r="176" spans="1:30" ht="15">
+    <row r="176" spans="1:30" ht="15" hidden="1">
       <c r="A176" s="79" t="s">
         <v>125</v>
       </c>
@@ -17067,7 +17073,7 @@
       <c r="AC176" s="44"/>
       <c r="AD176" s="44"/>
     </row>
-    <row r="177" spans="1:30" ht="15">
+    <row r="177" spans="1:30" ht="15" hidden="1">
       <c r="A177" s="79" t="s">
         <v>125</v>
       </c>
@@ -17139,7 +17145,7 @@
       <c r="AC177" s="44"/>
       <c r="AD177" s="44"/>
     </row>
-    <row r="178" spans="1:30" ht="15">
+    <row r="178" spans="1:30" ht="15" hidden="1">
       <c r="A178" s="79" t="s">
         <v>125</v>
       </c>
@@ -17211,7 +17217,7 @@
       <c r="AC178" s="44"/>
       <c r="AD178" s="44"/>
     </row>
-    <row r="179" spans="1:30" ht="15">
+    <row r="179" spans="1:30" ht="15" hidden="1">
       <c r="A179" s="79" t="s">
         <v>125</v>
       </c>
@@ -17283,7 +17289,7 @@
       <c r="AC179" s="44"/>
       <c r="AD179" s="44"/>
     </row>
-    <row r="180" spans="1:30" ht="15">
+    <row r="180" spans="1:30" ht="15" hidden="1">
       <c r="A180" s="79" t="s">
         <v>125</v>
       </c>
@@ -17355,7 +17361,7 @@
       <c r="AC180" s="44"/>
       <c r="AD180" s="44"/>
     </row>
-    <row r="181" spans="1:30" ht="15">
+    <row r="181" spans="1:30" ht="15" hidden="1">
       <c r="A181" s="79" t="s">
         <v>125</v>
       </c>
@@ -17427,7 +17433,7 @@
       <c r="AC181" s="44"/>
       <c r="AD181" s="44"/>
     </row>
-    <row r="182" spans="1:30" ht="15">
+    <row r="182" spans="1:30" ht="15" hidden="1">
       <c r="A182" s="79" t="s">
         <v>127</v>
       </c>
@@ -17499,7 +17505,7 @@
       <c r="AC182" s="44"/>
       <c r="AD182" s="44"/>
     </row>
-    <row r="183" spans="1:30" ht="15">
+    <row r="183" spans="1:30" ht="15" hidden="1">
       <c r="A183" s="79" t="s">
         <v>127</v>
       </c>
@@ -17571,7 +17577,7 @@
       <c r="AC183" s="44"/>
       <c r="AD183" s="44"/>
     </row>
-    <row r="184" spans="1:30" ht="15">
+    <row r="184" spans="1:30" ht="15" hidden="1">
       <c r="A184" s="79" t="s">
         <v>127</v>
       </c>
@@ -17643,7 +17649,7 @@
       <c r="AC184" s="44"/>
       <c r="AD184" s="44"/>
     </row>
-    <row r="185" spans="1:30" ht="15">
+    <row r="185" spans="1:30" ht="15" hidden="1">
       <c r="A185" s="79" t="s">
         <v>127</v>
       </c>
@@ -17715,7 +17721,7 @@
       <c r="AC185" s="44"/>
       <c r="AD185" s="44"/>
     </row>
-    <row r="186" spans="1:30" ht="15">
+    <row r="186" spans="1:30" ht="15" hidden="1">
       <c r="A186" s="79" t="s">
         <v>127</v>
       </c>
@@ -17787,7 +17793,7 @@
       <c r="AC186" s="44"/>
       <c r="AD186" s="44"/>
     </row>
-    <row r="187" spans="1:30" ht="15">
+    <row r="187" spans="1:30" ht="15" hidden="1">
       <c r="A187" s="79" t="s">
         <v>127</v>
       </c>
@@ -17860,7 +17866,7 @@
       <c r="AC187" s="44"/>
       <c r="AD187" s="44"/>
     </row>
-    <row r="188" spans="1:30" ht="15">
+    <row r="188" spans="1:30" ht="15" hidden="1">
       <c r="A188" s="79" t="s">
         <v>127</v>
       </c>
@@ -17932,7 +17938,7 @@
       <c r="AC188" s="44"/>
       <c r="AD188" s="44"/>
     </row>
-    <row r="189" spans="1:30" ht="15">
+    <row r="189" spans="1:30" ht="15" hidden="1">
       <c r="A189" s="79" t="s">
         <v>127</v>
       </c>
@@ -18004,7 +18010,7 @@
       <c r="AC189" s="44"/>
       <c r="AD189" s="44"/>
     </row>
-    <row r="190" spans="1:30" ht="15">
+    <row r="190" spans="1:30" ht="15" hidden="1">
       <c r="A190" s="79" t="s">
         <v>127</v>
       </c>
@@ -18076,7 +18082,7 @@
       <c r="AC190" s="44"/>
       <c r="AD190" s="44"/>
     </row>
-    <row r="191" spans="1:30" ht="15">
+    <row r="191" spans="1:30" ht="15" hidden="1">
       <c r="A191" s="79" t="s">
         <v>127</v>
       </c>
@@ -18148,7 +18154,7 @@
       <c r="AC191" s="44"/>
       <c r="AD191" s="44"/>
     </row>
-    <row r="192" spans="1:30" ht="15">
+    <row r="192" spans="1:30" ht="15" hidden="1">
       <c r="A192" s="79" t="s">
         <v>127</v>
       </c>
@@ -18220,7 +18226,7 @@
       <c r="AC192" s="44"/>
       <c r="AD192" s="44"/>
     </row>
-    <row r="193" spans="1:30" ht="15">
+    <row r="193" spans="1:30" ht="15" hidden="1">
       <c r="A193" s="79" t="s">
         <v>127</v>
       </c>
@@ -18292,7 +18298,7 @@
       <c r="AC193" s="44"/>
       <c r="AD193" s="44"/>
     </row>
-    <row r="194" spans="1:30" ht="15">
+    <row r="194" spans="1:30" ht="15" hidden="1">
       <c r="A194" s="79" t="s">
         <v>127</v>
       </c>
@@ -18364,7 +18370,7 @@
       <c r="AC194" s="44"/>
       <c r="AD194" s="44"/>
     </row>
-    <row r="195" spans="1:30" ht="15">
+    <row r="195" spans="1:30" ht="15" hidden="1">
       <c r="A195" s="79" t="s">
         <v>127</v>
       </c>
@@ -18434,7 +18440,7 @@
       <c r="AC195" s="44"/>
       <c r="AD195" s="44"/>
     </row>
-    <row r="196" spans="1:30" ht="15">
+    <row r="196" spans="1:30" ht="15" hidden="1">
       <c r="A196" s="79" t="s">
         <v>165</v>
       </c>
@@ -18513,7 +18519,7 @@
       <c r="AC196" s="44"/>
       <c r="AD196" s="44"/>
     </row>
-    <row r="197" spans="1:30" ht="15">
+    <row r="197" spans="1:30" ht="15" hidden="1">
       <c r="A197" s="79" t="s">
         <v>167</v>
       </c>
@@ -18592,7 +18598,7 @@
       <c r="AC197" s="44"/>
       <c r="AD197" s="44"/>
     </row>
-    <row r="198" spans="1:30" ht="15">
+    <row r="198" spans="1:30" ht="15" hidden="1">
       <c r="A198" s="79" t="s">
         <v>169</v>
       </c>
@@ -18671,7 +18677,7 @@
       <c r="AC198" s="44"/>
       <c r="AD198" s="44"/>
     </row>
-    <row r="199" spans="1:30" ht="15">
+    <row r="199" spans="1:30" ht="15" hidden="1">
       <c r="A199" s="85" t="s">
         <v>1</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1571" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DEC5E4B-8A2E-4F05-A5E9-1E2C0F05877A}"/>
+  <xr:revisionPtr revIDLastSave="1573" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AF8F544-F9F4-4DD9-B998-A7A0AA596D43}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView minimized="1" xWindow="29535" yWindow="735" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="accessoryList" sheetId="5" r:id="rId6"/>
     <sheet name="Data Lists" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3334,9 +3334,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
   <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
-    <filterColumn colId="8">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Open House Special"/>
+        <filter val="Beltone RIE Digital Envision 6 62S-DRWC"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4652,7 +4652,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="15">
+    <row r="5" spans="1:31" ht="15" hidden="1">
       <c r="A5" s="42" t="s">
         <v>130</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="15">
+    <row r="10" spans="1:31" ht="15" hidden="1">
       <c r="A10" s="42" t="s">
         <v>132</v>
       </c>
@@ -5347,7 +5347,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="15">
+    <row r="15" spans="1:31" ht="15" hidden="1">
       <c r="A15" s="42" t="s">
         <v>134</v>
       </c>
@@ -8417,7 +8417,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="15">
+    <row r="57" spans="1:32" ht="15" hidden="1">
       <c r="A57" s="42" t="s">
         <v>53</v>
       </c>
@@ -8634,7 +8634,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="15" hidden="1">
+    <row r="60" spans="1:32" ht="15">
       <c r="A60" s="42" t="s">
         <v>57</v>
       </c>
@@ -8712,7 +8712,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="15" hidden="1">
+    <row r="61" spans="1:32" ht="15">
       <c r="A61" s="42" t="s">
         <v>57</v>
       </c>
@@ -8791,7 +8791,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="15" hidden="1">
+    <row r="62" spans="1:32" ht="15">
       <c r="A62" s="42" t="s">
         <v>57</v>
       </c>
@@ -8870,7 +8870,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="15" hidden="1">
+    <row r="63" spans="1:32" ht="15">
       <c r="A63" s="42" t="s">
         <v>57</v>
       </c>
@@ -8949,7 +8949,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="15" hidden="1">
+    <row r="64" spans="1:32" ht="15">
       <c r="A64" s="42" t="s">
         <v>57</v>
       </c>
@@ -9025,7 +9025,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15" hidden="1">
+    <row r="65" spans="1:31" ht="15">
       <c r="A65" s="42" t="s">
         <v>57</v>
       </c>
@@ -9101,7 +9101,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15" hidden="1">
+    <row r="66" spans="1:31" ht="15">
       <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
@@ -9177,7 +9177,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15" hidden="1">
+    <row r="67" spans="1:31" ht="15">
       <c r="A67" s="42" t="s">
         <v>57</v>
       </c>
@@ -9253,7 +9253,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15" hidden="1">
+    <row r="68" spans="1:31" ht="15">
       <c r="A68" s="42" t="s">
         <v>57</v>
       </c>
@@ -9329,7 +9329,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15" hidden="1">
+    <row r="69" spans="1:31" ht="15">
       <c r="A69" s="42" t="s">
         <v>57</v>
       </c>
@@ -9399,7 +9399,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15" hidden="1">
+    <row r="70" spans="1:31" ht="15">
       <c r="A70" s="42" t="s">
         <v>57</v>
       </c>
@@ -9472,7 +9472,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15" hidden="1">
+    <row r="71" spans="1:31" ht="15">
       <c r="A71" s="42" t="s">
         <v>57</v>
       </c>
@@ -9545,7 +9545,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15" hidden="1">
+    <row r="72" spans="1:31" ht="15">
       <c r="A72" s="42" t="s">
         <v>57</v>
       </c>
@@ -9618,7 +9618,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15" hidden="1">
+    <row r="73" spans="1:31" ht="15">
       <c r="A73" s="42" t="s">
         <v>57</v>
       </c>
@@ -10599,7 +10599,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="15">
+    <row r="86" spans="1:31" ht="15" hidden="1">
       <c r="A86" s="42" t="s">
         <v>59</v>
       </c>
@@ -11406,7 +11406,7 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="15">
+    <row r="97" spans="1:31" ht="15" hidden="1">
       <c r="A97" s="42" t="s">
         <v>638</v>
       </c>
@@ -11477,7 +11477,7 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="15">
+    <row r="98" spans="1:31" ht="15" hidden="1">
       <c r="A98" s="42" t="s">
         <v>642</v>
       </c>
@@ -11548,7 +11548,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="15">
+    <row r="99" spans="1:31" ht="15" hidden="1">
       <c r="A99" s="42" t="s">
         <v>644</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1573" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AF8F544-F9F4-4DD9-B998-A7A0AA596D43}"/>
+  <xr:revisionPtr revIDLastSave="1576" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25B2A292-261B-48F2-8ED2-08D123E3FF90}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="29535" yWindow="735" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3336,7 +3336,7 @@
   <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Beltone RIE Digital Envision 6 62S-DRWC"/>
+        <filter val="Beltone RIE Digital Illuminate 9 62S-DRWC"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8634,7 +8634,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="15">
+    <row r="60" spans="1:32" ht="15" hidden="1">
       <c r="A60" s="42" t="s">
         <v>57</v>
       </c>
@@ -8712,7 +8712,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="15">
+    <row r="61" spans="1:32" ht="15" hidden="1">
       <c r="A61" s="42" t="s">
         <v>57</v>
       </c>
@@ -8791,7 +8791,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="15">
+    <row r="62" spans="1:32" ht="15" hidden="1">
       <c r="A62" s="42" t="s">
         <v>57</v>
       </c>
@@ -8870,7 +8870,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="15">
+    <row r="63" spans="1:32" ht="15" hidden="1">
       <c r="A63" s="42" t="s">
         <v>57</v>
       </c>
@@ -8949,7 +8949,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="15">
+    <row r="64" spans="1:32" ht="15" hidden="1">
       <c r="A64" s="42" t="s">
         <v>57</v>
       </c>
@@ -9025,7 +9025,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15">
+    <row r="65" spans="1:31" ht="15" hidden="1">
       <c r="A65" s="42" t="s">
         <v>57</v>
       </c>
@@ -9101,7 +9101,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15">
+    <row r="66" spans="1:31" ht="15" hidden="1">
       <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
@@ -9177,7 +9177,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15">
+    <row r="67" spans="1:31" ht="15" hidden="1">
       <c r="A67" s="42" t="s">
         <v>57</v>
       </c>
@@ -9253,7 +9253,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15">
+    <row r="68" spans="1:31" ht="15" hidden="1">
       <c r="A68" s="42" t="s">
         <v>57</v>
       </c>
@@ -9329,7 +9329,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15">
+    <row r="69" spans="1:31" ht="15" hidden="1">
       <c r="A69" s="42" t="s">
         <v>57</v>
       </c>
@@ -9399,7 +9399,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15">
+    <row r="70" spans="1:31" ht="15" hidden="1">
       <c r="A70" s="42" t="s">
         <v>57</v>
       </c>
@@ -9472,7 +9472,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15">
+    <row r="71" spans="1:31" ht="15" hidden="1">
       <c r="A71" s="42" t="s">
         <v>57</v>
       </c>
@@ -9545,7 +9545,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15">
+    <row r="72" spans="1:31" ht="15" hidden="1">
       <c r="A72" s="42" t="s">
         <v>57</v>
       </c>
@@ -9618,7 +9618,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15">
+    <row r="73" spans="1:31" ht="15" hidden="1">
       <c r="A73" s="42" t="s">
         <v>57</v>
       </c>
@@ -9692,7 +9692,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="15">
+    <row r="74" spans="1:31" ht="15" hidden="1">
       <c r="A74" s="42" t="s">
         <v>57</v>
       </c>
@@ -11117,7 +11117,7 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="15" hidden="1">
+    <row r="93" spans="1:31" ht="15">
       <c r="A93" s="42" t="s">
         <v>644</v>
       </c>
@@ -11136,14 +11136,14 @@
       </c>
       <c r="F93" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>926.5</v>
+        <v>927</v>
       </c>
       <c r="G93" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4112.5</v>
+        <v>4112</v>
       </c>
       <c r="H93" s="105">
-        <v>8550</v>
+        <v>8549</v>
       </c>
       <c r="I93" s="77" t="s">
         <v>45</v>
@@ -11153,11 +11153,11 @@
       </c>
       <c r="K93" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4112.5</v>
+        <v>4112</v>
       </c>
       <c r="L93" s="106">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
-        <v>8550</v>
+        <v>8549</v>
       </c>
       <c r="M93" s="46"/>
       <c r="N93" s="46"/>
@@ -11333,7 +11333,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="15" hidden="1">
+    <row r="96" spans="1:31" ht="15">
       <c r="A96" s="42" t="s">
         <v>644</v>
       </c>
@@ -11548,7 +11548,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="15" hidden="1">
+    <row r="99" spans="1:31" ht="15">
       <c r="A99" s="42" t="s">
         <v>644</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1576" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25B2A292-261B-48F2-8ED2-08D123E3FF90}"/>
+  <xr:revisionPtr revIDLastSave="1578" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F267D9F1-47F5-4BA7-A97F-F14D2224748D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -11136,14 +11136,14 @@
       </c>
       <c r="F93" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>927</v>
+        <v>926.5</v>
       </c>
       <c r="G93" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4112</v>
+        <v>4112.5</v>
       </c>
       <c r="H93" s="105">
-        <v>8549</v>
+        <v>8550</v>
       </c>
       <c r="I93" s="77" t="s">
         <v>45</v>
@@ -11153,11 +11153,10 @@
       </c>
       <c r="K93" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4112</v>
+        <v>4112.5</v>
       </c>
       <c r="L93" s="106">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
-        <v>8549</v>
+        <v>8550</v>
       </c>
       <c r="M93" s="46"/>
       <c r="N93" s="46"/>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1654" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7425D35E-B044-40C9-B761-CDB8A388AB72}"/>
+  <xr:revisionPtr revIDLastSave="1656" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{405FED6A-CA4F-462B-8263-C85670BCC77B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3096,7 +3096,7 @@
   <autoFilter ref="A1:V89" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Beltone RIE Digital Envision 17 62S-DRWC"/>
+        <filter val="Beltone RIE Digital Envision 9 62S-DRWC"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5775,7 +5775,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15">
+    <row r="24" spans="1:31" ht="15" hidden="1">
       <c r="A24" s="41" t="s">
         <v>53</v>
       </c>
@@ -5853,7 +5853,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15">
+    <row r="25" spans="1:31" ht="15" hidden="1">
       <c r="A25" s="41" t="s">
         <v>53</v>
       </c>
@@ -5931,7 +5931,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15">
+    <row r="26" spans="1:31" ht="15" hidden="1">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -6009,7 +6009,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15">
+    <row r="27" spans="1:31" ht="15" hidden="1">
       <c r="A27" s="41" t="s">
         <v>53</v>
       </c>
@@ -6087,7 +6087,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15">
+    <row r="28" spans="1:31" ht="15" hidden="1">
       <c r="A28" s="41" t="s">
         <v>53</v>
       </c>
@@ -6162,7 +6162,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15">
+    <row r="29" spans="1:31" ht="15" hidden="1">
       <c r="A29" s="41" t="s">
         <v>53</v>
       </c>
@@ -6237,7 +6237,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="15">
+    <row r="30" spans="1:31" ht="15" hidden="1">
       <c r="A30" s="41" t="s">
         <v>53</v>
       </c>
@@ -6313,7 +6313,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="15">
+    <row r="31" spans="1:31" ht="15" hidden="1">
       <c r="A31" s="41" t="s">
         <v>53</v>
       </c>
@@ -6389,7 +6389,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="15">
+    <row r="32" spans="1:31" ht="15" hidden="1">
       <c r="A32" s="41" t="s">
         <v>53</v>
       </c>
@@ -6465,7 +6465,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:32" ht="15">
+    <row r="33" spans="1:32" ht="15" hidden="1">
       <c r="A33" s="41" t="s">
         <v>53</v>
       </c>
@@ -6535,7 +6535,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:32" ht="15">
+    <row r="34" spans="1:32" ht="15" hidden="1">
       <c r="A34" s="41" t="s">
         <v>53</v>
       </c>
@@ -6608,7 +6608,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:32" ht="15">
+    <row r="35" spans="1:32" ht="15" hidden="1">
       <c r="A35" s="41" t="s">
         <v>53</v>
       </c>
@@ -6681,7 +6681,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:32" ht="15">
+    <row r="36" spans="1:32" ht="15" hidden="1">
       <c r="A36" s="41" t="s">
         <v>53</v>
       </c>
@@ -6754,7 +6754,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:32" ht="15">
+    <row r="37" spans="1:32" ht="15" hidden="1">
       <c r="A37" s="41" t="s">
         <v>53</v>
       </c>
@@ -6828,7 +6828,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:32" ht="15">
+    <row r="38" spans="1:32" ht="15" hidden="1">
       <c r="A38" s="41" t="s">
         <v>53</v>
       </c>
@@ -7962,7 +7962,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:31" ht="15" hidden="1">
+    <row r="53" spans="1:31" ht="15">
       <c r="A53" s="41" t="s">
         <v>59</v>
       </c>
@@ -8035,7 +8035,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:31" ht="15" hidden="1">
+    <row r="54" spans="1:31" ht="15">
       <c r="A54" s="41" t="s">
         <v>59</v>
       </c>
@@ -8114,7 +8114,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:31" ht="15" hidden="1">
+    <row r="55" spans="1:31" ht="15">
       <c r="A55" s="41" t="s">
         <v>59</v>
       </c>
@@ -8147,14 +8147,14 @@
       </c>
       <c r="J55" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1380</v>
+        <v>1280</v>
       </c>
       <c r="K55" s="45">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
+        <v>2832.5</v>
       </c>
       <c r="L55" s="98">
-        <v>5790</v>
+        <v>5990</v>
       </c>
       <c r="M55" s="45"/>
       <c r="N55" s="45"/>
@@ -8187,7 +8187,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:31" ht="15" hidden="1">
+    <row r="56" spans="1:31" ht="15">
       <c r="A56" s="41" t="s">
         <v>59</v>
       </c>
@@ -8260,7 +8260,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:31" ht="15" hidden="1">
+    <row r="57" spans="1:31" ht="15">
       <c r="A57" s="41" t="s">
         <v>59</v>
       </c>
@@ -8339,7 +8339,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:31" ht="15" hidden="1">
+    <row r="58" spans="1:31" ht="15">
       <c r="A58" s="41" t="s">
         <v>59</v>
       </c>
@@ -8418,7 +8418,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:31" ht="15" hidden="1">
+    <row r="59" spans="1:31" ht="15">
       <c r="A59" s="41" t="s">
         <v>59</v>
       </c>
@@ -8497,7 +8497,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:31" ht="15" hidden="1">
+    <row r="60" spans="1:31" ht="15">
       <c r="A60" s="41" t="s">
         <v>59</v>
       </c>
@@ -8571,7 +8571,7 @@
       <c r="AD60"/>
       <c r="AE60"/>
     </row>
-    <row r="61" spans="1:31" ht="15" hidden="1">
+    <row r="61" spans="1:31" ht="15">
       <c r="A61" s="41" t="s">
         <v>59</v>
       </c>
@@ -8647,7 +8647,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:31" ht="15" hidden="1">
+    <row r="62" spans="1:31" ht="15">
       <c r="A62" s="41" t="s">
         <v>59</v>
       </c>
@@ -8723,7 +8723,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:31" ht="15" hidden="1">
+    <row r="63" spans="1:31" ht="15">
       <c r="A63" s="41" t="s">
         <v>59</v>
       </c>
@@ -8796,7 +8796,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:31" ht="15" hidden="1">
+    <row r="64" spans="1:31" ht="15">
       <c r="A64" s="41" t="s">
         <v>59</v>
       </c>
@@ -8872,7 +8872,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15" hidden="1">
+    <row r="65" spans="1:31" ht="15">
       <c r="A65" s="41" t="s">
         <v>59</v>
       </c>
@@ -8948,7 +8948,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15" hidden="1">
+    <row r="66" spans="1:31" ht="15">
       <c r="A66" s="41" t="s">
         <v>59</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1656" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{405FED6A-CA4F-462B-8263-C85670BCC77B}"/>
+  <xr:revisionPtr revIDLastSave="1664" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3E8475F-34CF-4897-BB73-88F017C5FF19}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView minimized="1" xWindow="1755" yWindow="3210" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="accessoryList" sheetId="5" r:id="rId6"/>
     <sheet name="Data Lists" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3096,7 +3096,8 @@
   <autoFilter ref="A1:V89" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Beltone RIE Digital Envision 9 62S-DRWC"/>
+        <filter val="Beltone RIE Digital Commence 3 62-DRWC"/>
+        <filter val="Beltone RIE Digital Envision 4 62S-DRWC"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4839,7 +4840,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="15" hidden="1">
+    <row r="11" spans="1:31" ht="15">
       <c r="A11" s="41" t="s">
         <v>47</v>
       </c>
@@ -4911,7 +4912,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="15" hidden="1">
+    <row r="12" spans="1:31" ht="15">
       <c r="A12" s="41" t="s">
         <v>47</v>
       </c>
@@ -4982,7 +4983,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="15" hidden="1">
+    <row r="13" spans="1:31" ht="15">
       <c r="A13" s="41" t="s">
         <v>47</v>
       </c>
@@ -5054,7 +5055,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="15" hidden="1">
+    <row r="14" spans="1:31" ht="15">
       <c r="A14" s="41" t="s">
         <v>47</v>
       </c>
@@ -5126,7 +5127,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="15" hidden="1">
+    <row r="15" spans="1:31" ht="15">
       <c r="A15" s="41" t="s">
         <v>47</v>
       </c>
@@ -5198,7 +5199,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="15" hidden="1">
+    <row r="16" spans="1:31" ht="15">
       <c r="A16" s="41" t="s">
         <v>47</v>
       </c>
@@ -5270,7 +5271,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="15" hidden="1">
+    <row r="17" spans="1:31" ht="15">
       <c r="A17" s="41" t="s">
         <v>47</v>
       </c>
@@ -5343,7 +5344,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="15" hidden="1">
+    <row r="18" spans="1:31" ht="15">
       <c r="A18" s="41" t="s">
         <v>47</v>
       </c>
@@ -5415,7 +5416,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="15" hidden="1">
+    <row r="19" spans="1:31" ht="15">
       <c r="A19" s="41" t="s">
         <v>47</v>
       </c>
@@ -5487,7 +5488,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="15" hidden="1">
+    <row r="20" spans="1:31" ht="15">
       <c r="A20" s="41" t="s">
         <v>47</v>
       </c>
@@ -5559,7 +5560,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="15" hidden="1">
+    <row r="21" spans="1:31" ht="15">
       <c r="A21" s="41" t="s">
         <v>47</v>
       </c>
@@ -5631,7 +5632,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="15" hidden="1">
+    <row r="22" spans="1:31" ht="15">
       <c r="A22" s="41" t="s">
         <v>47</v>
       </c>
@@ -5703,7 +5704,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="15" hidden="1">
+    <row r="23" spans="1:31" ht="15">
       <c r="A23" s="41" t="s">
         <v>47</v>
       </c>
@@ -6901,7 +6902,7 @@
       <c r="AE38" s="15"/>
       <c r="AF38" s="15"/>
     </row>
-    <row r="39" spans="1:32" ht="15" hidden="1">
+    <row r="39" spans="1:32" ht="15">
       <c r="A39" s="41" t="s">
         <v>50</v>
       </c>
@@ -7962,7 +7963,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:31" ht="15">
+    <row r="53" spans="1:31" ht="15" hidden="1">
       <c r="A53" s="41" t="s">
         <v>59</v>
       </c>
@@ -8035,7 +8036,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:31" ht="15">
+    <row r="54" spans="1:31" ht="15" hidden="1">
       <c r="A54" s="41" t="s">
         <v>59</v>
       </c>
@@ -8114,7 +8115,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:31" ht="15">
+    <row r="55" spans="1:31" ht="15" hidden="1">
       <c r="A55" s="41" t="s">
         <v>59</v>
       </c>
@@ -8187,7 +8188,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:31" ht="15">
+    <row r="56" spans="1:31" ht="15" hidden="1">
       <c r="A56" s="41" t="s">
         <v>59</v>
       </c>
@@ -8260,7 +8261,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:31" ht="15">
+    <row r="57" spans="1:31" ht="15" hidden="1">
       <c r="A57" s="41" t="s">
         <v>59</v>
       </c>
@@ -8339,7 +8340,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:31" ht="15">
+    <row r="58" spans="1:31" ht="15" hidden="1">
       <c r="A58" s="41" t="s">
         <v>59</v>
       </c>
@@ -8418,7 +8419,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:31" ht="15">
+    <row r="59" spans="1:31" ht="15" hidden="1">
       <c r="A59" s="41" t="s">
         <v>59</v>
       </c>
@@ -8497,7 +8498,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:31" ht="15">
+    <row r="60" spans="1:31" ht="15" hidden="1">
       <c r="A60" s="41" t="s">
         <v>59</v>
       </c>
@@ -8571,7 +8572,7 @@
       <c r="AD60"/>
       <c r="AE60"/>
     </row>
-    <row r="61" spans="1:31" ht="15">
+    <row r="61" spans="1:31" ht="15" hidden="1">
       <c r="A61" s="41" t="s">
         <v>59</v>
       </c>
@@ -8647,7 +8648,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:31" ht="15">
+    <row r="62" spans="1:31" ht="15" hidden="1">
       <c r="A62" s="41" t="s">
         <v>59</v>
       </c>
@@ -8723,7 +8724,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:31" ht="15">
+    <row r="63" spans="1:31" ht="15" hidden="1">
       <c r="A63" s="41" t="s">
         <v>59</v>
       </c>
@@ -8796,7 +8797,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:31" ht="15">
+    <row r="64" spans="1:31" ht="15" hidden="1">
       <c r="A64" s="41" t="s">
         <v>59</v>
       </c>
@@ -8872,7 +8873,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15">
+    <row r="65" spans="1:31" ht="15" hidden="1">
       <c r="A65" s="41" t="s">
         <v>59</v>
       </c>
@@ -8948,7 +8949,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15">
+    <row r="66" spans="1:31" ht="15" hidden="1">
       <c r="A66" s="41" t="s">
         <v>59</v>
       </c>
@@ -10059,7 +10060,7 @@
       <c r="AC80" s="43"/>
       <c r="AD80" s="43"/>
     </row>
-    <row r="81" spans="1:30" ht="15" hidden="1">
+    <row r="81" spans="1:30" ht="15">
       <c r="A81" s="41" t="s">
         <v>50</v>
       </c>
@@ -10137,7 +10138,7 @@
       <c r="AC81" s="43"/>
       <c r="AD81" s="43"/>
     </row>
-    <row r="82" spans="1:30" ht="15" hidden="1">
+    <row r="82" spans="1:30" ht="15">
       <c r="A82" s="41" t="s">
         <v>50</v>
       </c>
@@ -10215,7 +10216,7 @@
       <c r="AC82" s="43"/>
       <c r="AD82" s="43"/>
     </row>
-    <row r="83" spans="1:30" ht="15" hidden="1">
+    <row r="83" spans="1:30" ht="15">
       <c r="A83" s="41" t="s">
         <v>50</v>
       </c>
@@ -10293,7 +10294,7 @@
       <c r="AC83" s="43"/>
       <c r="AD83" s="43"/>
     </row>
-    <row r="84" spans="1:30" ht="15" hidden="1">
+    <row r="84" spans="1:30" ht="15">
       <c r="A84" s="41" t="s">
         <v>50</v>
       </c>
@@ -10371,7 +10372,7 @@
       <c r="AC84" s="43"/>
       <c r="AD84" s="43"/>
     </row>
-    <row r="85" spans="1:30" ht="15" hidden="1">
+    <row r="85" spans="1:30" ht="15">
       <c r="A85" s="41" t="s">
         <v>50</v>
       </c>
@@ -10449,7 +10450,7 @@
       <c r="AC85" s="43"/>
       <c r="AD85" s="43"/>
     </row>
-    <row r="86" spans="1:30" ht="15" hidden="1">
+    <row r="86" spans="1:30" ht="15">
       <c r="A86" s="41" t="s">
         <v>50</v>
       </c>
@@ -10527,7 +10528,7 @@
       <c r="AC86" s="43"/>
       <c r="AD86" s="43"/>
     </row>
-    <row r="87" spans="1:30" ht="15" hidden="1">
+    <row r="87" spans="1:30" ht="15">
       <c r="A87" s="41" t="s">
         <v>50</v>
       </c>
@@ -10605,7 +10606,7 @@
       <c r="AC87" s="43"/>
       <c r="AD87" s="43"/>
     </row>
-    <row r="88" spans="1:30" ht="15" hidden="1">
+    <row r="88" spans="1:30" ht="15">
       <c r="A88" s="41" t="s">
         <v>50</v>
       </c>
@@ -10683,7 +10684,7 @@
       <c r="AC88" s="43"/>
       <c r="AD88" s="43"/>
     </row>
-    <row r="89" spans="1:30" ht="15" hidden="1">
+    <row r="89" spans="1:30" ht="15">
       <c r="A89" s="41" t="s">
         <v>50</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1664" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3E8475F-34CF-4897-BB73-88F017C5FF19}"/>
+  <xr:revisionPtr revIDLastSave="1665" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0907BD64-5ECE-4EF0-8494-A08296220B36}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1755" yWindow="3210" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="15990" yWindow="16080" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3093,14 +3093,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V89" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:V89" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Beltone RIE Digital Commence 3 62-DRWC"/>
-        <filter val="Beltone RIE Digital Envision 4 62S-DRWC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A67:V76">
     <sortCondition ref="I1:I80"/>
   </sortState>
@@ -4202,7 +4194,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="15" hidden="1">
+    <row r="2" spans="1:31" ht="15">
       <c r="A2" s="41" t="s">
         <v>66</v>
       </c>
@@ -4274,7 +4266,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="15" hidden="1">
+    <row r="3" spans="1:31" ht="15">
       <c r="A3" s="41" t="s">
         <v>66</v>
       </c>
@@ -4346,7 +4338,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="15" hidden="1">
+    <row r="4" spans="1:31" ht="15">
       <c r="A4" s="41" t="s">
         <v>62</v>
       </c>
@@ -4414,7 +4406,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="15" hidden="1">
+    <row r="5" spans="1:31" ht="15">
       <c r="A5" s="41" t="s">
         <v>68</v>
       </c>
@@ -4487,7 +4479,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="15" hidden="1">
+    <row r="6" spans="1:31" ht="15">
       <c r="A6" s="41" t="s">
         <v>68</v>
       </c>
@@ -4559,7 +4551,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="15" hidden="1">
+    <row r="7" spans="1:31" ht="15">
       <c r="A7" s="41" t="s">
         <v>70</v>
       </c>
@@ -4632,7 +4624,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="15" hidden="1">
+    <row r="8" spans="1:31" ht="15">
       <c r="A8" s="41" t="s">
         <v>70</v>
       </c>
@@ -4705,7 +4697,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="15" hidden="1">
+    <row r="9" spans="1:31" ht="15">
       <c r="A9" s="41" t="s">
         <v>43</v>
       </c>
@@ -4768,7 +4760,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="15" hidden="1">
+    <row r="10" spans="1:31" ht="15">
       <c r="A10" s="41" t="s">
         <v>43</v>
       </c>
@@ -5776,7 +5768,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15" hidden="1">
+    <row r="24" spans="1:31" ht="15">
       <c r="A24" s="41" t="s">
         <v>53</v>
       </c>
@@ -5854,7 +5846,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15" hidden="1">
+    <row r="25" spans="1:31" ht="15">
       <c r="A25" s="41" t="s">
         <v>53</v>
       </c>
@@ -5932,7 +5924,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15" hidden="1">
+    <row r="26" spans="1:31" ht="15">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -6010,7 +6002,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15" hidden="1">
+    <row r="27" spans="1:31" ht="15">
       <c r="A27" s="41" t="s">
         <v>53</v>
       </c>
@@ -6088,7 +6080,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15" hidden="1">
+    <row r="28" spans="1:31" ht="15">
       <c r="A28" s="41" t="s">
         <v>53</v>
       </c>
@@ -6163,7 +6155,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15" hidden="1">
+    <row r="29" spans="1:31" ht="15">
       <c r="A29" s="41" t="s">
         <v>53</v>
       </c>
@@ -6238,7 +6230,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="15" hidden="1">
+    <row r="30" spans="1:31" ht="15">
       <c r="A30" s="41" t="s">
         <v>53</v>
       </c>
@@ -6314,7 +6306,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="15" hidden="1">
+    <row r="31" spans="1:31" ht="15">
       <c r="A31" s="41" t="s">
         <v>53</v>
       </c>
@@ -6390,7 +6382,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="15" hidden="1">
+    <row r="32" spans="1:31" ht="15">
       <c r="A32" s="41" t="s">
         <v>53</v>
       </c>
@@ -6466,7 +6458,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:32" ht="15" hidden="1">
+    <row r="33" spans="1:32" ht="15">
       <c r="A33" s="41" t="s">
         <v>53</v>
       </c>
@@ -6536,7 +6528,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:32" ht="15" hidden="1">
+    <row r="34" spans="1:32" ht="15">
       <c r="A34" s="41" t="s">
         <v>53</v>
       </c>
@@ -6609,7 +6601,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:32" ht="15" hidden="1">
+    <row r="35" spans="1:32" ht="15">
       <c r="A35" s="41" t="s">
         <v>53</v>
       </c>
@@ -6682,7 +6674,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:32" ht="15" hidden="1">
+    <row r="36" spans="1:32" ht="15">
       <c r="A36" s="41" t="s">
         <v>53</v>
       </c>
@@ -6755,7 +6747,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:32" ht="15" hidden="1">
+    <row r="37" spans="1:32" ht="15">
       <c r="A37" s="41" t="s">
         <v>53</v>
       </c>
@@ -6829,7 +6821,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:32" ht="15" hidden="1">
+    <row r="38" spans="1:32" ht="15">
       <c r="A38" s="41" t="s">
         <v>53</v>
       </c>
@@ -6975,7 +6967,7 @@
       <c r="AE39" s="15"/>
       <c r="AF39" s="15"/>
     </row>
-    <row r="40" spans="1:32" ht="15" hidden="1">
+    <row r="40" spans="1:32" ht="15">
       <c r="A40" s="41" t="s">
         <v>57</v>
       </c>
@@ -7053,7 +7045,7 @@
       <c r="AE40" s="15"/>
       <c r="AF40" s="15"/>
     </row>
-    <row r="41" spans="1:32" ht="15" hidden="1">
+    <row r="41" spans="1:32" ht="15">
       <c r="A41" s="41" t="s">
         <v>57</v>
       </c>
@@ -7132,7 +7124,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:32" ht="15" hidden="1">
+    <row r="42" spans="1:32" ht="15">
       <c r="A42" s="41" t="s">
         <v>57</v>
       </c>
@@ -7211,7 +7203,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:32" ht="15" hidden="1">
+    <row r="43" spans="1:32" ht="15">
       <c r="A43" s="41" t="s">
         <v>57</v>
       </c>
@@ -7290,7 +7282,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:32" ht="15" hidden="1">
+    <row r="44" spans="1:32" ht="15">
       <c r="A44" s="41" t="s">
         <v>57</v>
       </c>
@@ -7366,7 +7358,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:32" ht="15" hidden="1">
+    <row r="45" spans="1:32" ht="15">
       <c r="A45" s="41" t="s">
         <v>57</v>
       </c>
@@ -7442,7 +7434,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:32" ht="15" hidden="1">
+    <row r="46" spans="1:32" ht="15">
       <c r="A46" s="41" t="s">
         <v>57</v>
       </c>
@@ -7518,7 +7510,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:32" ht="15" hidden="1">
+    <row r="47" spans="1:32" ht="15">
       <c r="A47" s="41" t="s">
         <v>57</v>
       </c>
@@ -7594,7 +7586,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:32" ht="15" hidden="1">
+    <row r="48" spans="1:32" ht="15">
       <c r="A48" s="41" t="s">
         <v>57</v>
       </c>
@@ -7670,7 +7662,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:31" ht="15" hidden="1">
+    <row r="49" spans="1:31" ht="15">
       <c r="A49" s="41" t="s">
         <v>57</v>
       </c>
@@ -7743,7 +7735,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:31" ht="15" hidden="1">
+    <row r="50" spans="1:31" ht="15">
       <c r="A50" s="41" t="s">
         <v>57</v>
       </c>
@@ -7816,7 +7808,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:31" ht="15" hidden="1">
+    <row r="51" spans="1:31" ht="15">
       <c r="A51" s="41" t="s">
         <v>57</v>
       </c>
@@ -7890,7 +7882,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:31" ht="15" hidden="1">
+    <row r="52" spans="1:31" ht="15">
       <c r="A52" s="41" t="s">
         <v>57</v>
       </c>
@@ -7963,7 +7955,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:31" ht="15" hidden="1">
+    <row r="53" spans="1:31" ht="15">
       <c r="A53" s="41" t="s">
         <v>59</v>
       </c>
@@ -8036,7 +8028,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:31" ht="15" hidden="1">
+    <row r="54" spans="1:31" ht="15">
       <c r="A54" s="41" t="s">
         <v>59</v>
       </c>
@@ -8115,7 +8107,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:31" ht="15" hidden="1">
+    <row r="55" spans="1:31" ht="15">
       <c r="A55" s="41" t="s">
         <v>59</v>
       </c>
@@ -8188,7 +8180,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:31" ht="15" hidden="1">
+    <row r="56" spans="1:31" ht="15">
       <c r="A56" s="41" t="s">
         <v>59</v>
       </c>
@@ -8261,7 +8253,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:31" ht="15" hidden="1">
+    <row r="57" spans="1:31" ht="15">
       <c r="A57" s="41" t="s">
         <v>59</v>
       </c>
@@ -8340,7 +8332,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:31" ht="15" hidden="1">
+    <row r="58" spans="1:31" ht="15">
       <c r="A58" s="41" t="s">
         <v>59</v>
       </c>
@@ -8419,7 +8411,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:31" ht="15" hidden="1">
+    <row r="59" spans="1:31" ht="15">
       <c r="A59" s="41" t="s">
         <v>59</v>
       </c>
@@ -8498,7 +8490,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:31" ht="15" hidden="1">
+    <row r="60" spans="1:31" ht="15">
       <c r="A60" s="41" t="s">
         <v>59</v>
       </c>
@@ -8572,7 +8564,7 @@
       <c r="AD60"/>
       <c r="AE60"/>
     </row>
-    <row r="61" spans="1:31" ht="15" hidden="1">
+    <row r="61" spans="1:31" ht="15">
       <c r="A61" s="41" t="s">
         <v>59</v>
       </c>
@@ -8648,7 +8640,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:31" ht="15" hidden="1">
+    <row r="62" spans="1:31" ht="15">
       <c r="A62" s="41" t="s">
         <v>59</v>
       </c>
@@ -8724,7 +8716,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:31" ht="15" hidden="1">
+    <row r="63" spans="1:31" ht="15">
       <c r="A63" s="41" t="s">
         <v>59</v>
       </c>
@@ -8797,7 +8789,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:31" ht="15" hidden="1">
+    <row r="64" spans="1:31" ht="15">
       <c r="A64" s="41" t="s">
         <v>59</v>
       </c>
@@ -8873,7 +8865,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15" hidden="1">
+    <row r="65" spans="1:31" ht="15">
       <c r="A65" s="41" t="s">
         <v>59</v>
       </c>
@@ -8949,7 +8941,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15" hidden="1">
+    <row r="66" spans="1:31" ht="15">
       <c r="A66" s="41" t="s">
         <v>59</v>
       </c>
@@ -9025,7 +9017,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15" hidden="1">
+    <row r="67" spans="1:31" ht="15">
       <c r="A67" s="41" t="s">
         <v>562</v>
       </c>
@@ -9098,7 +9090,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15" hidden="1">
+    <row r="68" spans="1:31" ht="15">
       <c r="A68" s="41" t="s">
         <v>564</v>
       </c>
@@ -9170,7 +9162,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15" hidden="1">
+    <row r="69" spans="1:31" ht="15">
       <c r="A69" s="41" t="s">
         <v>566</v>
       </c>
@@ -9242,7 +9234,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15" hidden="1">
+    <row r="70" spans="1:31" ht="15">
       <c r="A70" s="41" t="s">
         <v>568</v>
       </c>
@@ -9314,7 +9306,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15" hidden="1">
+    <row r="71" spans="1:31" ht="15">
       <c r="A71" s="41" t="s">
         <v>562</v>
       </c>
@@ -9386,7 +9378,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15" hidden="1">
+    <row r="72" spans="1:31" ht="15">
       <c r="A72" s="41" t="s">
         <v>566</v>
       </c>
@@ -9458,7 +9450,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15" hidden="1">
+    <row r="73" spans="1:31" ht="15">
       <c r="A73" s="41" t="s">
         <v>568</v>
       </c>
@@ -9531,7 +9523,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="15" hidden="1">
+    <row r="74" spans="1:31" ht="15">
       <c r="A74" s="41" t="s">
         <v>562</v>
       </c>
@@ -9602,7 +9594,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="15" hidden="1">
+    <row r="75" spans="1:31" ht="15">
       <c r="A75" s="41" t="s">
         <v>566</v>
       </c>
@@ -9673,7 +9665,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="15" hidden="1">
+    <row r="76" spans="1:31" ht="15">
       <c r="A76" s="41" t="s">
         <v>568</v>
       </c>
@@ -9744,7 +9736,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="15" hidden="1">
+    <row r="77" spans="1:31" ht="15">
       <c r="A77" s="78" t="s">
         <v>89</v>
       </c>
@@ -9823,7 +9815,7 @@
       <c r="AC77" s="43"/>
       <c r="AD77" s="43"/>
     </row>
-    <row r="78" spans="1:31" ht="15" hidden="1">
+    <row r="78" spans="1:31" ht="15">
       <c r="A78" s="78" t="s">
         <v>91</v>
       </c>
@@ -9902,7 +9894,7 @@
       <c r="AC78" s="43"/>
       <c r="AD78" s="43"/>
     </row>
-    <row r="79" spans="1:31" ht="15" hidden="1">
+    <row r="79" spans="1:31" ht="15">
       <c r="A79" s="78" t="s">
         <v>93</v>
       </c>
@@ -9981,7 +9973,7 @@
       <c r="AC79" s="43"/>
       <c r="AD79" s="43"/>
     </row>
-    <row r="80" spans="1:31" ht="15" hidden="1">
+    <row r="80" spans="1:31" ht="15">
       <c r="A80" s="81" t="s">
         <v>1</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1665" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0907BD64-5ECE-4EF0-8494-A08296220B36}"/>
+  <xr:revisionPtr revIDLastSave="1666" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C17E882-7771-4BF5-8966-9410F93B36B4}"/>
   <bookViews>
-    <workbookView xWindow="15990" yWindow="16080" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="-12810" yWindow="16080" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -1865,7 +1865,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1899,6 +1899,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2134,7 +2140,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2215,9 +2221,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2326,6 +2329,22 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="11" fillId="7" borderId="19" xfId="3" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="11" fillId="7" borderId="19" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3542,13 +3561,13 @@
       <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" thickBot="1">
-      <c r="A3" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="102" t="s">
+      <c r="A3" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="103"/>
+      <c r="C3" s="102"/>
       <c r="D3" s="41"/>
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
@@ -3556,7 +3575,7 @@
       <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" thickBot="1">
-      <c r="A4" s="55"/>
+      <c r="A4" s="54"/>
       <c r="B4" s="41"/>
       <c r="C4" s="41"/>
       <c r="D4" s="41"/>
@@ -3566,13 +3585,13 @@
       <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" thickBot="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="102">
+      <c r="B5" s="101">
         <v>2</v>
       </c>
-      <c r="C5" s="103"/>
+      <c r="C5" s="102"/>
       <c r="D5" s="41"/>
       <c r="E5" s="41"/>
       <c r="F5" s="41"/>
@@ -3580,7 +3599,7 @@
       <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" thickBot="1">
-      <c r="A6" s="55"/>
+      <c r="A6" s="54"/>
       <c r="B6" s="41"/>
       <c r="C6" s="41"/>
       <c r="D6" s="41"/>
@@ -3590,13 +3609,13 @@
       <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:8" ht="13.5" thickBot="1">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="103"/>
+      <c r="C7" s="102"/>
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
       <c r="F7" s="41"/>
@@ -3604,7 +3623,7 @@
       <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="55"/>
+      <c r="A8" s="54"/>
       <c r="B8" s="41"/>
       <c r="C8" s="41"/>
       <c r="D8" s="41"/>
@@ -3614,25 +3633,25 @@
       <c r="H8" s="41"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="56"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="55"/>
       <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" thickBot="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="56"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="55"/>
       <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8">
@@ -3657,19 +3676,19 @@
       <c r="A13" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="58" cm="1">
+      <c r="B13" s="57" cm="1">
         <f t="array" ref="B13">IF($B$3="","",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!A:A&amp;haList!I:I,haList!D:D))</f>
         <v>5579</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="59" cm="1">
+      <c r="D13" s="58" cm="1">
         <f t="array" ref="D13">IF($B$5=1,"",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!A:A&amp;haList!I:I,haList!D:D))</f>
         <v>5579</v>
       </c>
       <c r="E13" s="41"/>
-      <c r="F13" s="60"/>
+      <c r="F13" s="59"/>
       <c r="G13" s="41"/>
       <c r="H13" s="41"/>
     </row>
@@ -3677,19 +3696,19 @@
       <c r="A14" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="61" cm="1">
+      <c r="B14" s="60" cm="1">
         <f t="array" ref="B14">_xlfn.XLOOKUP($B$3,haList!$A:$A,-haList!$F:$F)</f>
         <v>162.5</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="61" cm="1">
+      <c r="D14" s="60" cm="1">
         <f t="array" ref="D14">IF(B5=1,"",_xlfn.XLOOKUP($B$3,haList!$A:$A,-haList!$F:$F))</f>
         <v>162.5</v>
       </c>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
       <c r="G14" s="41"/>
       <c r="H14" s="41"/>
     </row>
@@ -3697,19 +3716,19 @@
       <c r="A15" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="58">
+      <c r="B15" s="57">
         <f>B13+B14</f>
         <v>5741.5</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="61">
         <f>IF(B5=1,"",D13+D14)</f>
         <v>5741.5</v>
       </c>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
       <c r="G15" s="41"/>
       <c r="H15" s="41"/>
     </row>
@@ -3717,19 +3736,19 @@
       <c r="A16" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="58" cm="1">
+      <c r="B16" s="57" cm="1">
         <f t="array" ref="B16">_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,-haList!$J:$J)</f>
         <v>-3405</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="58" cm="1">
+      <c r="D16" s="57" cm="1">
         <f t="array" ref="D16">IF(B5=1,"",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,-haList!$J:$J))</f>
         <v>-3405</v>
       </c>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
       <c r="G16" s="41"/>
       <c r="H16" s="41"/>
     </row>
@@ -3737,19 +3756,19 @@
       <c r="A17" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="58">
+      <c r="B17" s="57">
         <f>B15+B16</f>
         <v>2336.5</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="61">
         <f>IF(B5=1,"",D15+D16)</f>
         <v>2336.5</v>
       </c>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
       <c r="G17" s="41"/>
       <c r="H17" s="41"/>
       <c r="I17" s="41"/>
@@ -3758,19 +3777,19 @@
       <c r="A18" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="58" cm="1">
+      <c r="B18" s="57" cm="1">
         <f t="array" ref="B18">IF($B$7="Open House Special",_xlfn.XLOOKUP($B$3&amp;"Marketing Offer",haList!$A:$A&amp;haList!$M:$M,-haList!$N:$N),0)</f>
         <v>0</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="58" cm="1">
+      <c r="D18" s="57" cm="1">
         <f t="array" ref="D18">IF(B5=1,"",IF($B$7="Open House Special",_xlfn.XLOOKUP($B$3&amp;"Marketing Offer",haList!$A:$A&amp;haList!$M:$M,-haList!$N:$N),0))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
       <c r="G18" s="41"/>
       <c r="H18" s="41"/>
       <c r="I18" s="41"/>
@@ -3779,19 +3798,19 @@
       <c r="A19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="63">
+      <c r="B19" s="62">
         <f>B17+B18</f>
         <v>2336.5</v>
       </c>
       <c r="C19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="64">
+      <c r="D19" s="63">
         <f>IF(B5=1,"",D17+D18)</f>
         <v>2336.5</v>
       </c>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
       <c r="G19" s="41"/>
       <c r="H19" s="41"/>
       <c r="I19" s="41"/>
@@ -3800,9 +3819,9 @@
       <c r="A20" s="41"/>
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
       <c r="G20" s="41"/>
       <c r="H20" s="41"/>
       <c r="I20" s="41"/>
@@ -3811,125 +3830,125 @@
       <c r="A21" s="41"/>
       <c r="B21" s="41"/>
       <c r="C21" s="41"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
       <c r="G21" s="41"/>
       <c r="H21" s="41"/>
       <c r="I21" s="41"/>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1">
       <c r="A22" s="41"/>
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="54" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="42">
         <f>B19</f>
         <v>2336.5</v>
       </c>
-      <c r="D22" s="65"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
       <c r="G22" s="41"/>
       <c r="H22" s="41"/>
       <c r="I22" s="41"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1">
       <c r="A23" s="41"/>
-      <c r="B23" s="55" t="str">
+      <c r="B23" s="54" t="str">
         <f>IF($B$5=1,"",B22)</f>
         <v>Hearing Aid 1</v>
       </c>
-      <c r="C23" s="66">
+      <c r="C23" s="65">
         <f>IF(B5=2,D19,0)</f>
         <v>2336.5</v>
       </c>
-      <c r="D23" s="65"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
       <c r="G23" s="41"/>
       <c r="H23" s="41"/>
       <c r="I23" s="41"/>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1">
       <c r="A24" s="41"/>
-      <c r="B24" s="55" t="str" cm="1">
+      <c r="B24" s="54" t="str" cm="1">
         <f t="array" ref="B24">IF($B$3="","",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,haList!$R:$R))</f>
         <v>Standard Charger</v>
       </c>
-      <c r="C24" s="60" cm="1">
+      <c r="C24" s="59" cm="1">
         <f t="array" ref="C24">IF($B$24="","",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,haList!$S:$S))</f>
         <v>325</v>
       </c>
       <c r="D24" s="41"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
       <c r="G24" s="41"/>
       <c r="H24" s="41"/>
       <c r="I24" s="42"/>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1">
       <c r="A25" s="41"/>
-      <c r="B25" s="55" t="str" cm="1">
+      <c r="B25" s="54" t="str" cm="1">
         <f t="array" ref="B25">IF($B$3="","",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,haList!$T:$T))</f>
         <v>SureFit3 or M@RIE Receiver</v>
       </c>
-      <c r="C25" s="60" cm="1">
+      <c r="C25" s="59" cm="1">
         <f t="array" ref="C25">IF($B$24="","",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,haList!$U:$U))</f>
         <v>0</v>
       </c>
-      <c r="D25" s="67"/>
+      <c r="D25" s="66"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="60"/>
+      <c r="F25" s="59"/>
       <c r="G25" s="41"/>
       <c r="H25" s="41"/>
       <c r="I25" s="42"/>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1">
       <c r="A26" s="41"/>
-      <c r="B26" s="55" t="str">
+      <c r="B26" s="54" t="str">
         <f>IF($B$5=1,"",B25)</f>
         <v>SureFit3 or M@RIE Receiver</v>
       </c>
-      <c r="C26" s="60">
+      <c r="C26" s="59">
         <f>IF(B5=2,C25,0)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="67"/>
+      <c r="D26" s="66"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="60"/>
+      <c r="F26" s="59"/>
       <c r="G26" s="41"/>
       <c r="H26" s="41"/>
       <c r="I26" s="41"/>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1">
       <c r="A27" s="41"/>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="54" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="42">
         <f>C22+C23+C24+C25+C26</f>
         <v>4998</v>
       </c>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="60"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="59"/>
       <c r="G27" s="41"/>
       <c r="H27" s="41"/>
       <c r="I27" s="41"/>
     </row>
     <row r="28" spans="1:9" ht="18" customHeight="1">
       <c r="A28" s="41"/>
-      <c r="B28" s="55" t="str" cm="1">
+      <c r="B28" s="54" t="str" cm="1">
         <f t="array" ref="B28">IF($B$3="","",IF(_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,haList!$Q:$Q)=1,"PA Fitting Fee","(do not charge a PA Fitting Fee)"))</f>
         <v>PA Fitting Fee</v>
       </c>
-      <c r="C28" s="68" cm="1">
+      <c r="C28" s="67" cm="1">
         <f t="array" ref="C28">IF($B$3="","",IF(_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,haList!$Q:$Q)=1,400,""))</f>
         <v>400</v>
       </c>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
       <c r="F28" s="41"/>
       <c r="G28" s="41" t="str">
         <f>IF(B7="Anthem BCBS","&lt;---Needs to be on a separate invoice.  Private Pay only!","")</f>
@@ -3951,13 +3970,13 @@
       <c r="E29" s="35"/>
       <c r="F29" s="25"/>
       <c r="G29" s="41"/>
-      <c r="H29" s="60"/>
+      <c r="H29" s="59"/>
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1">
-      <c r="A30" s="101"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="101"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="100"/>
       <c r="D30" s="35"/>
       <c r="E30" s="35"/>
       <c r="F30" s="25"/>
@@ -3990,11 +4009,11 @@
       <c r="I32" s="41"/>
     </row>
     <row r="33" spans="1:6" ht="18" customHeight="1" thickBot="1">
-      <c r="A33" s="69"/>
-      <c r="B33" s="70" t="s">
+      <c r="A33" s="68"/>
+      <c r="B33" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="60">
+      <c r="C33" s="59">
         <f>C29</f>
         <v>5398</v>
       </c>
@@ -4004,11 +4023,11 @@
     </row>
     <row r="34" spans="1:6" ht="18" customHeight="1" thickBot="1">
       <c r="A34" s="35"/>
-      <c r="B34" s="55" t="str">
+      <c r="B34" s="54" t="str">
         <f>IF($B$33='Data Lists'!C3,"Down Payment Type is Needed",IF($B$33='Data Lists'!C4,"20% down payment needed",IF($B$33='Data Lists'!C5,"20% down payment needed",IF($B$33='Data Lists'!C6,"$800 down payment needed",IF(AND($B$33='Data Lists'!C7,F29&gt;5555),"Down Payment Needed",IF(AND($B$33='Data Lists'!C7,F29&lt;5555),"10% Down Payment Needed"))))))</f>
         <v>10% Down Payment Needed</v>
       </c>
-      <c r="C34" s="60">
+      <c r="C34" s="59">
         <f>IF(B33='Data Lists'!C3,0,
 IF(B33='Data Lists'!C4,'Price Calculator'!C33*20%,
 IF(B33='Data Lists'!C5,'Price Calculator'!C33*20%,
@@ -4017,13 +4036,13 @@
 IF(AND('Price Calculator'!B33='Data Lists'!C7,C33&gt;5555),C33-5000,""))))))</f>
         <v>539.80000000000007</v>
       </c>
-      <c r="D34" s="60"/>
+      <c r="D34" s="59"/>
       <c r="E34" s="41"/>
-      <c r="F34" s="60"/>
+      <c r="F34" s="59"/>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" thickBot="1">
-      <c r="A35" s="55"/>
-      <c r="B35" s="55" t="str">
+      <c r="A35" s="54"/>
+      <c r="B35" s="54" t="str">
         <f>IF($B$33='Data Lists'!C3,"Down Payment Type is Needed",IF($B$33='Data Lists'!C4,"Balance due from Patient at delivery",IF(OR($B$33='Data Lists'!C5,$B$33='Data Lists'!C6,$B$33='Data Lists'!C7),"Balance due from AllWell at delivery")))</f>
         <v>Balance due from AllWell at delivery</v>
       </c>
@@ -4183,7 +4202,7 @@
       <c r="U1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V1" s="49" t="s">
+      <c r="V1" s="48" t="s">
         <v>42</v>
       </c>
       <c r="Y1" s="15"/>
@@ -4205,10 +4224,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12103</v>
       </c>
-      <c r="D2" s="98">
+      <c r="D2" s="97">
         <v>5939</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="43">
@@ -4219,43 +4238,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4712.5</v>
       </c>
-      <c r="H2" s="98">
+      <c r="H2" s="97">
         <v>9650</v>
       </c>
-      <c r="I2" s="76" t="s">
+      <c r="I2" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="45">
+      <c r="J2" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>500</v>
       </c>
-      <c r="K2" s="45">
+      <c r="K2" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4212.5</v>
       </c>
-      <c r="L2" s="98">
+      <c r="L2" s="97">
         <v>8650</v>
       </c>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="46">
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="45">
         <v>1</v>
       </c>
-      <c r="R2" s="71" t="s">
+      <c r="R2" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="72">
+      <c r="S2" s="71">
         <v>225</v>
       </c>
-      <c r="T2" s="48" t="s">
+      <c r="T2" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U2" s="48">
-        <v>0</v>
-      </c>
-      <c r="V2" s="48" t="s">
+      <c r="U2" s="47">
+        <v>0</v>
+      </c>
+      <c r="V2" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y2" s="15"/>
@@ -4277,10 +4296,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12103</v>
       </c>
-      <c r="D3" s="98">
+      <c r="D3" s="97">
         <v>5939</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="43">
@@ -4291,43 +4310,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4712.5</v>
       </c>
-      <c r="H3" s="98">
+      <c r="H3" s="97">
         <v>9650</v>
       </c>
-      <c r="I3" s="76" t="s">
+      <c r="I3" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="45">
+      <c r="J3" s="44">
         <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1025</v>
       </c>
-      <c r="K3" s="45">
+      <c r="K3" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3687.5</v>
       </c>
-      <c r="L3" s="98">
+      <c r="L3" s="97">
         <v>7600</v>
       </c>
-      <c r="M3" s="76"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="46">
+      <c r="M3" s="75"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="45">
         <v>1</v>
       </c>
-      <c r="R3" s="71" t="s">
+      <c r="R3" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S3" s="72">
+      <c r="S3" s="71">
         <v>225</v>
       </c>
-      <c r="T3" s="48" t="s">
+      <c r="T3" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U3" s="48">
-        <v>0</v>
-      </c>
-      <c r="V3" s="48" t="s">
+      <c r="U3" s="47">
+        <v>0</v>
+      </c>
+      <c r="V3" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y3" s="15"/>
@@ -4349,10 +4368,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6523</v>
       </c>
-      <c r="D4" s="98">
+      <c r="D4" s="97">
         <v>3149</v>
       </c>
-      <c r="E4" s="45" t="s">
+      <c r="E4" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="43">
@@ -4363,41 +4382,41 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2562.5</v>
       </c>
-      <c r="H4" s="98">
+      <c r="H4" s="97">
         <v>5350</v>
       </c>
-      <c r="I4" s="76" t="s">
+      <c r="I4" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="45">
+      <c r="J4" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>0</v>
       </c>
-      <c r="K4" s="45">
+      <c r="K4" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2562.5</v>
       </c>
-      <c r="L4" s="99">
+      <c r="L4" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>5350</v>
       </c>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="46">
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="45">
         <v>1</v>
       </c>
-      <c r="R4" s="71" t="s">
+      <c r="R4" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S4" s="72">
+      <c r="S4" s="71">
         <v>225</v>
       </c>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="W4" s="45"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
+      <c r="V4" s="47"/>
+      <c r="W4" s="44"/>
       <c r="Y4" s="15"/>
       <c r="Z4" s="15"/>
       <c r="AA4" s="15"/>
@@ -4417,10 +4436,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7903</v>
       </c>
-      <c r="D5" s="98">
+      <c r="D5" s="97">
         <v>3839</v>
       </c>
-      <c r="E5" s="45" t="s">
+      <c r="E5" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="43">
@@ -4431,44 +4450,44 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3612.5</v>
       </c>
-      <c r="H5" s="98">
+      <c r="H5" s="97">
         <v>7450</v>
       </c>
-      <c r="I5" s="76" t="s">
+      <c r="I5" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>500</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3112.5</v>
       </c>
-      <c r="L5" s="99">
+      <c r="L5" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>6450</v>
       </c>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="46">
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="45">
         <v>1</v>
       </c>
-      <c r="R5" s="71" t="s">
+      <c r="R5" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S5" s="72">
+      <c r="S5" s="71">
         <v>225</v>
       </c>
-      <c r="T5" s="48" t="s">
+      <c r="T5" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U5" s="48">
-        <v>0</v>
-      </c>
-      <c r="V5" s="48" t="s">
+      <c r="U5" s="47">
+        <v>0</v>
+      </c>
+      <c r="V5" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y5" s="15"/>
@@ -4490,10 +4509,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7903</v>
       </c>
-      <c r="D6" s="98">
+      <c r="D6" s="97">
         <v>3839</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="43">
@@ -4504,43 +4523,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3612.5</v>
       </c>
-      <c r="H6" s="98">
+      <c r="H6" s="97">
         <v>7450</v>
       </c>
-      <c r="I6" s="76" t="s">
+      <c r="I6" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="44">
         <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>525</v>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3087.5</v>
       </c>
-      <c r="L6" s="99">
+      <c r="L6" s="98">
         <v>6400</v>
       </c>
-      <c r="M6" s="76"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="46">
+      <c r="M6" s="75"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="45">
         <v>1</v>
       </c>
-      <c r="R6" s="71" t="s">
+      <c r="R6" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S6" s="72">
+      <c r="S6" s="71">
         <v>225</v>
       </c>
-      <c r="T6" s="48" t="s">
+      <c r="T6" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U6" s="48">
-        <v>0</v>
-      </c>
-      <c r="V6" s="48" t="s">
+      <c r="U6" s="47">
+        <v>0</v>
+      </c>
+      <c r="V6" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y6" s="15"/>
@@ -4562,10 +4581,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10303</v>
       </c>
-      <c r="D7" s="98">
+      <c r="D7" s="97">
         <v>5039</v>
       </c>
-      <c r="E7" s="45" t="s">
+      <c r="E7" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="43">
@@ -4576,44 +4595,44 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4162.5</v>
       </c>
-      <c r="H7" s="98">
+      <c r="H7" s="97">
         <v>8550</v>
       </c>
-      <c r="I7" s="76" t="s">
+      <c r="I7" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="J7" s="45">
+      <c r="J7" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>500</v>
       </c>
-      <c r="K7" s="45">
+      <c r="K7" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3662.5</v>
       </c>
-      <c r="L7" s="99">
+      <c r="L7" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>7550</v>
       </c>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="46">
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="45">
         <v>1</v>
       </c>
-      <c r="R7" s="71" t="s">
+      <c r="R7" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="71">
         <v>225</v>
       </c>
-      <c r="T7" s="48" t="s">
+      <c r="T7" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U7" s="48">
-        <v>0</v>
-      </c>
-      <c r="V7" s="48" t="s">
+      <c r="U7" s="47">
+        <v>0</v>
+      </c>
+      <c r="V7" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y7" s="15"/>
@@ -4635,10 +4654,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10303</v>
       </c>
-      <c r="D8" s="98">
+      <c r="D8" s="97">
         <v>5039</v>
       </c>
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="43">
@@ -4649,43 +4668,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4162.5</v>
       </c>
-      <c r="H8" s="98">
+      <c r="H8" s="97">
         <v>8550</v>
       </c>
-      <c r="I8" s="76" t="s">
+      <c r="I8" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="J8" s="45">
+      <c r="J8" s="44">
         <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>625</v>
       </c>
-      <c r="K8" s="45">
+      <c r="K8" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3537.5</v>
       </c>
-      <c r="L8" s="99">
+      <c r="L8" s="98">
         <v>7300</v>
       </c>
-      <c r="M8" s="76"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="76"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="46">
+      <c r="M8" s="75"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="45">
         <v>1</v>
       </c>
-      <c r="R8" s="71" t="s">
+      <c r="R8" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S8" s="72">
+      <c r="S8" s="71">
         <v>225</v>
       </c>
-      <c r="T8" s="48" t="s">
+      <c r="T8" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U8" s="48">
-        <v>0</v>
-      </c>
-      <c r="V8" s="48" t="s">
+      <c r="U8" s="47">
+        <v>0</v>
+      </c>
+      <c r="V8" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W8" s="4"/>
@@ -4708,7 +4727,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3898</v>
       </c>
-      <c r="D9" s="98">
+      <c r="D9" s="97">
         <v>1949</v>
       </c>
       <c r="E9" s="43" t="s">
@@ -4722,36 +4741,36 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H9" s="98">
+      <c r="H9" s="97">
         <v>3100</v>
       </c>
-      <c r="I9" s="54" t="s">
+      <c r="I9" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="45">
-        <v>0</v>
-      </c>
-      <c r="K9" s="45">
+      <c r="J9" s="44">
+        <v>0</v>
+      </c>
+      <c r="K9" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L9" s="98"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="46">
+      <c r="L9" s="97"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="45">
         <v>1</v>
       </c>
-      <c r="R9" s="45" t="s">
+      <c r="R9" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="S9" s="45">
-        <v>0</v>
-      </c>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="47"/>
+      <c r="S9" s="44">
+        <v>0</v>
+      </c>
+      <c r="T9" s="47"/>
+      <c r="U9" s="47"/>
+      <c r="V9" s="46"/>
       <c r="Y9" s="15"/>
       <c r="Z9" s="15"/>
       <c r="AA9" s="15"/>
@@ -4771,7 +4790,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3898</v>
       </c>
-      <c r="D10" s="98">
+      <c r="D10" s="97">
         <v>1949</v>
       </c>
       <c r="E10" s="43" t="s">
@@ -4785,43 +4804,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H10" s="98">
+      <c r="H10" s="97">
         <v>3100</v>
       </c>
-      <c r="I10" s="54" t="s">
+      <c r="I10" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>0</v>
       </c>
-      <c r="K10" s="45">
+      <c r="K10" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L10" s="98">
+      <c r="L10" s="97">
         <v>3100</v>
       </c>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="46">
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="45">
         <v>1</v>
       </c>
-      <c r="R10" s="45" t="s">
+      <c r="R10" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="S10" s="45">
-        <v>0</v>
-      </c>
-      <c r="T10" s="47" t="s">
+      <c r="S10" s="44">
+        <v>0</v>
+      </c>
+      <c r="T10" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="U10" s="48">
-        <v>0</v>
-      </c>
-      <c r="V10" s="47" t="s">
+      <c r="U10" s="47">
+        <v>0</v>
+      </c>
+      <c r="V10" s="46" t="s">
         <v>56</v>
       </c>
       <c r="Y10" s="15"/>
@@ -4843,7 +4862,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D11" s="98">
+      <c r="D11" s="97">
         <v>2459</v>
       </c>
       <c r="E11" s="43" t="s">
@@ -4857,43 +4876,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H11" s="98">
+      <c r="H11" s="97">
         <v>3990</v>
       </c>
-      <c r="I11" s="54" t="s">
+      <c r="I11" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="45">
+      <c r="J11" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K11" s="45">
+      <c r="K11" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L11" s="98">
+      <c r="L11" s="97">
         <v>3390</v>
       </c>
-      <c r="M11" s="45"/>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="73">
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="72">
         <v>1</v>
       </c>
-      <c r="R11" s="74" t="s">
+      <c r="R11" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="S11" s="72">
+      <c r="S11" s="71">
         <v>225</v>
       </c>
-      <c r="T11" s="75" t="s">
+      <c r="T11" s="74" t="s">
         <v>61</v>
       </c>
       <c r="U11" s="15">
         <v>0</v>
       </c>
-      <c r="V11" s="51" t="s">
+      <c r="V11" s="50" t="s">
         <v>56</v>
       </c>
       <c r="Y11" s="15"/>
@@ -4915,7 +4934,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D12" s="98">
+      <c r="D12" s="97">
         <v>2459</v>
       </c>
       <c r="E12" s="43" t="s">
@@ -4929,42 +4948,42 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H12" s="98">
+      <c r="H12" s="97">
         <v>3990</v>
       </c>
-      <c r="I12" s="54" t="s">
+      <c r="I12" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="45">
-        <v>0</v>
-      </c>
-      <c r="K12" s="45">
+      <c r="J12" s="44">
+        <v>0</v>
+      </c>
+      <c r="K12" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1882.5</v>
       </c>
-      <c r="L12" s="98">
+      <c r="L12" s="97">
         <v>3990</v>
       </c>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="46">
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="45">
         <v>1</v>
       </c>
-      <c r="R12" s="71" t="s">
+      <c r="R12" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S12" s="45">
+      <c r="S12" s="44">
         <v>225</v>
       </c>
-      <c r="T12" s="75" t="s">
+      <c r="T12" s="74" t="s">
         <v>61</v>
       </c>
       <c r="U12" s="15">
         <v>0</v>
       </c>
-      <c r="V12" s="51" t="s">
+      <c r="V12" s="50" t="s">
         <v>56</v>
       </c>
       <c r="Y12" s="15"/>
@@ -4986,7 +5005,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D13" s="98">
+      <c r="D13" s="97">
         <v>2459</v>
       </c>
       <c r="E13" s="43" t="s">
@@ -5000,43 +5019,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H13" s="98">
+      <c r="H13" s="97">
         <v>3990</v>
       </c>
-      <c r="I13" s="54" t="s">
+      <c r="I13" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="J13" s="45">
+      <c r="J13" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K13" s="45">
+      <c r="K13" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L13" s="98">
+      <c r="L13" s="97">
         <v>3390</v>
       </c>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="46">
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="45">
         <v>1</v>
       </c>
-      <c r="R13" s="71" t="s">
+      <c r="R13" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S13" s="72">
+      <c r="S13" s="71">
         <v>225</v>
       </c>
-      <c r="T13" s="48" t="s">
+      <c r="T13" s="47" t="s">
         <v>61</v>
       </c>
       <c r="U13" s="15">
         <v>0</v>
       </c>
-      <c r="V13" s="47" t="s">
+      <c r="V13" s="46" t="s">
         <v>56</v>
       </c>
       <c r="Y13" s="15"/>
@@ -5058,7 +5077,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D14" s="98">
+      <c r="D14" s="97">
         <v>2459</v>
       </c>
       <c r="E14" s="43" t="s">
@@ -5072,43 +5091,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H14" s="98">
+      <c r="H14" s="97">
         <v>3990</v>
       </c>
-      <c r="I14" s="54" t="s">
+      <c r="I14" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K14" s="45">
+      <c r="K14" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L14" s="98">
+      <c r="L14" s="97">
         <v>3390</v>
       </c>
-      <c r="M14" s="45"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="73">
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="72">
         <v>1</v>
       </c>
-      <c r="R14" s="74" t="s">
+      <c r="R14" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="S14" s="72">
+      <c r="S14" s="71">
         <v>225</v>
       </c>
-      <c r="T14" s="75" t="s">
+      <c r="T14" s="74" t="s">
         <v>61</v>
       </c>
       <c r="U14" s="15">
         <v>0</v>
       </c>
-      <c r="V14" s="51" t="s">
+      <c r="V14" s="50" t="s">
         <v>56</v>
       </c>
       <c r="Y14" s="15"/>
@@ -5130,7 +5149,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D15" s="98">
+      <c r="D15" s="97">
         <v>2459</v>
       </c>
       <c r="E15" s="43" t="s">
@@ -5144,43 +5163,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H15" s="98">
+      <c r="H15" s="97">
         <v>3990</v>
       </c>
-      <c r="I15" s="54" t="s">
+      <c r="I15" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L15" s="98">
+      <c r="L15" s="97">
         <v>3390</v>
       </c>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="73">
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="72">
         <v>1</v>
       </c>
-      <c r="R15" s="74" t="s">
+      <c r="R15" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="S15" s="72">
+      <c r="S15" s="71">
         <v>225</v>
       </c>
-      <c r="T15" s="75" t="s">
+      <c r="T15" s="74" t="s">
         <v>61</v>
       </c>
       <c r="U15" s="15">
         <v>0</v>
       </c>
-      <c r="V15" s="51" t="s">
+      <c r="V15" s="50" t="s">
         <v>56</v>
       </c>
       <c r="Y15" s="15"/>
@@ -5202,7 +5221,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D16" s="98">
+      <c r="D16" s="97">
         <v>2459</v>
       </c>
       <c r="E16" s="43" t="s">
@@ -5216,43 +5235,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H16" s="98">
+      <c r="H16" s="97">
         <v>3990</v>
       </c>
-      <c r="I16" s="54" t="s">
+      <c r="I16" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="J16" s="45">
+      <c r="J16" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K16" s="45">
+      <c r="K16" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L16" s="98">
+      <c r="L16" s="97">
         <v>3390</v>
       </c>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="73">
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="72">
         <v>1</v>
       </c>
-      <c r="R16" s="74" t="s">
+      <c r="R16" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="S16" s="72">
+      <c r="S16" s="71">
         <v>225</v>
       </c>
-      <c r="T16" s="75" t="s">
+      <c r="T16" s="74" t="s">
         <v>61</v>
       </c>
       <c r="U16" s="15">
         <v>0</v>
       </c>
-      <c r="V16" s="51" t="s">
+      <c r="V16" s="50" t="s">
         <v>56</v>
       </c>
       <c r="Y16" s="15"/>
@@ -5274,7 +5293,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D17" s="98">
+      <c r="D17" s="97">
         <v>2459</v>
       </c>
       <c r="E17" s="43" t="s">
@@ -5288,43 +5307,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H17" s="98">
+      <c r="H17" s="97">
         <v>3990</v>
       </c>
-      <c r="I17" s="54" t="s">
+      <c r="I17" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L17" s="98">
+      <c r="L17" s="97">
         <v>3390</v>
       </c>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="73">
+      <c r="M17" s="44"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="72">
         <v>1</v>
       </c>
-      <c r="R17" s="74" t="s">
+      <c r="R17" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="S17" s="72">
+      <c r="S17" s="71">
         <v>225</v>
       </c>
-      <c r="T17" s="75" t="s">
+      <c r="T17" s="74" t="s">
         <v>61</v>
       </c>
       <c r="U17" s="15">
         <v>0</v>
       </c>
-      <c r="V17" s="51" t="s">
+      <c r="V17" s="50" t="s">
         <v>56</v>
       </c>
       <c r="W17" s="4"/>
@@ -5347,10 +5366,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D18" s="98">
+      <c r="D18" s="97">
         <v>2459</v>
       </c>
-      <c r="E18" s="45" t="s">
+      <c r="E18" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="43">
@@ -5361,43 +5380,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H18" s="98">
+      <c r="H18" s="97">
         <v>3990</v>
       </c>
-      <c r="I18" s="54" t="s">
+      <c r="I18" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="J18" s="45">
+      <c r="J18" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K18" s="45">
+      <c r="K18" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L18" s="98">
+      <c r="L18" s="97">
         <v>3390</v>
       </c>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="92">
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91">
         <v>1</v>
       </c>
-      <c r="R18" s="93" t="s">
+      <c r="R18" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="S18" s="72">
+      <c r="S18" s="71">
         <v>225</v>
       </c>
-      <c r="T18" s="94" t="s">
+      <c r="T18" s="93" t="s">
         <v>61</v>
       </c>
       <c r="U18" s="20">
         <v>0</v>
       </c>
-      <c r="V18" s="96" t="s">
+      <c r="V18" s="95" t="s">
         <v>56</v>
       </c>
       <c r="Y18" s="15"/>
@@ -5419,10 +5438,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D19" s="98">
+      <c r="D19" s="97">
         <v>2459</v>
       </c>
-      <c r="E19" s="45" t="s">
+      <c r="E19" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="43">
@@ -5433,43 +5452,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H19" s="98">
+      <c r="H19" s="97">
         <v>3990</v>
       </c>
-      <c r="I19" s="54" t="s">
+      <c r="I19" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="45">
+      <c r="J19" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L19" s="98">
+      <c r="L19" s="97">
         <v>3390</v>
       </c>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="92">
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="91">
         <v>1</v>
       </c>
-      <c r="R19" s="93" t="s">
+      <c r="R19" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="S19" s="91">
+      <c r="S19" s="90">
         <v>225</v>
       </c>
-      <c r="T19" s="94" t="s">
+      <c r="T19" s="93" t="s">
         <v>61</v>
       </c>
       <c r="U19" s="20">
         <v>0</v>
       </c>
-      <c r="V19" s="96" t="s">
+      <c r="V19" s="95" t="s">
         <v>56</v>
       </c>
       <c r="Y19" s="15"/>
@@ -5491,10 +5510,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D20" s="98">
+      <c r="D20" s="97">
         <v>2459</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="43">
@@ -5505,43 +5524,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H20" s="98">
+      <c r="H20" s="97">
         <v>3990</v>
       </c>
-      <c r="I20" s="54" t="s">
+      <c r="I20" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L20" s="98">
+      <c r="L20" s="97">
         <v>3390</v>
       </c>
-      <c r="M20" s="45"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="91"/>
-      <c r="Q20" s="46">
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="45">
         <v>1</v>
       </c>
-      <c r="R20" s="71" t="s">
+      <c r="R20" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S20" s="91">
+      <c r="S20" s="90">
         <v>225</v>
       </c>
-      <c r="T20" s="48" t="s">
+      <c r="T20" s="47" t="s">
         <v>61</v>
       </c>
       <c r="U20" s="4">
         <v>0</v>
       </c>
-      <c r="V20" s="53" t="s">
+      <c r="V20" s="52" t="s">
         <v>56</v>
       </c>
       <c r="Y20" s="15"/>
@@ -5563,10 +5582,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D21" s="98">
+      <c r="D21" s="97">
         <v>2459</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="43">
@@ -5577,43 +5596,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H21" s="98">
+      <c r="H21" s="97">
         <v>3990</v>
       </c>
-      <c r="I21" s="76" t="s">
+      <c r="I21" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L21" s="99">
+      <c r="L21" s="98">
         <v>3390</v>
       </c>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="46">
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="45">
         <v>1</v>
       </c>
-      <c r="R21" s="71" t="s">
+      <c r="R21" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S21" s="91">
+      <c r="S21" s="90">
         <v>225</v>
       </c>
-      <c r="T21" s="48" t="s">
+      <c r="T21" s="47" t="s">
         <v>61</v>
       </c>
       <c r="U21" s="15">
         <v>0</v>
       </c>
-      <c r="V21" s="48" t="s">
+      <c r="V21" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y21" s="15"/>
@@ -5635,10 +5654,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D22" s="98">
+      <c r="D22" s="97">
         <v>2459</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="43">
@@ -5649,43 +5668,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H22" s="98">
+      <c r="H22" s="97">
         <v>3990</v>
       </c>
-      <c r="I22" s="54" t="s">
+      <c r="I22" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="J22" s="45">
+      <c r="J22" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K22" s="45">
+      <c r="K22" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L22" s="98">
+      <c r="L22" s="97">
         <v>3390</v>
       </c>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="91"/>
-      <c r="Q22" s="46">
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="45">
         <v>1</v>
       </c>
-      <c r="R22" s="71" t="s">
+      <c r="R22" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="S22" s="91">
+      <c r="S22" s="90">
         <v>225</v>
       </c>
-      <c r="T22" s="48" t="s">
+      <c r="T22" s="47" t="s">
         <v>61</v>
       </c>
       <c r="U22" s="4">
         <v>0</v>
       </c>
-      <c r="V22" s="53" t="s">
+      <c r="V22" s="52" t="s">
         <v>56</v>
       </c>
       <c r="Y22" s="15"/>
@@ -5707,10 +5726,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D23" s="98">
+      <c r="D23" s="97">
         <v>2459</v>
       </c>
-      <c r="E23" s="45" t="s">
+      <c r="E23" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="43">
@@ -5721,43 +5740,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H23" s="98">
+      <c r="H23" s="97">
         <v>3990</v>
       </c>
-      <c r="I23" s="54" t="s">
+      <c r="I23" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="J23" s="45">
+      <c r="J23" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>300</v>
       </c>
-      <c r="K23" s="45">
+      <c r="K23" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L23" s="98">
+      <c r="L23" s="97">
         <v>3390</v>
       </c>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="92">
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="91">
         <v>1</v>
       </c>
-      <c r="R23" s="93" t="s">
+      <c r="R23" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="S23" s="91">
+      <c r="S23" s="90">
         <v>225</v>
       </c>
-      <c r="T23" s="94" t="s">
+      <c r="T23" s="93" t="s">
         <v>61</v>
       </c>
       <c r="U23" s="20">
         <v>0</v>
       </c>
-      <c r="V23" s="96" t="s">
+      <c r="V23" s="95" t="s">
         <v>56</v>
       </c>
       <c r="Y23" s="15"/>
@@ -5772,17 +5791,17 @@
       <c r="A24" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="89" t="s">
+      <c r="B24" s="88" t="s">
         <v>54</v>
       </c>
       <c r="C24" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D24" s="98">
+      <c r="D24" s="97">
         <v>5939</v>
       </c>
-      <c r="E24" s="45" t="s">
+      <c r="E24" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F24" s="43">
@@ -5793,49 +5812,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H24" s="98">
+      <c r="H24" s="97">
         <v>9650</v>
       </c>
-      <c r="I24" s="76" t="s">
+      <c r="I24" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="J24" s="45">
+      <c r="J24" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K24" s="45">
+      <c r="K24" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L24" s="98">
+      <c r="L24" s="97">
         <v>6690</v>
       </c>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45">
+      <c r="M24" s="44"/>
+      <c r="N24" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="O24" s="45">
+      <c r="O24" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="46">
+      <c r="P24" s="44"/>
+      <c r="Q24" s="45">
         <v>1</v>
       </c>
-      <c r="R24" s="46" t="s">
+      <c r="R24" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S24" s="46">
+      <c r="S24" s="45">
         <v>325</v>
       </c>
-      <c r="T24" s="48" t="s">
+      <c r="T24" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U24" s="48">
-        <v>0</v>
-      </c>
-      <c r="V24" s="48" t="s">
+      <c r="U24" s="47">
+        <v>0</v>
+      </c>
+      <c r="V24" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y24" s="15"/>
@@ -5857,10 +5876,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D25" s="98">
+      <c r="D25" s="97">
         <v>5939</v>
       </c>
-      <c r="E25" s="45" t="s">
+      <c r="E25" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F25" s="43">
@@ -5871,49 +5890,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H25" s="98">
+      <c r="H25" s="97">
         <v>9650</v>
       </c>
-      <c r="I25" s="76" t="s">
+      <c r="I25" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="J25" s="45">
+      <c r="J25" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K25" s="45">
+      <c r="K25" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L25" s="98">
+      <c r="L25" s="97">
         <v>6690</v>
       </c>
-      <c r="M25" s="45"/>
-      <c r="N25" s="45">
+      <c r="M25" s="44"/>
+      <c r="N25" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="O25" s="45">
+      <c r="O25" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="46">
+      <c r="P25" s="44"/>
+      <c r="Q25" s="45">
         <v>1</v>
       </c>
-      <c r="R25" s="46" t="s">
+      <c r="R25" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S25" s="46">
+      <c r="S25" s="45">
         <v>325</v>
       </c>
-      <c r="T25" s="48" t="s">
+      <c r="T25" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U25" s="48">
-        <v>0</v>
-      </c>
-      <c r="V25" s="48" t="s">
+      <c r="U25" s="47">
+        <v>0</v>
+      </c>
+      <c r="V25" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y25" s="15"/>
@@ -5928,17 +5947,17 @@
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="89" t="s">
+      <c r="B26" s="88" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D26" s="98">
+      <c r="D26" s="97">
         <v>5939</v>
       </c>
-      <c r="E26" s="45" t="s">
+      <c r="E26" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F26" s="43">
@@ -5949,49 +5968,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H26" s="98">
+      <c r="H26" s="97">
         <v>9650</v>
       </c>
-      <c r="I26" s="76" t="s">
+      <c r="I26" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="J26" s="45">
+      <c r="J26" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K26" s="45">
+      <c r="K26" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L26" s="98">
+      <c r="L26" s="97">
         <v>6690</v>
       </c>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45">
+      <c r="M26" s="44"/>
+      <c r="N26" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="O26" s="45">
+      <c r="O26" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="46">
+      <c r="P26" s="44"/>
+      <c r="Q26" s="45">
         <v>1</v>
       </c>
-      <c r="R26" s="46" t="s">
+      <c r="R26" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S26" s="46">
+      <c r="S26" s="45">
         <v>325</v>
       </c>
-      <c r="T26" s="48" t="s">
+      <c r="T26" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U26" s="48">
-        <v>0</v>
-      </c>
-      <c r="V26" s="48" t="s">
+      <c r="U26" s="47">
+        <v>0</v>
+      </c>
+      <c r="V26" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y26" s="15"/>
@@ -6006,17 +6025,17 @@
       <c r="A27" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="89" t="s">
+      <c r="B27" s="88" t="s">
         <v>54</v>
       </c>
       <c r="C27" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D27" s="98">
+      <c r="D27" s="97">
         <v>5939</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F27" s="43">
@@ -6027,49 +6046,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H27" s="98">
+      <c r="H27" s="97">
         <v>9650</v>
       </c>
-      <c r="I27" s="76" t="s">
+      <c r="I27" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="J27" s="45">
+      <c r="J27" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K27" s="45">
+      <c r="K27" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L27" s="98">
+      <c r="L27" s="97">
         <v>6690</v>
       </c>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45">
+      <c r="M27" s="44"/>
+      <c r="N27" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="O27" s="45">
+      <c r="O27" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="46">
+      <c r="P27" s="44"/>
+      <c r="Q27" s="45">
         <v>1</v>
       </c>
-      <c r="R27" s="46" t="s">
+      <c r="R27" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S27" s="46">
+      <c r="S27" s="45">
         <v>325</v>
       </c>
-      <c r="T27" s="48" t="s">
+      <c r="T27" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U27" s="48">
-        <v>0</v>
-      </c>
-      <c r="V27" s="48" t="s">
+      <c r="U27" s="47">
+        <v>0</v>
+      </c>
+      <c r="V27" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y27" s="15"/>
@@ -6091,10 +6110,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D28" s="98">
+      <c r="D28" s="97">
         <v>5939</v>
       </c>
-      <c r="E28" s="45" t="s">
+      <c r="E28" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F28" s="43">
@@ -6105,46 +6124,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H28" s="98">
+      <c r="H28" s="97">
         <v>9650</v>
       </c>
-      <c r="I28" s="76" t="s">
+      <c r="I28" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="J28" s="45">
+      <c r="J28" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K28" s="45">
+      <c r="K28" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L28" s="98">
+      <c r="L28" s="97">
         <v>6690</v>
       </c>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45">
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>3182.5</v>
       </c>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="46">
+      <c r="P28" s="44"/>
+      <c r="Q28" s="45">
         <v>1</v>
       </c>
-      <c r="R28" s="46" t="s">
+      <c r="R28" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S28" s="46">
+      <c r="S28" s="45">
         <v>325</v>
       </c>
-      <c r="T28" s="48" t="s">
+      <c r="T28" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U28" s="48">
-        <v>0</v>
-      </c>
-      <c r="V28" s="48" t="s">
+      <c r="U28" s="47">
+        <v>0</v>
+      </c>
+      <c r="V28" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y28" s="15"/>
@@ -6159,17 +6178,17 @@
       <c r="A29" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="89" t="s">
+      <c r="B29" s="88" t="s">
         <v>54</v>
       </c>
       <c r="C29" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D29" s="98">
+      <c r="D29" s="97">
         <v>5939</v>
       </c>
-      <c r="E29" s="45" t="s">
+      <c r="E29" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F29" s="43">
@@ -6180,46 +6199,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H29" s="98">
+      <c r="H29" s="97">
         <v>9650</v>
       </c>
-      <c r="I29" s="76" t="s">
+      <c r="I29" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="J29" s="45">
+      <c r="J29" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K29" s="45">
+      <c r="K29" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L29" s="98">
+      <c r="L29" s="97">
         <v>6690</v>
       </c>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45">
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>3182.5</v>
       </c>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="46">
+      <c r="P29" s="44"/>
+      <c r="Q29" s="45">
         <v>1</v>
       </c>
-      <c r="R29" s="46" t="s">
+      <c r="R29" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S29" s="46">
+      <c r="S29" s="45">
         <v>325</v>
       </c>
-      <c r="T29" s="48" t="s">
+      <c r="T29" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U29" s="48">
-        <v>0</v>
-      </c>
-      <c r="V29" s="48" t="s">
+      <c r="U29" s="47">
+        <v>0</v>
+      </c>
+      <c r="V29" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y29" s="15"/>
@@ -6241,10 +6260,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D30" s="98">
+      <c r="D30" s="97">
         <v>5939</v>
       </c>
-      <c r="E30" s="45" t="s">
+      <c r="E30" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="43">
@@ -6255,49 +6274,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H30" s="98">
+      <c r="H30" s="97">
         <v>9650</v>
       </c>
-      <c r="I30" s="76" t="s">
+      <c r="I30" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="J30" s="45">
+      <c r="J30" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K30" s="45">
+      <c r="K30" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L30" s="98">
+      <c r="L30" s="97">
         <v>6690</v>
       </c>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="45">
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>3182.5</v>
       </c>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="46">
+      <c r="P30" s="44"/>
+      <c r="Q30" s="45">
         <v>1</v>
       </c>
-      <c r="R30" s="46" t="s">
+      <c r="R30" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S30" s="46">
+      <c r="S30" s="45">
         <v>325</v>
       </c>
-      <c r="T30" s="48" t="s">
+      <c r="T30" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U30" s="48">
-        <v>0</v>
-      </c>
-      <c r="V30" s="48" t="s">
+      <c r="U30" s="47">
+        <v>0</v>
+      </c>
+      <c r="V30" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="W30" s="45"/>
+      <c r="W30" s="44"/>
       <c r="Y30" s="15"/>
       <c r="Z30" s="15"/>
       <c r="AA30" s="15"/>
@@ -6310,17 +6329,17 @@
       <c r="A31" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="89" t="s">
+      <c r="B31" s="88" t="s">
         <v>54</v>
       </c>
       <c r="C31" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D31" s="98">
+      <c r="D31" s="97">
         <v>5939</v>
       </c>
-      <c r="E31" s="45" t="s">
+      <c r="E31" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="43">
@@ -6331,49 +6350,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H31" s="98">
+      <c r="H31" s="97">
         <v>9650</v>
       </c>
-      <c r="I31" s="76" t="s">
+      <c r="I31" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="J31" s="45">
+      <c r="J31" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K31" s="45">
+      <c r="K31" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L31" s="98">
+      <c r="L31" s="97">
         <v>6690</v>
       </c>
-      <c r="M31" s="45"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="45">
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>3182.5</v>
       </c>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="46">
+      <c r="P31" s="44"/>
+      <c r="Q31" s="45">
         <v>1</v>
       </c>
-      <c r="R31" s="46" t="s">
+      <c r="R31" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S31" s="46">
+      <c r="S31" s="45">
         <v>325</v>
       </c>
-      <c r="T31" s="48" t="s">
+      <c r="T31" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U31" s="48">
-        <v>0</v>
-      </c>
-      <c r="V31" s="48" t="s">
+      <c r="U31" s="47">
+        <v>0</v>
+      </c>
+      <c r="V31" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="W31" s="45"/>
+      <c r="W31" s="44"/>
       <c r="Y31" s="15"/>
       <c r="Z31" s="15"/>
       <c r="AA31" s="15"/>
@@ -6393,10 +6412,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D32" s="98">
+      <c r="D32" s="97">
         <v>5939</v>
       </c>
-      <c r="E32" s="45" t="s">
+      <c r="E32" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F32" s="43">
@@ -6407,49 +6426,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H32" s="98">
+      <c r="H32" s="97">
         <v>9650</v>
       </c>
-      <c r="I32" s="76" t="s">
+      <c r="I32" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="J32" s="45">
+      <c r="J32" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K32" s="45">
+      <c r="K32" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L32" s="98">
+      <c r="L32" s="97">
         <v>6690</v>
       </c>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45">
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>3182.5</v>
       </c>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="46">
+      <c r="P32" s="44"/>
+      <c r="Q32" s="45">
         <v>1</v>
       </c>
-      <c r="R32" s="46" t="s">
+      <c r="R32" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S32" s="46">
+      <c r="S32" s="45">
         <v>325</v>
       </c>
-      <c r="T32" s="48" t="s">
+      <c r="T32" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U32" s="48">
-        <v>0</v>
-      </c>
-      <c r="V32" s="48" t="s">
+      <c r="U32" s="47">
+        <v>0</v>
+      </c>
+      <c r="V32" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="W32" s="45"/>
+      <c r="W32" s="44"/>
       <c r="Y32" s="15"/>
       <c r="Z32" s="15"/>
       <c r="AA32" s="15"/>
@@ -6469,7 +6488,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D33" s="98">
+      <c r="D33" s="97">
         <v>5939</v>
       </c>
       <c r="E33" s="43" t="s">
@@ -6483,43 +6502,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H33" s="98">
+      <c r="H33" s="97">
         <v>9650</v>
       </c>
-      <c r="I33" s="54" t="s">
+      <c r="I33" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="J33" s="45">
-        <v>0</v>
-      </c>
-      <c r="K33" s="45">
+      <c r="J33" s="44">
+        <v>0</v>
+      </c>
+      <c r="K33" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4662.5</v>
       </c>
-      <c r="L33" s="98"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="46">
+      <c r="L33" s="97"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="45">
         <v>1</v>
       </c>
-      <c r="R33" s="45" t="s">
+      <c r="R33" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S33" s="45">
+      <c r="S33" s="44">
         <v>325</v>
       </c>
-      <c r="T33" s="47" t="s">
+      <c r="T33" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="U33" s="48">
-        <v>0</v>
-      </c>
-      <c r="V33" s="47" t="s">
+      <c r="U33" s="47">
+        <v>0</v>
+      </c>
+      <c r="V33" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="W33" s="45"/>
+      <c r="W33" s="44"/>
       <c r="Y33" s="15"/>
       <c r="Z33" s="15"/>
       <c r="AA33" s="15"/>
@@ -6539,7 +6558,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D34" s="98">
+      <c r="D34" s="97">
         <v>5939</v>
       </c>
       <c r="E34" s="43" t="s">
@@ -6553,46 +6572,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H34" s="98">
+      <c r="H34" s="97">
         <v>9650</v>
       </c>
-      <c r="I34" s="54" t="s">
+      <c r="I34" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="J34" s="45">
+      <c r="J34" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>0</v>
       </c>
-      <c r="K34" s="45">
+      <c r="K34" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4662.5</v>
       </c>
-      <c r="L34" s="98">
+      <c r="L34" s="97">
         <v>9650</v>
       </c>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="46">
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="45">
         <v>1</v>
       </c>
-      <c r="R34" s="45" t="s">
+      <c r="R34" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S34" s="45">
+      <c r="S34" s="44">
         <v>325</v>
       </c>
       <c r="T34" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="U34" s="45">
-        <v>0</v>
-      </c>
-      <c r="V34" s="50" t="s">
+      <c r="U34" s="44">
+        <v>0</v>
+      </c>
+      <c r="V34" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="W34" s="45"/>
+      <c r="W34" s="44"/>
       <c r="Y34" s="15"/>
       <c r="Z34" s="15"/>
       <c r="AA34" s="15"/>
@@ -6601,78 +6620,74 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:32" ht="15">
-      <c r="A35" s="41" t="s">
+    <row r="35" spans="1:32" s="113" customFormat="1" ht="15">
+      <c r="A35" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="104">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D35" s="98">
+      <c r="D35" s="105">
         <v>5939</v>
       </c>
-      <c r="E35" s="43" t="s">
+      <c r="E35" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="F35" s="43">
+      <c r="F35" s="106">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1276.5</v>
       </c>
-      <c r="G35" s="43">
+      <c r="G35" s="106">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H35" s="98">
+      <c r="H35" s="105">
         <v>9650</v>
       </c>
-      <c r="I35" s="44" t="s">
+      <c r="I35" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="J35" s="45">
+      <c r="J35" s="108">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1480</v>
       </c>
-      <c r="K35" s="45">
+      <c r="K35" s="108">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L35" s="99">
+      <c r="L35" s="109">
         <v>6690</v>
       </c>
-      <c r="M35" s="45"/>
-      <c r="N35" s="45"/>
-      <c r="O35" s="45"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" s="46">
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="108"/>
+      <c r="Q35" s="110">
         <v>1</v>
       </c>
-      <c r="R35" s="46" t="s">
+      <c r="R35" s="110" t="s">
         <v>52</v>
       </c>
-      <c r="S35" s="72">
+      <c r="S35" s="106">
         <v>325</v>
       </c>
-      <c r="T35" s="47" t="s">
+      <c r="T35" s="111" t="s">
         <v>55</v>
       </c>
-      <c r="U35" s="48">
-        <v>0</v>
-      </c>
-      <c r="V35" s="47" t="s">
+      <c r="U35" s="112">
+        <v>0</v>
+      </c>
+      <c r="V35" s="111" t="s">
         <v>56</v>
       </c>
-      <c r="W35" s="45"/>
-      <c r="Y35" s="15"/>
-      <c r="Z35" s="15"/>
-      <c r="AA35" s="15"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
+      <c r="W35" s="108"/>
+      <c r="Y35" s="114"/>
+      <c r="Z35" s="114"/>
+      <c r="AA35" s="114"/>
     </row>
     <row r="36" spans="1:32" ht="15">
       <c r="A36" s="41" t="s">
@@ -6685,7 +6700,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D36" s="98">
+      <c r="D36" s="97">
         <v>5939</v>
       </c>
       <c r="E36" s="43" t="s">
@@ -6699,46 +6714,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H36" s="98">
+      <c r="H36" s="97">
         <v>9650</v>
       </c>
-      <c r="I36" s="54" t="s">
+      <c r="I36" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="J36" s="45">
+      <c r="J36" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>100</v>
       </c>
-      <c r="K36" s="45">
+      <c r="K36" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4562.5</v>
       </c>
-      <c r="L36" s="98">
+      <c r="L36" s="97">
         <v>9450</v>
       </c>
-      <c r="M36" s="45"/>
-      <c r="N36" s="45"/>
-      <c r="O36" s="45"/>
-      <c r="P36" s="45"/>
-      <c r="Q36" s="46">
+      <c r="M36" s="44"/>
+      <c r="N36" s="44"/>
+      <c r="O36" s="44"/>
+      <c r="P36" s="44"/>
+      <c r="Q36" s="45">
         <v>1</v>
       </c>
-      <c r="R36" s="45" t="s">
+      <c r="R36" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S36" s="45">
+      <c r="S36" s="44">
         <v>325</v>
       </c>
-      <c r="T36" s="47" t="s">
+      <c r="T36" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="U36" s="48">
-        <v>0</v>
-      </c>
-      <c r="V36" s="47" t="s">
+      <c r="U36" s="47">
+        <v>0</v>
+      </c>
+      <c r="V36" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="W36" s="45"/>
+      <c r="W36" s="44"/>
       <c r="Y36" s="15"/>
       <c r="Z36" s="15"/>
       <c r="AA36" s="15"/>
@@ -6758,7 +6773,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D37" s="98">
+      <c r="D37" s="97">
         <v>5939</v>
       </c>
       <c r="E37" s="43" t="s">
@@ -6772,47 +6787,47 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H37" s="98">
+      <c r="H37" s="97">
         <v>9650</v>
       </c>
-      <c r="I37" s="54" t="s">
+      <c r="I37" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="J37" s="45">
+      <c r="J37" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>500</v>
       </c>
-      <c r="K37" s="45">
+      <c r="K37" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4162.5</v>
       </c>
-      <c r="L37" s="98">
+      <c r="L37" s="97">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>8650</v>
       </c>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="45"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" s="46">
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="44"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="45">
         <v>1</v>
       </c>
-      <c r="R37" s="45" t="s">
+      <c r="R37" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S37" s="45">
+      <c r="S37" s="44">
         <v>325</v>
       </c>
-      <c r="T37" s="47" t="s">
+      <c r="T37" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="U37" s="48">
-        <v>0</v>
-      </c>
-      <c r="V37" s="47" t="s">
+      <c r="U37" s="47">
+        <v>0</v>
+      </c>
+      <c r="V37" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="W37" s="45"/>
+      <c r="W37" s="44"/>
       <c r="Y37" s="15"/>
       <c r="Z37" s="15"/>
       <c r="AA37" s="15"/>
@@ -6832,10 +6847,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D38" s="98">
+      <c r="D38" s="97">
         <v>5939</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F38" s="43">
@@ -6846,46 +6861,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H38" s="98">
+      <c r="H38" s="97">
         <v>9650</v>
       </c>
-      <c r="I38" s="54" t="s">
+      <c r="I38" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="J38" s="45">
+      <c r="J38" s="44">
         <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1025</v>
       </c>
-      <c r="K38" s="45">
+      <c r="K38" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3637.5</v>
       </c>
-      <c r="L38" s="98">
+      <c r="L38" s="97">
         <v>7600</v>
       </c>
-      <c r="M38" s="54"/>
-      <c r="N38" s="45"/>
-      <c r="O38" s="100"/>
-      <c r="P38" s="45"/>
-      <c r="Q38" s="46">
+      <c r="M38" s="53"/>
+      <c r="N38" s="44"/>
+      <c r="O38" s="99"/>
+      <c r="P38" s="44"/>
+      <c r="Q38" s="45">
         <v>1</v>
       </c>
-      <c r="R38" s="45" t="s">
+      <c r="R38" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S38" s="45">
+      <c r="S38" s="44">
         <v>325</v>
       </c>
-      <c r="T38" s="94" t="s">
+      <c r="T38" s="93" t="s">
         <v>55</v>
       </c>
       <c r="U38" s="20">
         <v>0</v>
       </c>
-      <c r="V38" s="96" t="s">
+      <c r="V38" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="W38" s="45"/>
+      <c r="W38" s="44"/>
       <c r="Y38" s="15"/>
       <c r="Z38" s="15"/>
       <c r="AA38" s="15"/>
@@ -6905,10 +6920,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D39" s="98">
+      <c r="D39" s="97">
         <v>3149</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F39" s="43">
@@ -6919,46 +6934,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H39" s="98">
+      <c r="H39" s="97">
         <v>5350</v>
       </c>
-      <c r="I39" s="54" t="s">
+      <c r="I39" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="J39" s="45">
-        <v>0</v>
-      </c>
-      <c r="K39" s="45">
+      <c r="J39" s="44">
+        <v>0</v>
+      </c>
+      <c r="K39" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2512.5</v>
       </c>
-      <c r="L39" s="99">
+      <c r="L39" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>5350</v>
       </c>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="46">
+      <c r="M39" s="44"/>
+      <c r="N39" s="44"/>
+      <c r="O39" s="44"/>
+      <c r="P39" s="44"/>
+      <c r="Q39" s="45">
         <v>1</v>
       </c>
-      <c r="R39" s="93" t="s">
+      <c r="R39" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="S39" s="72">
+      <c r="S39" s="71">
         <v>325</v>
       </c>
-      <c r="T39" s="48" t="s">
+      <c r="T39" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U39" s="48">
-        <v>0</v>
-      </c>
-      <c r="V39" s="48" t="s">
+      <c r="U39" s="47">
+        <v>0</v>
+      </c>
+      <c r="V39" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="W39" s="45"/>
+      <c r="W39" s="44"/>
       <c r="Y39" s="15"/>
       <c r="Z39" s="15"/>
       <c r="AA39" s="15"/>
@@ -6978,10 +6993,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D40" s="98">
+      <c r="D40" s="97">
         <v>3839</v>
       </c>
-      <c r="E40" s="45" t="s">
+      <c r="E40" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F40" s="43">
@@ -6992,49 +7007,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H40" s="98">
+      <c r="H40" s="97">
         <v>7450</v>
       </c>
-      <c r="I40" s="76" t="s">
+      <c r="I40" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="J40" s="45">
+      <c r="J40" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1230</v>
       </c>
-      <c r="K40" s="45">
+      <c r="K40" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L40" s="98">
+      <c r="L40" s="97">
         <v>4990</v>
       </c>
-      <c r="M40" s="45"/>
-      <c r="N40" s="45">
+      <c r="M40" s="44"/>
+      <c r="N40" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="O40" s="45">
+      <c r="O40" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="46">
+      <c r="P40" s="44"/>
+      <c r="Q40" s="45">
         <v>1</v>
       </c>
-      <c r="R40" s="46" t="s">
+      <c r="R40" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S40" s="46">
+      <c r="S40" s="45">
         <v>325</v>
       </c>
-      <c r="T40" s="48" t="s">
+      <c r="T40" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U40" s="48">
-        <v>0</v>
-      </c>
-      <c r="V40" s="48" t="s">
+      <c r="U40" s="47">
+        <v>0</v>
+      </c>
+      <c r="V40" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W40" s="4"/>
@@ -7049,17 +7064,17 @@
       <c r="A41" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="B41" s="89" t="s">
+      <c r="B41" s="88" t="s">
         <v>58</v>
       </c>
       <c r="C41" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D41" s="98">
+      <c r="D41" s="97">
         <v>3839</v>
       </c>
-      <c r="E41" s="45" t="s">
+      <c r="E41" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F41" s="43">
@@ -7070,49 +7085,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H41" s="98">
+      <c r="H41" s="97">
         <v>7450</v>
       </c>
-      <c r="I41" s="76" t="s">
+      <c r="I41" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="J41" s="45">
+      <c r="J41" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1230</v>
       </c>
-      <c r="K41" s="45">
+      <c r="K41" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L41" s="98">
+      <c r="L41" s="97">
         <v>4990</v>
       </c>
-      <c r="M41" s="45"/>
-      <c r="N41" s="45">
+      <c r="M41" s="44"/>
+      <c r="N41" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="O41" s="45">
+      <c r="O41" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P41" s="45"/>
-      <c r="Q41" s="46">
+      <c r="P41" s="44"/>
+      <c r="Q41" s="45">
         <v>1</v>
       </c>
-      <c r="R41" s="46" t="s">
+      <c r="R41" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S41" s="46">
+      <c r="S41" s="45">
         <v>325</v>
       </c>
-      <c r="T41" s="48" t="s">
+      <c r="T41" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U41" s="48">
-        <v>0</v>
-      </c>
-      <c r="V41" s="48" t="s">
+      <c r="U41" s="47">
+        <v>0</v>
+      </c>
+      <c r="V41" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W41" s="4"/>
@@ -7135,10 +7150,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D42" s="98">
+      <c r="D42" s="97">
         <v>3839</v>
       </c>
-      <c r="E42" s="45" t="s">
+      <c r="E42" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F42" s="43">
@@ -7149,49 +7164,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H42" s="98">
+      <c r="H42" s="97">
         <v>7450</v>
       </c>
-      <c r="I42" s="76" t="s">
+      <c r="I42" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="J42" s="45">
+      <c r="J42" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1230</v>
       </c>
-      <c r="K42" s="45">
+      <c r="K42" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L42" s="98">
+      <c r="L42" s="97">
         <v>4990</v>
       </c>
-      <c r="M42" s="45"/>
-      <c r="N42" s="45">
+      <c r="M42" s="44"/>
+      <c r="N42" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="O42" s="45">
+      <c r="O42" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P42" s="45"/>
-      <c r="Q42" s="46">
+      <c r="P42" s="44"/>
+      <c r="Q42" s="45">
         <v>1</v>
       </c>
-      <c r="R42" s="46" t="s">
+      <c r="R42" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S42" s="46">
+      <c r="S42" s="45">
         <v>325</v>
       </c>
-      <c r="T42" s="48" t="s">
+      <c r="T42" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U42" s="48">
-        <v>0</v>
-      </c>
-      <c r="V42" s="48" t="s">
+      <c r="U42" s="47">
+        <v>0</v>
+      </c>
+      <c r="V42" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W42" s="4"/>
@@ -7214,10 +7229,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D43" s="98">
+      <c r="D43" s="97">
         <v>3839</v>
       </c>
-      <c r="E43" s="45" t="s">
+      <c r="E43" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F43" s="43">
@@ -7228,49 +7243,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H43" s="98">
+      <c r="H43" s="97">
         <v>7450</v>
       </c>
-      <c r="I43" s="76" t="s">
+      <c r="I43" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="J43" s="45">
+      <c r="J43" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1230</v>
       </c>
-      <c r="K43" s="45">
+      <c r="K43" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L43" s="98">
+      <c r="L43" s="97">
         <v>4990</v>
       </c>
-      <c r="M43" s="45"/>
-      <c r="N43" s="45">
+      <c r="M43" s="44"/>
+      <c r="N43" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="O43" s="45">
+      <c r="O43" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P43" s="45"/>
-      <c r="Q43" s="46">
+      <c r="P43" s="44"/>
+      <c r="Q43" s="45">
         <v>1</v>
       </c>
-      <c r="R43" s="46" t="s">
+      <c r="R43" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S43" s="46">
+      <c r="S43" s="45">
         <v>325</v>
       </c>
-      <c r="T43" s="48" t="s">
+      <c r="T43" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U43" s="48">
-        <v>0</v>
-      </c>
-      <c r="V43" s="48" t="s">
+      <c r="U43" s="47">
+        <v>0</v>
+      </c>
+      <c r="V43" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W43" s="4"/>
@@ -7286,17 +7301,17 @@
       <c r="A44" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="89" t="s">
+      <c r="B44" s="88" t="s">
         <v>58</v>
       </c>
       <c r="C44" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D44" s="98">
+      <c r="D44" s="97">
         <v>3839</v>
       </c>
-      <c r="E44" s="45" t="s">
+      <c r="E44" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F44" s="43">
@@ -7307,46 +7322,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H44" s="98">
+      <c r="H44" s="97">
         <v>7450</v>
       </c>
-      <c r="I44" s="76" t="s">
+      <c r="I44" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="J44" s="45">
+      <c r="J44" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1230</v>
       </c>
-      <c r="K44" s="45">
+      <c r="K44" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L44" s="98">
+      <c r="L44" s="97">
         <v>4990</v>
       </c>
-      <c r="M44" s="45"/>
-      <c r="N44" s="45"/>
-      <c r="O44" s="45">
+      <c r="M44" s="44"/>
+      <c r="N44" s="44"/>
+      <c r="O44" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2332.5</v>
       </c>
-      <c r="P44" s="45"/>
-      <c r="Q44" s="46">
+      <c r="P44" s="44"/>
+      <c r="Q44" s="45">
         <v>1</v>
       </c>
-      <c r="R44" s="46" t="s">
+      <c r="R44" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S44" s="46">
+      <c r="S44" s="45">
         <v>325</v>
       </c>
-      <c r="T44" s="48" t="s">
+      <c r="T44" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U44" s="48">
-        <v>0</v>
-      </c>
-      <c r="V44" s="48" t="s">
+      <c r="U44" s="47">
+        <v>0</v>
+      </c>
+      <c r="V44" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W44" s="4"/>
@@ -7369,10 +7384,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D45" s="98">
+      <c r="D45" s="97">
         <v>3839</v>
       </c>
-      <c r="E45" s="45" t="s">
+      <c r="E45" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F45" s="43">
@@ -7383,46 +7398,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H45" s="98">
+      <c r="H45" s="97">
         <v>7450</v>
       </c>
-      <c r="I45" s="76" t="s">
+      <c r="I45" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="J45" s="45">
+      <c r="J45" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1230</v>
       </c>
-      <c r="K45" s="45">
+      <c r="K45" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L45" s="98">
+      <c r="L45" s="97">
         <v>4990</v>
       </c>
-      <c r="M45" s="45"/>
-      <c r="N45" s="45"/>
-      <c r="O45" s="45">
+      <c r="M45" s="44"/>
+      <c r="N45" s="44"/>
+      <c r="O45" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2332.5</v>
       </c>
-      <c r="P45" s="45"/>
-      <c r="Q45" s="46">
+      <c r="P45" s="44"/>
+      <c r="Q45" s="45">
         <v>1</v>
       </c>
-      <c r="R45" s="46" t="s">
+      <c r="R45" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S45" s="46">
+      <c r="S45" s="45">
         <v>325</v>
       </c>
-      <c r="T45" s="48" t="s">
+      <c r="T45" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U45" s="48">
-        <v>0</v>
-      </c>
-      <c r="V45" s="48" t="s">
+      <c r="U45" s="47">
+        <v>0</v>
+      </c>
+      <c r="V45" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W45" s="4"/>
@@ -7438,17 +7453,17 @@
       <c r="A46" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="89" t="s">
+      <c r="B46" s="88" t="s">
         <v>58</v>
       </c>
       <c r="C46" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D46" s="98">
+      <c r="D46" s="97">
         <v>3839</v>
       </c>
-      <c r="E46" s="45" t="s">
+      <c r="E46" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F46" s="43">
@@ -7459,46 +7474,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H46" s="98">
+      <c r="H46" s="97">
         <v>7450</v>
       </c>
-      <c r="I46" s="76" t="s">
+      <c r="I46" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="J46" s="45">
+      <c r="J46" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1230</v>
       </c>
-      <c r="K46" s="45">
+      <c r="K46" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L46" s="98">
+      <c r="L46" s="97">
         <v>4990</v>
       </c>
-      <c r="M46" s="45"/>
-      <c r="N46" s="45"/>
-      <c r="O46" s="45">
+      <c r="M46" s="44"/>
+      <c r="N46" s="44"/>
+      <c r="O46" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2332.5</v>
       </c>
-      <c r="P46" s="45"/>
-      <c r="Q46" s="46">
+      <c r="P46" s="44"/>
+      <c r="Q46" s="45">
         <v>1</v>
       </c>
-      <c r="R46" s="46" t="s">
+      <c r="R46" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S46" s="46">
+      <c r="S46" s="45">
         <v>325</v>
       </c>
-      <c r="T46" s="48" t="s">
+      <c r="T46" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U46" s="48">
-        <v>0</v>
-      </c>
-      <c r="V46" s="48" t="s">
+      <c r="U46" s="47">
+        <v>0</v>
+      </c>
+      <c r="V46" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W46" s="4"/>
@@ -7521,10 +7536,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D47" s="98">
+      <c r="D47" s="97">
         <v>3839</v>
       </c>
-      <c r="E47" s="45" t="s">
+      <c r="E47" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F47" s="43">
@@ -7535,46 +7550,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H47" s="98">
+      <c r="H47" s="97">
         <v>7450</v>
       </c>
-      <c r="I47" s="76" t="s">
+      <c r="I47" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="J47" s="45">
+      <c r="J47" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1230</v>
       </c>
-      <c r="K47" s="45">
+      <c r="K47" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L47" s="98">
+      <c r="L47" s="97">
         <v>4990</v>
       </c>
-      <c r="M47" s="45"/>
-      <c r="N47" s="45"/>
-      <c r="O47" s="45">
+      <c r="M47" s="44"/>
+      <c r="N47" s="44"/>
+      <c r="O47" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2332.5</v>
       </c>
-      <c r="P47" s="45"/>
-      <c r="Q47" s="46">
+      <c r="P47" s="44"/>
+      <c r="Q47" s="45">
         <v>1</v>
       </c>
-      <c r="R47" s="46" t="s">
+      <c r="R47" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S47" s="46">
+      <c r="S47" s="45">
         <v>325</v>
       </c>
-      <c r="T47" s="48" t="s">
+      <c r="T47" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U47" s="48">
-        <v>0</v>
-      </c>
-      <c r="V47" s="48" t="s">
+      <c r="U47" s="47">
+        <v>0</v>
+      </c>
+      <c r="V47" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W47" s="4"/>
@@ -7590,17 +7605,17 @@
       <c r="A48" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="89" t="s">
+      <c r="B48" s="88" t="s">
         <v>58</v>
       </c>
       <c r="C48" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D48" s="98">
+      <c r="D48" s="97">
         <v>3839</v>
       </c>
-      <c r="E48" s="45" t="s">
+      <c r="E48" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F48" s="43">
@@ -7611,46 +7626,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H48" s="98">
+      <c r="H48" s="97">
         <v>7450</v>
       </c>
-      <c r="I48" s="76" t="s">
+      <c r="I48" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="J48" s="45">
+      <c r="J48" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1230</v>
       </c>
-      <c r="K48" s="45">
+      <c r="K48" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L48" s="98">
+      <c r="L48" s="97">
         <v>4990</v>
       </c>
-      <c r="M48" s="45"/>
-      <c r="N48" s="45"/>
-      <c r="O48" s="45">
+      <c r="M48" s="44"/>
+      <c r="N48" s="44"/>
+      <c r="O48" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2332.5</v>
       </c>
-      <c r="P48" s="45"/>
-      <c r="Q48" s="46">
+      <c r="P48" s="44"/>
+      <c r="Q48" s="45">
         <v>1</v>
       </c>
-      <c r="R48" s="46" t="s">
+      <c r="R48" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S48" s="46">
+      <c r="S48" s="45">
         <v>325</v>
       </c>
-      <c r="T48" s="48" t="s">
+      <c r="T48" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U48" s="48">
-        <v>0</v>
-      </c>
-      <c r="V48" s="48" t="s">
+      <c r="U48" s="47">
+        <v>0</v>
+      </c>
+      <c r="V48" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W48" s="4"/>
@@ -7673,10 +7688,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D49" s="98">
+      <c r="D49" s="97">
         <v>3839</v>
       </c>
-      <c r="E49" s="45" t="s">
+      <c r="E49" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F49" s="43">
@@ -7687,43 +7702,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H49" s="98">
+      <c r="H49" s="97">
         <v>7450</v>
       </c>
-      <c r="I49" s="54" t="s">
+      <c r="I49" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="J49" s="45">
-        <v>0</v>
-      </c>
-      <c r="K49" s="45">
+      <c r="J49" s="44">
+        <v>0</v>
+      </c>
+      <c r="K49" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3562.5</v>
       </c>
-      <c r="L49" s="99">
+      <c r="L49" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>7450</v>
       </c>
-      <c r="M49" s="45"/>
-      <c r="N49" s="45"/>
-      <c r="O49" s="45"/>
-      <c r="P49" s="45"/>
-      <c r="Q49" s="46">
+      <c r="M49" s="44"/>
+      <c r="N49" s="44"/>
+      <c r="O49" s="44"/>
+      <c r="P49" s="44"/>
+      <c r="Q49" s="45">
         <v>1</v>
       </c>
-      <c r="R49" s="45" t="s">
+      <c r="R49" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S49" s="45">
+      <c r="S49" s="44">
         <v>325</v>
       </c>
-      <c r="T49" s="48" t="s">
+      <c r="T49" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U49" s="48">
-        <v>0</v>
-      </c>
-      <c r="V49" s="48" t="s">
+      <c r="U49" s="47">
+        <v>0</v>
+      </c>
+      <c r="V49" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W49" s="4"/>
@@ -7746,10 +7761,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D50" s="98">
+      <c r="D50" s="97">
         <v>3839</v>
       </c>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F50" s="43">
@@ -7760,43 +7775,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H50" s="98">
+      <c r="H50" s="97">
         <v>7450</v>
       </c>
-      <c r="I50" s="76" t="s">
+      <c r="I50" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="J50" s="45">
+      <c r="J50" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>0</v>
       </c>
-      <c r="K50" s="45">
+      <c r="K50" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3562.5</v>
       </c>
-      <c r="L50" s="98">
+      <c r="L50" s="97">
         <v>7450</v>
       </c>
-      <c r="M50" s="45"/>
-      <c r="N50" s="45"/>
-      <c r="O50" s="45"/>
-      <c r="P50" s="45"/>
-      <c r="Q50" s="46">
+      <c r="M50" s="44"/>
+      <c r="N50" s="44"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="45">
         <v>1</v>
       </c>
-      <c r="R50" s="46" t="s">
+      <c r="R50" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S50" s="91">
+      <c r="S50" s="90">
         <v>325</v>
       </c>
-      <c r="T50" s="48" t="s">
+      <c r="T50" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U50" s="48">
-        <v>0</v>
-      </c>
-      <c r="V50" s="48" t="s">
+      <c r="U50" s="47">
+        <v>0</v>
+      </c>
+      <c r="V50" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W50" s="4"/>
@@ -7819,10 +7834,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D51" s="98">
+      <c r="D51" s="97">
         <v>3839</v>
       </c>
-      <c r="E51" s="45" t="s">
+      <c r="E51" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F51" s="43">
@@ -7833,44 +7848,44 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H51" s="98">
+      <c r="H51" s="97">
         <v>7450</v>
       </c>
-      <c r="I51" s="54" t="s">
+      <c r="I51" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="J51" s="45">
+      <c r="J51" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>500</v>
       </c>
-      <c r="K51" s="45">
+      <c r="K51" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3062.5</v>
       </c>
-      <c r="L51" s="98">
+      <c r="L51" s="97">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>6450</v>
       </c>
-      <c r="M51" s="45"/>
-      <c r="N51" s="45"/>
-      <c r="O51" s="45"/>
-      <c r="P51" s="45"/>
-      <c r="Q51" s="46">
+      <c r="M51" s="44"/>
+      <c r="N51" s="44"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
+      <c r="Q51" s="45">
         <v>1</v>
       </c>
-      <c r="R51" s="45" t="s">
+      <c r="R51" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S51" s="45">
+      <c r="S51" s="44">
         <v>325</v>
       </c>
-      <c r="T51" s="48" t="s">
+      <c r="T51" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U51" s="48">
-        <v>0</v>
-      </c>
-      <c r="V51" s="48" t="s">
+      <c r="U51" s="47">
+        <v>0</v>
+      </c>
+      <c r="V51" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W51" s="4"/>
@@ -7893,10 +7908,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D52" s="98">
+      <c r="D52" s="97">
         <v>3839</v>
       </c>
-      <c r="E52" s="45" t="s">
+      <c r="E52" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F52" s="43">
@@ -7907,43 +7922,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H52" s="98">
+      <c r="H52" s="97">
         <v>7450</v>
       </c>
-      <c r="I52" s="54" t="s">
+      <c r="I52" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="J52" s="45">
+      <c r="J52" s="44">
         <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>825</v>
       </c>
-      <c r="K52" s="45">
+      <c r="K52" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2737.5</v>
       </c>
-      <c r="L52" s="98">
+      <c r="L52" s="97">
         <v>5800</v>
       </c>
-      <c r="M52" s="54"/>
-      <c r="N52" s="45"/>
-      <c r="O52" s="100"/>
-      <c r="P52" s="45"/>
-      <c r="Q52" s="46">
+      <c r="M52" s="53"/>
+      <c r="N52" s="44"/>
+      <c r="O52" s="99"/>
+      <c r="P52" s="44"/>
+      <c r="Q52" s="45">
         <v>1</v>
       </c>
-      <c r="R52" s="45" t="s">
+      <c r="R52" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S52" s="45">
+      <c r="S52" s="44">
         <v>325</v>
       </c>
-      <c r="T52" s="94" t="s">
+      <c r="T52" s="93" t="s">
         <v>55</v>
       </c>
       <c r="U52" s="20">
         <v>0</v>
       </c>
-      <c r="V52" s="96" t="s">
+      <c r="V52" s="95" t="s">
         <v>56</v>
       </c>
       <c r="W52" s="4"/>
@@ -7966,10 +7981,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D53" s="98">
+      <c r="D53" s="97">
         <v>5039</v>
       </c>
-      <c r="E53" s="45" t="s">
+      <c r="E53" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F53" s="43">
@@ -7980,43 +7995,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H53" s="98">
+      <c r="H53" s="97">
         <v>8550</v>
       </c>
-      <c r="I53" s="54" t="s">
+      <c r="I53" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="J53" s="45">
-        <v>0</v>
-      </c>
-      <c r="K53" s="45">
+      <c r="J53" s="44">
+        <v>0</v>
+      </c>
+      <c r="K53" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4112.5</v>
       </c>
-      <c r="L53" s="98">
+      <c r="L53" s="97">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>8550</v>
       </c>
-      <c r="M53" s="45"/>
-      <c r="N53" s="45"/>
-      <c r="O53" s="45"/>
-      <c r="P53" s="45"/>
-      <c r="Q53" s="46">
+      <c r="M53" s="44"/>
+      <c r="N53" s="44"/>
+      <c r="O53" s="44"/>
+      <c r="P53" s="44"/>
+      <c r="Q53" s="45">
         <v>1</v>
       </c>
-      <c r="R53" s="45" t="s">
+      <c r="R53" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S53" s="45">
+      <c r="S53" s="44">
         <v>325</v>
       </c>
-      <c r="T53" s="48" t="s">
+      <c r="T53" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U53" s="48">
-        <v>0</v>
-      </c>
-      <c r="V53" s="48" t="s">
+      <c r="U53" s="47">
+        <v>0</v>
+      </c>
+      <c r="V53" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W53" s="4"/>
@@ -8032,17 +8047,17 @@
       <c r="A54" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="89" t="s">
+      <c r="B54" s="88" t="s">
         <v>60</v>
       </c>
       <c r="C54" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D54" s="98">
+      <c r="D54" s="97">
         <v>5039</v>
       </c>
-      <c r="E54" s="45" t="s">
+      <c r="E54" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F54" s="43">
@@ -8053,49 +8068,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H54" s="98">
+      <c r="H54" s="97">
         <v>8550</v>
       </c>
-      <c r="I54" s="76" t="s">
+      <c r="I54" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="J54" s="45">
+      <c r="J54" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1380</v>
       </c>
-      <c r="K54" s="45">
+      <c r="K54" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L54" s="98">
+      <c r="L54" s="97">
         <v>5790</v>
       </c>
-      <c r="M54" s="45"/>
-      <c r="N54" s="45">
+      <c r="M54" s="44"/>
+      <c r="N54" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="O54" s="45">
+      <c r="O54" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P54" s="45"/>
-      <c r="Q54" s="46">
+      <c r="P54" s="44"/>
+      <c r="Q54" s="45">
         <v>1</v>
       </c>
-      <c r="R54" s="46" t="s">
+      <c r="R54" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S54" s="46">
+      <c r="S54" s="45">
         <v>325</v>
       </c>
-      <c r="T54" s="48" t="s">
+      <c r="T54" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U54" s="48">
-        <v>0</v>
-      </c>
-      <c r="V54" s="48" t="s">
+      <c r="U54" s="47">
+        <v>0</v>
+      </c>
+      <c r="V54" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W54" s="4"/>
@@ -8118,10 +8133,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D55" s="98">
+      <c r="D55" s="97">
         <v>5039</v>
       </c>
-      <c r="E55" s="45" t="s">
+      <c r="E55" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F55" s="43">
@@ -8132,43 +8147,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H55" s="98">
+      <c r="H55" s="97">
         <v>8550</v>
       </c>
-      <c r="I55" s="76" t="s">
+      <c r="I55" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="J55" s="45">
+      <c r="J55" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1280</v>
       </c>
-      <c r="K55" s="45">
+      <c r="K55" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2832.5</v>
       </c>
-      <c r="L55" s="98">
+      <c r="L55" s="97">
         <v>5990</v>
       </c>
-      <c r="M55" s="45"/>
-      <c r="N55" s="45"/>
-      <c r="O55" s="45"/>
-      <c r="P55" s="45"/>
-      <c r="Q55" s="46">
+      <c r="M55" s="44"/>
+      <c r="N55" s="44"/>
+      <c r="O55" s="44"/>
+      <c r="P55" s="44"/>
+      <c r="Q55" s="45">
         <v>1</v>
       </c>
-      <c r="R55" s="46" t="s">
+      <c r="R55" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S55" s="91">
+      <c r="S55" s="90">
         <v>325</v>
       </c>
-      <c r="T55" s="48" t="s">
+      <c r="T55" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U55" s="48">
-        <v>0</v>
-      </c>
-      <c r="V55" s="48" t="s">
+      <c r="U55" s="47">
+        <v>0</v>
+      </c>
+      <c r="V55" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W55" s="4"/>
@@ -8191,10 +8206,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D56" s="98">
+      <c r="D56" s="97">
         <v>5039</v>
       </c>
-      <c r="E56" s="45" t="s">
+      <c r="E56" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F56" s="43">
@@ -8205,43 +8220,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H56" s="98">
+      <c r="H56" s="97">
         <v>8550</v>
       </c>
-      <c r="I56" s="54" t="s">
+      <c r="I56" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="J56" s="45">
+      <c r="J56" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>100</v>
       </c>
-      <c r="K56" s="45">
+      <c r="K56" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4012.5</v>
       </c>
-      <c r="L56" s="98">
+      <c r="L56" s="97">
         <v>8350</v>
       </c>
-      <c r="M56" s="45"/>
-      <c r="N56" s="45"/>
-      <c r="O56" s="45"/>
-      <c r="P56" s="45"/>
-      <c r="Q56" s="46">
+      <c r="M56" s="44"/>
+      <c r="N56" s="44"/>
+      <c r="O56" s="44"/>
+      <c r="P56" s="44"/>
+      <c r="Q56" s="45">
         <v>1</v>
       </c>
-      <c r="R56" s="45" t="s">
+      <c r="R56" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S56" s="45">
+      <c r="S56" s="44">
         <v>325</v>
       </c>
-      <c r="T56" s="48" t="s">
+      <c r="T56" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U56" s="48">
-        <v>0</v>
-      </c>
-      <c r="V56" s="48" t="s">
+      <c r="U56" s="47">
+        <v>0</v>
+      </c>
+      <c r="V56" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W56" s="4"/>
@@ -8264,10 +8279,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D57" s="98">
+      <c r="D57" s="97">
         <v>5039</v>
       </c>
-      <c r="E57" s="45" t="s">
+      <c r="E57" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F57" s="43">
@@ -8278,49 +8293,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H57" s="98">
+      <c r="H57" s="97">
         <v>8550</v>
       </c>
-      <c r="I57" s="76" t="s">
+      <c r="I57" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="J57" s="45">
+      <c r="J57" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1380</v>
       </c>
-      <c r="K57" s="45">
+      <c r="K57" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L57" s="98">
+      <c r="L57" s="97">
         <v>5790</v>
       </c>
-      <c r="M57" s="45"/>
-      <c r="N57" s="45">
+      <c r="M57" s="44"/>
+      <c r="N57" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="O57" s="45">
+      <c r="O57" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P57" s="45"/>
-      <c r="Q57" s="46">
+      <c r="P57" s="44"/>
+      <c r="Q57" s="45">
         <v>1</v>
       </c>
-      <c r="R57" s="46" t="s">
+      <c r="R57" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S57" s="46">
+      <c r="S57" s="45">
         <v>325</v>
       </c>
-      <c r="T57" s="48" t="s">
+      <c r="T57" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U57" s="48">
-        <v>0</v>
-      </c>
-      <c r="V57" s="48" t="s">
+      <c r="U57" s="47">
+        <v>0</v>
+      </c>
+      <c r="V57" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W57" s="4"/>
@@ -8336,17 +8351,17 @@
       <c r="A58" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="89" t="s">
+      <c r="B58" s="88" t="s">
         <v>60</v>
       </c>
       <c r="C58" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D58" s="98">
+      <c r="D58" s="97">
         <v>5039</v>
       </c>
-      <c r="E58" s="45" t="s">
+      <c r="E58" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F58" s="43">
@@ -8357,49 +8372,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H58" s="98">
+      <c r="H58" s="97">
         <v>8550</v>
       </c>
-      <c r="I58" s="76" t="s">
+      <c r="I58" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="J58" s="45">
+      <c r="J58" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1380</v>
       </c>
-      <c r="K58" s="45">
+      <c r="K58" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L58" s="98">
+      <c r="L58" s="97">
         <v>5790</v>
       </c>
-      <c r="M58" s="45"/>
-      <c r="N58" s="45">
+      <c r="M58" s="44"/>
+      <c r="N58" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="O58" s="45">
+      <c r="O58" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P58" s="45"/>
-      <c r="Q58" s="46">
+      <c r="P58" s="44"/>
+      <c r="Q58" s="45">
         <v>1</v>
       </c>
-      <c r="R58" s="46" t="s">
+      <c r="R58" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S58" s="46">
+      <c r="S58" s="45">
         <v>325</v>
       </c>
-      <c r="T58" s="48" t="s">
+      <c r="T58" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U58" s="48">
-        <v>0</v>
-      </c>
-      <c r="V58" s="48" t="s">
+      <c r="U58" s="47">
+        <v>0</v>
+      </c>
+      <c r="V58" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W58" s="4"/>
@@ -8415,17 +8430,17 @@
       <c r="A59" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="89" t="s">
+      <c r="B59" s="88" t="s">
         <v>60</v>
       </c>
       <c r="C59" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D59" s="98">
+      <c r="D59" s="97">
         <v>5039</v>
       </c>
-      <c r="E59" s="45" t="s">
+      <c r="E59" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F59" s="43">
@@ -8436,49 +8451,49 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H59" s="98">
+      <c r="H59" s="97">
         <v>8550</v>
       </c>
-      <c r="I59" s="76" t="s">
+      <c r="I59" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="J59" s="45">
+      <c r="J59" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1380</v>
       </c>
-      <c r="K59" s="45">
+      <c r="K59" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L59" s="98">
+      <c r="L59" s="97">
         <v>5790</v>
       </c>
-      <c r="M59" s="45"/>
-      <c r="N59" s="45">
+      <c r="M59" s="44"/>
+      <c r="N59" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="O59" s="45">
+      <c r="O59" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P59" s="45"/>
-      <c r="Q59" s="46">
+      <c r="P59" s="44"/>
+      <c r="Q59" s="45">
         <v>1</v>
       </c>
-      <c r="R59" s="46" t="s">
+      <c r="R59" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S59" s="46">
+      <c r="S59" s="45">
         <v>325</v>
       </c>
-      <c r="T59" s="48" t="s">
+      <c r="T59" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U59" s="48">
-        <v>0</v>
-      </c>
-      <c r="V59" s="48" t="s">
+      <c r="U59" s="47">
+        <v>0</v>
+      </c>
+      <c r="V59" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W59" s="4"/>
@@ -8501,10 +8516,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D60" s="98">
+      <c r="D60" s="97">
         <v>5039</v>
       </c>
-      <c r="E60" s="45" t="s">
+      <c r="E60" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F60" s="43">
@@ -8515,44 +8530,44 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H60" s="98">
+      <c r="H60" s="97">
         <v>8550</v>
       </c>
-      <c r="I60" s="54" t="s">
+      <c r="I60" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="J60" s="45">
+      <c r="J60" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>500</v>
       </c>
-      <c r="K60" s="45">
+      <c r="K60" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3612.5</v>
       </c>
-      <c r="L60" s="98">
+      <c r="L60" s="97">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>7550</v>
       </c>
-      <c r="M60" s="45"/>
-      <c r="N60" s="45"/>
-      <c r="O60" s="45"/>
-      <c r="P60" s="45"/>
-      <c r="Q60" s="46">
+      <c r="M60" s="44"/>
+      <c r="N60" s="44"/>
+      <c r="O60" s="44"/>
+      <c r="P60" s="44"/>
+      <c r="Q60" s="45">
         <v>1</v>
       </c>
-      <c r="R60" s="45" t="s">
+      <c r="R60" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S60" s="45">
+      <c r="S60" s="44">
         <v>325</v>
       </c>
-      <c r="T60" s="48" t="s">
+      <c r="T60" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U60" s="48">
-        <v>0</v>
-      </c>
-      <c r="V60" s="48" t="s">
+      <c r="U60" s="47">
+        <v>0</v>
+      </c>
+      <c r="V60" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W60" s="4"/>
@@ -8575,10 +8590,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D61" s="98">
+      <c r="D61" s="97">
         <v>5039</v>
       </c>
-      <c r="E61" s="45" t="s">
+      <c r="E61" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F61" s="43">
@@ -8589,46 +8604,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H61" s="98">
+      <c r="H61" s="97">
         <v>8550</v>
       </c>
-      <c r="I61" s="76" t="s">
+      <c r="I61" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="J61" s="45">
+      <c r="J61" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1380</v>
       </c>
-      <c r="K61" s="45">
+      <c r="K61" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L61" s="98">
+      <c r="L61" s="97">
         <v>5790</v>
       </c>
-      <c r="M61" s="45"/>
-      <c r="N61" s="45"/>
-      <c r="O61" s="45">
+      <c r="M61" s="44"/>
+      <c r="N61" s="44"/>
+      <c r="O61" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2732.5</v>
       </c>
-      <c r="P61" s="45"/>
-      <c r="Q61" s="46">
+      <c r="P61" s="44"/>
+      <c r="Q61" s="45">
         <v>1</v>
       </c>
-      <c r="R61" s="46" t="s">
+      <c r="R61" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S61" s="46">
+      <c r="S61" s="45">
         <v>325</v>
       </c>
-      <c r="T61" s="48" t="s">
+      <c r="T61" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U61" s="48">
-        <v>0</v>
-      </c>
-      <c r="V61" s="48" t="s">
+      <c r="U61" s="47">
+        <v>0</v>
+      </c>
+      <c r="V61" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W61" s="4"/>
@@ -8644,17 +8659,17 @@
       <c r="A62" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="89" t="s">
+      <c r="B62" s="88" t="s">
         <v>60</v>
       </c>
       <c r="C62" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D62" s="98">
+      <c r="D62" s="97">
         <v>5039</v>
       </c>
-      <c r="E62" s="45" t="s">
+      <c r="E62" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F62" s="43">
@@ -8665,46 +8680,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H62" s="98">
+      <c r="H62" s="97">
         <v>8550</v>
       </c>
-      <c r="I62" s="76" t="s">
+      <c r="I62" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="J62" s="45">
+      <c r="J62" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1380</v>
       </c>
-      <c r="K62" s="45">
+      <c r="K62" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L62" s="98">
+      <c r="L62" s="97">
         <v>5790</v>
       </c>
-      <c r="M62" s="45"/>
-      <c r="N62" s="45"/>
-      <c r="O62" s="45">
+      <c r="M62" s="44"/>
+      <c r="N62" s="44"/>
+      <c r="O62" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2732.5</v>
       </c>
-      <c r="P62" s="45"/>
-      <c r="Q62" s="46">
+      <c r="P62" s="44"/>
+      <c r="Q62" s="45">
         <v>1</v>
       </c>
-      <c r="R62" s="46" t="s">
+      <c r="R62" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S62" s="46">
+      <c r="S62" s="45">
         <v>325</v>
       </c>
-      <c r="T62" s="48" t="s">
+      <c r="T62" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U62" s="48">
-        <v>0</v>
-      </c>
-      <c r="V62" s="48" t="s">
+      <c r="U62" s="47">
+        <v>0</v>
+      </c>
+      <c r="V62" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W62" s="4"/>
@@ -8727,10 +8742,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D63" s="98">
+      <c r="D63" s="97">
         <v>5039</v>
       </c>
-      <c r="E63" s="45" t="s">
+      <c r="E63" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F63" s="43">
@@ -8741,43 +8756,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H63" s="98">
+      <c r="H63" s="97">
         <v>8550</v>
       </c>
-      <c r="I63" s="54" t="s">
+      <c r="I63" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="J63" s="45">
+      <c r="J63" s="44">
         <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>975</v>
       </c>
-      <c r="K63" s="45">
+      <c r="K63" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3137.5</v>
       </c>
-      <c r="L63" s="98">
+      <c r="L63" s="97">
         <v>6600</v>
       </c>
-      <c r="M63" s="54"/>
-      <c r="N63" s="45"/>
-      <c r="O63" s="100"/>
-      <c r="P63" s="45"/>
-      <c r="Q63" s="46">
+      <c r="M63" s="53"/>
+      <c r="N63" s="44"/>
+      <c r="O63" s="99"/>
+      <c r="P63" s="44"/>
+      <c r="Q63" s="45">
         <v>1</v>
       </c>
-      <c r="R63" s="45" t="s">
+      <c r="R63" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S63" s="45">
+      <c r="S63" s="44">
         <v>325</v>
       </c>
-      <c r="T63" s="94" t="s">
+      <c r="T63" s="93" t="s">
         <v>55</v>
       </c>
       <c r="U63" s="20">
         <v>0</v>
       </c>
-      <c r="V63" s="96" t="s">
+      <c r="V63" s="95" t="s">
         <v>56</v>
       </c>
       <c r="W63" s="4"/>
@@ -8800,10 +8815,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D64" s="98">
+      <c r="D64" s="97">
         <v>5039</v>
       </c>
-      <c r="E64" s="45" t="s">
+      <c r="E64" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F64" s="43">
@@ -8814,46 +8829,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H64" s="98">
+      <c r="H64" s="97">
         <v>8550</v>
       </c>
-      <c r="I64" s="76" t="s">
+      <c r="I64" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="J64" s="45">
+      <c r="J64" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1380</v>
       </c>
-      <c r="K64" s="45">
+      <c r="K64" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L64" s="98">
+      <c r="L64" s="97">
         <v>5790</v>
       </c>
-      <c r="M64" s="45"/>
-      <c r="N64" s="45"/>
-      <c r="O64" s="45">
+      <c r="M64" s="44"/>
+      <c r="N64" s="44"/>
+      <c r="O64" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2732.5</v>
       </c>
-      <c r="P64" s="45"/>
-      <c r="Q64" s="46">
+      <c r="P64" s="44"/>
+      <c r="Q64" s="45">
         <v>1</v>
       </c>
-      <c r="R64" s="46" t="s">
+      <c r="R64" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S64" s="46">
+      <c r="S64" s="45">
         <v>325</v>
       </c>
-      <c r="T64" s="48" t="s">
+      <c r="T64" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U64" s="48">
-        <v>0</v>
-      </c>
-      <c r="V64" s="48" t="s">
+      <c r="U64" s="47">
+        <v>0</v>
+      </c>
+      <c r="V64" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W64" s="4"/>
@@ -8869,17 +8884,17 @@
       <c r="A65" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B65" s="89" t="s">
+      <c r="B65" s="88" t="s">
         <v>60</v>
       </c>
       <c r="C65" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D65" s="98">
+      <c r="D65" s="97">
         <v>5039</v>
       </c>
-      <c r="E65" s="45" t="s">
+      <c r="E65" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F65" s="43">
@@ -8890,46 +8905,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H65" s="98">
+      <c r="H65" s="97">
         <v>8550</v>
       </c>
-      <c r="I65" s="76" t="s">
+      <c r="I65" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="J65" s="45">
+      <c r="J65" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1380</v>
       </c>
-      <c r="K65" s="45">
+      <c r="K65" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L65" s="98">
+      <c r="L65" s="97">
         <v>5790</v>
       </c>
-      <c r="M65" s="45"/>
-      <c r="N65" s="45"/>
-      <c r="O65" s="45">
+      <c r="M65" s="44"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2732.5</v>
       </c>
-      <c r="P65" s="45"/>
-      <c r="Q65" s="46">
+      <c r="P65" s="44"/>
+      <c r="Q65" s="45">
         <v>1</v>
       </c>
-      <c r="R65" s="46" t="s">
+      <c r="R65" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S65" s="46">
+      <c r="S65" s="45">
         <v>325</v>
       </c>
-      <c r="T65" s="48" t="s">
+      <c r="T65" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U65" s="48">
-        <v>0</v>
-      </c>
-      <c r="V65" s="48" t="s">
+      <c r="U65" s="47">
+        <v>0</v>
+      </c>
+      <c r="V65" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W65" s="4"/>
@@ -8952,10 +8967,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D66" s="98">
+      <c r="D66" s="97">
         <v>5039</v>
       </c>
-      <c r="E66" s="45" t="s">
+      <c r="E66" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F66" s="43">
@@ -8966,46 +8981,46 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H66" s="98">
+      <c r="H66" s="97">
         <v>8550</v>
       </c>
-      <c r="I66" s="76" t="s">
+      <c r="I66" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="J66" s="45">
+      <c r="J66" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1380</v>
       </c>
-      <c r="K66" s="45">
+      <c r="K66" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L66" s="98">
+      <c r="L66" s="97">
         <v>5790</v>
       </c>
-      <c r="M66" s="45"/>
-      <c r="N66" s="45"/>
-      <c r="O66" s="45">
+      <c r="M66" s="44"/>
+      <c r="N66" s="44"/>
+      <c r="O66" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>2732.5</v>
       </c>
-      <c r="P66" s="45"/>
-      <c r="Q66" s="46">
+      <c r="P66" s="44"/>
+      <c r="Q66" s="45">
         <v>1</v>
       </c>
-      <c r="R66" s="46" t="s">
+      <c r="R66" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S66" s="46">
+      <c r="S66" s="45">
         <v>325</v>
       </c>
-      <c r="T66" s="48" t="s">
+      <c r="T66" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U66" s="48">
-        <v>0</v>
-      </c>
-      <c r="V66" s="48" t="s">
+      <c r="U66" s="47">
+        <v>0</v>
+      </c>
+      <c r="V66" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W66" s="4"/>
@@ -9021,17 +9036,17 @@
       <c r="A67" s="41" t="s">
         <v>562</v>
       </c>
-      <c r="B67" s="89" t="s">
+      <c r="B67" s="88" t="s">
         <v>563</v>
       </c>
       <c r="C67" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D67" s="98">
+      <c r="D67" s="97">
         <v>5939</v>
       </c>
-      <c r="E67" s="45" t="s">
+      <c r="E67" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F67" s="43">
@@ -9042,43 +9057,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H67" s="98">
+      <c r="H67" s="97">
         <v>9650</v>
       </c>
-      <c r="I67" s="76" t="s">
+      <c r="I67" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="J67" s="45">
-        <v>0</v>
-      </c>
-      <c r="K67" s="45">
+      <c r="J67" s="44">
+        <v>0</v>
+      </c>
+      <c r="K67" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4662.5</v>
       </c>
-      <c r="L67" s="99">
+      <c r="L67" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>9650</v>
       </c>
-      <c r="M67" s="45"/>
-      <c r="N67" s="45"/>
-      <c r="O67" s="45"/>
-      <c r="P67" s="45"/>
-      <c r="Q67" s="46">
+      <c r="M67" s="44"/>
+      <c r="N67" s="44"/>
+      <c r="O67" s="44"/>
+      <c r="P67" s="44"/>
+      <c r="Q67" s="45">
         <v>1</v>
       </c>
-      <c r="R67" s="46" t="s">
+      <c r="R67" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S67" s="46">
+      <c r="S67" s="45">
         <v>325</v>
       </c>
-      <c r="T67" s="48" t="s">
+      <c r="T67" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U67" s="48">
-        <v>0</v>
-      </c>
-      <c r="V67" s="48" t="s">
+      <c r="U67" s="47">
+        <v>0</v>
+      </c>
+      <c r="V67" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W67" s="4"/>
@@ -9094,17 +9109,17 @@
       <c r="A68" s="41" t="s">
         <v>564</v>
       </c>
-      <c r="B68" s="89" t="s">
+      <c r="B68" s="88" t="s">
         <v>565</v>
       </c>
       <c r="C68" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D68" s="98">
+      <c r="D68" s="97">
         <v>3149</v>
       </c>
-      <c r="E68" s="45" t="s">
+      <c r="E68" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F68" s="43">
@@ -9115,43 +9130,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H68" s="98">
+      <c r="H68" s="97">
         <v>5350</v>
       </c>
-      <c r="I68" s="76" t="s">
+      <c r="I68" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="J68" s="45">
-        <v>0</v>
-      </c>
-      <c r="K68" s="45">
+      <c r="J68" s="44">
+        <v>0</v>
+      </c>
+      <c r="K68" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2512.5</v>
       </c>
-      <c r="L68" s="99">
+      <c r="L68" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>5350</v>
       </c>
-      <c r="M68" s="45"/>
-      <c r="N68" s="45"/>
-      <c r="O68" s="45"/>
-      <c r="P68" s="45"/>
-      <c r="Q68" s="46">
+      <c r="M68" s="44"/>
+      <c r="N68" s="44"/>
+      <c r="O68" s="44"/>
+      <c r="P68" s="44"/>
+      <c r="Q68" s="45">
         <v>1</v>
       </c>
-      <c r="R68" s="46" t="s">
+      <c r="R68" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S68" s="46">
+      <c r="S68" s="45">
         <v>325</v>
       </c>
-      <c r="T68" s="48" t="s">
+      <c r="T68" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U68" s="48">
-        <v>0</v>
-      </c>
-      <c r="V68" s="48" t="s">
+      <c r="U68" s="47">
+        <v>0</v>
+      </c>
+      <c r="V68" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y68" s="15"/>
@@ -9166,17 +9181,17 @@
       <c r="A69" s="41" t="s">
         <v>566</v>
       </c>
-      <c r="B69" s="89" t="s">
+      <c r="B69" s="88" t="s">
         <v>567</v>
       </c>
       <c r="C69" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D69" s="98">
+      <c r="D69" s="97">
         <v>3839</v>
       </c>
-      <c r="E69" s="45" t="s">
+      <c r="E69" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F69" s="43">
@@ -9187,43 +9202,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H69" s="98">
+      <c r="H69" s="97">
         <v>7450</v>
       </c>
-      <c r="I69" s="76" t="s">
+      <c r="I69" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="J69" s="45">
-        <v>0</v>
-      </c>
-      <c r="K69" s="45">
+      <c r="J69" s="44">
+        <v>0</v>
+      </c>
+      <c r="K69" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3562.5</v>
       </c>
-      <c r="L69" s="99">
+      <c r="L69" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>7450</v>
       </c>
-      <c r="M69" s="45"/>
-      <c r="N69" s="45"/>
-      <c r="O69" s="45"/>
-      <c r="P69" s="45"/>
-      <c r="Q69" s="46">
+      <c r="M69" s="44"/>
+      <c r="N69" s="44"/>
+      <c r="O69" s="44"/>
+      <c r="P69" s="44"/>
+      <c r="Q69" s="45">
         <v>1</v>
       </c>
-      <c r="R69" s="46" t="s">
+      <c r="R69" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S69" s="46">
+      <c r="S69" s="45">
         <v>325</v>
       </c>
-      <c r="T69" s="48" t="s">
+      <c r="T69" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U69" s="48">
-        <v>0</v>
-      </c>
-      <c r="V69" s="48" t="s">
+      <c r="U69" s="47">
+        <v>0</v>
+      </c>
+      <c r="V69" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y69" s="15"/>
@@ -9238,17 +9253,17 @@
       <c r="A70" s="41" t="s">
         <v>568</v>
       </c>
-      <c r="B70" s="89" t="s">
+      <c r="B70" s="88" t="s">
         <v>569</v>
       </c>
       <c r="C70" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D70" s="98">
+      <c r="D70" s="97">
         <v>5039</v>
       </c>
-      <c r="E70" s="45" t="s">
+      <c r="E70" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F70" s="43">
@@ -9259,43 +9274,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H70" s="98">
+      <c r="H70" s="97">
         <v>8550</v>
       </c>
-      <c r="I70" s="76" t="s">
+      <c r="I70" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="J70" s="45">
-        <v>0</v>
-      </c>
-      <c r="K70" s="45">
+      <c r="J70" s="44">
+        <v>0</v>
+      </c>
+      <c r="K70" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4112.5</v>
       </c>
-      <c r="L70" s="99">
+      <c r="L70" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>8550</v>
       </c>
-      <c r="M70" s="45"/>
-      <c r="N70" s="45"/>
-      <c r="O70" s="45"/>
-      <c r="P70" s="45"/>
-      <c r="Q70" s="46">
+      <c r="M70" s="44"/>
+      <c r="N70" s="44"/>
+      <c r="O70" s="44"/>
+      <c r="P70" s="44"/>
+      <c r="Q70" s="45">
         <v>1</v>
       </c>
-      <c r="R70" s="46" t="s">
+      <c r="R70" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S70" s="46">
+      <c r="S70" s="45">
         <v>325</v>
       </c>
-      <c r="T70" s="48" t="s">
+      <c r="T70" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U70" s="48">
-        <v>0</v>
-      </c>
-      <c r="V70" s="48" t="s">
+      <c r="U70" s="47">
+        <v>0</v>
+      </c>
+      <c r="V70" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y70" s="15"/>
@@ -9310,17 +9325,17 @@
       <c r="A71" s="41" t="s">
         <v>562</v>
       </c>
-      <c r="B71" s="89" t="s">
+      <c r="B71" s="88" t="s">
         <v>563</v>
       </c>
       <c r="C71" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D71" s="98">
+      <c r="D71" s="97">
         <v>5939</v>
       </c>
-      <c r="E71" s="45" t="s">
+      <c r="E71" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F71" s="43">
@@ -9331,43 +9346,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H71" s="98">
+      <c r="H71" s="97">
         <v>9650</v>
       </c>
-      <c r="I71" s="76" t="s">
+      <c r="I71" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="J71" s="45">
+      <c r="J71" s="44">
         <v>500</v>
       </c>
-      <c r="K71" s="45">
+      <c r="K71" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4162.5</v>
       </c>
-      <c r="L71" s="99">
+      <c r="L71" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>8650</v>
       </c>
-      <c r="M71" s="45"/>
-      <c r="N71" s="45"/>
-      <c r="O71" s="45"/>
-      <c r="P71" s="45"/>
-      <c r="Q71" s="46">
+      <c r="M71" s="44"/>
+      <c r="N71" s="44"/>
+      <c r="O71" s="44"/>
+      <c r="P71" s="44"/>
+      <c r="Q71" s="45">
         <v>1</v>
       </c>
-      <c r="R71" s="46" t="s">
+      <c r="R71" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S71" s="46">
+      <c r="S71" s="45">
         <v>325</v>
       </c>
-      <c r="T71" s="48" t="s">
+      <c r="T71" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U71" s="48">
-        <v>0</v>
-      </c>
-      <c r="V71" s="48" t="s">
+      <c r="U71" s="47">
+        <v>0</v>
+      </c>
+      <c r="V71" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y71" s="15"/>
@@ -9382,17 +9397,17 @@
       <c r="A72" s="41" t="s">
         <v>566</v>
       </c>
-      <c r="B72" s="89" t="s">
+      <c r="B72" s="88" t="s">
         <v>567</v>
       </c>
       <c r="C72" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D72" s="98">
+      <c r="D72" s="97">
         <v>3839</v>
       </c>
-      <c r="E72" s="45" t="s">
+      <c r="E72" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F72" s="43">
@@ -9403,43 +9418,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H72" s="98">
+      <c r="H72" s="97">
         <v>7450</v>
       </c>
-      <c r="I72" s="76" t="s">
+      <c r="I72" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="J72" s="45">
+      <c r="J72" s="44">
         <v>500</v>
       </c>
-      <c r="K72" s="45">
+      <c r="K72" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3062.5</v>
       </c>
-      <c r="L72" s="99">
+      <c r="L72" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>6450</v>
       </c>
-      <c r="M72" s="45"/>
-      <c r="N72" s="45"/>
-      <c r="O72" s="45"/>
-      <c r="P72" s="45"/>
-      <c r="Q72" s="46">
+      <c r="M72" s="44"/>
+      <c r="N72" s="44"/>
+      <c r="O72" s="44"/>
+      <c r="P72" s="44"/>
+      <c r="Q72" s="45">
         <v>1</v>
       </c>
-      <c r="R72" s="46" t="s">
+      <c r="R72" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S72" s="46">
+      <c r="S72" s="45">
         <v>325</v>
       </c>
-      <c r="T72" s="48" t="s">
+      <c r="T72" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U72" s="48">
-        <v>0</v>
-      </c>
-      <c r="V72" s="48" t="s">
+      <c r="U72" s="47">
+        <v>0</v>
+      </c>
+      <c r="V72" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y72" s="15"/>
@@ -9454,17 +9469,17 @@
       <c r="A73" s="41" t="s">
         <v>568</v>
       </c>
-      <c r="B73" s="89" t="s">
+      <c r="B73" s="88" t="s">
         <v>569</v>
       </c>
       <c r="C73" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D73" s="98">
+      <c r="D73" s="97">
         <v>5039</v>
       </c>
-      <c r="E73" s="45" t="s">
+      <c r="E73" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F73" s="43">
@@ -9475,43 +9490,43 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H73" s="98">
+      <c r="H73" s="97">
         <v>8550</v>
       </c>
-      <c r="I73" s="76" t="s">
+      <c r="I73" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="J73" s="45">
+      <c r="J73" s="44">
         <v>500</v>
       </c>
-      <c r="K73" s="45">
+      <c r="K73" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3612.5</v>
       </c>
-      <c r="L73" s="99">
+      <c r="L73" s="98">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>7550</v>
       </c>
-      <c r="M73" s="45"/>
-      <c r="N73" s="45"/>
-      <c r="O73" s="45"/>
-      <c r="P73" s="45"/>
-      <c r="Q73" s="46">
+      <c r="M73" s="44"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+      <c r="Q73" s="45">
         <v>1</v>
       </c>
-      <c r="R73" s="46" t="s">
+      <c r="R73" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S73" s="46">
+      <c r="S73" s="45">
         <v>325</v>
       </c>
-      <c r="T73" s="48" t="s">
+      <c r="T73" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U73" s="48">
-        <v>0</v>
-      </c>
-      <c r="V73" s="48" t="s">
+      <c r="U73" s="47">
+        <v>0</v>
+      </c>
+      <c r="V73" s="47" t="s">
         <v>56</v>
       </c>
       <c r="W73" s="4"/>
@@ -9534,10 +9549,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D74" s="98">
+      <c r="D74" s="97">
         <v>5939</v>
       </c>
-      <c r="E74" s="45" t="s">
+      <c r="E74" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F74" s="43">
@@ -9548,42 +9563,42 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H74" s="98">
+      <c r="H74" s="97">
         <v>9650</v>
       </c>
-      <c r="I74" s="76" t="s">
+      <c r="I74" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="J74" s="45">
+      <c r="J74" s="44">
         <v>925</v>
       </c>
-      <c r="K74" s="45">
+      <c r="K74" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3737.5</v>
       </c>
-      <c r="L74" s="99">
+      <c r="L74" s="98">
         <v>8200</v>
       </c>
-      <c r="M74" s="76"/>
-      <c r="N74" s="45"/>
-      <c r="O74" s="76"/>
-      <c r="P74" s="45"/>
-      <c r="Q74" s="46">
+      <c r="M74" s="75"/>
+      <c r="N74" s="44"/>
+      <c r="O74" s="75"/>
+      <c r="P74" s="44"/>
+      <c r="Q74" s="45">
         <v>1</v>
       </c>
-      <c r="R74" s="46" t="s">
+      <c r="R74" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S74" s="46">
+      <c r="S74" s="45">
         <v>325</v>
       </c>
-      <c r="T74" s="48" t="s">
+      <c r="T74" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U74" s="48">
-        <v>0</v>
-      </c>
-      <c r="V74" s="48" t="s">
+      <c r="U74" s="47">
+        <v>0</v>
+      </c>
+      <c r="V74" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y74" s="15"/>
@@ -9605,10 +9620,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D75" s="98">
+      <c r="D75" s="97">
         <v>3839</v>
       </c>
-      <c r="E75" s="45" t="s">
+      <c r="E75" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F75" s="43">
@@ -9619,42 +9634,42 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H75" s="98">
+      <c r="H75" s="97">
         <v>7450</v>
       </c>
-      <c r="I75" s="76" t="s">
+      <c r="I75" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="J75" s="45">
+      <c r="J75" s="44">
         <v>525</v>
       </c>
-      <c r="K75" s="45">
+      <c r="K75" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3037.5</v>
       </c>
-      <c r="L75" s="99">
+      <c r="L75" s="98">
         <v>6400</v>
       </c>
-      <c r="M75" s="76"/>
-      <c r="N75" s="45"/>
-      <c r="O75" s="76"/>
-      <c r="P75" s="45"/>
-      <c r="Q75" s="46">
+      <c r="M75" s="75"/>
+      <c r="N75" s="44"/>
+      <c r="O75" s="75"/>
+      <c r="P75" s="44"/>
+      <c r="Q75" s="45">
         <v>1</v>
       </c>
-      <c r="R75" s="46" t="s">
+      <c r="R75" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S75" s="46">
+      <c r="S75" s="45">
         <v>325</v>
       </c>
-      <c r="T75" s="48" t="s">
+      <c r="T75" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U75" s="48">
-        <v>0</v>
-      </c>
-      <c r="V75" s="48" t="s">
+      <c r="U75" s="47">
+        <v>0</v>
+      </c>
+      <c r="V75" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y75" s="15"/>
@@ -9676,10 +9691,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D76" s="98">
+      <c r="D76" s="97">
         <v>5039</v>
       </c>
-      <c r="E76" s="45" t="s">
+      <c r="E76" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F76" s="43">
@@ -9690,42 +9705,42 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H76" s="98">
+      <c r="H76" s="97">
         <v>8550</v>
       </c>
-      <c r="I76" s="76" t="s">
+      <c r="I76" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="J76" s="45">
+      <c r="J76" s="44">
         <v>625</v>
       </c>
-      <c r="K76" s="45">
+      <c r="K76" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3487.5</v>
       </c>
-      <c r="L76" s="99">
+      <c r="L76" s="98">
         <v>7300</v>
       </c>
-      <c r="M76" s="76"/>
-      <c r="N76" s="45"/>
-      <c r="O76" s="76"/>
-      <c r="P76" s="45"/>
-      <c r="Q76" s="46">
+      <c r="M76" s="75"/>
+      <c r="N76" s="44"/>
+      <c r="O76" s="75"/>
+      <c r="P76" s="44"/>
+      <c r="Q76" s="45">
         <v>1</v>
       </c>
-      <c r="R76" s="46" t="s">
+      <c r="R76" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S76" s="46">
+      <c r="S76" s="45">
         <v>325</v>
       </c>
-      <c r="T76" s="48" t="s">
+      <c r="T76" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U76" s="48">
-        <v>0</v>
-      </c>
-      <c r="V76" s="48" t="s">
+      <c r="U76" s="47">
+        <v>0</v>
+      </c>
+      <c r="V76" s="47" t="s">
         <v>56</v>
       </c>
       <c r="Y76" s="15"/>
@@ -9737,20 +9752,20 @@
       <c r="AE76"/>
     </row>
     <row r="77" spans="1:31" ht="15">
-      <c r="A77" s="78" t="s">
+      <c r="A77" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="B77" s="84" t="s">
+      <c r="B77" s="83" t="s">
         <v>90</v>
       </c>
       <c r="C77" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6043</v>
       </c>
-      <c r="D77" s="98">
+      <c r="D77" s="97">
         <v>2909</v>
       </c>
-      <c r="E77" s="79" t="s">
+      <c r="E77" s="78" t="s">
         <v>10</v>
       </c>
       <c r="F77" s="43">
@@ -9761,50 +9776,50 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3021.5</v>
       </c>
-      <c r="H77" s="98">
+      <c r="H77" s="97">
         <v>6268</v>
       </c>
-      <c r="I77" s="77" t="s">
+      <c r="I77" s="76" t="s">
         <v>4</v>
       </c>
       <c r="J77" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1935</v>
       </c>
-      <c r="K77" s="45">
+      <c r="K77" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1086.5</v>
       </c>
-      <c r="L77" s="99">
+      <c r="L77" s="98">
         <f>1199*2</f>
         <v>2398</v>
       </c>
-      <c r="M77" s="79"/>
-      <c r="N77" s="79">
+      <c r="M77" s="78"/>
+      <c r="N77" s="78">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>1086.5</v>
       </c>
-      <c r="O77" s="79">
+      <c r="O77" s="78">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P77" s="79"/>
-      <c r="Q77" s="80">
+      <c r="P77" s="78"/>
+      <c r="Q77" s="79">
         <v>1</v>
       </c>
-      <c r="R77" s="90" t="s">
+      <c r="R77" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="S77" s="85">
+      <c r="S77" s="84">
         <v>225</v>
       </c>
-      <c r="T77" s="86" t="s">
+      <c r="T77" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="U77" s="79">
-        <v>0</v>
-      </c>
-      <c r="V77" s="52" t="s">
+      <c r="U77" s="78">
+        <v>0</v>
+      </c>
+      <c r="V77" s="51" t="s">
         <v>56</v>
       </c>
       <c r="X77" s="43"/>
@@ -9816,20 +9831,20 @@
       <c r="AD77" s="43"/>
     </row>
     <row r="78" spans="1:31" ht="15">
-      <c r="A78" s="78" t="s">
+      <c r="A78" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="B78" s="84" t="s">
+      <c r="B78" s="83" t="s">
         <v>92</v>
       </c>
       <c r="C78" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7463</v>
       </c>
-      <c r="D78" s="98">
+      <c r="D78" s="97">
         <v>3569</v>
       </c>
-      <c r="E78" s="79" t="s">
+      <c r="E78" s="78" t="s">
         <v>10</v>
       </c>
       <c r="F78" s="43">
@@ -9840,50 +9855,50 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3731.5</v>
       </c>
-      <c r="H78" s="98">
+      <c r="H78" s="97">
         <v>7788</v>
       </c>
-      <c r="I78" s="77" t="s">
+      <c r="I78" s="76" t="s">
         <v>4</v>
       </c>
       <c r="J78" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>2095</v>
       </c>
-      <c r="K78" s="45">
+      <c r="K78" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1636.5</v>
       </c>
-      <c r="L78" s="99">
+      <c r="L78" s="98">
         <f>1799*2</f>
         <v>3598</v>
       </c>
-      <c r="M78" s="79"/>
-      <c r="N78" s="79">
+      <c r="M78" s="78"/>
+      <c r="N78" s="78">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>1636.5</v>
       </c>
-      <c r="O78" s="79">
+      <c r="O78" s="78">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P78" s="79"/>
-      <c r="Q78" s="80">
+      <c r="P78" s="78"/>
+      <c r="Q78" s="79">
         <v>1</v>
       </c>
-      <c r="R78" s="79" t="s">
+      <c r="R78" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="S78" s="79">
+      <c r="S78" s="78">
         <v>325</v>
       </c>
       <c r="T78" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="U78" s="79">
-        <v>0</v>
-      </c>
-      <c r="V78" s="52" t="s">
+      <c r="U78" s="78">
+        <v>0</v>
+      </c>
+      <c r="V78" s="51" t="s">
         <v>56</v>
       </c>
       <c r="X78" s="43"/>
@@ -9895,20 +9910,20 @@
       <c r="AD78" s="43"/>
     </row>
     <row r="79" spans="1:31" ht="15">
-      <c r="A79" s="78" t="s">
+      <c r="A79" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="B79" s="84" t="s">
+      <c r="B79" s="83" t="s">
         <v>94</v>
       </c>
       <c r="C79" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9323</v>
       </c>
-      <c r="D79" s="98">
+      <c r="D79" s="97">
         <v>4499</v>
       </c>
-      <c r="E79" s="79" t="s">
+      <c r="E79" s="78" t="s">
         <v>10</v>
       </c>
       <c r="F79" s="43">
@@ -9919,50 +9934,50 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4661.5</v>
       </c>
-      <c r="H79" s="98">
+      <c r="H79" s="97">
         <v>9648</v>
       </c>
-      <c r="I79" s="77" t="s">
+      <c r="I79" s="76" t="s">
         <v>4</v>
       </c>
       <c r="J79" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>2575</v>
       </c>
-      <c r="K79" s="45">
+      <c r="K79" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2086.5</v>
       </c>
-      <c r="L79" s="99">
+      <c r="L79" s="98">
         <f>2249*2</f>
         <v>4498</v>
       </c>
-      <c r="M79" s="79"/>
-      <c r="N79" s="79">
+      <c r="M79" s="78"/>
+      <c r="N79" s="78">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2086.5</v>
       </c>
-      <c r="O79" s="79">
+      <c r="O79" s="78">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P79" s="79"/>
-      <c r="Q79" s="80">
+      <c r="P79" s="78"/>
+      <c r="Q79" s="79">
         <v>1</v>
       </c>
-      <c r="R79" s="79" t="s">
+      <c r="R79" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="S79" s="79">
+      <c r="S79" s="78">
         <v>325</v>
       </c>
       <c r="T79" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="U79" s="79">
-        <v>0</v>
-      </c>
-      <c r="V79" s="52" t="s">
+      <c r="U79" s="78">
+        <v>0</v>
+      </c>
+      <c r="V79" s="51" t="s">
         <v>56</v>
       </c>
       <c r="X79" s="43"/>
@@ -9974,20 +9989,20 @@
       <c r="AD79" s="43"/>
     </row>
     <row r="80" spans="1:31" ht="15">
-      <c r="A80" s="81" t="s">
+      <c r="A80" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B80" s="87" t="s">
+      <c r="B80" s="86" t="s">
         <v>95</v>
       </c>
       <c r="C80" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11483</v>
       </c>
-      <c r="D80" s="98">
+      <c r="D80" s="97">
         <v>5579</v>
       </c>
-      <c r="E80" s="82" t="s">
+      <c r="E80" s="81" t="s">
         <v>10</v>
       </c>
       <c r="F80" s="43">
@@ -9998,50 +10013,50 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>5741.5</v>
       </c>
-      <c r="H80" s="98">
+      <c r="H80" s="97">
         <v>11808</v>
       </c>
-      <c r="I80" s="88" t="s">
+      <c r="I80" s="87" t="s">
         <v>4</v>
       </c>
       <c r="J80" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>3405</v>
       </c>
-      <c r="K80" s="45">
+      <c r="K80" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2336.5</v>
       </c>
-      <c r="L80" s="99">
+      <c r="L80" s="98">
         <f>2499*2</f>
         <v>4998</v>
       </c>
-      <c r="M80" s="82"/>
-      <c r="N80" s="82">
+      <c r="M80" s="81"/>
+      <c r="N80" s="81">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>2336.5</v>
       </c>
-      <c r="O80" s="82">
+      <c r="O80" s="81">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P80" s="82"/>
-      <c r="Q80" s="83">
+      <c r="P80" s="81"/>
+      <c r="Q80" s="82">
         <v>1</v>
       </c>
-      <c r="R80" s="82" t="s">
+      <c r="R80" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S80" s="82">
+      <c r="S80" s="81">
         <v>325</v>
       </c>
-      <c r="T80" s="95" t="s">
+      <c r="T80" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="U80" s="82">
-        <v>0</v>
-      </c>
-      <c r="V80" s="97" t="s">
+      <c r="U80" s="81">
+        <v>0</v>
+      </c>
+      <c r="V80" s="96" t="s">
         <v>56</v>
       </c>
       <c r="X80" s="43"/>
@@ -10063,10 +10078,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D81" s="98">
+      <c r="D81" s="97">
         <v>3149</v>
       </c>
-      <c r="E81" s="45" t="s">
+      <c r="E81" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F81" s="43">
@@ -10077,10 +10092,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H81" s="98">
+      <c r="H81" s="97">
         <v>5350</v>
       </c>
-      <c r="I81" s="76" t="s">
+      <c r="I81" s="75" t="s">
         <v>64</v>
       </c>
       <c r="J81" s="43">
@@ -10091,7 +10106,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="L81" s="99">
+      <c r="L81" s="98">
         <v>4190</v>
       </c>
       <c r="M81" s="43"/>
@@ -10104,22 +10119,22 @@
         <v>0</v>
       </c>
       <c r="P81" s="43"/>
-      <c r="Q81" s="46">
+      <c r="Q81" s="45">
         <v>1</v>
       </c>
-      <c r="R81" s="46" t="s">
+      <c r="R81" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S81" s="46">
+      <c r="S81" s="45">
         <v>325</v>
       </c>
-      <c r="T81" s="48" t="s">
+      <c r="T81" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U81" s="48">
-        <v>0</v>
-      </c>
-      <c r="V81" s="48" t="s">
+      <c r="U81" s="47">
+        <v>0</v>
+      </c>
+      <c r="V81" s="47" t="s">
         <v>56</v>
       </c>
       <c r="X81" s="43"/>
@@ -10141,10 +10156,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D82" s="98">
+      <c r="D82" s="97">
         <v>3149</v>
       </c>
-      <c r="E82" s="45" t="s">
+      <c r="E82" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F82" s="43">
@@ -10155,10 +10170,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H82" s="98">
+      <c r="H82" s="97">
         <v>5350</v>
       </c>
-      <c r="I82" s="76" t="s">
+      <c r="I82" s="75" t="s">
         <v>76</v>
       </c>
       <c r="J82" s="43">
@@ -10169,7 +10184,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="L82" s="99">
+      <c r="L82" s="98">
         <v>4190</v>
       </c>
       <c r="M82" s="43"/>
@@ -10182,22 +10197,22 @@
         <v>0</v>
       </c>
       <c r="P82" s="43"/>
-      <c r="Q82" s="46">
+      <c r="Q82" s="45">
         <v>1</v>
       </c>
-      <c r="R82" s="46" t="s">
+      <c r="R82" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S82" s="46">
+      <c r="S82" s="45">
         <v>325</v>
       </c>
-      <c r="T82" s="48" t="s">
+      <c r="T82" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U82" s="48">
-        <v>0</v>
-      </c>
-      <c r="V82" s="48" t="s">
+      <c r="U82" s="47">
+        <v>0</v>
+      </c>
+      <c r="V82" s="47" t="s">
         <v>56</v>
       </c>
       <c r="X82" s="43"/>
@@ -10219,10 +10234,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D83" s="98">
+      <c r="D83" s="97">
         <v>3149</v>
       </c>
-      <c r="E83" s="45" t="s">
+      <c r="E83" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F83" s="43">
@@ -10233,10 +10248,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H83" s="98">
+      <c r="H83" s="97">
         <v>5350</v>
       </c>
-      <c r="I83" s="76" t="s">
+      <c r="I83" s="75" t="s">
         <v>77</v>
       </c>
       <c r="J83" s="43">
@@ -10247,7 +10262,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="L83" s="99">
+      <c r="L83" s="98">
         <v>4190</v>
       </c>
       <c r="M83" s="43"/>
@@ -10260,22 +10275,22 @@
         <v>0</v>
       </c>
       <c r="P83" s="43"/>
-      <c r="Q83" s="46">
+      <c r="Q83" s="45">
         <v>1</v>
       </c>
-      <c r="R83" s="46" t="s">
+      <c r="R83" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S83" s="46">
+      <c r="S83" s="45">
         <v>325</v>
       </c>
-      <c r="T83" s="48" t="s">
+      <c r="T83" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U83" s="48">
-        <v>0</v>
-      </c>
-      <c r="V83" s="48" t="s">
+      <c r="U83" s="47">
+        <v>0</v>
+      </c>
+      <c r="V83" s="47" t="s">
         <v>56</v>
       </c>
       <c r="X83" s="43"/>
@@ -10297,10 +10312,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D84" s="98">
+      <c r="D84" s="97">
         <v>3149</v>
       </c>
-      <c r="E84" s="45" t="s">
+      <c r="E84" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F84" s="43">
@@ -10311,10 +10326,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H84" s="98">
+      <c r="H84" s="97">
         <v>5350</v>
       </c>
-      <c r="I84" s="76" t="s">
+      <c r="I84" s="75" t="s">
         <v>78</v>
       </c>
       <c r="J84" s="43">
@@ -10325,7 +10340,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="L84" s="99">
+      <c r="L84" s="98">
         <v>4190</v>
       </c>
       <c r="M84" s="43"/>
@@ -10338,22 +10353,22 @@
         <v>0</v>
       </c>
       <c r="P84" s="43"/>
-      <c r="Q84" s="46">
+      <c r="Q84" s="45">
         <v>1</v>
       </c>
-      <c r="R84" s="46" t="s">
+      <c r="R84" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S84" s="46">
+      <c r="S84" s="45">
         <v>325</v>
       </c>
-      <c r="T84" s="48" t="s">
+      <c r="T84" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U84" s="48">
-        <v>0</v>
-      </c>
-      <c r="V84" s="48" t="s">
+      <c r="U84" s="47">
+        <v>0</v>
+      </c>
+      <c r="V84" s="47" t="s">
         <v>56</v>
       </c>
       <c r="X84" s="43"/>
@@ -10375,10 +10390,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D85" s="98">
+      <c r="D85" s="97">
         <v>3149</v>
       </c>
-      <c r="E85" s="45" t="s">
+      <c r="E85" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F85" s="43">
@@ -10389,10 +10404,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H85" s="98">
+      <c r="H85" s="97">
         <v>5350</v>
       </c>
-      <c r="I85" s="76" t="s">
+      <c r="I85" s="75" t="s">
         <v>81</v>
       </c>
       <c r="J85" s="43">
@@ -10403,7 +10418,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="L85" s="99">
+      <c r="L85" s="98">
         <v>4190</v>
       </c>
       <c r="M85" s="43"/>
@@ -10416,22 +10431,22 @@
         <v>0</v>
       </c>
       <c r="P85" s="43"/>
-      <c r="Q85" s="46">
+      <c r="Q85" s="45">
         <v>1</v>
       </c>
-      <c r="R85" s="46" t="s">
+      <c r="R85" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S85" s="46">
+      <c r="S85" s="45">
         <v>325</v>
       </c>
-      <c r="T85" s="48" t="s">
+      <c r="T85" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U85" s="48">
-        <v>0</v>
-      </c>
-      <c r="V85" s="48" t="s">
+      <c r="U85" s="47">
+        <v>0</v>
+      </c>
+      <c r="V85" s="47" t="s">
         <v>56</v>
       </c>
       <c r="X85" s="43"/>
@@ -10453,10 +10468,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D86" s="98">
+      <c r="D86" s="97">
         <v>3149</v>
       </c>
-      <c r="E86" s="45" t="s">
+      <c r="E86" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F86" s="43">
@@ -10467,10 +10482,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H86" s="98">
+      <c r="H86" s="97">
         <v>5350</v>
       </c>
-      <c r="I86" s="76" t="s">
+      <c r="I86" s="75" t="s">
         <v>82</v>
       </c>
       <c r="J86" s="43">
@@ -10481,7 +10496,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="L86" s="99">
+      <c r="L86" s="98">
         <v>4190</v>
       </c>
       <c r="M86" s="43"/>
@@ -10494,22 +10509,22 @@
         <v>0</v>
       </c>
       <c r="P86" s="43"/>
-      <c r="Q86" s="46">
+      <c r="Q86" s="45">
         <v>1</v>
       </c>
-      <c r="R86" s="46" t="s">
+      <c r="R86" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S86" s="46">
+      <c r="S86" s="45">
         <v>325</v>
       </c>
-      <c r="T86" s="48" t="s">
+      <c r="T86" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U86" s="48">
-        <v>0</v>
-      </c>
-      <c r="V86" s="48" t="s">
+      <c r="U86" s="47">
+        <v>0</v>
+      </c>
+      <c r="V86" s="47" t="s">
         <v>56</v>
       </c>
       <c r="X86" s="43"/>
@@ -10531,10 +10546,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D87" s="98">
+      <c r="D87" s="97">
         <v>3149</v>
       </c>
-      <c r="E87" s="45" t="s">
+      <c r="E87" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F87" s="43">
@@ -10545,10 +10560,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H87" s="98">
+      <c r="H87" s="97">
         <v>5350</v>
       </c>
-      <c r="I87" s="76" t="s">
+      <c r="I87" s="75" t="s">
         <v>85</v>
       </c>
       <c r="J87" s="43">
@@ -10559,7 +10574,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="L87" s="99">
+      <c r="L87" s="98">
         <v>4190</v>
       </c>
       <c r="M87" s="43"/>
@@ -10572,22 +10587,22 @@
         <v>0</v>
       </c>
       <c r="P87" s="43"/>
-      <c r="Q87" s="46">
+      <c r="Q87" s="45">
         <v>1</v>
       </c>
-      <c r="R87" s="46" t="s">
+      <c r="R87" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S87" s="46">
+      <c r="S87" s="45">
         <v>325</v>
       </c>
-      <c r="T87" s="48" t="s">
+      <c r="T87" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U87" s="48">
-        <v>0</v>
-      </c>
-      <c r="V87" s="48" t="s">
+      <c r="U87" s="47">
+        <v>0</v>
+      </c>
+      <c r="V87" s="47" t="s">
         <v>56</v>
       </c>
       <c r="X87" s="43"/>
@@ -10609,10 +10624,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D88" s="98">
+      <c r="D88" s="97">
         <v>3149</v>
       </c>
-      <c r="E88" s="45" t="s">
+      <c r="E88" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F88" s="43">
@@ -10623,10 +10638,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H88" s="98">
+      <c r="H88" s="97">
         <v>5350</v>
       </c>
-      <c r="I88" s="76" t="s">
+      <c r="I88" s="75" t="s">
         <v>86</v>
       </c>
       <c r="J88" s="43">
@@ -10637,7 +10652,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="L88" s="99">
+      <c r="L88" s="98">
         <v>4190</v>
       </c>
       <c r="M88" s="43"/>
@@ -10650,22 +10665,22 @@
         <v>0</v>
       </c>
       <c r="P88" s="43"/>
-      <c r="Q88" s="46">
+      <c r="Q88" s="45">
         <v>1</v>
       </c>
-      <c r="R88" s="46" t="s">
+      <c r="R88" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S88" s="46">
+      <c r="S88" s="45">
         <v>325</v>
       </c>
-      <c r="T88" s="48" t="s">
+      <c r="T88" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U88" s="48">
-        <v>0</v>
-      </c>
-      <c r="V88" s="48" t="s">
+      <c r="U88" s="47">
+        <v>0</v>
+      </c>
+      <c r="V88" s="47" t="s">
         <v>56</v>
       </c>
       <c r="X88" s="43"/>
@@ -10687,63 +10702,63 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D89" s="98">
+      <c r="D89" s="97">
         <v>3149</v>
       </c>
-      <c r="E89" s="45" t="s">
+      <c r="E89" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F89" s="45">
+      <c r="F89" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>636.5</v>
       </c>
-      <c r="G89" s="45">
+      <c r="G89" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H89" s="98">
+      <c r="H89" s="97">
         <v>5350</v>
       </c>
-      <c r="I89" s="76" t="s">
+      <c r="I89" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="J89" s="45">
+      <c r="J89" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>580</v>
       </c>
-      <c r="K89" s="45">
+      <c r="K89" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="L89" s="99">
+      <c r="L89" s="98">
         <v>4190</v>
       </c>
-      <c r="M89" s="45"/>
-      <c r="N89" s="45">
+      <c r="M89" s="44"/>
+      <c r="N89" s="44">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>1932.5</v>
       </c>
-      <c r="O89" s="45">
+      <c r="O89" s="44">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
-      <c r="P89" s="45"/>
-      <c r="Q89" s="46">
+      <c r="P89" s="44"/>
+      <c r="Q89" s="45">
         <v>1</v>
       </c>
-      <c r="R89" s="46" t="s">
+      <c r="R89" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="S89" s="46">
+      <c r="S89" s="45">
         <v>325</v>
       </c>
-      <c r="T89" s="48" t="s">
+      <c r="T89" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="U89" s="48">
-        <v>0</v>
-      </c>
-      <c r="V89" s="48" t="s">
+      <c r="U89" s="47">
+        <v>0</v>
+      </c>
+      <c r="V89" s="47" t="s">
         <v>56</v>
       </c>
       <c r="X89" s="43"/>
@@ -10763,7 +10778,7 @@
       <c r="K90" s="43"/>
       <c r="N90" s="43"/>
       <c r="O90" s="43"/>
-      <c r="Q90" s="54"/>
+      <c r="Q90" s="53"/>
       <c r="U90" s="43"/>
       <c r="X90" s="43"/>
       <c r="Y90" s="43"/>
@@ -10782,7 +10797,7 @@
       <c r="K91" s="43"/>
       <c r="N91" s="43"/>
       <c r="O91" s="43"/>
-      <c r="Q91" s="54"/>
+      <c r="Q91" s="53"/>
       <c r="U91" s="43"/>
     </row>
     <row r="92" spans="1:30" ht="12.75">
@@ -10794,7 +10809,7 @@
       <c r="K92" s="43"/>
       <c r="N92" s="43"/>
       <c r="O92" s="43"/>
-      <c r="Q92" s="54"/>
+      <c r="Q92" s="53"/>
       <c r="U92" s="43"/>
     </row>
     <row r="93" spans="1:30" ht="12.75">
@@ -10806,7 +10821,7 @@
       <c r="K93" s="43"/>
       <c r="N93" s="43"/>
       <c r="O93" s="43"/>
-      <c r="Q93" s="54"/>
+      <c r="Q93" s="53"/>
       <c r="U93" s="43"/>
     </row>
   </sheetData>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1666" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C17E882-7771-4BF5-8966-9410F93B36B4}"/>
+  <xr:revisionPtr revIDLastSave="1667" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE47B69F-99BE-4388-8C0C-58007A29C9BE}"/>
   <bookViews>
-    <workbookView xWindow="-12810" yWindow="16080" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -2318,17 +2318,6 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="11" fillId="7" borderId="19" xfId="3" applyNumberFormat="1" applyFill="1"/>
@@ -2345,6 +2334,17 @@
     <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3564,10 +3564,10 @@
       <c r="A3" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="102"/>
+      <c r="C3" s="114"/>
       <c r="D3" s="41"/>
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
@@ -3588,10 +3588,10 @@
       <c r="A5" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="101">
+      <c r="B5" s="113">
         <v>2</v>
       </c>
-      <c r="C5" s="102"/>
+      <c r="C5" s="114"/>
       <c r="D5" s="41"/>
       <c r="E5" s="41"/>
       <c r="F5" s="41"/>
@@ -3612,10 +3612,10 @@
       <c r="A7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="101" t="s">
+      <c r="B7" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="102"/>
+      <c r="C7" s="114"/>
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
       <c r="F7" s="41"/>
@@ -3974,9 +3974,9 @@
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1">
-      <c r="A30" s="100"/>
-      <c r="B30" s="100"/>
-      <c r="C30" s="100"/>
+      <c r="A30" s="112"/>
+      <c r="B30" s="112"/>
+      <c r="C30" s="112"/>
       <c r="D30" s="35"/>
       <c r="E30" s="35"/>
       <c r="F30" s="25"/>
@@ -6620,74 +6620,74 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:32" s="113" customFormat="1" ht="15">
-      <c r="A35" s="103" t="s">
+    <row r="35" spans="1:32" s="110" customFormat="1" ht="15">
+      <c r="A35" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="103" t="s">
+      <c r="B35" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="104">
+      <c r="C35" s="101">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D35" s="105">
+      <c r="D35" s="102">
         <v>5939</v>
       </c>
-      <c r="E35" s="106" t="s">
+      <c r="E35" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="F35" s="106">
+      <c r="F35" s="103">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1276.5</v>
       </c>
-      <c r="G35" s="106">
+      <c r="G35" s="103">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H35" s="105">
+      <c r="H35" s="102">
         <v>9650</v>
       </c>
-      <c r="I35" s="107" t="s">
+      <c r="I35" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="J35" s="108">
+      <c r="J35" s="105">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1480</v>
-      </c>
-      <c r="K35" s="108">
+        <v>1330</v>
+      </c>
+      <c r="K35" s="105">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3182.5</v>
-      </c>
-      <c r="L35" s="109">
-        <v>6690</v>
-      </c>
-      <c r="M35" s="108"/>
-      <c r="N35" s="108"/>
-      <c r="O35" s="108"/>
-      <c r="P35" s="108"/>
-      <c r="Q35" s="110">
+        <v>3332.5</v>
+      </c>
+      <c r="L35" s="106">
+        <v>6990</v>
+      </c>
+      <c r="M35" s="105"/>
+      <c r="N35" s="105"/>
+      <c r="O35" s="105"/>
+      <c r="P35" s="105"/>
+      <c r="Q35" s="107">
         <v>1</v>
       </c>
-      <c r="R35" s="110" t="s">
+      <c r="R35" s="107" t="s">
         <v>52</v>
       </c>
-      <c r="S35" s="106">
+      <c r="S35" s="103">
         <v>325</v>
       </c>
-      <c r="T35" s="111" t="s">
+      <c r="T35" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="U35" s="112">
-        <v>0</v>
-      </c>
-      <c r="V35" s="111" t="s">
+      <c r="U35" s="109">
+        <v>0</v>
+      </c>
+      <c r="V35" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="W35" s="108"/>
-      <c r="Y35" s="114"/>
-      <c r="Z35" s="114"/>
-      <c r="AA35" s="114"/>
+      <c r="W35" s="105"/>
+      <c r="Y35" s="111"/>
+      <c r="Z35" s="111"/>
+      <c r="AA35" s="111"/>
     </row>
     <row r="36" spans="1:32" ht="15">
       <c r="A36" s="41" t="s">

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1667" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE47B69F-99BE-4388-8C0C-58007A29C9BE}"/>
+  <xr:revisionPtr revIDLastSave="1671" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{568E5B34-FC27-4C88-8056-F3C06743ADBB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -1865,7 +1865,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1899,12 +1899,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2140,7 +2134,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2318,22 +2312,6 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="11" fillId="7" borderId="19" xfId="3" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="11" fillId="7" borderId="19" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3539,18 +3517,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7B380E-1396-4B6E-A468-8A3D9AA81345}">
   <dimension ref="A2:I36"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="36.140625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="27" customWidth="1"/>
+    <col min="1" max="1" width="36.125" style="27" customWidth="1"/>
+    <col min="2" max="2" width="16.625" style="27" customWidth="1"/>
     <col min="3" max="3" width="22" style="27" customWidth="1"/>
-    <col min="4" max="5" width="19.28515625" style="27" customWidth="1"/>
-    <col min="6" max="6" width="38.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="27" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="27"/>
+    <col min="4" max="5" width="19.25" style="27" customWidth="1"/>
+    <col min="6" max="6" width="38.25" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="27" customWidth="1"/>
+    <col min="8" max="16384" width="9.125" style="27"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="13.5" thickBot="1">
+    <row r="2" spans="1:8" ht="13.8" thickBot="1">
       <c r="A2" s="41"/>
       <c r="B2" s="41"/>
       <c r="C2" s="41"/>
@@ -3560,21 +3538,21 @@
       <c r="G2" s="41"/>
       <c r="H2" s="41"/>
     </row>
-    <row r="3" spans="1:8" ht="13.5" thickBot="1">
+    <row r="3" spans="1:8" ht="13.8" thickBot="1">
       <c r="A3" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="114"/>
+      <c r="C3" s="102"/>
       <c r="D3" s="41"/>
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
       <c r="G3" s="41"/>
       <c r="H3" s="41"/>
     </row>
-    <row r="4" spans="1:8" ht="13.5" thickBot="1">
+    <row r="4" spans="1:8" ht="13.8" thickBot="1">
       <c r="A4" s="54"/>
       <c r="B4" s="41"/>
       <c r="C4" s="41"/>
@@ -3584,21 +3562,21 @@
       <c r="G4" s="41"/>
       <c r="H4" s="41"/>
     </row>
-    <row r="5" spans="1:8" ht="13.5" thickBot="1">
+    <row r="5" spans="1:8" ht="13.8" thickBot="1">
       <c r="A5" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="101">
         <v>2</v>
       </c>
-      <c r="C5" s="114"/>
+      <c r="C5" s="102"/>
       <c r="D5" s="41"/>
       <c r="E5" s="41"/>
       <c r="F5" s="41"/>
       <c r="G5" s="41"/>
       <c r="H5" s="41"/>
     </row>
-    <row r="6" spans="1:8" ht="13.5" thickBot="1">
+    <row r="6" spans="1:8" ht="13.8" thickBot="1">
       <c r="A6" s="54"/>
       <c r="B6" s="41"/>
       <c r="C6" s="41"/>
@@ -3608,14 +3586,14 @@
       <c r="G6" s="28"/>
       <c r="H6" s="29"/>
     </row>
-    <row r="7" spans="1:8" ht="13.5" thickBot="1">
+    <row r="7" spans="1:8" ht="13.8" thickBot="1">
       <c r="A7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="113" t="s">
+      <c r="B7" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="114"/>
+      <c r="C7" s="102"/>
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
       <c r="F7" s="41"/>
@@ -3644,7 +3622,7 @@
       <c r="G10" s="55"/>
       <c r="H10" s="41"/>
     </row>
-    <row r="11" spans="1:8" ht="13.5" thickBot="1">
+    <row r="11" spans="1:8" ht="13.8" thickBot="1">
       <c r="A11" s="56"/>
       <c r="B11" s="56"/>
       <c r="C11" s="56"/>
@@ -3974,9 +3952,9 @@
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1">
-      <c r="A30" s="112"/>
-      <c r="B30" s="112"/>
-      <c r="C30" s="112"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="100"/>
       <c r="D30" s="35"/>
       <c r="E30" s="35"/>
       <c r="F30" s="25"/>
@@ -4107,38 +4085,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8E355-D10F-45CB-8710-0B743D2C5CA5}">
   <dimension ref="A1:AF93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="53.85546875" customWidth="1"/>
+    <col min="1" max="1" width="53.875" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.625" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="24.140625" customWidth="1"/>
-    <col min="16" max="16" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.25" customWidth="1"/>
+    <col min="9" max="9" width="25.75" customWidth="1"/>
+    <col min="10" max="10" width="23.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="24.125" customWidth="1"/>
+    <col min="16" max="16" width="23.75" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17" style="39" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.125" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="26" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.75" style="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="38" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.140625" customWidth="1"/>
-    <col min="25" max="25" width="16.85546875" customWidth="1"/>
-    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="9.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.125" customWidth="1"/>
+    <col min="25" max="25" width="16.875" customWidth="1"/>
+    <col min="26" max="26" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="9.875" style="15" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" ht="12">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -4213,7 +4191,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="15">
+    <row r="2" spans="1:31" ht="14.4">
       <c r="A2" s="41" t="s">
         <v>66</v>
       </c>
@@ -4285,7 +4263,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="15">
+    <row r="3" spans="1:31" ht="14.4">
       <c r="A3" s="41" t="s">
         <v>66</v>
       </c>
@@ -4357,7 +4335,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="15">
+    <row r="4" spans="1:31" ht="14.4">
       <c r="A4" s="41" t="s">
         <v>62</v>
       </c>
@@ -4425,7 +4403,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="15">
+    <row r="5" spans="1:31" ht="14.4">
       <c r="A5" s="41" t="s">
         <v>68</v>
       </c>
@@ -4498,7 +4476,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="15">
+    <row r="6" spans="1:31" ht="14.4">
       <c r="A6" s="41" t="s">
         <v>68</v>
       </c>
@@ -4570,7 +4548,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="15">
+    <row r="7" spans="1:31" ht="14.4">
       <c r="A7" s="41" t="s">
         <v>70</v>
       </c>
@@ -4643,7 +4621,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="15">
+    <row r="8" spans="1:31" ht="14.4">
       <c r="A8" s="41" t="s">
         <v>70</v>
       </c>
@@ -4716,7 +4694,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="15">
+    <row r="9" spans="1:31" ht="14.4">
       <c r="A9" s="41" t="s">
         <v>43</v>
       </c>
@@ -4779,7 +4757,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="15">
+    <row r="10" spans="1:31" ht="14.4">
       <c r="A10" s="41" t="s">
         <v>43</v>
       </c>
@@ -4851,7 +4829,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="15">
+    <row r="11" spans="1:31" ht="14.4">
       <c r="A11" s="41" t="s">
         <v>47</v>
       </c>
@@ -4923,7 +4901,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="15">
+    <row r="12" spans="1:31" ht="14.4">
       <c r="A12" s="41" t="s">
         <v>47</v>
       </c>
@@ -4994,7 +4972,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="15">
+    <row r="13" spans="1:31" ht="14.4">
       <c r="A13" s="41" t="s">
         <v>47</v>
       </c>
@@ -5066,7 +5044,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="15">
+    <row r="14" spans="1:31" ht="14.4">
       <c r="A14" s="41" t="s">
         <v>47</v>
       </c>
@@ -5138,7 +5116,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="15">
+    <row r="15" spans="1:31" ht="14.4">
       <c r="A15" s="41" t="s">
         <v>47</v>
       </c>
@@ -5210,7 +5188,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="15">
+    <row r="16" spans="1:31" ht="14.4">
       <c r="A16" s="41" t="s">
         <v>47</v>
       </c>
@@ -5282,7 +5260,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="15">
+    <row r="17" spans="1:31" ht="14.4">
       <c r="A17" s="41" t="s">
         <v>47</v>
       </c>
@@ -5355,7 +5333,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="15">
+    <row r="18" spans="1:31" ht="14.4">
       <c r="A18" s="41" t="s">
         <v>47</v>
       </c>
@@ -5427,7 +5405,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="15">
+    <row r="19" spans="1:31" ht="14.4">
       <c r="A19" s="41" t="s">
         <v>47</v>
       </c>
@@ -5499,7 +5477,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="15">
+    <row r="20" spans="1:31" ht="14.4">
       <c r="A20" s="41" t="s">
         <v>47</v>
       </c>
@@ -5571,7 +5549,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="15">
+    <row r="21" spans="1:31" ht="14.4">
       <c r="A21" s="41" t="s">
         <v>47</v>
       </c>
@@ -5643,7 +5621,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="15">
+    <row r="22" spans="1:31" ht="14.4">
       <c r="A22" s="41" t="s">
         <v>47</v>
       </c>
@@ -5715,7 +5693,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="15">
+    <row r="23" spans="1:31" ht="14.4">
       <c r="A23" s="41" t="s">
         <v>47</v>
       </c>
@@ -5787,7 +5765,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15">
+    <row r="24" spans="1:31" ht="14.4">
       <c r="A24" s="41" t="s">
         <v>53</v>
       </c>
@@ -5865,7 +5843,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15">
+    <row r="25" spans="1:31" ht="14.4">
       <c r="A25" s="41" t="s">
         <v>53</v>
       </c>
@@ -5943,7 +5921,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15">
+    <row r="26" spans="1:31" ht="14.4">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -6021,7 +5999,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15">
+    <row r="27" spans="1:31" ht="14.4">
       <c r="A27" s="41" t="s">
         <v>53</v>
       </c>
@@ -6099,7 +6077,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15">
+    <row r="28" spans="1:31" ht="14.4">
       <c r="A28" s="41" t="s">
         <v>53</v>
       </c>
@@ -6174,7 +6152,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15">
+    <row r="29" spans="1:31" ht="14.4">
       <c r="A29" s="41" t="s">
         <v>53</v>
       </c>
@@ -6249,7 +6227,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="15">
+    <row r="30" spans="1:31" ht="14.4">
       <c r="A30" s="41" t="s">
         <v>53</v>
       </c>
@@ -6325,7 +6303,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="15">
+    <row r="31" spans="1:31" ht="14.4">
       <c r="A31" s="41" t="s">
         <v>53</v>
       </c>
@@ -6401,7 +6379,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="15">
+    <row r="32" spans="1:31" ht="14.4">
       <c r="A32" s="41" t="s">
         <v>53</v>
       </c>
@@ -6477,7 +6455,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:32" ht="15">
+    <row r="33" spans="1:32" ht="14.4">
       <c r="A33" s="41" t="s">
         <v>53</v>
       </c>
@@ -6547,7 +6525,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:32" ht="15">
+    <row r="34" spans="1:32" ht="14.4">
       <c r="A34" s="41" t="s">
         <v>53</v>
       </c>
@@ -6620,76 +6598,80 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:32" s="110" customFormat="1" ht="15">
-      <c r="A35" s="100" t="s">
+    <row r="35" spans="1:32" ht="14.4">
+      <c r="A35" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="100" t="s">
+      <c r="B35" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="101">
+      <c r="C35" s="42">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D35" s="102">
+      <c r="D35" s="97">
         <v>5939</v>
       </c>
-      <c r="E35" s="103" t="s">
+      <c r="E35" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="F35" s="103">
+      <c r="F35" s="43">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1276.5</v>
       </c>
-      <c r="G35" s="103">
+      <c r="G35" s="43">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H35" s="102">
+      <c r="H35" s="97">
         <v>9650</v>
       </c>
-      <c r="I35" s="104" t="s">
+      <c r="I35" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="J35" s="105">
+      <c r="J35" s="44">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1330</v>
       </c>
-      <c r="K35" s="105">
+      <c r="K35" s="44">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3332.5</v>
       </c>
-      <c r="L35" s="106">
+      <c r="L35" s="97">
         <v>6990</v>
       </c>
-      <c r="M35" s="105"/>
-      <c r="N35" s="105"/>
-      <c r="O35" s="105"/>
-      <c r="P35" s="105"/>
-      <c r="Q35" s="107">
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
+      <c r="O35" s="44"/>
+      <c r="P35" s="44"/>
+      <c r="Q35" s="45">
         <v>1</v>
       </c>
-      <c r="R35" s="107" t="s">
+      <c r="R35" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="S35" s="103">
+      <c r="S35" s="44">
         <v>325</v>
       </c>
-      <c r="T35" s="108" t="s">
+      <c r="T35" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="U35" s="109">
-        <v>0</v>
-      </c>
-      <c r="V35" s="108" t="s">
+      <c r="U35" s="47">
+        <v>0</v>
+      </c>
+      <c r="V35" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="W35" s="105"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="111"/>
-      <c r="AA35" s="111"/>
-    </row>
-    <row r="36" spans="1:32" ht="15">
+      <c r="W35" s="44"/>
+      <c r="Y35" s="15"/>
+      <c r="Z35" s="15"/>
+      <c r="AA35" s="15"/>
+      <c r="AB35"/>
+      <c r="AC35"/>
+      <c r="AD35"/>
+      <c r="AE35"/>
+    </row>
+    <row r="36" spans="1:32" ht="14.4">
       <c r="A36" s="41" t="s">
         <v>53</v>
       </c>
@@ -6762,7 +6744,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:32" ht="15">
+    <row r="37" spans="1:32" ht="14.4">
       <c r="A37" s="41" t="s">
         <v>53</v>
       </c>
@@ -6836,7 +6818,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:32" ht="15">
+    <row r="38" spans="1:32" ht="14.4">
       <c r="A38" s="41" t="s">
         <v>53</v>
       </c>
@@ -6909,7 +6891,7 @@
       <c r="AE38" s="15"/>
       <c r="AF38" s="15"/>
     </row>
-    <row r="39" spans="1:32" ht="15">
+    <row r="39" spans="1:32" ht="14.4">
       <c r="A39" s="41" t="s">
         <v>50</v>
       </c>
@@ -6982,7 +6964,7 @@
       <c r="AE39" s="15"/>
       <c r="AF39" s="15"/>
     </row>
-    <row r="40" spans="1:32" ht="15">
+    <row r="40" spans="1:32" ht="14.4">
       <c r="A40" s="41" t="s">
         <v>57</v>
       </c>
@@ -7060,7 +7042,7 @@
       <c r="AE40" s="15"/>
       <c r="AF40" s="15"/>
     </row>
-    <row r="41" spans="1:32" ht="15">
+    <row r="41" spans="1:32" ht="14.4">
       <c r="A41" s="41" t="s">
         <v>57</v>
       </c>
@@ -7139,7 +7121,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:32" ht="15">
+    <row r="42" spans="1:32" ht="14.4">
       <c r="A42" s="41" t="s">
         <v>57</v>
       </c>
@@ -7218,7 +7200,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:32" ht="15">
+    <row r="43" spans="1:32" ht="14.4">
       <c r="A43" s="41" t="s">
         <v>57</v>
       </c>
@@ -7297,7 +7279,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:32" ht="15">
+    <row r="44" spans="1:32" ht="14.4">
       <c r="A44" s="41" t="s">
         <v>57</v>
       </c>
@@ -7373,7 +7355,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:32" ht="15">
+    <row r="45" spans="1:32" ht="14.4">
       <c r="A45" s="41" t="s">
         <v>57</v>
       </c>
@@ -7449,7 +7431,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:32" ht="15">
+    <row r="46" spans="1:32" ht="14.4">
       <c r="A46" s="41" t="s">
         <v>57</v>
       </c>
@@ -7525,7 +7507,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:32" ht="15">
+    <row r="47" spans="1:32" ht="14.4">
       <c r="A47" s="41" t="s">
         <v>57</v>
       </c>
@@ -7601,7 +7583,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:32" ht="15">
+    <row r="48" spans="1:32" ht="14.4">
       <c r="A48" s="41" t="s">
         <v>57</v>
       </c>
@@ -7677,7 +7659,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:31" ht="15">
+    <row r="49" spans="1:31" ht="14.4">
       <c r="A49" s="41" t="s">
         <v>57</v>
       </c>
@@ -7750,7 +7732,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:31" ht="15">
+    <row r="50" spans="1:31" ht="14.4">
       <c r="A50" s="41" t="s">
         <v>57</v>
       </c>
@@ -7823,7 +7805,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:31" ht="15">
+    <row r="51" spans="1:31" ht="14.4">
       <c r="A51" s="41" t="s">
         <v>57</v>
       </c>
@@ -7897,7 +7879,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:31" ht="15">
+    <row r="52" spans="1:31" ht="14.4">
       <c r="A52" s="41" t="s">
         <v>57</v>
       </c>
@@ -7970,7 +7952,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:31" ht="15">
+    <row r="53" spans="1:31" ht="14.4">
       <c r="A53" s="41" t="s">
         <v>59</v>
       </c>
@@ -8043,7 +8025,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:31" ht="15">
+    <row r="54" spans="1:31" ht="14.4">
       <c r="A54" s="41" t="s">
         <v>59</v>
       </c>
@@ -8122,7 +8104,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:31" ht="15">
+    <row r="55" spans="1:31" ht="14.4">
       <c r="A55" s="41" t="s">
         <v>59</v>
       </c>
@@ -8195,7 +8177,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:31" ht="15">
+    <row r="56" spans="1:31" ht="14.4">
       <c r="A56" s="41" t="s">
         <v>59</v>
       </c>
@@ -8268,7 +8250,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:31" ht="15">
+    <row r="57" spans="1:31" ht="14.4">
       <c r="A57" s="41" t="s">
         <v>59</v>
       </c>
@@ -8347,7 +8329,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:31" ht="15">
+    <row r="58" spans="1:31" ht="14.4">
       <c r="A58" s="41" t="s">
         <v>59</v>
       </c>
@@ -8426,7 +8408,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:31" ht="15">
+    <row r="59" spans="1:31" ht="14.4">
       <c r="A59" s="41" t="s">
         <v>59</v>
       </c>
@@ -8505,7 +8487,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:31" ht="15">
+    <row r="60" spans="1:31" ht="14.4">
       <c r="A60" s="41" t="s">
         <v>59</v>
       </c>
@@ -8579,7 +8561,7 @@
       <c r="AD60"/>
       <c r="AE60"/>
     </row>
-    <row r="61" spans="1:31" ht="15">
+    <row r="61" spans="1:31" ht="14.4">
       <c r="A61" s="41" t="s">
         <v>59</v>
       </c>
@@ -8655,7 +8637,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:31" ht="15">
+    <row r="62" spans="1:31" ht="14.4">
       <c r="A62" s="41" t="s">
         <v>59</v>
       </c>
@@ -8731,7 +8713,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:31" ht="15">
+    <row r="63" spans="1:31" ht="14.4">
       <c r="A63" s="41" t="s">
         <v>59</v>
       </c>
@@ -8804,7 +8786,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:31" ht="15">
+    <row r="64" spans="1:31" ht="14.4">
       <c r="A64" s="41" t="s">
         <v>59</v>
       </c>
@@ -8880,7 +8862,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15">
+    <row r="65" spans="1:31" ht="14.4">
       <c r="A65" s="41" t="s">
         <v>59</v>
       </c>
@@ -8956,7 +8938,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15">
+    <row r="66" spans="1:31" ht="14.4">
       <c r="A66" s="41" t="s">
         <v>59</v>
       </c>
@@ -9032,7 +9014,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15">
+    <row r="67" spans="1:31" ht="14.4">
       <c r="A67" s="41" t="s">
         <v>562</v>
       </c>
@@ -9105,7 +9087,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15">
+    <row r="68" spans="1:31" ht="14.4">
       <c r="A68" s="41" t="s">
         <v>564</v>
       </c>
@@ -9177,7 +9159,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15">
+    <row r="69" spans="1:31" ht="14.4">
       <c r="A69" s="41" t="s">
         <v>566</v>
       </c>
@@ -9249,7 +9231,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15">
+    <row r="70" spans="1:31" ht="14.4">
       <c r="A70" s="41" t="s">
         <v>568</v>
       </c>
@@ -9321,7 +9303,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15">
+    <row r="71" spans="1:31" ht="14.4">
       <c r="A71" s="41" t="s">
         <v>562</v>
       </c>
@@ -9393,7 +9375,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15">
+    <row r="72" spans="1:31" ht="14.4">
       <c r="A72" s="41" t="s">
         <v>566</v>
       </c>
@@ -9465,7 +9447,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15">
+    <row r="73" spans="1:31" ht="14.4">
       <c r="A73" s="41" t="s">
         <v>568</v>
       </c>
@@ -9538,7 +9520,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="15">
+    <row r="74" spans="1:31" ht="14.4">
       <c r="A74" s="41" t="s">
         <v>562</v>
       </c>
@@ -9609,7 +9591,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="15">
+    <row r="75" spans="1:31" ht="14.4">
       <c r="A75" s="41" t="s">
         <v>566</v>
       </c>
@@ -9680,7 +9662,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="15">
+    <row r="76" spans="1:31" ht="14.4">
       <c r="A76" s="41" t="s">
         <v>568</v>
       </c>
@@ -9751,7 +9733,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="15">
+    <row r="77" spans="1:31" ht="14.4">
       <c r="A77" s="77" t="s">
         <v>89</v>
       </c>
@@ -9830,7 +9812,7 @@
       <c r="AC77" s="43"/>
       <c r="AD77" s="43"/>
     </row>
-    <row r="78" spans="1:31" ht="15">
+    <row r="78" spans="1:31" ht="14.4">
       <c r="A78" s="77" t="s">
         <v>91</v>
       </c>
@@ -9909,7 +9891,7 @@
       <c r="AC78" s="43"/>
       <c r="AD78" s="43"/>
     </row>
-    <row r="79" spans="1:31" ht="15">
+    <row r="79" spans="1:31" ht="14.4">
       <c r="A79" s="77" t="s">
         <v>93</v>
       </c>
@@ -9988,7 +9970,7 @@
       <c r="AC79" s="43"/>
       <c r="AD79" s="43"/>
     </row>
-    <row r="80" spans="1:31" ht="15">
+    <row r="80" spans="1:31" ht="14.4">
       <c r="A80" s="80" t="s">
         <v>1</v>
       </c>
@@ -10067,7 +10049,7 @@
       <c r="AC80" s="43"/>
       <c r="AD80" s="43"/>
     </row>
-    <row r="81" spans="1:30" ht="15">
+    <row r="81" spans="1:30" ht="14.4">
       <c r="A81" s="41" t="s">
         <v>50</v>
       </c>
@@ -10145,7 +10127,7 @@
       <c r="AC81" s="43"/>
       <c r="AD81" s="43"/>
     </row>
-    <row r="82" spans="1:30" ht="15">
+    <row r="82" spans="1:30" ht="14.4">
       <c r="A82" s="41" t="s">
         <v>50</v>
       </c>
@@ -10223,7 +10205,7 @@
       <c r="AC82" s="43"/>
       <c r="AD82" s="43"/>
     </row>
-    <row r="83" spans="1:30" ht="15">
+    <row r="83" spans="1:30" ht="14.4">
       <c r="A83" s="41" t="s">
         <v>50</v>
       </c>
@@ -10301,7 +10283,7 @@
       <c r="AC83" s="43"/>
       <c r="AD83" s="43"/>
     </row>
-    <row r="84" spans="1:30" ht="15">
+    <row r="84" spans="1:30" ht="14.4">
       <c r="A84" s="41" t="s">
         <v>50</v>
       </c>
@@ -10379,7 +10361,7 @@
       <c r="AC84" s="43"/>
       <c r="AD84" s="43"/>
     </row>
-    <row r="85" spans="1:30" ht="15">
+    <row r="85" spans="1:30" ht="14.4">
       <c r="A85" s="41" t="s">
         <v>50</v>
       </c>
@@ -10457,7 +10439,7 @@
       <c r="AC85" s="43"/>
       <c r="AD85" s="43"/>
     </row>
-    <row r="86" spans="1:30" ht="15">
+    <row r="86" spans="1:30" ht="14.4">
       <c r="A86" s="41" t="s">
         <v>50</v>
       </c>
@@ -10535,7 +10517,7 @@
       <c r="AC86" s="43"/>
       <c r="AD86" s="43"/>
     </row>
-    <row r="87" spans="1:30" ht="15">
+    <row r="87" spans="1:30" ht="14.4">
       <c r="A87" s="41" t="s">
         <v>50</v>
       </c>
@@ -10613,7 +10595,7 @@
       <c r="AC87" s="43"/>
       <c r="AD87" s="43"/>
     </row>
-    <row r="88" spans="1:30" ht="15">
+    <row r="88" spans="1:30" ht="14.4">
       <c r="A88" s="41" t="s">
         <v>50</v>
       </c>
@@ -10691,7 +10673,7 @@
       <c r="AC88" s="43"/>
       <c r="AD88" s="43"/>
     </row>
-    <row r="89" spans="1:30" ht="15">
+    <row r="89" spans="1:30" ht="14.4">
       <c r="A89" s="41" t="s">
         <v>50</v>
       </c>
@@ -10769,7 +10751,7 @@
       <c r="AC89" s="43"/>
       <c r="AD89" s="43"/>
     </row>
-    <row r="90" spans="1:30" ht="12.75">
+    <row r="90" spans="1:30" ht="13.2">
       <c r="A90" s="41"/>
       <c r="B90" s="41"/>
       <c r="C90" s="41"/>
@@ -10788,7 +10770,7 @@
       <c r="AC90" s="43"/>
       <c r="AD90" s="43"/>
     </row>
-    <row r="91" spans="1:30" ht="12.75">
+    <row r="91" spans="1:30" ht="13.2">
       <c r="A91" s="41"/>
       <c r="B91" s="41"/>
       <c r="C91" s="41"/>
@@ -10800,7 +10782,7 @@
       <c r="Q91" s="53"/>
       <c r="U91" s="43"/>
     </row>
-    <row r="92" spans="1:30" ht="12.75">
+    <row r="92" spans="1:30" ht="13.2">
       <c r="A92" s="41"/>
       <c r="B92" s="41"/>
       <c r="C92" s="41"/>
@@ -10812,7 +10794,7 @@
       <c r="Q92" s="53"/>
       <c r="U92" s="43"/>
     </row>
-    <row r="93" spans="1:30" ht="12.75">
+    <row r="93" spans="1:30" ht="13.2">
       <c r="A93" s="41"/>
       <c r="B93" s="41"/>
       <c r="C93" s="41"/>
@@ -10839,15 +10821,15 @@
   <dimension ref="A1:I286"/>
   <sheetFormatPr defaultRowHeight="18.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.75" customWidth="1"/>
+    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.75" customWidth="1"/>
+    <col min="7" max="7" width="23.875" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.25" customWidth="1"/>
+    <col min="10" max="10" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" customHeight="1">
@@ -10879,7 +10861,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="12">
+    <row r="2" spans="1:9" ht="11.4">
       <c r="A2" s="10" t="s">
         <v>105</v>
       </c>
@@ -18921,16 +18903,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2051AA2F-ED82-497D-A0D7-BA51300AC6DC}">
   <dimension ref="A1:J92"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="7" width="23.28515625" customWidth="1"/>
-    <col min="8" max="8" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="19.25" customWidth="1"/>
+    <col min="6" max="7" width="23.25" customWidth="1"/>
+    <col min="8" max="8" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" ht="12">
       <c r="A1" s="11" t="s">
         <v>96</v>
       </c>
@@ -21515,18 +21497,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{197CD5C8-84EF-4E52-92C3-639A9DF2089C}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="25.625" customWidth="1"/>
+    <col min="6" max="6" width="25.375" customWidth="1"/>
+    <col min="7" max="7" width="22.625" customWidth="1"/>
+    <col min="8" max="8" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" ht="12">
       <c r="A1" s="11" t="s">
         <v>96</v>
       </c>
@@ -21618,13 +21600,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD50CF4B-F9EC-407F-8C73-9C597C45A3D8}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="24.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24.75" customWidth="1"/>
+    <col min="6" max="6" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21710,16 +21692,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B02B6F-B860-41DC-9D50-B3B43A9E1932}">
   <dimension ref="A2:E7"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="12">
       <c r="A2" s="1" t="s">
         <v>556</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1671" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{568E5B34-FC27-4C88-8056-F3C06743ADBB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="-12810" yWindow="16080" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3517,18 +3517,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7B380E-1396-4B6E-A468-8A3D9AA81345}">
   <dimension ref="A2:I36"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="36.125" style="27" customWidth="1"/>
-    <col min="2" max="2" width="16.625" style="27" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="27" customWidth="1"/>
     <col min="3" max="3" width="22" style="27" customWidth="1"/>
-    <col min="4" max="5" width="19.25" style="27" customWidth="1"/>
-    <col min="6" max="6" width="38.25" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="27" customWidth="1"/>
-    <col min="8" max="16384" width="9.125" style="27"/>
+    <col min="4" max="5" width="19.28515625" style="27" customWidth="1"/>
+    <col min="6" max="6" width="38.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="27" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="13.8" thickBot="1">
+    <row r="2" spans="1:8" ht="13.5" thickBot="1">
       <c r="A2" s="41"/>
       <c r="B2" s="41"/>
       <c r="C2" s="41"/>
@@ -3538,7 +3538,7 @@
       <c r="G2" s="41"/>
       <c r="H2" s="41"/>
     </row>
-    <row r="3" spans="1:8" ht="13.8" thickBot="1">
+    <row r="3" spans="1:8" ht="13.5" thickBot="1">
       <c r="A3" s="54" t="s">
         <v>0</v>
       </c>
@@ -3552,7 +3552,7 @@
       <c r="G3" s="41"/>
       <c r="H3" s="41"/>
     </row>
-    <row r="4" spans="1:8" ht="13.8" thickBot="1">
+    <row r="4" spans="1:8" ht="13.5" thickBot="1">
       <c r="A4" s="54"/>
       <c r="B4" s="41"/>
       <c r="C4" s="41"/>
@@ -3562,7 +3562,7 @@
       <c r="G4" s="41"/>
       <c r="H4" s="41"/>
     </row>
-    <row r="5" spans="1:8" ht="13.8" thickBot="1">
+    <row r="5" spans="1:8" ht="13.5" thickBot="1">
       <c r="A5" s="54" t="s">
         <v>2</v>
       </c>
@@ -3576,7 +3576,7 @@
       <c r="G5" s="41"/>
       <c r="H5" s="41"/>
     </row>
-    <row r="6" spans="1:8" ht="13.8" thickBot="1">
+    <row r="6" spans="1:8" ht="13.5" thickBot="1">
       <c r="A6" s="54"/>
       <c r="B6" s="41"/>
       <c r="C6" s="41"/>
@@ -3586,7 +3586,7 @@
       <c r="G6" s="28"/>
       <c r="H6" s="29"/>
     </row>
-    <row r="7" spans="1:8" ht="13.8" thickBot="1">
+    <row r="7" spans="1:8" ht="13.5" thickBot="1">
       <c r="A7" s="54" t="s">
         <v>3</v>
       </c>
@@ -3622,7 +3622,7 @@
       <c r="G10" s="55"/>
       <c r="H10" s="41"/>
     </row>
-    <row r="11" spans="1:8" ht="13.8" thickBot="1">
+    <row r="11" spans="1:8" ht="13.5" thickBot="1">
       <c r="A11" s="56"/>
       <c r="B11" s="56"/>
       <c r="C11" s="56"/>
@@ -4085,38 +4085,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8E355-D10F-45CB-8710-0B743D2C5CA5}">
   <dimension ref="A1:AF93"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="53.875" customWidth="1"/>
+    <col min="1" max="1" width="53.85546875" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="28.625" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="20.25" customWidth="1"/>
-    <col min="9" max="9" width="25.75" customWidth="1"/>
-    <col min="10" max="10" width="23.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="24.125" customWidth="1"/>
-    <col min="16" max="16" width="23.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="24.140625" customWidth="1"/>
+    <col min="16" max="16" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17" style="39" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="26" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="38" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.125" customWidth="1"/>
-    <col min="25" max="25" width="16.875" customWidth="1"/>
-    <col min="26" max="26" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="9.875" style="15" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.140625" customWidth="1"/>
+    <col min="25" max="25" width="16.85546875" customWidth="1"/>
+    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="9.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="12">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -4191,7 +4191,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="14.4">
+    <row r="2" spans="1:31" ht="15">
       <c r="A2" s="41" t="s">
         <v>66</v>
       </c>
@@ -4263,7 +4263,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="14.4">
+    <row r="3" spans="1:31" ht="15">
       <c r="A3" s="41" t="s">
         <v>66</v>
       </c>
@@ -4335,7 +4335,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="14.4">
+    <row r="4" spans="1:31" ht="15">
       <c r="A4" s="41" t="s">
         <v>62</v>
       </c>
@@ -4403,7 +4403,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="14.4">
+    <row r="5" spans="1:31" ht="15">
       <c r="A5" s="41" t="s">
         <v>68</v>
       </c>
@@ -4476,7 +4476,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="14.4">
+    <row r="6" spans="1:31" ht="15">
       <c r="A6" s="41" t="s">
         <v>68</v>
       </c>
@@ -4548,7 +4548,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="14.4">
+    <row r="7" spans="1:31" ht="15">
       <c r="A7" s="41" t="s">
         <v>70</v>
       </c>
@@ -4621,7 +4621,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="14.4">
+    <row r="8" spans="1:31" ht="15">
       <c r="A8" s="41" t="s">
         <v>70</v>
       </c>
@@ -4694,7 +4694,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="14.4">
+    <row r="9" spans="1:31" ht="15">
       <c r="A9" s="41" t="s">
         <v>43</v>
       </c>
@@ -4757,7 +4757,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="14.4">
+    <row r="10" spans="1:31" ht="15">
       <c r="A10" s="41" t="s">
         <v>43</v>
       </c>
@@ -4829,7 +4829,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="14.4">
+    <row r="11" spans="1:31" ht="15">
       <c r="A11" s="41" t="s">
         <v>47</v>
       </c>
@@ -4901,7 +4901,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="14.4">
+    <row r="12" spans="1:31" ht="15">
       <c r="A12" s="41" t="s">
         <v>47</v>
       </c>
@@ -4972,7 +4972,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="14.4">
+    <row r="13" spans="1:31" ht="15">
       <c r="A13" s="41" t="s">
         <v>47</v>
       </c>
@@ -5044,7 +5044,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="14.4">
+    <row r="14" spans="1:31" ht="15">
       <c r="A14" s="41" t="s">
         <v>47</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="14.4">
+    <row r="15" spans="1:31" ht="15">
       <c r="A15" s="41" t="s">
         <v>47</v>
       </c>
@@ -5188,7 +5188,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="14.4">
+    <row r="16" spans="1:31" ht="15">
       <c r="A16" s="41" t="s">
         <v>47</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="14.4">
+    <row r="17" spans="1:31" ht="15">
       <c r="A17" s="41" t="s">
         <v>47</v>
       </c>
@@ -5333,7 +5333,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="14.4">
+    <row r="18" spans="1:31" ht="15">
       <c r="A18" s="41" t="s">
         <v>47</v>
       </c>
@@ -5405,7 +5405,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="14.4">
+    <row r="19" spans="1:31" ht="15">
       <c r="A19" s="41" t="s">
         <v>47</v>
       </c>
@@ -5477,7 +5477,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="14.4">
+    <row r="20" spans="1:31" ht="15">
       <c r="A20" s="41" t="s">
         <v>47</v>
       </c>
@@ -5549,7 +5549,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="14.4">
+    <row r="21" spans="1:31" ht="15">
       <c r="A21" s="41" t="s">
         <v>47</v>
       </c>
@@ -5621,7 +5621,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="14.4">
+    <row r="22" spans="1:31" ht="15">
       <c r="A22" s="41" t="s">
         <v>47</v>
       </c>
@@ -5693,7 +5693,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="14.4">
+    <row r="23" spans="1:31" ht="15">
       <c r="A23" s="41" t="s">
         <v>47</v>
       </c>
@@ -5765,7 +5765,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="14.4">
+    <row r="24" spans="1:31" ht="15">
       <c r="A24" s="41" t="s">
         <v>53</v>
       </c>
@@ -5843,7 +5843,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="14.4">
+    <row r="25" spans="1:31" ht="15">
       <c r="A25" s="41" t="s">
         <v>53</v>
       </c>
@@ -5921,7 +5921,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="14.4">
+    <row r="26" spans="1:31" ht="15">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -5999,7 +5999,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="14.4">
+    <row r="27" spans="1:31" ht="15">
       <c r="A27" s="41" t="s">
         <v>53</v>
       </c>
@@ -6077,7 +6077,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="14.4">
+    <row r="28" spans="1:31" ht="15">
       <c r="A28" s="41" t="s">
         <v>53</v>
       </c>
@@ -6152,7 +6152,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="14.4">
+    <row r="29" spans="1:31" ht="15">
       <c r="A29" s="41" t="s">
         <v>53</v>
       </c>
@@ -6227,7 +6227,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="14.4">
+    <row r="30" spans="1:31" ht="15">
       <c r="A30" s="41" t="s">
         <v>53</v>
       </c>
@@ -6303,7 +6303,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="14.4">
+    <row r="31" spans="1:31" ht="15">
       <c r="A31" s="41" t="s">
         <v>53</v>
       </c>
@@ -6379,7 +6379,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="14.4">
+    <row r="32" spans="1:31" ht="15">
       <c r="A32" s="41" t="s">
         <v>53</v>
       </c>
@@ -6455,7 +6455,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:32" ht="14.4">
+    <row r="33" spans="1:32" ht="15">
       <c r="A33" s="41" t="s">
         <v>53</v>
       </c>
@@ -6525,7 +6525,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:32" ht="14.4">
+    <row r="34" spans="1:32" ht="15">
       <c r="A34" s="41" t="s">
         <v>53</v>
       </c>
@@ -6598,7 +6598,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:32" ht="14.4">
+    <row r="35" spans="1:32" ht="15">
       <c r="A35" s="41" t="s">
         <v>53</v>
       </c>
@@ -6671,7 +6671,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:32" ht="14.4">
+    <row r="36" spans="1:32" ht="15">
       <c r="A36" s="41" t="s">
         <v>53</v>
       </c>
@@ -6744,7 +6744,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:32" ht="14.4">
+    <row r="37" spans="1:32" ht="15">
       <c r="A37" s="41" t="s">
         <v>53</v>
       </c>
@@ -6818,7 +6818,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:32" ht="14.4">
+    <row r="38" spans="1:32" ht="15">
       <c r="A38" s="41" t="s">
         <v>53</v>
       </c>
@@ -6891,7 +6891,7 @@
       <c r="AE38" s="15"/>
       <c r="AF38" s="15"/>
     </row>
-    <row r="39" spans="1:32" ht="14.4">
+    <row r="39" spans="1:32" ht="15">
       <c r="A39" s="41" t="s">
         <v>50</v>
       </c>
@@ -6964,7 +6964,7 @@
       <c r="AE39" s="15"/>
       <c r="AF39" s="15"/>
     </row>
-    <row r="40" spans="1:32" ht="14.4">
+    <row r="40" spans="1:32" ht="15">
       <c r="A40" s="41" t="s">
         <v>57</v>
       </c>
@@ -7042,7 +7042,7 @@
       <c r="AE40" s="15"/>
       <c r="AF40" s="15"/>
     </row>
-    <row r="41" spans="1:32" ht="14.4">
+    <row r="41" spans="1:32" ht="15">
       <c r="A41" s="41" t="s">
         <v>57</v>
       </c>
@@ -7121,7 +7121,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:32" ht="14.4">
+    <row r="42" spans="1:32" ht="15">
       <c r="A42" s="41" t="s">
         <v>57</v>
       </c>
@@ -7200,7 +7200,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:32" ht="14.4">
+    <row r="43" spans="1:32" ht="15">
       <c r="A43" s="41" t="s">
         <v>57</v>
       </c>
@@ -7279,7 +7279,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:32" ht="14.4">
+    <row r="44" spans="1:32" ht="15">
       <c r="A44" s="41" t="s">
         <v>57</v>
       </c>
@@ -7355,7 +7355,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:32" ht="14.4">
+    <row r="45" spans="1:32" ht="15">
       <c r="A45" s="41" t="s">
         <v>57</v>
       </c>
@@ -7431,7 +7431,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:32" ht="14.4">
+    <row r="46" spans="1:32" ht="15">
       <c r="A46" s="41" t="s">
         <v>57</v>
       </c>
@@ -7507,7 +7507,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:32" ht="14.4">
+    <row r="47" spans="1:32" ht="15">
       <c r="A47" s="41" t="s">
         <v>57</v>
       </c>
@@ -7583,7 +7583,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:32" ht="14.4">
+    <row r="48" spans="1:32" ht="15">
       <c r="A48" s="41" t="s">
         <v>57</v>
       </c>
@@ -7659,7 +7659,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:31" ht="14.4">
+    <row r="49" spans="1:31" ht="15">
       <c r="A49" s="41" t="s">
         <v>57</v>
       </c>
@@ -7732,7 +7732,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:31" ht="14.4">
+    <row r="50" spans="1:31" ht="15">
       <c r="A50" s="41" t="s">
         <v>57</v>
       </c>
@@ -7805,7 +7805,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:31" ht="14.4">
+    <row r="51" spans="1:31" ht="15">
       <c r="A51" s="41" t="s">
         <v>57</v>
       </c>
@@ -7879,7 +7879,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:31" ht="14.4">
+    <row r="52" spans="1:31" ht="15">
       <c r="A52" s="41" t="s">
         <v>57</v>
       </c>
@@ -7952,7 +7952,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:31" ht="14.4">
+    <row r="53" spans="1:31" ht="15">
       <c r="A53" s="41" t="s">
         <v>59</v>
       </c>
@@ -8025,7 +8025,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:31" ht="14.4">
+    <row r="54" spans="1:31" ht="15">
       <c r="A54" s="41" t="s">
         <v>59</v>
       </c>
@@ -8104,7 +8104,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:31" ht="14.4">
+    <row r="55" spans="1:31" ht="15">
       <c r="A55" s="41" t="s">
         <v>59</v>
       </c>
@@ -8177,7 +8177,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:31" ht="14.4">
+    <row r="56" spans="1:31" ht="15">
       <c r="A56" s="41" t="s">
         <v>59</v>
       </c>
@@ -8250,7 +8250,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:31" ht="14.4">
+    <row r="57" spans="1:31" ht="15">
       <c r="A57" s="41" t="s">
         <v>59</v>
       </c>
@@ -8329,7 +8329,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:31" ht="14.4">
+    <row r="58" spans="1:31" ht="15">
       <c r="A58" s="41" t="s">
         <v>59</v>
       </c>
@@ -8408,7 +8408,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:31" ht="14.4">
+    <row r="59" spans="1:31" ht="15">
       <c r="A59" s="41" t="s">
         <v>59</v>
       </c>
@@ -8487,7 +8487,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:31" ht="14.4">
+    <row r="60" spans="1:31" ht="15">
       <c r="A60" s="41" t="s">
         <v>59</v>
       </c>
@@ -8561,7 +8561,7 @@
       <c r="AD60"/>
       <c r="AE60"/>
     </row>
-    <row r="61" spans="1:31" ht="14.4">
+    <row r="61" spans="1:31" ht="15">
       <c r="A61" s="41" t="s">
         <v>59</v>
       </c>
@@ -8637,7 +8637,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:31" ht="14.4">
+    <row r="62" spans="1:31" ht="15">
       <c r="A62" s="41" t="s">
         <v>59</v>
       </c>
@@ -8713,7 +8713,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:31" ht="14.4">
+    <row r="63" spans="1:31" ht="15">
       <c r="A63" s="41" t="s">
         <v>59</v>
       </c>
@@ -8786,7 +8786,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:31" ht="14.4">
+    <row r="64" spans="1:31" ht="15">
       <c r="A64" s="41" t="s">
         <v>59</v>
       </c>
@@ -8862,7 +8862,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="14.4">
+    <row r="65" spans="1:31" ht="15">
       <c r="A65" s="41" t="s">
         <v>59</v>
       </c>
@@ -8938,7 +8938,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="14.4">
+    <row r="66" spans="1:31" ht="15">
       <c r="A66" s="41" t="s">
         <v>59</v>
       </c>
@@ -9014,7 +9014,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="14.4">
+    <row r="67" spans="1:31" ht="15">
       <c r="A67" s="41" t="s">
         <v>562</v>
       </c>
@@ -9087,7 +9087,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="14.4">
+    <row r="68" spans="1:31" ht="15">
       <c r="A68" s="41" t="s">
         <v>564</v>
       </c>
@@ -9159,7 +9159,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="14.4">
+    <row r="69" spans="1:31" ht="15">
       <c r="A69" s="41" t="s">
         <v>566</v>
       </c>
@@ -9231,7 +9231,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="14.4">
+    <row r="70" spans="1:31" ht="15">
       <c r="A70" s="41" t="s">
         <v>568</v>
       </c>
@@ -9303,7 +9303,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="14.4">
+    <row r="71" spans="1:31" ht="15">
       <c r="A71" s="41" t="s">
         <v>562</v>
       </c>
@@ -9375,7 +9375,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="14.4">
+    <row r="72" spans="1:31" ht="15">
       <c r="A72" s="41" t="s">
         <v>566</v>
       </c>
@@ -9447,7 +9447,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="14.4">
+    <row r="73" spans="1:31" ht="15">
       <c r="A73" s="41" t="s">
         <v>568</v>
       </c>
@@ -9520,7 +9520,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="14.4">
+    <row r="74" spans="1:31" ht="15">
       <c r="A74" s="41" t="s">
         <v>562</v>
       </c>
@@ -9591,7 +9591,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="14.4">
+    <row r="75" spans="1:31" ht="15">
       <c r="A75" s="41" t="s">
         <v>566</v>
       </c>
@@ -9662,7 +9662,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="14.4">
+    <row r="76" spans="1:31" ht="15">
       <c r="A76" s="41" t="s">
         <v>568</v>
       </c>
@@ -9733,7 +9733,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="14.4">
+    <row r="77" spans="1:31" ht="15">
       <c r="A77" s="77" t="s">
         <v>89</v>
       </c>
@@ -9812,7 +9812,7 @@
       <c r="AC77" s="43"/>
       <c r="AD77" s="43"/>
     </row>
-    <row r="78" spans="1:31" ht="14.4">
+    <row r="78" spans="1:31" ht="15">
       <c r="A78" s="77" t="s">
         <v>91</v>
       </c>
@@ -9891,7 +9891,7 @@
       <c r="AC78" s="43"/>
       <c r="AD78" s="43"/>
     </row>
-    <row r="79" spans="1:31" ht="14.4">
+    <row r="79" spans="1:31" ht="15">
       <c r="A79" s="77" t="s">
         <v>93</v>
       </c>
@@ -9970,7 +9970,7 @@
       <c r="AC79" s="43"/>
       <c r="AD79" s="43"/>
     </row>
-    <row r="80" spans="1:31" ht="14.4">
+    <row r="80" spans="1:31" ht="15">
       <c r="A80" s="80" t="s">
         <v>1</v>
       </c>
@@ -10049,7 +10049,7 @@
       <c r="AC80" s="43"/>
       <c r="AD80" s="43"/>
     </row>
-    <row r="81" spans="1:30" ht="14.4">
+    <row r="81" spans="1:30" ht="15">
       <c r="A81" s="41" t="s">
         <v>50</v>
       </c>
@@ -10127,7 +10127,7 @@
       <c r="AC81" s="43"/>
       <c r="AD81" s="43"/>
     </row>
-    <row r="82" spans="1:30" ht="14.4">
+    <row r="82" spans="1:30" ht="15">
       <c r="A82" s="41" t="s">
         <v>50</v>
       </c>
@@ -10205,7 +10205,7 @@
       <c r="AC82" s="43"/>
       <c r="AD82" s="43"/>
     </row>
-    <row r="83" spans="1:30" ht="14.4">
+    <row r="83" spans="1:30" ht="15">
       <c r="A83" s="41" t="s">
         <v>50</v>
       </c>
@@ -10283,7 +10283,7 @@
       <c r="AC83" s="43"/>
       <c r="AD83" s="43"/>
     </row>
-    <row r="84" spans="1:30" ht="14.4">
+    <row r="84" spans="1:30" ht="15">
       <c r="A84" s="41" t="s">
         <v>50</v>
       </c>
@@ -10361,7 +10361,7 @@
       <c r="AC84" s="43"/>
       <c r="AD84" s="43"/>
     </row>
-    <row r="85" spans="1:30" ht="14.4">
+    <row r="85" spans="1:30" ht="15">
       <c r="A85" s="41" t="s">
         <v>50</v>
       </c>
@@ -10439,7 +10439,7 @@
       <c r="AC85" s="43"/>
       <c r="AD85" s="43"/>
     </row>
-    <row r="86" spans="1:30" ht="14.4">
+    <row r="86" spans="1:30" ht="15">
       <c r="A86" s="41" t="s">
         <v>50</v>
       </c>
@@ -10517,7 +10517,7 @@
       <c r="AC86" s="43"/>
       <c r="AD86" s="43"/>
     </row>
-    <row r="87" spans="1:30" ht="14.4">
+    <row r="87" spans="1:30" ht="15">
       <c r="A87" s="41" t="s">
         <v>50</v>
       </c>
@@ -10595,7 +10595,7 @@
       <c r="AC87" s="43"/>
       <c r="AD87" s="43"/>
     </row>
-    <row r="88" spans="1:30" ht="14.4">
+    <row r="88" spans="1:30" ht="15">
       <c r="A88" s="41" t="s">
         <v>50</v>
       </c>
@@ -10673,7 +10673,7 @@
       <c r="AC88" s="43"/>
       <c r="AD88" s="43"/>
     </row>
-    <row r="89" spans="1:30" ht="14.4">
+    <row r="89" spans="1:30" ht="15">
       <c r="A89" s="41" t="s">
         <v>50</v>
       </c>
@@ -10751,7 +10751,7 @@
       <c r="AC89" s="43"/>
       <c r="AD89" s="43"/>
     </row>
-    <row r="90" spans="1:30" ht="13.2">
+    <row r="90" spans="1:30" ht="12.75">
       <c r="A90" s="41"/>
       <c r="B90" s="41"/>
       <c r="C90" s="41"/>
@@ -10770,7 +10770,7 @@
       <c r="AC90" s="43"/>
       <c r="AD90" s="43"/>
     </row>
-    <row r="91" spans="1:30" ht="13.2">
+    <row r="91" spans="1:30" ht="12.75">
       <c r="A91" s="41"/>
       <c r="B91" s="41"/>
       <c r="C91" s="41"/>
@@ -10782,7 +10782,7 @@
       <c r="Q91" s="53"/>
       <c r="U91" s="43"/>
     </row>
-    <row r="92" spans="1:30" ht="13.2">
+    <row r="92" spans="1:30" ht="12.75">
       <c r="A92" s="41"/>
       <c r="B92" s="41"/>
       <c r="C92" s="41"/>
@@ -10794,7 +10794,7 @@
       <c r="Q92" s="53"/>
       <c r="U92" s="43"/>
     </row>
-    <row r="93" spans="1:30" ht="13.2">
+    <row r="93" spans="1:30" ht="12.75">
       <c r="A93" s="41"/>
       <c r="B93" s="41"/>
       <c r="C93" s="41"/>
@@ -10821,15 +10821,15 @@
   <dimension ref="A1:I286"/>
   <sheetFormatPr defaultRowHeight="18.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.75" customWidth="1"/>
-    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.75" customWidth="1"/>
-    <col min="7" max="7" width="23.875" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.25" customWidth="1"/>
-    <col min="10" max="10" width="26.25" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" customHeight="1">
@@ -10861,7 +10861,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="11.4">
+    <row r="2" spans="1:9" ht="12">
       <c r="A2" s="10" t="s">
         <v>105</v>
       </c>
@@ -18903,16 +18903,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2051AA2F-ED82-497D-A0D7-BA51300AC6DC}">
   <dimension ref="A1:J92"/>
-  <sheetFormatPr defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="19.25" customWidth="1"/>
-    <col min="6" max="7" width="23.25" customWidth="1"/>
-    <col min="8" max="8" width="26.125" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="7" width="23.28515625" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="12">
+    <row r="1" spans="1:8">
       <c r="A1" s="11" t="s">
         <v>96</v>
       </c>
@@ -21497,18 +21497,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{197CD5C8-84EF-4E52-92C3-639A9DF2089C}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="25.625" customWidth="1"/>
-    <col min="6" max="6" width="25.375" customWidth="1"/>
-    <col min="7" max="7" width="22.625" customWidth="1"/>
-    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="12">
+    <row r="1" spans="1:8">
       <c r="A1" s="11" t="s">
         <v>96</v>
       </c>
@@ -21600,13 +21600,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD50CF4B-F9EC-407F-8C73-9C597C45A3D8}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="24.75" customWidth="1"/>
-    <col min="6" max="6" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21692,16 +21692,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B02B6F-B860-41DC-9D50-B3B43A9E1932}">
   <dimension ref="A2:E7"/>
-  <sheetFormatPr defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="12">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>556</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1671" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{568E5B34-FC27-4C88-8056-F3C06743ADBB}"/>
+  <xr:revisionPtr revIDLastSave="1678" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DF0CFE0-2BA1-4FDF-956A-E5E95D45BA41}"/>
   <bookViews>
-    <workbookView xWindow="-12810" yWindow="16080" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3090,6 +3090,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V89" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+  <autoFilter ref="A1:V89" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A67:V76">
     <sortCondition ref="I1:I80"/>
   </sortState>
